--- a/backend_api/templates/on_off_spot_template.xlsx
+++ b/backend_api/templates/on_off_spot_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B29702-41A3-43B2-84E4-711E54FB1AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5F229C-B7EF-4BB2-85E0-DB516FD8B16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" xr2:uid="{07ADC957-8ABD-40B3-B8CA-6432964576F2}"/>
+    <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{07ADC957-8ABD-40B3-B8CA-6432964576F2}"/>
   </bookViews>
   <sheets>
     <sheet name="CERTIFICATE" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="644">
   <si>
     <t>Name of Ship:</t>
   </si>
@@ -663,9 +663,6 @@
   </si>
   <si>
     <t xml:space="preserve">                     NORMAL WEAR AND TEAR EXCEPTED WITHOUT DAMAGE</t>
-  </si>
-  <si>
-    <t>ENGINE LOG BOOK FIGURES DECLARATION</t>
   </si>
   <si>
     <t xml:space="preserve">carried out a On hire Bunker Survey in the </t>
@@ -4441,6 +4438,25 @@
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4466,30 +4482,6 @@
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="37" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="37" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="40" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="40" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="35" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4501,19 +4493,258 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="35" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="40" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="40" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="56" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="64" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="62" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="14" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="32" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="32" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="32" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="32" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="65" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="32" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="32" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="32" fillId="3" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="32" fillId="3" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="65" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="14" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4527,213 +4758,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="56" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="14" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="32" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="32" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="32" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="32" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="64" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="62" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4808,33 +4832,6 @@
     </xf>
     <xf numFmtId="0" fontId="58" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="32" fillId="3" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="32" fillId="3" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5643,13 +5640,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>72672</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>89545</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>371243</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>181719</xdr:rowOff>
@@ -5728,12 +5725,12 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>300405</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>536382</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>285470</xdr:rowOff>
@@ -5801,13 +5798,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>337464</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>249029</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>152399</xdr:rowOff>
@@ -7315,7 +7312,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="362" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="J1" s="361">
         <f>+'Data from DB'!B3</f>
@@ -7358,24 +7355,24 @@
         <v>0</v>
       </c>
       <c r="C4" s="6"/>
-      <c r="D4" s="366">
+      <c r="D4" s="372">
         <f>+'Data from DB'!B4</f>
         <v>0</v>
       </c>
-      <c r="E4" s="366"/>
-      <c r="F4" s="366"/>
+      <c r="E4" s="372"/>
+      <c r="F4" s="372"/>
       <c r="G4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
-      <c r="J4" s="366">
+      <c r="J4" s="372">
         <f>+'Data from DB'!B5</f>
         <v>0</v>
       </c>
-      <c r="K4" s="366"/>
-      <c r="L4" s="366"/>
-      <c r="M4" s="366"/>
+      <c r="K4" s="372"/>
+      <c r="L4" s="372"/>
+      <c r="M4" s="372"/>
     </row>
     <row r="5" spans="1:13" ht="17.399999999999999">
       <c r="A5" s="7"/>
@@ -7397,24 +7394,24 @@
         <v>2</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="367">
+      <c r="D6" s="373">
         <f>+'Data from DB'!B6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="367"/>
-      <c r="F6" s="367"/>
+      <c r="E6" s="373"/>
+      <c r="F6" s="373"/>
       <c r="G6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
-      <c r="J6" s="370">
+      <c r="J6" s="376">
         <f>+'Data from DB'!B7</f>
         <v>0</v>
       </c>
-      <c r="K6" s="370"/>
-      <c r="L6" s="370"/>
-      <c r="M6" s="370"/>
+      <c r="K6" s="376"/>
+      <c r="L6" s="376"/>
+      <c r="M6" s="376"/>
     </row>
     <row r="7" spans="1:13" ht="14.4" customHeight="1">
       <c r="A7" s="9"/>
@@ -7475,7 +7472,7 @@
     </row>
     <row r="11" spans="1:13" ht="17.399999999999999">
       <c r="B11" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" s="15"/>
       <c r="E11" s="6" t="str">
@@ -7527,7 +7524,7 @@
       <c r="B14" s="339" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="476" t="str">
+      <c r="C14" s="368" t="str">
         <f>CONCATENATE("Vessel arrived to ",'Data from DB'!B446,"on"," ",'Data from DB'!B13,"at ",'Data from DB'!B470,":",'Data from DB'!B471," ","LT")</f>
         <v>Vessel arrived to on at : LT</v>
       </c>
@@ -7742,22 +7739,22 @@
       <c r="B27" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="368" t="str">
+      <c r="C27" s="374" t="str">
         <f>CONCATENATE("DLOSP at ",'Data from DB'!B16," ","on "," ",'Data from DB'!B15,"at "," ",'Data from DB'!B458,":",'Data from DB'!B459," ","LT")</f>
         <v>DLOSP at  on  at  : LT</v>
       </c>
-      <c r="D27" s="368"/>
-      <c r="E27" s="368"/>
-      <c r="F27" s="368"/>
-      <c r="G27" s="368"/>
-      <c r="H27" s="368"/>
-      <c r="I27" s="368"/>
+      <c r="D27" s="374"/>
+      <c r="E27" s="374"/>
+      <c r="F27" s="374"/>
+      <c r="G27" s="374"/>
+      <c r="H27" s="374"/>
+      <c r="I27" s="374"/>
       <c r="J27" s="354">
         <f>+'Data from DB'!B8</f>
         <v>0</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="18" customHeight="1" thickBot="1"/>
@@ -7830,7 +7827,7 @@
     </row>
     <row r="31" spans="1:15" ht="18" customHeight="1">
       <c r="A31" s="7"/>
-      <c r="B31" s="471">
+      <c r="B31" s="363">
         <f>+'Data from DB'!B410</f>
         <v>0</v>
       </c>
@@ -7862,7 +7859,7 @@
       <c r="M31" s="34"/>
     </row>
     <row r="32" spans="1:15" ht="18" customHeight="1">
-      <c r="B32" s="471">
+      <c r="B32" s="363">
         <f>+'Data from DB'!B414</f>
         <v>0</v>
       </c>
@@ -7925,7 +7922,7 @@
     <row r="34" spans="1:13" ht="18" customHeight="1" thickBot="1">
       <c r="A34" s="6"/>
       <c r="B34" s="342" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C34" s="355">
         <v>45956</v>
@@ -7969,7 +7966,7 @@
     <row r="37" spans="1:13" ht="18" customHeight="1"/>
     <row r="38" spans="1:13" ht="18" customHeight="1">
       <c r="C38" s="308" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D38" s="39"/>
     </row>
@@ -7986,37 +7983,37 @@
       <c r="M40" s="40"/>
     </row>
     <row r="41" spans="1:13" ht="19.95" customHeight="1">
-      <c r="B41" s="365" t="s">
-        <v>162</v>
-      </c>
-      <c r="C41" s="365"/>
+      <c r="B41" s="371" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" s="371"/>
       <c r="D41" s="41"/>
       <c r="H41" s="176"/>
-      <c r="I41" s="369"/>
-      <c r="J41" s="369"/>
-      <c r="K41" s="369"/>
-      <c r="L41" s="369"/>
-      <c r="M41" s="369"/>
+      <c r="I41" s="375"/>
+      <c r="J41" s="375"/>
+      <c r="K41" s="375"/>
+      <c r="L41" s="375"/>
+      <c r="M41" s="375"/>
     </row>
     <row r="42" spans="1:13" ht="19.8">
       <c r="A42" s="7"/>
-      <c r="B42" s="363" t="s">
+      <c r="B42" s="369" t="s">
         <v>28</v>
       </c>
-      <c r="C42" s="363"/>
+      <c r="C42" s="369"/>
       <c r="D42" s="43"/>
       <c r="E42" s="43"/>
       <c r="F42" s="15"/>
       <c r="G42" s="5"/>
       <c r="H42" s="10"/>
-      <c r="I42" s="364" t="str">
+      <c r="I42" s="370" t="str">
         <f xml:space="preserve"> +" Master  "  &amp; + D4</f>
         <v xml:space="preserve"> Master  0</v>
       </c>
-      <c r="J42" s="364"/>
-      <c r="K42" s="364"/>
-      <c r="L42" s="364"/>
-      <c r="M42" s="364"/>
+      <c r="J42" s="370"/>
+      <c r="K42" s="370"/>
+      <c r="L42" s="370"/>
+      <c r="M42" s="370"/>
     </row>
     <row r="43" spans="1:13" ht="19.8">
       <c r="C43" s="42" t="s">
@@ -8068,7 +8065,7 @@
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="J6:M6"/>
   </mergeCells>
-  <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.86614173228346458" bottom="0.59055118110236227" header="0" footer="0.35433070866141736"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="77" fitToHeight="2" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"Palatino Linotype,Normal"&amp;9 MV NORD ATOLL ON HIRE  CERTIFICATE&amp;R&amp;"Palatino Linotype,Normal"&amp;9Page 1 of 3</oddFooter>
@@ -9109,8 +9106,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.6">
-      <c r="J1" s="475" t="s">
-        <v>635</v>
+      <c r="J1" s="367" t="s">
+        <v>634</v>
       </c>
       <c r="K1" s="360">
         <f>+'Data from DB'!B3</f>
@@ -9118,13 +9115,13 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="21.6" customHeight="1">
-      <c r="D2" s="377"/>
-      <c r="E2" s="377"/>
-      <c r="F2" s="377"/>
-      <c r="G2" s="377"/>
-      <c r="H2" s="377"/>
-      <c r="I2" s="377"/>
-      <c r="J2" s="377"/>
+      <c r="D2" s="381"/>
+      <c r="E2" s="381"/>
+      <c r="F2" s="381"/>
+      <c r="G2" s="381"/>
+      <c r="H2" s="381"/>
+      <c r="I2" s="381"/>
+      <c r="J2" s="381"/>
     </row>
     <row r="3" spans="1:22" ht="39" customHeight="1">
       <c r="G3" s="52"/>
@@ -9141,19 +9138,19 @@
       <c r="V3" s="55"/>
     </row>
     <row r="4" spans="1:22" ht="13.5" customHeight="1">
-      <c r="A4" s="378" t="s">
+      <c r="A4" s="387" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="378"/>
-      <c r="C4" s="378"/>
-      <c r="D4" s="378"/>
-      <c r="E4" s="378"/>
-      <c r="F4" s="378"/>
-      <c r="G4" s="378"/>
-      <c r="H4" s="378"/>
-      <c r="I4" s="378"/>
-      <c r="J4" s="378"/>
-      <c r="K4" s="378"/>
+      <c r="B4" s="387"/>
+      <c r="C4" s="387"/>
+      <c r="D4" s="387"/>
+      <c r="E4" s="387"/>
+      <c r="F4" s="387"/>
+      <c r="G4" s="387"/>
+      <c r="H4" s="387"/>
+      <c r="I4" s="387"/>
+      <c r="J4" s="387"/>
+      <c r="K4" s="387"/>
       <c r="M4" s="53"/>
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
@@ -9213,11 +9210,11 @@
         <v>44</v>
       </c>
       <c r="P7" s="76"/>
-      <c r="Q7" s="375">
+      <c r="Q7" s="382">
         <f>O10/Q9</f>
         <v>2.9000000000000002E-3</v>
       </c>
-      <c r="R7" s="375"/>
+      <c r="R7" s="382"/>
     </row>
     <row r="8" spans="1:22" ht="13.5" customHeight="1" thickBot="1">
       <c r="A8" s="60"/>
@@ -9238,10 +9235,10 @@
       <c r="P8" s="83">
         <v>1.5</v>
       </c>
-      <c r="Q8" s="371" t="s">
+      <c r="Q8" s="383" t="s">
         <v>51</v>
       </c>
-      <c r="R8" s="372"/>
+      <c r="R8" s="384"/>
     </row>
     <row r="9" spans="1:22" ht="13.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A9" s="60"/>
@@ -9280,10 +9277,10 @@
       <c r="P9" s="91">
         <v>2.6</v>
       </c>
-      <c r="Q9" s="373">
+      <c r="Q9" s="385">
         <v>1000</v>
       </c>
-      <c r="R9" s="374"/>
+      <c r="R9" s="386"/>
     </row>
     <row r="10" spans="1:22" ht="13.5" customHeight="1" thickBot="1">
       <c r="A10" s="79"/>
@@ -9338,7 +9335,7 @@
     </row>
     <row r="11" spans="1:22" ht="13.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A11" s="79"/>
-      <c r="B11" s="472">
+      <c r="B11" s="364">
         <f>+'Data from DB'!B81</f>
         <v>0</v>
       </c>
@@ -9392,7 +9389,7 @@
     </row>
     <row r="12" spans="1:22" ht="13.5" customHeight="1" thickBot="1">
       <c r="A12" s="79"/>
-      <c r="B12" s="472">
+      <c r="B12" s="364">
         <f>+'Data from DB'!B89</f>
         <v>0</v>
       </c>
@@ -9435,7 +9432,7 @@
     </row>
     <row r="13" spans="1:22" ht="13.5" customHeight="1" thickBot="1">
       <c r="A13" s="79"/>
-      <c r="B13" s="472">
+      <c r="B13" s="364">
         <f>+'Data from DB'!B97</f>
         <v>0</v>
       </c>
@@ -9477,15 +9474,15 @@
         <v>55</v>
       </c>
       <c r="P13" s="76"/>
-      <c r="Q13" s="375">
+      <c r="Q13" s="382">
         <f>O16/Q15</f>
         <v>5.8614199999999998E-2</v>
       </c>
-      <c r="R13" s="375"/>
+      <c r="R13" s="382"/>
     </row>
     <row r="14" spans="1:22" ht="13.5" customHeight="1" thickBot="1">
       <c r="A14" s="79"/>
-      <c r="B14" s="472">
+      <c r="B14" s="364">
         <f>+'Data from DB'!B105</f>
         <v>0</v>
       </c>
@@ -9530,44 +9527,44 @@
       <c r="P14" s="83">
         <v>3</v>
       </c>
-      <c r="Q14" s="371" t="s">
+      <c r="Q14" s="383" t="s">
         <v>51</v>
       </c>
-      <c r="R14" s="372"/>
+      <c r="R14" s="384"/>
     </row>
     <row r="15" spans="1:22" ht="13.5" customHeight="1" thickBot="1">
       <c r="A15" s="79"/>
-      <c r="B15" s="472">
+      <c r="B15" s="364">
         <f>+'Data from DB'!B113</f>
         <v>0</v>
       </c>
       <c r="C15" s="347"/>
       <c r="D15" s="84"/>
-      <c r="E15" s="472" t="e">
+      <c r="E15" s="364" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F15" s="472" t="e">
+      <c r="F15" s="364" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="G15" s="472" t="e">
+      <c r="G15" s="364" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H15" s="472" t="e">
+      <c r="H15" s="364" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="I15" s="472" t="e">
+      <c r="I15" s="364" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J15" s="472" t="e">
+      <c r="J15" s="364" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="K15" s="472" t="e">
+      <c r="K15" s="364" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
@@ -9581,14 +9578,14 @@
       <c r="P15" s="91">
         <v>5.1660000000000004</v>
       </c>
-      <c r="Q15" s="373">
+      <c r="Q15" s="385">
         <v>100</v>
       </c>
-      <c r="R15" s="374"/>
+      <c r="R15" s="386"/>
     </row>
     <row r="16" spans="1:22" ht="13.5" customHeight="1" thickBot="1">
       <c r="A16" s="79"/>
-      <c r="B16" s="472">
+      <c r="B16" s="364">
         <f>+'Data from DB'!B121</f>
         <v>0</v>
       </c>
@@ -9647,7 +9644,7 @@
     </row>
     <row r="17" spans="1:18" ht="13.5" customHeight="1" thickBot="1">
       <c r="A17" s="60"/>
-      <c r="B17" s="472">
+      <c r="B17" s="364">
         <f>+'Data from DB'!B129</f>
         <v>0</v>
       </c>
@@ -9700,7 +9697,7 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B18" s="472">
+      <c r="B18" s="364">
         <f>+'Data from DB'!B137</f>
         <v>0</v>
       </c>
@@ -9737,7 +9734,7 @@
     </row>
     <row r="19" spans="1:18" ht="13.5" customHeight="1">
       <c r="A19" s="60"/>
-      <c r="B19" s="472">
+      <c r="B19" s="364">
         <f>+'Data from DB'!B145</f>
         <v>0</v>
       </c>
@@ -9782,7 +9779,7 @@
     </row>
     <row r="20" spans="1:18" ht="13.5" customHeight="1">
       <c r="A20" s="60"/>
-      <c r="B20" s="472">
+      <c r="B20" s="364">
         <f>+'Data from DB'!B153</f>
         <v>0</v>
       </c>
@@ -9831,7 +9828,7 @@
     </row>
     <row r="21" spans="1:18" ht="13.5" customHeight="1" thickBot="1">
       <c r="A21" s="60"/>
-      <c r="B21" s="473">
+      <c r="B21" s="365">
         <f>+'Data from DB'!B161</f>
         <v>0</v>
       </c>
@@ -9940,11 +9937,11 @@
         <v>44</v>
       </c>
       <c r="P25" s="76"/>
-      <c r="Q25" s="375">
+      <c r="Q25" s="382">
         <f>O28/Q27</f>
         <v>2.1454865E-2</v>
       </c>
-      <c r="R25" s="375"/>
+      <c r="R25" s="382"/>
     </row>
     <row r="26" spans="1:18" ht="13.5" customHeight="1" thickBot="1">
       <c r="A26" s="60"/>
@@ -9969,10 +9966,10 @@
         <f>P8</f>
         <v>1.5</v>
       </c>
-      <c r="Q26" s="371" t="s">
+      <c r="Q26" s="383" t="s">
         <v>51</v>
       </c>
-      <c r="R26" s="372"/>
+      <c r="R26" s="384"/>
     </row>
     <row r="27" spans="1:18" ht="13.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="B27" s="307"/>
@@ -10009,10 +10006,10 @@
       <c r="P27" s="91">
         <v>19.54</v>
       </c>
-      <c r="Q27" s="373">
+      <c r="Q27" s="385">
         <v>1000</v>
       </c>
-      <c r="R27" s="374"/>
+      <c r="R27" s="386"/>
     </row>
     <row r="28" spans="1:18" ht="13.5" customHeight="1" thickBot="1">
       <c r="A28" s="79"/>
@@ -10067,7 +10064,7 @@
     </row>
     <row r="29" spans="1:18" ht="13.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A29" s="79"/>
-      <c r="B29" s="474">
+      <c r="B29" s="366">
         <f>+'Data from DB'!B241</f>
         <v>0</v>
       </c>
@@ -10121,7 +10118,7 @@
     </row>
     <row r="30" spans="1:18" ht="13.5" customHeight="1" thickBot="1">
       <c r="A30" s="60"/>
-      <c r="B30" s="472">
+      <c r="B30" s="364">
         <f>+'Data from DB'!B249</f>
         <v>0</v>
       </c>
@@ -10163,7 +10160,7 @@
     </row>
     <row r="31" spans="1:18" ht="13.5" customHeight="1" thickBot="1">
       <c r="A31" s="60"/>
-      <c r="B31" s="473">
+      <c r="B31" s="365">
         <f>+'Data from DB'!B257</f>
         <v>0</v>
       </c>
@@ -10205,11 +10202,11 @@
         <v>55</v>
       </c>
       <c r="P31" s="76"/>
-      <c r="Q31" s="375">
+      <c r="Q31" s="382">
         <f>O34/Q33</f>
         <v>0.19149999999999998</v>
       </c>
-      <c r="R31" s="375"/>
+      <c r="R31" s="382"/>
     </row>
     <row r="32" spans="1:18" ht="13.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A32" s="60"/>
@@ -10244,10 +10241,10 @@
       <c r="P32" s="83">
         <v>1.5</v>
       </c>
-      <c r="Q32" s="371" t="s">
+      <c r="Q32" s="383" t="s">
         <v>51</v>
       </c>
-      <c r="R32" s="372"/>
+      <c r="R32" s="384"/>
     </row>
     <row r="33" spans="1:20" ht="13.5" customHeight="1" thickBot="1">
       <c r="A33" s="60"/>
@@ -10262,10 +10259,10 @@
       <c r="P33" s="91">
         <v>191.1</v>
       </c>
-      <c r="Q33" s="373">
+      <c r="Q33" s="385">
         <v>1000</v>
       </c>
-      <c r="R33" s="374"/>
+      <c r="R33" s="386"/>
     </row>
     <row r="34" spans="1:20" ht="13.5" customHeight="1" thickBot="1">
       <c r="A34" s="60"/>
@@ -10413,45 +10410,45 @@
       <c r="R41" s="77"/>
     </row>
     <row r="42" spans="1:20" ht="13.5" customHeight="1">
-      <c r="B42" s="381" t="str">
+      <c r="B42" s="379" t="str">
         <f>CERTIFICATE!B41</f>
         <v>Pabel Peña</v>
       </c>
-      <c r="C42" s="381"/>
-      <c r="D42" s="381"/>
+      <c r="C42" s="379"/>
+      <c r="D42" s="379"/>
       <c r="E42" s="313"/>
-      <c r="F42" s="380">
+      <c r="F42" s="378">
         <f>+'Data from DB'!B472</f>
         <v>0</v>
       </c>
-      <c r="G42" s="380"/>
-      <c r="H42" s="380"/>
+      <c r="G42" s="378"/>
+      <c r="H42" s="378"/>
       <c r="I42" s="314"/>
-      <c r="J42" s="380">
+      <c r="J42" s="378">
         <f>CERTIFICATE!I41</f>
         <v>0</v>
       </c>
-      <c r="K42" s="380"/>
+      <c r="K42" s="378"/>
     </row>
     <row r="43" spans="1:20" ht="13.5" customHeight="1">
-      <c r="B43" s="376" t="s">
+      <c r="B43" s="380" t="s">
         <v>28</v>
       </c>
-      <c r="C43" s="376"/>
-      <c r="D43" s="376"/>
+      <c r="C43" s="380"/>
+      <c r="D43" s="380"/>
       <c r="E43" s="314"/>
-      <c r="F43" s="379" t="str">
+      <c r="F43" s="377" t="str">
         <f xml:space="preserve"> +" C. Engineer "  &amp; + CERTIFICATE!D4</f>
         <v xml:space="preserve"> C. Engineer 0</v>
       </c>
-      <c r="G43" s="379"/>
-      <c r="H43" s="379"/>
+      <c r="G43" s="377"/>
+      <c r="H43" s="377"/>
       <c r="I43" s="314"/>
-      <c r="J43" s="376" t="str">
+      <c r="J43" s="380" t="str">
         <f xml:space="preserve"> +" Master  "  &amp; + CERTIFICATE!D4</f>
         <v xml:space="preserve"> Master  0</v>
       </c>
-      <c r="K43" s="376"/>
+      <c r="K43" s="380"/>
     </row>
     <row r="44" spans="1:20" ht="13.5" customHeight="1"/>
     <row r="45" spans="1:20" ht="13.5" customHeight="1">
@@ -10474,17 +10471,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="A4:K4"/>
     <mergeCell ref="Q14:R14"/>
     <mergeCell ref="Q15:R15"/>
     <mergeCell ref="Q25:R25"/>
@@ -10494,9 +10480,20 @@
     <mergeCell ref="Q31:R31"/>
     <mergeCell ref="Q26:R26"/>
     <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
   </mergeCells>
   <phoneticPr fontId="75" type="noConversion"/>
-  <pageMargins left="0.35433070866141736" right="0.15748031496062992" top="0.86614173228346458" bottom="0.59055118110236227" header="0" footer="0.35433070866141736"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"Palatino Linotype,Normal"&amp;9 MV NORD ATOLL ON HIRE  CERTIFICATE&amp;C &amp;R&amp;"Palatino Linotype,Normal"&amp;9Page 2 of 3</oddFooter>
@@ -10508,1354 +10505,1338 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D299C9C2-B78D-425C-8780-85CE487DAC3E}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="51" customWidth="1"/>
-    <col min="2" max="4" width="9.5546875" style="51" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="51" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" style="51" customWidth="1"/>
-    <col min="8" max="11" width="9.5546875" style="51" customWidth="1"/>
-    <col min="12" max="67" width="9.109375" style="51"/>
-    <col min="68" max="68" width="3.109375" style="51" customWidth="1"/>
-    <col min="69" max="69" width="3.44140625" style="51" customWidth="1"/>
-    <col min="70" max="70" width="7.33203125" style="51" customWidth="1"/>
-    <col min="71" max="71" width="13.5546875" style="51" customWidth="1"/>
-    <col min="72" max="72" width="7.109375" style="51" customWidth="1"/>
-    <col min="73" max="73" width="8.5546875" style="51" customWidth="1"/>
-    <col min="74" max="74" width="9" style="51" customWidth="1"/>
-    <col min="75" max="75" width="5.109375" style="51" customWidth="1"/>
-    <col min="76" max="76" width="8.44140625" style="51" customWidth="1"/>
-    <col min="77" max="77" width="17.109375" style="51" customWidth="1"/>
-    <col min="78" max="78" width="18" style="51" customWidth="1"/>
-    <col min="79" max="79" width="3.88671875" style="51" customWidth="1"/>
-    <col min="80" max="81" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="82" max="84" width="9.109375" style="51"/>
-    <col min="85" max="85" width="11.33203125" style="51" customWidth="1"/>
-    <col min="86" max="323" width="9.109375" style="51"/>
-    <col min="324" max="324" width="3.109375" style="51" customWidth="1"/>
-    <col min="325" max="325" width="3.44140625" style="51" customWidth="1"/>
-    <col min="326" max="326" width="7.33203125" style="51" customWidth="1"/>
-    <col min="327" max="327" width="13.5546875" style="51" customWidth="1"/>
-    <col min="328" max="328" width="7.109375" style="51" customWidth="1"/>
-    <col min="329" max="329" width="8.5546875" style="51" customWidth="1"/>
-    <col min="330" max="330" width="9" style="51" customWidth="1"/>
-    <col min="331" max="331" width="5.109375" style="51" customWidth="1"/>
-    <col min="332" max="332" width="8.44140625" style="51" customWidth="1"/>
-    <col min="333" max="333" width="17.109375" style="51" customWidth="1"/>
-    <col min="334" max="334" width="18" style="51" customWidth="1"/>
-    <col min="335" max="335" width="3.88671875" style="51" customWidth="1"/>
-    <col min="336" max="337" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="338" max="340" width="9.109375" style="51"/>
-    <col min="341" max="341" width="11.33203125" style="51" customWidth="1"/>
-    <col min="342" max="579" width="9.109375" style="51"/>
-    <col min="580" max="580" width="3.109375" style="51" customWidth="1"/>
-    <col min="581" max="581" width="3.44140625" style="51" customWidth="1"/>
-    <col min="582" max="582" width="7.33203125" style="51" customWidth="1"/>
-    <col min="583" max="583" width="13.5546875" style="51" customWidth="1"/>
-    <col min="584" max="584" width="7.109375" style="51" customWidth="1"/>
-    <col min="585" max="585" width="8.5546875" style="51" customWidth="1"/>
-    <col min="586" max="586" width="9" style="51" customWidth="1"/>
-    <col min="587" max="587" width="5.109375" style="51" customWidth="1"/>
-    <col min="588" max="588" width="8.44140625" style="51" customWidth="1"/>
-    <col min="589" max="589" width="17.109375" style="51" customWidth="1"/>
-    <col min="590" max="590" width="18" style="51" customWidth="1"/>
-    <col min="591" max="591" width="3.88671875" style="51" customWidth="1"/>
-    <col min="592" max="593" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="594" max="596" width="9.109375" style="51"/>
-    <col min="597" max="597" width="11.33203125" style="51" customWidth="1"/>
-    <col min="598" max="835" width="9.109375" style="51"/>
-    <col min="836" max="836" width="3.109375" style="51" customWidth="1"/>
-    <col min="837" max="837" width="3.44140625" style="51" customWidth="1"/>
-    <col min="838" max="838" width="7.33203125" style="51" customWidth="1"/>
-    <col min="839" max="839" width="13.5546875" style="51" customWidth="1"/>
-    <col min="840" max="840" width="7.109375" style="51" customWidth="1"/>
-    <col min="841" max="841" width="8.5546875" style="51" customWidth="1"/>
-    <col min="842" max="842" width="9" style="51" customWidth="1"/>
-    <col min="843" max="843" width="5.109375" style="51" customWidth="1"/>
-    <col min="844" max="844" width="8.44140625" style="51" customWidth="1"/>
-    <col min="845" max="845" width="17.109375" style="51" customWidth="1"/>
-    <col min="846" max="846" width="18" style="51" customWidth="1"/>
-    <col min="847" max="847" width="3.88671875" style="51" customWidth="1"/>
-    <col min="848" max="849" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="850" max="852" width="9.109375" style="51"/>
-    <col min="853" max="853" width="11.33203125" style="51" customWidth="1"/>
-    <col min="854" max="1091" width="9.109375" style="51"/>
-    <col min="1092" max="1092" width="3.109375" style="51" customWidth="1"/>
-    <col min="1093" max="1093" width="3.44140625" style="51" customWidth="1"/>
-    <col min="1094" max="1094" width="7.33203125" style="51" customWidth="1"/>
-    <col min="1095" max="1095" width="13.5546875" style="51" customWidth="1"/>
-    <col min="1096" max="1096" width="7.109375" style="51" customWidth="1"/>
-    <col min="1097" max="1097" width="8.5546875" style="51" customWidth="1"/>
-    <col min="1098" max="1098" width="9" style="51" customWidth="1"/>
-    <col min="1099" max="1099" width="5.109375" style="51" customWidth="1"/>
-    <col min="1100" max="1100" width="8.44140625" style="51" customWidth="1"/>
-    <col min="1101" max="1101" width="17.109375" style="51" customWidth="1"/>
-    <col min="1102" max="1102" width="18" style="51" customWidth="1"/>
-    <col min="1103" max="1103" width="3.88671875" style="51" customWidth="1"/>
-    <col min="1104" max="1105" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="1106" max="1108" width="9.109375" style="51"/>
-    <col min="1109" max="1109" width="11.33203125" style="51" customWidth="1"/>
-    <col min="1110" max="1347" width="9.109375" style="51"/>
-    <col min="1348" max="1348" width="3.109375" style="51" customWidth="1"/>
-    <col min="1349" max="1349" width="3.44140625" style="51" customWidth="1"/>
-    <col min="1350" max="1350" width="7.33203125" style="51" customWidth="1"/>
-    <col min="1351" max="1351" width="13.5546875" style="51" customWidth="1"/>
-    <col min="1352" max="1352" width="7.109375" style="51" customWidth="1"/>
-    <col min="1353" max="1353" width="8.5546875" style="51" customWidth="1"/>
-    <col min="1354" max="1354" width="9" style="51" customWidth="1"/>
-    <col min="1355" max="1355" width="5.109375" style="51" customWidth="1"/>
-    <col min="1356" max="1356" width="8.44140625" style="51" customWidth="1"/>
-    <col min="1357" max="1357" width="17.109375" style="51" customWidth="1"/>
-    <col min="1358" max="1358" width="18" style="51" customWidth="1"/>
-    <col min="1359" max="1359" width="3.88671875" style="51" customWidth="1"/>
-    <col min="1360" max="1361" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="1362" max="1364" width="9.109375" style="51"/>
-    <col min="1365" max="1365" width="11.33203125" style="51" customWidth="1"/>
-    <col min="1366" max="1603" width="9.109375" style="51"/>
-    <col min="1604" max="1604" width="3.109375" style="51" customWidth="1"/>
-    <col min="1605" max="1605" width="3.44140625" style="51" customWidth="1"/>
-    <col min="1606" max="1606" width="7.33203125" style="51" customWidth="1"/>
-    <col min="1607" max="1607" width="13.5546875" style="51" customWidth="1"/>
-    <col min="1608" max="1608" width="7.109375" style="51" customWidth="1"/>
-    <col min="1609" max="1609" width="8.5546875" style="51" customWidth="1"/>
-    <col min="1610" max="1610" width="9" style="51" customWidth="1"/>
-    <col min="1611" max="1611" width="5.109375" style="51" customWidth="1"/>
-    <col min="1612" max="1612" width="8.44140625" style="51" customWidth="1"/>
-    <col min="1613" max="1613" width="17.109375" style="51" customWidth="1"/>
-    <col min="1614" max="1614" width="18" style="51" customWidth="1"/>
-    <col min="1615" max="1615" width="3.88671875" style="51" customWidth="1"/>
-    <col min="1616" max="1617" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="1618" max="1620" width="9.109375" style="51"/>
-    <col min="1621" max="1621" width="11.33203125" style="51" customWidth="1"/>
-    <col min="1622" max="1859" width="9.109375" style="51"/>
-    <col min="1860" max="1860" width="3.109375" style="51" customWidth="1"/>
-    <col min="1861" max="1861" width="3.44140625" style="51" customWidth="1"/>
-    <col min="1862" max="1862" width="7.33203125" style="51" customWidth="1"/>
-    <col min="1863" max="1863" width="13.5546875" style="51" customWidth="1"/>
-    <col min="1864" max="1864" width="7.109375" style="51" customWidth="1"/>
-    <col min="1865" max="1865" width="8.5546875" style="51" customWidth="1"/>
-    <col min="1866" max="1866" width="9" style="51" customWidth="1"/>
-    <col min="1867" max="1867" width="5.109375" style="51" customWidth="1"/>
-    <col min="1868" max="1868" width="8.44140625" style="51" customWidth="1"/>
-    <col min="1869" max="1869" width="17.109375" style="51" customWidth="1"/>
-    <col min="1870" max="1870" width="18" style="51" customWidth="1"/>
-    <col min="1871" max="1871" width="3.88671875" style="51" customWidth="1"/>
-    <col min="1872" max="1873" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="1874" max="1876" width="9.109375" style="51"/>
-    <col min="1877" max="1877" width="11.33203125" style="51" customWidth="1"/>
-    <col min="1878" max="2115" width="9.109375" style="51"/>
-    <col min="2116" max="2116" width="3.109375" style="51" customWidth="1"/>
-    <col min="2117" max="2117" width="3.44140625" style="51" customWidth="1"/>
-    <col min="2118" max="2118" width="7.33203125" style="51" customWidth="1"/>
-    <col min="2119" max="2119" width="13.5546875" style="51" customWidth="1"/>
-    <col min="2120" max="2120" width="7.109375" style="51" customWidth="1"/>
-    <col min="2121" max="2121" width="8.5546875" style="51" customWidth="1"/>
-    <col min="2122" max="2122" width="9" style="51" customWidth="1"/>
-    <col min="2123" max="2123" width="5.109375" style="51" customWidth="1"/>
-    <col min="2124" max="2124" width="8.44140625" style="51" customWidth="1"/>
-    <col min="2125" max="2125" width="17.109375" style="51" customWidth="1"/>
-    <col min="2126" max="2126" width="18" style="51" customWidth="1"/>
-    <col min="2127" max="2127" width="3.88671875" style="51" customWidth="1"/>
-    <col min="2128" max="2129" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="2130" max="2132" width="9.109375" style="51"/>
-    <col min="2133" max="2133" width="11.33203125" style="51" customWidth="1"/>
-    <col min="2134" max="2371" width="9.109375" style="51"/>
-    <col min="2372" max="2372" width="3.109375" style="51" customWidth="1"/>
-    <col min="2373" max="2373" width="3.44140625" style="51" customWidth="1"/>
-    <col min="2374" max="2374" width="7.33203125" style="51" customWidth="1"/>
-    <col min="2375" max="2375" width="13.5546875" style="51" customWidth="1"/>
-    <col min="2376" max="2376" width="7.109375" style="51" customWidth="1"/>
-    <col min="2377" max="2377" width="8.5546875" style="51" customWidth="1"/>
-    <col min="2378" max="2378" width="9" style="51" customWidth="1"/>
-    <col min="2379" max="2379" width="5.109375" style="51" customWidth="1"/>
-    <col min="2380" max="2380" width="8.44140625" style="51" customWidth="1"/>
-    <col min="2381" max="2381" width="17.109375" style="51" customWidth="1"/>
-    <col min="2382" max="2382" width="18" style="51" customWidth="1"/>
-    <col min="2383" max="2383" width="3.88671875" style="51" customWidth="1"/>
-    <col min="2384" max="2385" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="2386" max="2388" width="9.109375" style="51"/>
-    <col min="2389" max="2389" width="11.33203125" style="51" customWidth="1"/>
-    <col min="2390" max="2627" width="9.109375" style="51"/>
-    <col min="2628" max="2628" width="3.109375" style="51" customWidth="1"/>
-    <col min="2629" max="2629" width="3.44140625" style="51" customWidth="1"/>
-    <col min="2630" max="2630" width="7.33203125" style="51" customWidth="1"/>
-    <col min="2631" max="2631" width="13.5546875" style="51" customWidth="1"/>
-    <col min="2632" max="2632" width="7.109375" style="51" customWidth="1"/>
-    <col min="2633" max="2633" width="8.5546875" style="51" customWidth="1"/>
-    <col min="2634" max="2634" width="9" style="51" customWidth="1"/>
-    <col min="2635" max="2635" width="5.109375" style="51" customWidth="1"/>
-    <col min="2636" max="2636" width="8.44140625" style="51" customWidth="1"/>
-    <col min="2637" max="2637" width="17.109375" style="51" customWidth="1"/>
-    <col min="2638" max="2638" width="18" style="51" customWidth="1"/>
-    <col min="2639" max="2639" width="3.88671875" style="51" customWidth="1"/>
-    <col min="2640" max="2641" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="2642" max="2644" width="9.109375" style="51"/>
-    <col min="2645" max="2645" width="11.33203125" style="51" customWidth="1"/>
-    <col min="2646" max="2883" width="9.109375" style="51"/>
-    <col min="2884" max="2884" width="3.109375" style="51" customWidth="1"/>
-    <col min="2885" max="2885" width="3.44140625" style="51" customWidth="1"/>
-    <col min="2886" max="2886" width="7.33203125" style="51" customWidth="1"/>
-    <col min="2887" max="2887" width="13.5546875" style="51" customWidth="1"/>
-    <col min="2888" max="2888" width="7.109375" style="51" customWidth="1"/>
-    <col min="2889" max="2889" width="8.5546875" style="51" customWidth="1"/>
-    <col min="2890" max="2890" width="9" style="51" customWidth="1"/>
-    <col min="2891" max="2891" width="5.109375" style="51" customWidth="1"/>
-    <col min="2892" max="2892" width="8.44140625" style="51" customWidth="1"/>
-    <col min="2893" max="2893" width="17.109375" style="51" customWidth="1"/>
-    <col min="2894" max="2894" width="18" style="51" customWidth="1"/>
-    <col min="2895" max="2895" width="3.88671875" style="51" customWidth="1"/>
-    <col min="2896" max="2897" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="2898" max="2900" width="9.109375" style="51"/>
-    <col min="2901" max="2901" width="11.33203125" style="51" customWidth="1"/>
-    <col min="2902" max="3139" width="9.109375" style="51"/>
-    <col min="3140" max="3140" width="3.109375" style="51" customWidth="1"/>
-    <col min="3141" max="3141" width="3.44140625" style="51" customWidth="1"/>
-    <col min="3142" max="3142" width="7.33203125" style="51" customWidth="1"/>
-    <col min="3143" max="3143" width="13.5546875" style="51" customWidth="1"/>
-    <col min="3144" max="3144" width="7.109375" style="51" customWidth="1"/>
-    <col min="3145" max="3145" width="8.5546875" style="51" customWidth="1"/>
-    <col min="3146" max="3146" width="9" style="51" customWidth="1"/>
-    <col min="3147" max="3147" width="5.109375" style="51" customWidth="1"/>
-    <col min="3148" max="3148" width="8.44140625" style="51" customWidth="1"/>
-    <col min="3149" max="3149" width="17.109375" style="51" customWidth="1"/>
-    <col min="3150" max="3150" width="18" style="51" customWidth="1"/>
-    <col min="3151" max="3151" width="3.88671875" style="51" customWidth="1"/>
-    <col min="3152" max="3153" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="3154" max="3156" width="9.109375" style="51"/>
-    <col min="3157" max="3157" width="11.33203125" style="51" customWidth="1"/>
-    <col min="3158" max="3395" width="9.109375" style="51"/>
-    <col min="3396" max="3396" width="3.109375" style="51" customWidth="1"/>
-    <col min="3397" max="3397" width="3.44140625" style="51" customWidth="1"/>
-    <col min="3398" max="3398" width="7.33203125" style="51" customWidth="1"/>
-    <col min="3399" max="3399" width="13.5546875" style="51" customWidth="1"/>
-    <col min="3400" max="3400" width="7.109375" style="51" customWidth="1"/>
-    <col min="3401" max="3401" width="8.5546875" style="51" customWidth="1"/>
-    <col min="3402" max="3402" width="9" style="51" customWidth="1"/>
-    <col min="3403" max="3403" width="5.109375" style="51" customWidth="1"/>
-    <col min="3404" max="3404" width="8.44140625" style="51" customWidth="1"/>
-    <col min="3405" max="3405" width="17.109375" style="51" customWidth="1"/>
-    <col min="3406" max="3406" width="18" style="51" customWidth="1"/>
-    <col min="3407" max="3407" width="3.88671875" style="51" customWidth="1"/>
-    <col min="3408" max="3409" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="3410" max="3412" width="9.109375" style="51"/>
-    <col min="3413" max="3413" width="11.33203125" style="51" customWidth="1"/>
-    <col min="3414" max="3651" width="9.109375" style="51"/>
-    <col min="3652" max="3652" width="3.109375" style="51" customWidth="1"/>
-    <col min="3653" max="3653" width="3.44140625" style="51" customWidth="1"/>
-    <col min="3654" max="3654" width="7.33203125" style="51" customWidth="1"/>
-    <col min="3655" max="3655" width="13.5546875" style="51" customWidth="1"/>
-    <col min="3656" max="3656" width="7.109375" style="51" customWidth="1"/>
-    <col min="3657" max="3657" width="8.5546875" style="51" customWidth="1"/>
-    <col min="3658" max="3658" width="9" style="51" customWidth="1"/>
-    <col min="3659" max="3659" width="5.109375" style="51" customWidth="1"/>
-    <col min="3660" max="3660" width="8.44140625" style="51" customWidth="1"/>
-    <col min="3661" max="3661" width="17.109375" style="51" customWidth="1"/>
-    <col min="3662" max="3662" width="18" style="51" customWidth="1"/>
-    <col min="3663" max="3663" width="3.88671875" style="51" customWidth="1"/>
-    <col min="3664" max="3665" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="3666" max="3668" width="9.109375" style="51"/>
-    <col min="3669" max="3669" width="11.33203125" style="51" customWidth="1"/>
-    <col min="3670" max="3907" width="9.109375" style="51"/>
-    <col min="3908" max="3908" width="3.109375" style="51" customWidth="1"/>
-    <col min="3909" max="3909" width="3.44140625" style="51" customWidth="1"/>
-    <col min="3910" max="3910" width="7.33203125" style="51" customWidth="1"/>
-    <col min="3911" max="3911" width="13.5546875" style="51" customWidth="1"/>
-    <col min="3912" max="3912" width="7.109375" style="51" customWidth="1"/>
-    <col min="3913" max="3913" width="8.5546875" style="51" customWidth="1"/>
-    <col min="3914" max="3914" width="9" style="51" customWidth="1"/>
-    <col min="3915" max="3915" width="5.109375" style="51" customWidth="1"/>
-    <col min="3916" max="3916" width="8.44140625" style="51" customWidth="1"/>
-    <col min="3917" max="3917" width="17.109375" style="51" customWidth="1"/>
-    <col min="3918" max="3918" width="18" style="51" customWidth="1"/>
-    <col min="3919" max="3919" width="3.88671875" style="51" customWidth="1"/>
-    <col min="3920" max="3921" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="3922" max="3924" width="9.109375" style="51"/>
-    <col min="3925" max="3925" width="11.33203125" style="51" customWidth="1"/>
-    <col min="3926" max="4163" width="9.109375" style="51"/>
-    <col min="4164" max="4164" width="3.109375" style="51" customWidth="1"/>
-    <col min="4165" max="4165" width="3.44140625" style="51" customWidth="1"/>
-    <col min="4166" max="4166" width="7.33203125" style="51" customWidth="1"/>
-    <col min="4167" max="4167" width="13.5546875" style="51" customWidth="1"/>
-    <col min="4168" max="4168" width="7.109375" style="51" customWidth="1"/>
-    <col min="4169" max="4169" width="8.5546875" style="51" customWidth="1"/>
-    <col min="4170" max="4170" width="9" style="51" customWidth="1"/>
-    <col min="4171" max="4171" width="5.109375" style="51" customWidth="1"/>
-    <col min="4172" max="4172" width="8.44140625" style="51" customWidth="1"/>
-    <col min="4173" max="4173" width="17.109375" style="51" customWidth="1"/>
-    <col min="4174" max="4174" width="18" style="51" customWidth="1"/>
-    <col min="4175" max="4175" width="3.88671875" style="51" customWidth="1"/>
-    <col min="4176" max="4177" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="4178" max="4180" width="9.109375" style="51"/>
-    <col min="4181" max="4181" width="11.33203125" style="51" customWidth="1"/>
-    <col min="4182" max="4419" width="9.109375" style="51"/>
-    <col min="4420" max="4420" width="3.109375" style="51" customWidth="1"/>
-    <col min="4421" max="4421" width="3.44140625" style="51" customWidth="1"/>
-    <col min="4422" max="4422" width="7.33203125" style="51" customWidth="1"/>
-    <col min="4423" max="4423" width="13.5546875" style="51" customWidth="1"/>
-    <col min="4424" max="4424" width="7.109375" style="51" customWidth="1"/>
-    <col min="4425" max="4425" width="8.5546875" style="51" customWidth="1"/>
-    <col min="4426" max="4426" width="9" style="51" customWidth="1"/>
-    <col min="4427" max="4427" width="5.109375" style="51" customWidth="1"/>
-    <col min="4428" max="4428" width="8.44140625" style="51" customWidth="1"/>
-    <col min="4429" max="4429" width="17.109375" style="51" customWidth="1"/>
-    <col min="4430" max="4430" width="18" style="51" customWidth="1"/>
-    <col min="4431" max="4431" width="3.88671875" style="51" customWidth="1"/>
-    <col min="4432" max="4433" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="4434" max="4436" width="9.109375" style="51"/>
-    <col min="4437" max="4437" width="11.33203125" style="51" customWidth="1"/>
-    <col min="4438" max="4675" width="9.109375" style="51"/>
-    <col min="4676" max="4676" width="3.109375" style="51" customWidth="1"/>
-    <col min="4677" max="4677" width="3.44140625" style="51" customWidth="1"/>
-    <col min="4678" max="4678" width="7.33203125" style="51" customWidth="1"/>
-    <col min="4679" max="4679" width="13.5546875" style="51" customWidth="1"/>
-    <col min="4680" max="4680" width="7.109375" style="51" customWidth="1"/>
-    <col min="4681" max="4681" width="8.5546875" style="51" customWidth="1"/>
-    <col min="4682" max="4682" width="9" style="51" customWidth="1"/>
-    <col min="4683" max="4683" width="5.109375" style="51" customWidth="1"/>
-    <col min="4684" max="4684" width="8.44140625" style="51" customWidth="1"/>
-    <col min="4685" max="4685" width="17.109375" style="51" customWidth="1"/>
-    <col min="4686" max="4686" width="18" style="51" customWidth="1"/>
-    <col min="4687" max="4687" width="3.88671875" style="51" customWidth="1"/>
-    <col min="4688" max="4689" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="4690" max="4692" width="9.109375" style="51"/>
-    <col min="4693" max="4693" width="11.33203125" style="51" customWidth="1"/>
-    <col min="4694" max="4931" width="9.109375" style="51"/>
-    <col min="4932" max="4932" width="3.109375" style="51" customWidth="1"/>
-    <col min="4933" max="4933" width="3.44140625" style="51" customWidth="1"/>
-    <col min="4934" max="4934" width="7.33203125" style="51" customWidth="1"/>
-    <col min="4935" max="4935" width="13.5546875" style="51" customWidth="1"/>
-    <col min="4936" max="4936" width="7.109375" style="51" customWidth="1"/>
-    <col min="4937" max="4937" width="8.5546875" style="51" customWidth="1"/>
-    <col min="4938" max="4938" width="9" style="51" customWidth="1"/>
-    <col min="4939" max="4939" width="5.109375" style="51" customWidth="1"/>
-    <col min="4940" max="4940" width="8.44140625" style="51" customWidth="1"/>
-    <col min="4941" max="4941" width="17.109375" style="51" customWidth="1"/>
-    <col min="4942" max="4942" width="18" style="51" customWidth="1"/>
-    <col min="4943" max="4943" width="3.88671875" style="51" customWidth="1"/>
-    <col min="4944" max="4945" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="4946" max="4948" width="9.109375" style="51"/>
-    <col min="4949" max="4949" width="11.33203125" style="51" customWidth="1"/>
-    <col min="4950" max="5187" width="9.109375" style="51"/>
-    <col min="5188" max="5188" width="3.109375" style="51" customWidth="1"/>
-    <col min="5189" max="5189" width="3.44140625" style="51" customWidth="1"/>
-    <col min="5190" max="5190" width="7.33203125" style="51" customWidth="1"/>
-    <col min="5191" max="5191" width="13.5546875" style="51" customWidth="1"/>
-    <col min="5192" max="5192" width="7.109375" style="51" customWidth="1"/>
-    <col min="5193" max="5193" width="8.5546875" style="51" customWidth="1"/>
-    <col min="5194" max="5194" width="9" style="51" customWidth="1"/>
-    <col min="5195" max="5195" width="5.109375" style="51" customWidth="1"/>
-    <col min="5196" max="5196" width="8.44140625" style="51" customWidth="1"/>
-    <col min="5197" max="5197" width="17.109375" style="51" customWidth="1"/>
-    <col min="5198" max="5198" width="18" style="51" customWidth="1"/>
-    <col min="5199" max="5199" width="3.88671875" style="51" customWidth="1"/>
-    <col min="5200" max="5201" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="5202" max="5204" width="9.109375" style="51"/>
-    <col min="5205" max="5205" width="11.33203125" style="51" customWidth="1"/>
-    <col min="5206" max="5443" width="9.109375" style="51"/>
-    <col min="5444" max="5444" width="3.109375" style="51" customWidth="1"/>
-    <col min="5445" max="5445" width="3.44140625" style="51" customWidth="1"/>
-    <col min="5446" max="5446" width="7.33203125" style="51" customWidth="1"/>
-    <col min="5447" max="5447" width="13.5546875" style="51" customWidth="1"/>
-    <col min="5448" max="5448" width="7.109375" style="51" customWidth="1"/>
-    <col min="5449" max="5449" width="8.5546875" style="51" customWidth="1"/>
-    <col min="5450" max="5450" width="9" style="51" customWidth="1"/>
-    <col min="5451" max="5451" width="5.109375" style="51" customWidth="1"/>
-    <col min="5452" max="5452" width="8.44140625" style="51" customWidth="1"/>
-    <col min="5453" max="5453" width="17.109375" style="51" customWidth="1"/>
-    <col min="5454" max="5454" width="18" style="51" customWidth="1"/>
-    <col min="5455" max="5455" width="3.88671875" style="51" customWidth="1"/>
-    <col min="5456" max="5457" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="5458" max="5460" width="9.109375" style="51"/>
-    <col min="5461" max="5461" width="11.33203125" style="51" customWidth="1"/>
-    <col min="5462" max="5699" width="9.109375" style="51"/>
-    <col min="5700" max="5700" width="3.109375" style="51" customWidth="1"/>
-    <col min="5701" max="5701" width="3.44140625" style="51" customWidth="1"/>
-    <col min="5702" max="5702" width="7.33203125" style="51" customWidth="1"/>
-    <col min="5703" max="5703" width="13.5546875" style="51" customWidth="1"/>
-    <col min="5704" max="5704" width="7.109375" style="51" customWidth="1"/>
-    <col min="5705" max="5705" width="8.5546875" style="51" customWidth="1"/>
-    <col min="5706" max="5706" width="9" style="51" customWidth="1"/>
-    <col min="5707" max="5707" width="5.109375" style="51" customWidth="1"/>
-    <col min="5708" max="5708" width="8.44140625" style="51" customWidth="1"/>
-    <col min="5709" max="5709" width="17.109375" style="51" customWidth="1"/>
-    <col min="5710" max="5710" width="18" style="51" customWidth="1"/>
-    <col min="5711" max="5711" width="3.88671875" style="51" customWidth="1"/>
-    <col min="5712" max="5713" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="5714" max="5716" width="9.109375" style="51"/>
-    <col min="5717" max="5717" width="11.33203125" style="51" customWidth="1"/>
-    <col min="5718" max="5955" width="9.109375" style="51"/>
-    <col min="5956" max="5956" width="3.109375" style="51" customWidth="1"/>
-    <col min="5957" max="5957" width="3.44140625" style="51" customWidth="1"/>
-    <col min="5958" max="5958" width="7.33203125" style="51" customWidth="1"/>
-    <col min="5959" max="5959" width="13.5546875" style="51" customWidth="1"/>
-    <col min="5960" max="5960" width="7.109375" style="51" customWidth="1"/>
-    <col min="5961" max="5961" width="8.5546875" style="51" customWidth="1"/>
-    <col min="5962" max="5962" width="9" style="51" customWidth="1"/>
-    <col min="5963" max="5963" width="5.109375" style="51" customWidth="1"/>
-    <col min="5964" max="5964" width="8.44140625" style="51" customWidth="1"/>
-    <col min="5965" max="5965" width="17.109375" style="51" customWidth="1"/>
-    <col min="5966" max="5966" width="18" style="51" customWidth="1"/>
-    <col min="5967" max="5967" width="3.88671875" style="51" customWidth="1"/>
-    <col min="5968" max="5969" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="5970" max="5972" width="9.109375" style="51"/>
-    <col min="5973" max="5973" width="11.33203125" style="51" customWidth="1"/>
-    <col min="5974" max="6211" width="9.109375" style="51"/>
-    <col min="6212" max="6212" width="3.109375" style="51" customWidth="1"/>
-    <col min="6213" max="6213" width="3.44140625" style="51" customWidth="1"/>
-    <col min="6214" max="6214" width="7.33203125" style="51" customWidth="1"/>
-    <col min="6215" max="6215" width="13.5546875" style="51" customWidth="1"/>
-    <col min="6216" max="6216" width="7.109375" style="51" customWidth="1"/>
-    <col min="6217" max="6217" width="8.5546875" style="51" customWidth="1"/>
-    <col min="6218" max="6218" width="9" style="51" customWidth="1"/>
-    <col min="6219" max="6219" width="5.109375" style="51" customWidth="1"/>
-    <col min="6220" max="6220" width="8.44140625" style="51" customWidth="1"/>
-    <col min="6221" max="6221" width="17.109375" style="51" customWidth="1"/>
-    <col min="6222" max="6222" width="18" style="51" customWidth="1"/>
-    <col min="6223" max="6223" width="3.88671875" style="51" customWidth="1"/>
-    <col min="6224" max="6225" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="6226" max="6228" width="9.109375" style="51"/>
-    <col min="6229" max="6229" width="11.33203125" style="51" customWidth="1"/>
-    <col min="6230" max="6467" width="9.109375" style="51"/>
-    <col min="6468" max="6468" width="3.109375" style="51" customWidth="1"/>
-    <col min="6469" max="6469" width="3.44140625" style="51" customWidth="1"/>
-    <col min="6470" max="6470" width="7.33203125" style="51" customWidth="1"/>
-    <col min="6471" max="6471" width="13.5546875" style="51" customWidth="1"/>
-    <col min="6472" max="6472" width="7.109375" style="51" customWidth="1"/>
-    <col min="6473" max="6473" width="8.5546875" style="51" customWidth="1"/>
-    <col min="6474" max="6474" width="9" style="51" customWidth="1"/>
-    <col min="6475" max="6475" width="5.109375" style="51" customWidth="1"/>
-    <col min="6476" max="6476" width="8.44140625" style="51" customWidth="1"/>
-    <col min="6477" max="6477" width="17.109375" style="51" customWidth="1"/>
-    <col min="6478" max="6478" width="18" style="51" customWidth="1"/>
-    <col min="6479" max="6479" width="3.88671875" style="51" customWidth="1"/>
-    <col min="6480" max="6481" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="6482" max="6484" width="9.109375" style="51"/>
-    <col min="6485" max="6485" width="11.33203125" style="51" customWidth="1"/>
-    <col min="6486" max="6723" width="9.109375" style="51"/>
-    <col min="6724" max="6724" width="3.109375" style="51" customWidth="1"/>
-    <col min="6725" max="6725" width="3.44140625" style="51" customWidth="1"/>
-    <col min="6726" max="6726" width="7.33203125" style="51" customWidth="1"/>
-    <col min="6727" max="6727" width="13.5546875" style="51" customWidth="1"/>
-    <col min="6728" max="6728" width="7.109375" style="51" customWidth="1"/>
-    <col min="6729" max="6729" width="8.5546875" style="51" customWidth="1"/>
-    <col min="6730" max="6730" width="9" style="51" customWidth="1"/>
-    <col min="6731" max="6731" width="5.109375" style="51" customWidth="1"/>
-    <col min="6732" max="6732" width="8.44140625" style="51" customWidth="1"/>
-    <col min="6733" max="6733" width="17.109375" style="51" customWidth="1"/>
-    <col min="6734" max="6734" width="18" style="51" customWidth="1"/>
-    <col min="6735" max="6735" width="3.88671875" style="51" customWidth="1"/>
-    <col min="6736" max="6737" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="6738" max="6740" width="9.109375" style="51"/>
-    <col min="6741" max="6741" width="11.33203125" style="51" customWidth="1"/>
-    <col min="6742" max="6979" width="9.109375" style="51"/>
-    <col min="6980" max="6980" width="3.109375" style="51" customWidth="1"/>
-    <col min="6981" max="6981" width="3.44140625" style="51" customWidth="1"/>
-    <col min="6982" max="6982" width="7.33203125" style="51" customWidth="1"/>
-    <col min="6983" max="6983" width="13.5546875" style="51" customWidth="1"/>
-    <col min="6984" max="6984" width="7.109375" style="51" customWidth="1"/>
-    <col min="6985" max="6985" width="8.5546875" style="51" customWidth="1"/>
-    <col min="6986" max="6986" width="9" style="51" customWidth="1"/>
-    <col min="6987" max="6987" width="5.109375" style="51" customWidth="1"/>
-    <col min="6988" max="6988" width="8.44140625" style="51" customWidth="1"/>
-    <col min="6989" max="6989" width="17.109375" style="51" customWidth="1"/>
-    <col min="6990" max="6990" width="18" style="51" customWidth="1"/>
-    <col min="6991" max="6991" width="3.88671875" style="51" customWidth="1"/>
-    <col min="6992" max="6993" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="6994" max="6996" width="9.109375" style="51"/>
-    <col min="6997" max="6997" width="11.33203125" style="51" customWidth="1"/>
-    <col min="6998" max="7235" width="9.109375" style="51"/>
-    <col min="7236" max="7236" width="3.109375" style="51" customWidth="1"/>
-    <col min="7237" max="7237" width="3.44140625" style="51" customWidth="1"/>
-    <col min="7238" max="7238" width="7.33203125" style="51" customWidth="1"/>
-    <col min="7239" max="7239" width="13.5546875" style="51" customWidth="1"/>
-    <col min="7240" max="7240" width="7.109375" style="51" customWidth="1"/>
-    <col min="7241" max="7241" width="8.5546875" style="51" customWidth="1"/>
-    <col min="7242" max="7242" width="9" style="51" customWidth="1"/>
-    <col min="7243" max="7243" width="5.109375" style="51" customWidth="1"/>
-    <col min="7244" max="7244" width="8.44140625" style="51" customWidth="1"/>
-    <col min="7245" max="7245" width="17.109375" style="51" customWidth="1"/>
-    <col min="7246" max="7246" width="18" style="51" customWidth="1"/>
-    <col min="7247" max="7247" width="3.88671875" style="51" customWidth="1"/>
-    <col min="7248" max="7249" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="7250" max="7252" width="9.109375" style="51"/>
-    <col min="7253" max="7253" width="11.33203125" style="51" customWidth="1"/>
-    <col min="7254" max="7491" width="9.109375" style="51"/>
-    <col min="7492" max="7492" width="3.109375" style="51" customWidth="1"/>
-    <col min="7493" max="7493" width="3.44140625" style="51" customWidth="1"/>
-    <col min="7494" max="7494" width="7.33203125" style="51" customWidth="1"/>
-    <col min="7495" max="7495" width="13.5546875" style="51" customWidth="1"/>
-    <col min="7496" max="7496" width="7.109375" style="51" customWidth="1"/>
-    <col min="7497" max="7497" width="8.5546875" style="51" customWidth="1"/>
-    <col min="7498" max="7498" width="9" style="51" customWidth="1"/>
-    <col min="7499" max="7499" width="5.109375" style="51" customWidth="1"/>
-    <col min="7500" max="7500" width="8.44140625" style="51" customWidth="1"/>
-    <col min="7501" max="7501" width="17.109375" style="51" customWidth="1"/>
-    <col min="7502" max="7502" width="18" style="51" customWidth="1"/>
-    <col min="7503" max="7503" width="3.88671875" style="51" customWidth="1"/>
-    <col min="7504" max="7505" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="7506" max="7508" width="9.109375" style="51"/>
-    <col min="7509" max="7509" width="11.33203125" style="51" customWidth="1"/>
-    <col min="7510" max="7747" width="9.109375" style="51"/>
-    <col min="7748" max="7748" width="3.109375" style="51" customWidth="1"/>
-    <col min="7749" max="7749" width="3.44140625" style="51" customWidth="1"/>
-    <col min="7750" max="7750" width="7.33203125" style="51" customWidth="1"/>
-    <col min="7751" max="7751" width="13.5546875" style="51" customWidth="1"/>
-    <col min="7752" max="7752" width="7.109375" style="51" customWidth="1"/>
-    <col min="7753" max="7753" width="8.5546875" style="51" customWidth="1"/>
-    <col min="7754" max="7754" width="9" style="51" customWidth="1"/>
-    <col min="7755" max="7755" width="5.109375" style="51" customWidth="1"/>
-    <col min="7756" max="7756" width="8.44140625" style="51" customWidth="1"/>
-    <col min="7757" max="7757" width="17.109375" style="51" customWidth="1"/>
-    <col min="7758" max="7758" width="18" style="51" customWidth="1"/>
-    <col min="7759" max="7759" width="3.88671875" style="51" customWidth="1"/>
-    <col min="7760" max="7761" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="7762" max="7764" width="9.109375" style="51"/>
-    <col min="7765" max="7765" width="11.33203125" style="51" customWidth="1"/>
-    <col min="7766" max="8003" width="9.109375" style="51"/>
-    <col min="8004" max="8004" width="3.109375" style="51" customWidth="1"/>
-    <col min="8005" max="8005" width="3.44140625" style="51" customWidth="1"/>
-    <col min="8006" max="8006" width="7.33203125" style="51" customWidth="1"/>
-    <col min="8007" max="8007" width="13.5546875" style="51" customWidth="1"/>
-    <col min="8008" max="8008" width="7.109375" style="51" customWidth="1"/>
-    <col min="8009" max="8009" width="8.5546875" style="51" customWidth="1"/>
-    <col min="8010" max="8010" width="9" style="51" customWidth="1"/>
-    <col min="8011" max="8011" width="5.109375" style="51" customWidth="1"/>
-    <col min="8012" max="8012" width="8.44140625" style="51" customWidth="1"/>
-    <col min="8013" max="8013" width="17.109375" style="51" customWidth="1"/>
-    <col min="8014" max="8014" width="18" style="51" customWidth="1"/>
-    <col min="8015" max="8015" width="3.88671875" style="51" customWidth="1"/>
-    <col min="8016" max="8017" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="8018" max="8020" width="9.109375" style="51"/>
-    <col min="8021" max="8021" width="11.33203125" style="51" customWidth="1"/>
-    <col min="8022" max="8259" width="9.109375" style="51"/>
-    <col min="8260" max="8260" width="3.109375" style="51" customWidth="1"/>
-    <col min="8261" max="8261" width="3.44140625" style="51" customWidth="1"/>
-    <col min="8262" max="8262" width="7.33203125" style="51" customWidth="1"/>
-    <col min="8263" max="8263" width="13.5546875" style="51" customWidth="1"/>
-    <col min="8264" max="8264" width="7.109375" style="51" customWidth="1"/>
-    <col min="8265" max="8265" width="8.5546875" style="51" customWidth="1"/>
-    <col min="8266" max="8266" width="9" style="51" customWidth="1"/>
-    <col min="8267" max="8267" width="5.109375" style="51" customWidth="1"/>
-    <col min="8268" max="8268" width="8.44140625" style="51" customWidth="1"/>
-    <col min="8269" max="8269" width="17.109375" style="51" customWidth="1"/>
-    <col min="8270" max="8270" width="18" style="51" customWidth="1"/>
-    <col min="8271" max="8271" width="3.88671875" style="51" customWidth="1"/>
-    <col min="8272" max="8273" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="8274" max="8276" width="9.109375" style="51"/>
-    <col min="8277" max="8277" width="11.33203125" style="51" customWidth="1"/>
-    <col min="8278" max="8515" width="9.109375" style="51"/>
-    <col min="8516" max="8516" width="3.109375" style="51" customWidth="1"/>
-    <col min="8517" max="8517" width="3.44140625" style="51" customWidth="1"/>
-    <col min="8518" max="8518" width="7.33203125" style="51" customWidth="1"/>
-    <col min="8519" max="8519" width="13.5546875" style="51" customWidth="1"/>
-    <col min="8520" max="8520" width="7.109375" style="51" customWidth="1"/>
-    <col min="8521" max="8521" width="8.5546875" style="51" customWidth="1"/>
-    <col min="8522" max="8522" width="9" style="51" customWidth="1"/>
-    <col min="8523" max="8523" width="5.109375" style="51" customWidth="1"/>
-    <col min="8524" max="8524" width="8.44140625" style="51" customWidth="1"/>
-    <col min="8525" max="8525" width="17.109375" style="51" customWidth="1"/>
-    <col min="8526" max="8526" width="18" style="51" customWidth="1"/>
-    <col min="8527" max="8527" width="3.88671875" style="51" customWidth="1"/>
-    <col min="8528" max="8529" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="8530" max="8532" width="9.109375" style="51"/>
-    <col min="8533" max="8533" width="11.33203125" style="51" customWidth="1"/>
-    <col min="8534" max="8771" width="9.109375" style="51"/>
-    <col min="8772" max="8772" width="3.109375" style="51" customWidth="1"/>
-    <col min="8773" max="8773" width="3.44140625" style="51" customWidth="1"/>
-    <col min="8774" max="8774" width="7.33203125" style="51" customWidth="1"/>
-    <col min="8775" max="8775" width="13.5546875" style="51" customWidth="1"/>
-    <col min="8776" max="8776" width="7.109375" style="51" customWidth="1"/>
-    <col min="8777" max="8777" width="8.5546875" style="51" customWidth="1"/>
-    <col min="8778" max="8778" width="9" style="51" customWidth="1"/>
-    <col min="8779" max="8779" width="5.109375" style="51" customWidth="1"/>
-    <col min="8780" max="8780" width="8.44140625" style="51" customWidth="1"/>
-    <col min="8781" max="8781" width="17.109375" style="51" customWidth="1"/>
-    <col min="8782" max="8782" width="18" style="51" customWidth="1"/>
-    <col min="8783" max="8783" width="3.88671875" style="51" customWidth="1"/>
-    <col min="8784" max="8785" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="8786" max="8788" width="9.109375" style="51"/>
-    <col min="8789" max="8789" width="11.33203125" style="51" customWidth="1"/>
-    <col min="8790" max="9027" width="9.109375" style="51"/>
-    <col min="9028" max="9028" width="3.109375" style="51" customWidth="1"/>
-    <col min="9029" max="9029" width="3.44140625" style="51" customWidth="1"/>
-    <col min="9030" max="9030" width="7.33203125" style="51" customWidth="1"/>
-    <col min="9031" max="9031" width="13.5546875" style="51" customWidth="1"/>
-    <col min="9032" max="9032" width="7.109375" style="51" customWidth="1"/>
-    <col min="9033" max="9033" width="8.5546875" style="51" customWidth="1"/>
-    <col min="9034" max="9034" width="9" style="51" customWidth="1"/>
-    <col min="9035" max="9035" width="5.109375" style="51" customWidth="1"/>
-    <col min="9036" max="9036" width="8.44140625" style="51" customWidth="1"/>
-    <col min="9037" max="9037" width="17.109375" style="51" customWidth="1"/>
-    <col min="9038" max="9038" width="18" style="51" customWidth="1"/>
-    <col min="9039" max="9039" width="3.88671875" style="51" customWidth="1"/>
-    <col min="9040" max="9041" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="9042" max="9044" width="9.109375" style="51"/>
-    <col min="9045" max="9045" width="11.33203125" style="51" customWidth="1"/>
-    <col min="9046" max="9283" width="9.109375" style="51"/>
-    <col min="9284" max="9284" width="3.109375" style="51" customWidth="1"/>
-    <col min="9285" max="9285" width="3.44140625" style="51" customWidth="1"/>
-    <col min="9286" max="9286" width="7.33203125" style="51" customWidth="1"/>
-    <col min="9287" max="9287" width="13.5546875" style="51" customWidth="1"/>
-    <col min="9288" max="9288" width="7.109375" style="51" customWidth="1"/>
-    <col min="9289" max="9289" width="8.5546875" style="51" customWidth="1"/>
-    <col min="9290" max="9290" width="9" style="51" customWidth="1"/>
-    <col min="9291" max="9291" width="5.109375" style="51" customWidth="1"/>
-    <col min="9292" max="9292" width="8.44140625" style="51" customWidth="1"/>
-    <col min="9293" max="9293" width="17.109375" style="51" customWidth="1"/>
-    <col min="9294" max="9294" width="18" style="51" customWidth="1"/>
-    <col min="9295" max="9295" width="3.88671875" style="51" customWidth="1"/>
-    <col min="9296" max="9297" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="9298" max="9300" width="9.109375" style="51"/>
-    <col min="9301" max="9301" width="11.33203125" style="51" customWidth="1"/>
-    <col min="9302" max="9539" width="9.109375" style="51"/>
-    <col min="9540" max="9540" width="3.109375" style="51" customWidth="1"/>
-    <col min="9541" max="9541" width="3.44140625" style="51" customWidth="1"/>
-    <col min="9542" max="9542" width="7.33203125" style="51" customWidth="1"/>
-    <col min="9543" max="9543" width="13.5546875" style="51" customWidth="1"/>
-    <col min="9544" max="9544" width="7.109375" style="51" customWidth="1"/>
-    <col min="9545" max="9545" width="8.5546875" style="51" customWidth="1"/>
-    <col min="9546" max="9546" width="9" style="51" customWidth="1"/>
-    <col min="9547" max="9547" width="5.109375" style="51" customWidth="1"/>
-    <col min="9548" max="9548" width="8.44140625" style="51" customWidth="1"/>
-    <col min="9549" max="9549" width="17.109375" style="51" customWidth="1"/>
-    <col min="9550" max="9550" width="18" style="51" customWidth="1"/>
-    <col min="9551" max="9551" width="3.88671875" style="51" customWidth="1"/>
-    <col min="9552" max="9553" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="9554" max="9556" width="9.109375" style="51"/>
-    <col min="9557" max="9557" width="11.33203125" style="51" customWidth="1"/>
-    <col min="9558" max="9795" width="9.109375" style="51"/>
-    <col min="9796" max="9796" width="3.109375" style="51" customWidth="1"/>
-    <col min="9797" max="9797" width="3.44140625" style="51" customWidth="1"/>
-    <col min="9798" max="9798" width="7.33203125" style="51" customWidth="1"/>
-    <col min="9799" max="9799" width="13.5546875" style="51" customWidth="1"/>
-    <col min="9800" max="9800" width="7.109375" style="51" customWidth="1"/>
-    <col min="9801" max="9801" width="8.5546875" style="51" customWidth="1"/>
-    <col min="9802" max="9802" width="9" style="51" customWidth="1"/>
-    <col min="9803" max="9803" width="5.109375" style="51" customWidth="1"/>
-    <col min="9804" max="9804" width="8.44140625" style="51" customWidth="1"/>
-    <col min="9805" max="9805" width="17.109375" style="51" customWidth="1"/>
-    <col min="9806" max="9806" width="18" style="51" customWidth="1"/>
-    <col min="9807" max="9807" width="3.88671875" style="51" customWidth="1"/>
-    <col min="9808" max="9809" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="9810" max="9812" width="9.109375" style="51"/>
-    <col min="9813" max="9813" width="11.33203125" style="51" customWidth="1"/>
-    <col min="9814" max="10051" width="9.109375" style="51"/>
-    <col min="10052" max="10052" width="3.109375" style="51" customWidth="1"/>
-    <col min="10053" max="10053" width="3.44140625" style="51" customWidth="1"/>
-    <col min="10054" max="10054" width="7.33203125" style="51" customWidth="1"/>
-    <col min="10055" max="10055" width="13.5546875" style="51" customWidth="1"/>
-    <col min="10056" max="10056" width="7.109375" style="51" customWidth="1"/>
-    <col min="10057" max="10057" width="8.5546875" style="51" customWidth="1"/>
-    <col min="10058" max="10058" width="9" style="51" customWidth="1"/>
-    <col min="10059" max="10059" width="5.109375" style="51" customWidth="1"/>
-    <col min="10060" max="10060" width="8.44140625" style="51" customWidth="1"/>
-    <col min="10061" max="10061" width="17.109375" style="51" customWidth="1"/>
-    <col min="10062" max="10062" width="18" style="51" customWidth="1"/>
-    <col min="10063" max="10063" width="3.88671875" style="51" customWidth="1"/>
-    <col min="10064" max="10065" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="10066" max="10068" width="9.109375" style="51"/>
-    <col min="10069" max="10069" width="11.33203125" style="51" customWidth="1"/>
-    <col min="10070" max="10307" width="9.109375" style="51"/>
-    <col min="10308" max="10308" width="3.109375" style="51" customWidth="1"/>
-    <col min="10309" max="10309" width="3.44140625" style="51" customWidth="1"/>
-    <col min="10310" max="10310" width="7.33203125" style="51" customWidth="1"/>
-    <col min="10311" max="10311" width="13.5546875" style="51" customWidth="1"/>
-    <col min="10312" max="10312" width="7.109375" style="51" customWidth="1"/>
-    <col min="10313" max="10313" width="8.5546875" style="51" customWidth="1"/>
-    <col min="10314" max="10314" width="9" style="51" customWidth="1"/>
-    <col min="10315" max="10315" width="5.109375" style="51" customWidth="1"/>
-    <col min="10316" max="10316" width="8.44140625" style="51" customWidth="1"/>
-    <col min="10317" max="10317" width="17.109375" style="51" customWidth="1"/>
-    <col min="10318" max="10318" width="18" style="51" customWidth="1"/>
-    <col min="10319" max="10319" width="3.88671875" style="51" customWidth="1"/>
-    <col min="10320" max="10321" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="10322" max="10324" width="9.109375" style="51"/>
-    <col min="10325" max="10325" width="11.33203125" style="51" customWidth="1"/>
-    <col min="10326" max="10563" width="9.109375" style="51"/>
-    <col min="10564" max="10564" width="3.109375" style="51" customWidth="1"/>
-    <col min="10565" max="10565" width="3.44140625" style="51" customWidth="1"/>
-    <col min="10566" max="10566" width="7.33203125" style="51" customWidth="1"/>
-    <col min="10567" max="10567" width="13.5546875" style="51" customWidth="1"/>
-    <col min="10568" max="10568" width="7.109375" style="51" customWidth="1"/>
-    <col min="10569" max="10569" width="8.5546875" style="51" customWidth="1"/>
-    <col min="10570" max="10570" width="9" style="51" customWidth="1"/>
-    <col min="10571" max="10571" width="5.109375" style="51" customWidth="1"/>
-    <col min="10572" max="10572" width="8.44140625" style="51" customWidth="1"/>
-    <col min="10573" max="10573" width="17.109375" style="51" customWidth="1"/>
-    <col min="10574" max="10574" width="18" style="51" customWidth="1"/>
-    <col min="10575" max="10575" width="3.88671875" style="51" customWidth="1"/>
-    <col min="10576" max="10577" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="10578" max="10580" width="9.109375" style="51"/>
-    <col min="10581" max="10581" width="11.33203125" style="51" customWidth="1"/>
-    <col min="10582" max="10819" width="9.109375" style="51"/>
-    <col min="10820" max="10820" width="3.109375" style="51" customWidth="1"/>
-    <col min="10821" max="10821" width="3.44140625" style="51" customWidth="1"/>
-    <col min="10822" max="10822" width="7.33203125" style="51" customWidth="1"/>
-    <col min="10823" max="10823" width="13.5546875" style="51" customWidth="1"/>
-    <col min="10824" max="10824" width="7.109375" style="51" customWidth="1"/>
-    <col min="10825" max="10825" width="8.5546875" style="51" customWidth="1"/>
-    <col min="10826" max="10826" width="9" style="51" customWidth="1"/>
-    <col min="10827" max="10827" width="5.109375" style="51" customWidth="1"/>
-    <col min="10828" max="10828" width="8.44140625" style="51" customWidth="1"/>
-    <col min="10829" max="10829" width="17.109375" style="51" customWidth="1"/>
-    <col min="10830" max="10830" width="18" style="51" customWidth="1"/>
-    <col min="10831" max="10831" width="3.88671875" style="51" customWidth="1"/>
-    <col min="10832" max="10833" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="10834" max="10836" width="9.109375" style="51"/>
-    <col min="10837" max="10837" width="11.33203125" style="51" customWidth="1"/>
-    <col min="10838" max="11075" width="9.109375" style="51"/>
-    <col min="11076" max="11076" width="3.109375" style="51" customWidth="1"/>
-    <col min="11077" max="11077" width="3.44140625" style="51" customWidth="1"/>
-    <col min="11078" max="11078" width="7.33203125" style="51" customWidth="1"/>
-    <col min="11079" max="11079" width="13.5546875" style="51" customWidth="1"/>
-    <col min="11080" max="11080" width="7.109375" style="51" customWidth="1"/>
-    <col min="11081" max="11081" width="8.5546875" style="51" customWidth="1"/>
-    <col min="11082" max="11082" width="9" style="51" customWidth="1"/>
-    <col min="11083" max="11083" width="5.109375" style="51" customWidth="1"/>
-    <col min="11084" max="11084" width="8.44140625" style="51" customWidth="1"/>
-    <col min="11085" max="11085" width="17.109375" style="51" customWidth="1"/>
-    <col min="11086" max="11086" width="18" style="51" customWidth="1"/>
-    <col min="11087" max="11087" width="3.88671875" style="51" customWidth="1"/>
-    <col min="11088" max="11089" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="11090" max="11092" width="9.109375" style="51"/>
-    <col min="11093" max="11093" width="11.33203125" style="51" customWidth="1"/>
-    <col min="11094" max="11331" width="9.109375" style="51"/>
-    <col min="11332" max="11332" width="3.109375" style="51" customWidth="1"/>
-    <col min="11333" max="11333" width="3.44140625" style="51" customWidth="1"/>
-    <col min="11334" max="11334" width="7.33203125" style="51" customWidth="1"/>
-    <col min="11335" max="11335" width="13.5546875" style="51" customWidth="1"/>
-    <col min="11336" max="11336" width="7.109375" style="51" customWidth="1"/>
-    <col min="11337" max="11337" width="8.5546875" style="51" customWidth="1"/>
-    <col min="11338" max="11338" width="9" style="51" customWidth="1"/>
-    <col min="11339" max="11339" width="5.109375" style="51" customWidth="1"/>
-    <col min="11340" max="11340" width="8.44140625" style="51" customWidth="1"/>
-    <col min="11341" max="11341" width="17.109375" style="51" customWidth="1"/>
-    <col min="11342" max="11342" width="18" style="51" customWidth="1"/>
-    <col min="11343" max="11343" width="3.88671875" style="51" customWidth="1"/>
-    <col min="11344" max="11345" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="11346" max="11348" width="9.109375" style="51"/>
-    <col min="11349" max="11349" width="11.33203125" style="51" customWidth="1"/>
-    <col min="11350" max="11587" width="9.109375" style="51"/>
-    <col min="11588" max="11588" width="3.109375" style="51" customWidth="1"/>
-    <col min="11589" max="11589" width="3.44140625" style="51" customWidth="1"/>
-    <col min="11590" max="11590" width="7.33203125" style="51" customWidth="1"/>
-    <col min="11591" max="11591" width="13.5546875" style="51" customWidth="1"/>
-    <col min="11592" max="11592" width="7.109375" style="51" customWidth="1"/>
-    <col min="11593" max="11593" width="8.5546875" style="51" customWidth="1"/>
-    <col min="11594" max="11594" width="9" style="51" customWidth="1"/>
-    <col min="11595" max="11595" width="5.109375" style="51" customWidth="1"/>
-    <col min="11596" max="11596" width="8.44140625" style="51" customWidth="1"/>
-    <col min="11597" max="11597" width="17.109375" style="51" customWidth="1"/>
-    <col min="11598" max="11598" width="18" style="51" customWidth="1"/>
-    <col min="11599" max="11599" width="3.88671875" style="51" customWidth="1"/>
-    <col min="11600" max="11601" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="11602" max="11604" width="9.109375" style="51"/>
-    <col min="11605" max="11605" width="11.33203125" style="51" customWidth="1"/>
-    <col min="11606" max="11843" width="9.109375" style="51"/>
-    <col min="11844" max="11844" width="3.109375" style="51" customWidth="1"/>
-    <col min="11845" max="11845" width="3.44140625" style="51" customWidth="1"/>
-    <col min="11846" max="11846" width="7.33203125" style="51" customWidth="1"/>
-    <col min="11847" max="11847" width="13.5546875" style="51" customWidth="1"/>
-    <col min="11848" max="11848" width="7.109375" style="51" customWidth="1"/>
-    <col min="11849" max="11849" width="8.5546875" style="51" customWidth="1"/>
-    <col min="11850" max="11850" width="9" style="51" customWidth="1"/>
-    <col min="11851" max="11851" width="5.109375" style="51" customWidth="1"/>
-    <col min="11852" max="11852" width="8.44140625" style="51" customWidth="1"/>
-    <col min="11853" max="11853" width="17.109375" style="51" customWidth="1"/>
-    <col min="11854" max="11854" width="18" style="51" customWidth="1"/>
-    <col min="11855" max="11855" width="3.88671875" style="51" customWidth="1"/>
-    <col min="11856" max="11857" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="11858" max="11860" width="9.109375" style="51"/>
-    <col min="11861" max="11861" width="11.33203125" style="51" customWidth="1"/>
-    <col min="11862" max="12099" width="9.109375" style="51"/>
-    <col min="12100" max="12100" width="3.109375" style="51" customWidth="1"/>
-    <col min="12101" max="12101" width="3.44140625" style="51" customWidth="1"/>
-    <col min="12102" max="12102" width="7.33203125" style="51" customWidth="1"/>
-    <col min="12103" max="12103" width="13.5546875" style="51" customWidth="1"/>
-    <col min="12104" max="12104" width="7.109375" style="51" customWidth="1"/>
-    <col min="12105" max="12105" width="8.5546875" style="51" customWidth="1"/>
-    <col min="12106" max="12106" width="9" style="51" customWidth="1"/>
-    <col min="12107" max="12107" width="5.109375" style="51" customWidth="1"/>
-    <col min="12108" max="12108" width="8.44140625" style="51" customWidth="1"/>
-    <col min="12109" max="12109" width="17.109375" style="51" customWidth="1"/>
-    <col min="12110" max="12110" width="18" style="51" customWidth="1"/>
-    <col min="12111" max="12111" width="3.88671875" style="51" customWidth="1"/>
-    <col min="12112" max="12113" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="12114" max="12116" width="9.109375" style="51"/>
-    <col min="12117" max="12117" width="11.33203125" style="51" customWidth="1"/>
-    <col min="12118" max="12355" width="9.109375" style="51"/>
-    <col min="12356" max="12356" width="3.109375" style="51" customWidth="1"/>
-    <col min="12357" max="12357" width="3.44140625" style="51" customWidth="1"/>
-    <col min="12358" max="12358" width="7.33203125" style="51" customWidth="1"/>
-    <col min="12359" max="12359" width="13.5546875" style="51" customWidth="1"/>
-    <col min="12360" max="12360" width="7.109375" style="51" customWidth="1"/>
-    <col min="12361" max="12361" width="8.5546875" style="51" customWidth="1"/>
-    <col min="12362" max="12362" width="9" style="51" customWidth="1"/>
-    <col min="12363" max="12363" width="5.109375" style="51" customWidth="1"/>
-    <col min="12364" max="12364" width="8.44140625" style="51" customWidth="1"/>
-    <col min="12365" max="12365" width="17.109375" style="51" customWidth="1"/>
-    <col min="12366" max="12366" width="18" style="51" customWidth="1"/>
-    <col min="12367" max="12367" width="3.88671875" style="51" customWidth="1"/>
-    <col min="12368" max="12369" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="12370" max="12372" width="9.109375" style="51"/>
-    <col min="12373" max="12373" width="11.33203125" style="51" customWidth="1"/>
-    <col min="12374" max="12611" width="9.109375" style="51"/>
-    <col min="12612" max="12612" width="3.109375" style="51" customWidth="1"/>
-    <col min="12613" max="12613" width="3.44140625" style="51" customWidth="1"/>
-    <col min="12614" max="12614" width="7.33203125" style="51" customWidth="1"/>
-    <col min="12615" max="12615" width="13.5546875" style="51" customWidth="1"/>
-    <col min="12616" max="12616" width="7.109375" style="51" customWidth="1"/>
-    <col min="12617" max="12617" width="8.5546875" style="51" customWidth="1"/>
-    <col min="12618" max="12618" width="9" style="51" customWidth="1"/>
-    <col min="12619" max="12619" width="5.109375" style="51" customWidth="1"/>
-    <col min="12620" max="12620" width="8.44140625" style="51" customWidth="1"/>
-    <col min="12621" max="12621" width="17.109375" style="51" customWidth="1"/>
-    <col min="12622" max="12622" width="18" style="51" customWidth="1"/>
-    <col min="12623" max="12623" width="3.88671875" style="51" customWidth="1"/>
-    <col min="12624" max="12625" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="12626" max="12628" width="9.109375" style="51"/>
-    <col min="12629" max="12629" width="11.33203125" style="51" customWidth="1"/>
-    <col min="12630" max="12867" width="9.109375" style="51"/>
-    <col min="12868" max="12868" width="3.109375" style="51" customWidth="1"/>
-    <col min="12869" max="12869" width="3.44140625" style="51" customWidth="1"/>
-    <col min="12870" max="12870" width="7.33203125" style="51" customWidth="1"/>
-    <col min="12871" max="12871" width="13.5546875" style="51" customWidth="1"/>
-    <col min="12872" max="12872" width="7.109375" style="51" customWidth="1"/>
-    <col min="12873" max="12873" width="8.5546875" style="51" customWidth="1"/>
-    <col min="12874" max="12874" width="9" style="51" customWidth="1"/>
-    <col min="12875" max="12875" width="5.109375" style="51" customWidth="1"/>
-    <col min="12876" max="12876" width="8.44140625" style="51" customWidth="1"/>
-    <col min="12877" max="12877" width="17.109375" style="51" customWidth="1"/>
-    <col min="12878" max="12878" width="18" style="51" customWidth="1"/>
-    <col min="12879" max="12879" width="3.88671875" style="51" customWidth="1"/>
-    <col min="12880" max="12881" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="12882" max="12884" width="9.109375" style="51"/>
-    <col min="12885" max="12885" width="11.33203125" style="51" customWidth="1"/>
-    <col min="12886" max="13123" width="9.109375" style="51"/>
-    <col min="13124" max="13124" width="3.109375" style="51" customWidth="1"/>
-    <col min="13125" max="13125" width="3.44140625" style="51" customWidth="1"/>
-    <col min="13126" max="13126" width="7.33203125" style="51" customWidth="1"/>
-    <col min="13127" max="13127" width="13.5546875" style="51" customWidth="1"/>
-    <col min="13128" max="13128" width="7.109375" style="51" customWidth="1"/>
-    <col min="13129" max="13129" width="8.5546875" style="51" customWidth="1"/>
-    <col min="13130" max="13130" width="9" style="51" customWidth="1"/>
-    <col min="13131" max="13131" width="5.109375" style="51" customWidth="1"/>
-    <col min="13132" max="13132" width="8.44140625" style="51" customWidth="1"/>
-    <col min="13133" max="13133" width="17.109375" style="51" customWidth="1"/>
-    <col min="13134" max="13134" width="18" style="51" customWidth="1"/>
-    <col min="13135" max="13135" width="3.88671875" style="51" customWidth="1"/>
-    <col min="13136" max="13137" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="13138" max="13140" width="9.109375" style="51"/>
-    <col min="13141" max="13141" width="11.33203125" style="51" customWidth="1"/>
-    <col min="13142" max="13379" width="9.109375" style="51"/>
-    <col min="13380" max="13380" width="3.109375" style="51" customWidth="1"/>
-    <col min="13381" max="13381" width="3.44140625" style="51" customWidth="1"/>
-    <col min="13382" max="13382" width="7.33203125" style="51" customWidth="1"/>
-    <col min="13383" max="13383" width="13.5546875" style="51" customWidth="1"/>
-    <col min="13384" max="13384" width="7.109375" style="51" customWidth="1"/>
-    <col min="13385" max="13385" width="8.5546875" style="51" customWidth="1"/>
-    <col min="13386" max="13386" width="9" style="51" customWidth="1"/>
-    <col min="13387" max="13387" width="5.109375" style="51" customWidth="1"/>
-    <col min="13388" max="13388" width="8.44140625" style="51" customWidth="1"/>
-    <col min="13389" max="13389" width="17.109375" style="51" customWidth="1"/>
-    <col min="13390" max="13390" width="18" style="51" customWidth="1"/>
-    <col min="13391" max="13391" width="3.88671875" style="51" customWidth="1"/>
-    <col min="13392" max="13393" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="13394" max="13396" width="9.109375" style="51"/>
-    <col min="13397" max="13397" width="11.33203125" style="51" customWidth="1"/>
-    <col min="13398" max="13635" width="9.109375" style="51"/>
-    <col min="13636" max="13636" width="3.109375" style="51" customWidth="1"/>
-    <col min="13637" max="13637" width="3.44140625" style="51" customWidth="1"/>
-    <col min="13638" max="13638" width="7.33203125" style="51" customWidth="1"/>
-    <col min="13639" max="13639" width="13.5546875" style="51" customWidth="1"/>
-    <col min="13640" max="13640" width="7.109375" style="51" customWidth="1"/>
-    <col min="13641" max="13641" width="8.5546875" style="51" customWidth="1"/>
-    <col min="13642" max="13642" width="9" style="51" customWidth="1"/>
-    <col min="13643" max="13643" width="5.109375" style="51" customWidth="1"/>
-    <col min="13644" max="13644" width="8.44140625" style="51" customWidth="1"/>
-    <col min="13645" max="13645" width="17.109375" style="51" customWidth="1"/>
-    <col min="13646" max="13646" width="18" style="51" customWidth="1"/>
-    <col min="13647" max="13647" width="3.88671875" style="51" customWidth="1"/>
-    <col min="13648" max="13649" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="13650" max="13652" width="9.109375" style="51"/>
-    <col min="13653" max="13653" width="11.33203125" style="51" customWidth="1"/>
-    <col min="13654" max="13891" width="9.109375" style="51"/>
-    <col min="13892" max="13892" width="3.109375" style="51" customWidth="1"/>
-    <col min="13893" max="13893" width="3.44140625" style="51" customWidth="1"/>
-    <col min="13894" max="13894" width="7.33203125" style="51" customWidth="1"/>
-    <col min="13895" max="13895" width="13.5546875" style="51" customWidth="1"/>
-    <col min="13896" max="13896" width="7.109375" style="51" customWidth="1"/>
-    <col min="13897" max="13897" width="8.5546875" style="51" customWidth="1"/>
-    <col min="13898" max="13898" width="9" style="51" customWidth="1"/>
-    <col min="13899" max="13899" width="5.109375" style="51" customWidth="1"/>
-    <col min="13900" max="13900" width="8.44140625" style="51" customWidth="1"/>
-    <col min="13901" max="13901" width="17.109375" style="51" customWidth="1"/>
-    <col min="13902" max="13902" width="18" style="51" customWidth="1"/>
-    <col min="13903" max="13903" width="3.88671875" style="51" customWidth="1"/>
-    <col min="13904" max="13905" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="13906" max="13908" width="9.109375" style="51"/>
-    <col min="13909" max="13909" width="11.33203125" style="51" customWidth="1"/>
-    <col min="13910" max="14147" width="9.109375" style="51"/>
-    <col min="14148" max="14148" width="3.109375" style="51" customWidth="1"/>
-    <col min="14149" max="14149" width="3.44140625" style="51" customWidth="1"/>
-    <col min="14150" max="14150" width="7.33203125" style="51" customWidth="1"/>
-    <col min="14151" max="14151" width="13.5546875" style="51" customWidth="1"/>
-    <col min="14152" max="14152" width="7.109375" style="51" customWidth="1"/>
-    <col min="14153" max="14153" width="8.5546875" style="51" customWidth="1"/>
-    <col min="14154" max="14154" width="9" style="51" customWidth="1"/>
-    <col min="14155" max="14155" width="5.109375" style="51" customWidth="1"/>
-    <col min="14156" max="14156" width="8.44140625" style="51" customWidth="1"/>
-    <col min="14157" max="14157" width="17.109375" style="51" customWidth="1"/>
-    <col min="14158" max="14158" width="18" style="51" customWidth="1"/>
-    <col min="14159" max="14159" width="3.88671875" style="51" customWidth="1"/>
-    <col min="14160" max="14161" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="14162" max="14164" width="9.109375" style="51"/>
-    <col min="14165" max="14165" width="11.33203125" style="51" customWidth="1"/>
-    <col min="14166" max="14403" width="9.109375" style="51"/>
-    <col min="14404" max="14404" width="3.109375" style="51" customWidth="1"/>
-    <col min="14405" max="14405" width="3.44140625" style="51" customWidth="1"/>
-    <col min="14406" max="14406" width="7.33203125" style="51" customWidth="1"/>
-    <col min="14407" max="14407" width="13.5546875" style="51" customWidth="1"/>
-    <col min="14408" max="14408" width="7.109375" style="51" customWidth="1"/>
-    <col min="14409" max="14409" width="8.5546875" style="51" customWidth="1"/>
-    <col min="14410" max="14410" width="9" style="51" customWidth="1"/>
-    <col min="14411" max="14411" width="5.109375" style="51" customWidth="1"/>
-    <col min="14412" max="14412" width="8.44140625" style="51" customWidth="1"/>
-    <col min="14413" max="14413" width="17.109375" style="51" customWidth="1"/>
-    <col min="14414" max="14414" width="18" style="51" customWidth="1"/>
-    <col min="14415" max="14415" width="3.88671875" style="51" customWidth="1"/>
-    <col min="14416" max="14417" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="14418" max="14420" width="9.109375" style="51"/>
-    <col min="14421" max="14421" width="11.33203125" style="51" customWidth="1"/>
-    <col min="14422" max="14659" width="9.109375" style="51"/>
-    <col min="14660" max="14660" width="3.109375" style="51" customWidth="1"/>
-    <col min="14661" max="14661" width="3.44140625" style="51" customWidth="1"/>
-    <col min="14662" max="14662" width="7.33203125" style="51" customWidth="1"/>
-    <col min="14663" max="14663" width="13.5546875" style="51" customWidth="1"/>
-    <col min="14664" max="14664" width="7.109375" style="51" customWidth="1"/>
-    <col min="14665" max="14665" width="8.5546875" style="51" customWidth="1"/>
-    <col min="14666" max="14666" width="9" style="51" customWidth="1"/>
-    <col min="14667" max="14667" width="5.109375" style="51" customWidth="1"/>
-    <col min="14668" max="14668" width="8.44140625" style="51" customWidth="1"/>
-    <col min="14669" max="14669" width="17.109375" style="51" customWidth="1"/>
-    <col min="14670" max="14670" width="18" style="51" customWidth="1"/>
-    <col min="14671" max="14671" width="3.88671875" style="51" customWidth="1"/>
-    <col min="14672" max="14673" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="14674" max="14676" width="9.109375" style="51"/>
-    <col min="14677" max="14677" width="11.33203125" style="51" customWidth="1"/>
-    <col min="14678" max="14915" width="9.109375" style="51"/>
-    <col min="14916" max="14916" width="3.109375" style="51" customWidth="1"/>
-    <col min="14917" max="14917" width="3.44140625" style="51" customWidth="1"/>
-    <col min="14918" max="14918" width="7.33203125" style="51" customWidth="1"/>
-    <col min="14919" max="14919" width="13.5546875" style="51" customWidth="1"/>
-    <col min="14920" max="14920" width="7.109375" style="51" customWidth="1"/>
-    <col min="14921" max="14921" width="8.5546875" style="51" customWidth="1"/>
-    <col min="14922" max="14922" width="9" style="51" customWidth="1"/>
-    <col min="14923" max="14923" width="5.109375" style="51" customWidth="1"/>
-    <col min="14924" max="14924" width="8.44140625" style="51" customWidth="1"/>
-    <col min="14925" max="14925" width="17.109375" style="51" customWidth="1"/>
-    <col min="14926" max="14926" width="18" style="51" customWidth="1"/>
-    <col min="14927" max="14927" width="3.88671875" style="51" customWidth="1"/>
-    <col min="14928" max="14929" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="14930" max="14932" width="9.109375" style="51"/>
-    <col min="14933" max="14933" width="11.33203125" style="51" customWidth="1"/>
-    <col min="14934" max="15171" width="9.109375" style="51"/>
-    <col min="15172" max="15172" width="3.109375" style="51" customWidth="1"/>
-    <col min="15173" max="15173" width="3.44140625" style="51" customWidth="1"/>
-    <col min="15174" max="15174" width="7.33203125" style="51" customWidth="1"/>
-    <col min="15175" max="15175" width="13.5546875" style="51" customWidth="1"/>
-    <col min="15176" max="15176" width="7.109375" style="51" customWidth="1"/>
-    <col min="15177" max="15177" width="8.5546875" style="51" customWidth="1"/>
-    <col min="15178" max="15178" width="9" style="51" customWidth="1"/>
-    <col min="15179" max="15179" width="5.109375" style="51" customWidth="1"/>
-    <col min="15180" max="15180" width="8.44140625" style="51" customWidth="1"/>
-    <col min="15181" max="15181" width="17.109375" style="51" customWidth="1"/>
-    <col min="15182" max="15182" width="18" style="51" customWidth="1"/>
-    <col min="15183" max="15183" width="3.88671875" style="51" customWidth="1"/>
-    <col min="15184" max="15185" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="15186" max="15188" width="9.109375" style="51"/>
-    <col min="15189" max="15189" width="11.33203125" style="51" customWidth="1"/>
-    <col min="15190" max="15427" width="9.109375" style="51"/>
-    <col min="15428" max="15428" width="3.109375" style="51" customWidth="1"/>
-    <col min="15429" max="15429" width="3.44140625" style="51" customWidth="1"/>
-    <col min="15430" max="15430" width="7.33203125" style="51" customWidth="1"/>
-    <col min="15431" max="15431" width="13.5546875" style="51" customWidth="1"/>
-    <col min="15432" max="15432" width="7.109375" style="51" customWidth="1"/>
-    <col min="15433" max="15433" width="8.5546875" style="51" customWidth="1"/>
-    <col min="15434" max="15434" width="9" style="51" customWidth="1"/>
-    <col min="15435" max="15435" width="5.109375" style="51" customWidth="1"/>
-    <col min="15436" max="15436" width="8.44140625" style="51" customWidth="1"/>
-    <col min="15437" max="15437" width="17.109375" style="51" customWidth="1"/>
-    <col min="15438" max="15438" width="18" style="51" customWidth="1"/>
-    <col min="15439" max="15439" width="3.88671875" style="51" customWidth="1"/>
-    <col min="15440" max="15441" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="15442" max="15444" width="9.109375" style="51"/>
-    <col min="15445" max="15445" width="11.33203125" style="51" customWidth="1"/>
-    <col min="15446" max="15683" width="9.109375" style="51"/>
-    <col min="15684" max="15684" width="3.109375" style="51" customWidth="1"/>
-    <col min="15685" max="15685" width="3.44140625" style="51" customWidth="1"/>
-    <col min="15686" max="15686" width="7.33203125" style="51" customWidth="1"/>
-    <col min="15687" max="15687" width="13.5546875" style="51" customWidth="1"/>
-    <col min="15688" max="15688" width="7.109375" style="51" customWidth="1"/>
-    <col min="15689" max="15689" width="8.5546875" style="51" customWidth="1"/>
-    <col min="15690" max="15690" width="9" style="51" customWidth="1"/>
-    <col min="15691" max="15691" width="5.109375" style="51" customWidth="1"/>
-    <col min="15692" max="15692" width="8.44140625" style="51" customWidth="1"/>
-    <col min="15693" max="15693" width="17.109375" style="51" customWidth="1"/>
-    <col min="15694" max="15694" width="18" style="51" customWidth="1"/>
-    <col min="15695" max="15695" width="3.88671875" style="51" customWidth="1"/>
-    <col min="15696" max="15697" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="15698" max="15700" width="9.109375" style="51"/>
-    <col min="15701" max="15701" width="11.33203125" style="51" customWidth="1"/>
-    <col min="15702" max="15939" width="9.109375" style="51"/>
-    <col min="15940" max="15940" width="3.109375" style="51" customWidth="1"/>
-    <col min="15941" max="15941" width="3.44140625" style="51" customWidth="1"/>
-    <col min="15942" max="15942" width="7.33203125" style="51" customWidth="1"/>
-    <col min="15943" max="15943" width="13.5546875" style="51" customWidth="1"/>
-    <col min="15944" max="15944" width="7.109375" style="51" customWidth="1"/>
-    <col min="15945" max="15945" width="8.5546875" style="51" customWidth="1"/>
-    <col min="15946" max="15946" width="9" style="51" customWidth="1"/>
-    <col min="15947" max="15947" width="5.109375" style="51" customWidth="1"/>
-    <col min="15948" max="15948" width="8.44140625" style="51" customWidth="1"/>
-    <col min="15949" max="15949" width="17.109375" style="51" customWidth="1"/>
-    <col min="15950" max="15950" width="18" style="51" customWidth="1"/>
-    <col min="15951" max="15951" width="3.88671875" style="51" customWidth="1"/>
-    <col min="15952" max="15953" width="12.109375" style="51" bestFit="1" customWidth="1"/>
-    <col min="15954" max="15956" width="9.109375" style="51"/>
-    <col min="15957" max="15957" width="11.33203125" style="51" customWidth="1"/>
-    <col min="15958" max="16384" width="9.109375" style="51"/>
+    <col min="1" max="3" width="9.5546875" style="51" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" style="51" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" style="51" customWidth="1"/>
+    <col min="7" max="10" width="9.5546875" style="51" customWidth="1"/>
+    <col min="11" max="66" width="9.109375" style="51"/>
+    <col min="67" max="67" width="3.109375" style="51" customWidth="1"/>
+    <col min="68" max="68" width="3.44140625" style="51" customWidth="1"/>
+    <col min="69" max="69" width="7.33203125" style="51" customWidth="1"/>
+    <col min="70" max="70" width="13.5546875" style="51" customWidth="1"/>
+    <col min="71" max="71" width="7.109375" style="51" customWidth="1"/>
+    <col min="72" max="72" width="8.5546875" style="51" customWidth="1"/>
+    <col min="73" max="73" width="9" style="51" customWidth="1"/>
+    <col min="74" max="74" width="5.109375" style="51" customWidth="1"/>
+    <col min="75" max="75" width="8.44140625" style="51" customWidth="1"/>
+    <col min="76" max="76" width="17.109375" style="51" customWidth="1"/>
+    <col min="77" max="77" width="18" style="51" customWidth="1"/>
+    <col min="78" max="78" width="3.88671875" style="51" customWidth="1"/>
+    <col min="79" max="80" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="81" max="83" width="9.109375" style="51"/>
+    <col min="84" max="84" width="11.33203125" style="51" customWidth="1"/>
+    <col min="85" max="322" width="9.109375" style="51"/>
+    <col min="323" max="323" width="3.109375" style="51" customWidth="1"/>
+    <col min="324" max="324" width="3.44140625" style="51" customWidth="1"/>
+    <col min="325" max="325" width="7.33203125" style="51" customWidth="1"/>
+    <col min="326" max="326" width="13.5546875" style="51" customWidth="1"/>
+    <col min="327" max="327" width="7.109375" style="51" customWidth="1"/>
+    <col min="328" max="328" width="8.5546875" style="51" customWidth="1"/>
+    <col min="329" max="329" width="9" style="51" customWidth="1"/>
+    <col min="330" max="330" width="5.109375" style="51" customWidth="1"/>
+    <col min="331" max="331" width="8.44140625" style="51" customWidth="1"/>
+    <col min="332" max="332" width="17.109375" style="51" customWidth="1"/>
+    <col min="333" max="333" width="18" style="51" customWidth="1"/>
+    <col min="334" max="334" width="3.88671875" style="51" customWidth="1"/>
+    <col min="335" max="336" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="337" max="339" width="9.109375" style="51"/>
+    <col min="340" max="340" width="11.33203125" style="51" customWidth="1"/>
+    <col min="341" max="578" width="9.109375" style="51"/>
+    <col min="579" max="579" width="3.109375" style="51" customWidth="1"/>
+    <col min="580" max="580" width="3.44140625" style="51" customWidth="1"/>
+    <col min="581" max="581" width="7.33203125" style="51" customWidth="1"/>
+    <col min="582" max="582" width="13.5546875" style="51" customWidth="1"/>
+    <col min="583" max="583" width="7.109375" style="51" customWidth="1"/>
+    <col min="584" max="584" width="8.5546875" style="51" customWidth="1"/>
+    <col min="585" max="585" width="9" style="51" customWidth="1"/>
+    <col min="586" max="586" width="5.109375" style="51" customWidth="1"/>
+    <col min="587" max="587" width="8.44140625" style="51" customWidth="1"/>
+    <col min="588" max="588" width="17.109375" style="51" customWidth="1"/>
+    <col min="589" max="589" width="18" style="51" customWidth="1"/>
+    <col min="590" max="590" width="3.88671875" style="51" customWidth="1"/>
+    <col min="591" max="592" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="593" max="595" width="9.109375" style="51"/>
+    <col min="596" max="596" width="11.33203125" style="51" customWidth="1"/>
+    <col min="597" max="834" width="9.109375" style="51"/>
+    <col min="835" max="835" width="3.109375" style="51" customWidth="1"/>
+    <col min="836" max="836" width="3.44140625" style="51" customWidth="1"/>
+    <col min="837" max="837" width="7.33203125" style="51" customWidth="1"/>
+    <col min="838" max="838" width="13.5546875" style="51" customWidth="1"/>
+    <col min="839" max="839" width="7.109375" style="51" customWidth="1"/>
+    <col min="840" max="840" width="8.5546875" style="51" customWidth="1"/>
+    <col min="841" max="841" width="9" style="51" customWidth="1"/>
+    <col min="842" max="842" width="5.109375" style="51" customWidth="1"/>
+    <col min="843" max="843" width="8.44140625" style="51" customWidth="1"/>
+    <col min="844" max="844" width="17.109375" style="51" customWidth="1"/>
+    <col min="845" max="845" width="18" style="51" customWidth="1"/>
+    <col min="846" max="846" width="3.88671875" style="51" customWidth="1"/>
+    <col min="847" max="848" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="849" max="851" width="9.109375" style="51"/>
+    <col min="852" max="852" width="11.33203125" style="51" customWidth="1"/>
+    <col min="853" max="1090" width="9.109375" style="51"/>
+    <col min="1091" max="1091" width="3.109375" style="51" customWidth="1"/>
+    <col min="1092" max="1092" width="3.44140625" style="51" customWidth="1"/>
+    <col min="1093" max="1093" width="7.33203125" style="51" customWidth="1"/>
+    <col min="1094" max="1094" width="13.5546875" style="51" customWidth="1"/>
+    <col min="1095" max="1095" width="7.109375" style="51" customWidth="1"/>
+    <col min="1096" max="1096" width="8.5546875" style="51" customWidth="1"/>
+    <col min="1097" max="1097" width="9" style="51" customWidth="1"/>
+    <col min="1098" max="1098" width="5.109375" style="51" customWidth="1"/>
+    <col min="1099" max="1099" width="8.44140625" style="51" customWidth="1"/>
+    <col min="1100" max="1100" width="17.109375" style="51" customWidth="1"/>
+    <col min="1101" max="1101" width="18" style="51" customWidth="1"/>
+    <col min="1102" max="1102" width="3.88671875" style="51" customWidth="1"/>
+    <col min="1103" max="1104" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="1105" max="1107" width="9.109375" style="51"/>
+    <col min="1108" max="1108" width="11.33203125" style="51" customWidth="1"/>
+    <col min="1109" max="1346" width="9.109375" style="51"/>
+    <col min="1347" max="1347" width="3.109375" style="51" customWidth="1"/>
+    <col min="1348" max="1348" width="3.44140625" style="51" customWidth="1"/>
+    <col min="1349" max="1349" width="7.33203125" style="51" customWidth="1"/>
+    <col min="1350" max="1350" width="13.5546875" style="51" customWidth="1"/>
+    <col min="1351" max="1351" width="7.109375" style="51" customWidth="1"/>
+    <col min="1352" max="1352" width="8.5546875" style="51" customWidth="1"/>
+    <col min="1353" max="1353" width="9" style="51" customWidth="1"/>
+    <col min="1354" max="1354" width="5.109375" style="51" customWidth="1"/>
+    <col min="1355" max="1355" width="8.44140625" style="51" customWidth="1"/>
+    <col min="1356" max="1356" width="17.109375" style="51" customWidth="1"/>
+    <col min="1357" max="1357" width="18" style="51" customWidth="1"/>
+    <col min="1358" max="1358" width="3.88671875" style="51" customWidth="1"/>
+    <col min="1359" max="1360" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="1361" max="1363" width="9.109375" style="51"/>
+    <col min="1364" max="1364" width="11.33203125" style="51" customWidth="1"/>
+    <col min="1365" max="1602" width="9.109375" style="51"/>
+    <col min="1603" max="1603" width="3.109375" style="51" customWidth="1"/>
+    <col min="1604" max="1604" width="3.44140625" style="51" customWidth="1"/>
+    <col min="1605" max="1605" width="7.33203125" style="51" customWidth="1"/>
+    <col min="1606" max="1606" width="13.5546875" style="51" customWidth="1"/>
+    <col min="1607" max="1607" width="7.109375" style="51" customWidth="1"/>
+    <col min="1608" max="1608" width="8.5546875" style="51" customWidth="1"/>
+    <col min="1609" max="1609" width="9" style="51" customWidth="1"/>
+    <col min="1610" max="1610" width="5.109375" style="51" customWidth="1"/>
+    <col min="1611" max="1611" width="8.44140625" style="51" customWidth="1"/>
+    <col min="1612" max="1612" width="17.109375" style="51" customWidth="1"/>
+    <col min="1613" max="1613" width="18" style="51" customWidth="1"/>
+    <col min="1614" max="1614" width="3.88671875" style="51" customWidth="1"/>
+    <col min="1615" max="1616" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="1617" max="1619" width="9.109375" style="51"/>
+    <col min="1620" max="1620" width="11.33203125" style="51" customWidth="1"/>
+    <col min="1621" max="1858" width="9.109375" style="51"/>
+    <col min="1859" max="1859" width="3.109375" style="51" customWidth="1"/>
+    <col min="1860" max="1860" width="3.44140625" style="51" customWidth="1"/>
+    <col min="1861" max="1861" width="7.33203125" style="51" customWidth="1"/>
+    <col min="1862" max="1862" width="13.5546875" style="51" customWidth="1"/>
+    <col min="1863" max="1863" width="7.109375" style="51" customWidth="1"/>
+    <col min="1864" max="1864" width="8.5546875" style="51" customWidth="1"/>
+    <col min="1865" max="1865" width="9" style="51" customWidth="1"/>
+    <col min="1866" max="1866" width="5.109375" style="51" customWidth="1"/>
+    <col min="1867" max="1867" width="8.44140625" style="51" customWidth="1"/>
+    <col min="1868" max="1868" width="17.109375" style="51" customWidth="1"/>
+    <col min="1869" max="1869" width="18" style="51" customWidth="1"/>
+    <col min="1870" max="1870" width="3.88671875" style="51" customWidth="1"/>
+    <col min="1871" max="1872" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="1873" max="1875" width="9.109375" style="51"/>
+    <col min="1876" max="1876" width="11.33203125" style="51" customWidth="1"/>
+    <col min="1877" max="2114" width="9.109375" style="51"/>
+    <col min="2115" max="2115" width="3.109375" style="51" customWidth="1"/>
+    <col min="2116" max="2116" width="3.44140625" style="51" customWidth="1"/>
+    <col min="2117" max="2117" width="7.33203125" style="51" customWidth="1"/>
+    <col min="2118" max="2118" width="13.5546875" style="51" customWidth="1"/>
+    <col min="2119" max="2119" width="7.109375" style="51" customWidth="1"/>
+    <col min="2120" max="2120" width="8.5546875" style="51" customWidth="1"/>
+    <col min="2121" max="2121" width="9" style="51" customWidth="1"/>
+    <col min="2122" max="2122" width="5.109375" style="51" customWidth="1"/>
+    <col min="2123" max="2123" width="8.44140625" style="51" customWidth="1"/>
+    <col min="2124" max="2124" width="17.109375" style="51" customWidth="1"/>
+    <col min="2125" max="2125" width="18" style="51" customWidth="1"/>
+    <col min="2126" max="2126" width="3.88671875" style="51" customWidth="1"/>
+    <col min="2127" max="2128" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="2129" max="2131" width="9.109375" style="51"/>
+    <col min="2132" max="2132" width="11.33203125" style="51" customWidth="1"/>
+    <col min="2133" max="2370" width="9.109375" style="51"/>
+    <col min="2371" max="2371" width="3.109375" style="51" customWidth="1"/>
+    <col min="2372" max="2372" width="3.44140625" style="51" customWidth="1"/>
+    <col min="2373" max="2373" width="7.33203125" style="51" customWidth="1"/>
+    <col min="2374" max="2374" width="13.5546875" style="51" customWidth="1"/>
+    <col min="2375" max="2375" width="7.109375" style="51" customWidth="1"/>
+    <col min="2376" max="2376" width="8.5546875" style="51" customWidth="1"/>
+    <col min="2377" max="2377" width="9" style="51" customWidth="1"/>
+    <col min="2378" max="2378" width="5.109375" style="51" customWidth="1"/>
+    <col min="2379" max="2379" width="8.44140625" style="51" customWidth="1"/>
+    <col min="2380" max="2380" width="17.109375" style="51" customWidth="1"/>
+    <col min="2381" max="2381" width="18" style="51" customWidth="1"/>
+    <col min="2382" max="2382" width="3.88671875" style="51" customWidth="1"/>
+    <col min="2383" max="2384" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="2385" max="2387" width="9.109375" style="51"/>
+    <col min="2388" max="2388" width="11.33203125" style="51" customWidth="1"/>
+    <col min="2389" max="2626" width="9.109375" style="51"/>
+    <col min="2627" max="2627" width="3.109375" style="51" customWidth="1"/>
+    <col min="2628" max="2628" width="3.44140625" style="51" customWidth="1"/>
+    <col min="2629" max="2629" width="7.33203125" style="51" customWidth="1"/>
+    <col min="2630" max="2630" width="13.5546875" style="51" customWidth="1"/>
+    <col min="2631" max="2631" width="7.109375" style="51" customWidth="1"/>
+    <col min="2632" max="2632" width="8.5546875" style="51" customWidth="1"/>
+    <col min="2633" max="2633" width="9" style="51" customWidth="1"/>
+    <col min="2634" max="2634" width="5.109375" style="51" customWidth="1"/>
+    <col min="2635" max="2635" width="8.44140625" style="51" customWidth="1"/>
+    <col min="2636" max="2636" width="17.109375" style="51" customWidth="1"/>
+    <col min="2637" max="2637" width="18" style="51" customWidth="1"/>
+    <col min="2638" max="2638" width="3.88671875" style="51" customWidth="1"/>
+    <col min="2639" max="2640" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="2641" max="2643" width="9.109375" style="51"/>
+    <col min="2644" max="2644" width="11.33203125" style="51" customWidth="1"/>
+    <col min="2645" max="2882" width="9.109375" style="51"/>
+    <col min="2883" max="2883" width="3.109375" style="51" customWidth="1"/>
+    <col min="2884" max="2884" width="3.44140625" style="51" customWidth="1"/>
+    <col min="2885" max="2885" width="7.33203125" style="51" customWidth="1"/>
+    <col min="2886" max="2886" width="13.5546875" style="51" customWidth="1"/>
+    <col min="2887" max="2887" width="7.109375" style="51" customWidth="1"/>
+    <col min="2888" max="2888" width="8.5546875" style="51" customWidth="1"/>
+    <col min="2889" max="2889" width="9" style="51" customWidth="1"/>
+    <col min="2890" max="2890" width="5.109375" style="51" customWidth="1"/>
+    <col min="2891" max="2891" width="8.44140625" style="51" customWidth="1"/>
+    <col min="2892" max="2892" width="17.109375" style="51" customWidth="1"/>
+    <col min="2893" max="2893" width="18" style="51" customWidth="1"/>
+    <col min="2894" max="2894" width="3.88671875" style="51" customWidth="1"/>
+    <col min="2895" max="2896" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="2897" max="2899" width="9.109375" style="51"/>
+    <col min="2900" max="2900" width="11.33203125" style="51" customWidth="1"/>
+    <col min="2901" max="3138" width="9.109375" style="51"/>
+    <col min="3139" max="3139" width="3.109375" style="51" customWidth="1"/>
+    <col min="3140" max="3140" width="3.44140625" style="51" customWidth="1"/>
+    <col min="3141" max="3141" width="7.33203125" style="51" customWidth="1"/>
+    <col min="3142" max="3142" width="13.5546875" style="51" customWidth="1"/>
+    <col min="3143" max="3143" width="7.109375" style="51" customWidth="1"/>
+    <col min="3144" max="3144" width="8.5546875" style="51" customWidth="1"/>
+    <col min="3145" max="3145" width="9" style="51" customWidth="1"/>
+    <col min="3146" max="3146" width="5.109375" style="51" customWidth="1"/>
+    <col min="3147" max="3147" width="8.44140625" style="51" customWidth="1"/>
+    <col min="3148" max="3148" width="17.109375" style="51" customWidth="1"/>
+    <col min="3149" max="3149" width="18" style="51" customWidth="1"/>
+    <col min="3150" max="3150" width="3.88671875" style="51" customWidth="1"/>
+    <col min="3151" max="3152" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="3153" max="3155" width="9.109375" style="51"/>
+    <col min="3156" max="3156" width="11.33203125" style="51" customWidth="1"/>
+    <col min="3157" max="3394" width="9.109375" style="51"/>
+    <col min="3395" max="3395" width="3.109375" style="51" customWidth="1"/>
+    <col min="3396" max="3396" width="3.44140625" style="51" customWidth="1"/>
+    <col min="3397" max="3397" width="7.33203125" style="51" customWidth="1"/>
+    <col min="3398" max="3398" width="13.5546875" style="51" customWidth="1"/>
+    <col min="3399" max="3399" width="7.109375" style="51" customWidth="1"/>
+    <col min="3400" max="3400" width="8.5546875" style="51" customWidth="1"/>
+    <col min="3401" max="3401" width="9" style="51" customWidth="1"/>
+    <col min="3402" max="3402" width="5.109375" style="51" customWidth="1"/>
+    <col min="3403" max="3403" width="8.44140625" style="51" customWidth="1"/>
+    <col min="3404" max="3404" width="17.109375" style="51" customWidth="1"/>
+    <col min="3405" max="3405" width="18" style="51" customWidth="1"/>
+    <col min="3406" max="3406" width="3.88671875" style="51" customWidth="1"/>
+    <col min="3407" max="3408" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="3409" max="3411" width="9.109375" style="51"/>
+    <col min="3412" max="3412" width="11.33203125" style="51" customWidth="1"/>
+    <col min="3413" max="3650" width="9.109375" style="51"/>
+    <col min="3651" max="3651" width="3.109375" style="51" customWidth="1"/>
+    <col min="3652" max="3652" width="3.44140625" style="51" customWidth="1"/>
+    <col min="3653" max="3653" width="7.33203125" style="51" customWidth="1"/>
+    <col min="3654" max="3654" width="13.5546875" style="51" customWidth="1"/>
+    <col min="3655" max="3655" width="7.109375" style="51" customWidth="1"/>
+    <col min="3656" max="3656" width="8.5546875" style="51" customWidth="1"/>
+    <col min="3657" max="3657" width="9" style="51" customWidth="1"/>
+    <col min="3658" max="3658" width="5.109375" style="51" customWidth="1"/>
+    <col min="3659" max="3659" width="8.44140625" style="51" customWidth="1"/>
+    <col min="3660" max="3660" width="17.109375" style="51" customWidth="1"/>
+    <col min="3661" max="3661" width="18" style="51" customWidth="1"/>
+    <col min="3662" max="3662" width="3.88671875" style="51" customWidth="1"/>
+    <col min="3663" max="3664" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="3665" max="3667" width="9.109375" style="51"/>
+    <col min="3668" max="3668" width="11.33203125" style="51" customWidth="1"/>
+    <col min="3669" max="3906" width="9.109375" style="51"/>
+    <col min="3907" max="3907" width="3.109375" style="51" customWidth="1"/>
+    <col min="3908" max="3908" width="3.44140625" style="51" customWidth="1"/>
+    <col min="3909" max="3909" width="7.33203125" style="51" customWidth="1"/>
+    <col min="3910" max="3910" width="13.5546875" style="51" customWidth="1"/>
+    <col min="3911" max="3911" width="7.109375" style="51" customWidth="1"/>
+    <col min="3912" max="3912" width="8.5546875" style="51" customWidth="1"/>
+    <col min="3913" max="3913" width="9" style="51" customWidth="1"/>
+    <col min="3914" max="3914" width="5.109375" style="51" customWidth="1"/>
+    <col min="3915" max="3915" width="8.44140625" style="51" customWidth="1"/>
+    <col min="3916" max="3916" width="17.109375" style="51" customWidth="1"/>
+    <col min="3917" max="3917" width="18" style="51" customWidth="1"/>
+    <col min="3918" max="3918" width="3.88671875" style="51" customWidth="1"/>
+    <col min="3919" max="3920" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="3921" max="3923" width="9.109375" style="51"/>
+    <col min="3924" max="3924" width="11.33203125" style="51" customWidth="1"/>
+    <col min="3925" max="4162" width="9.109375" style="51"/>
+    <col min="4163" max="4163" width="3.109375" style="51" customWidth="1"/>
+    <col min="4164" max="4164" width="3.44140625" style="51" customWidth="1"/>
+    <col min="4165" max="4165" width="7.33203125" style="51" customWidth="1"/>
+    <col min="4166" max="4166" width="13.5546875" style="51" customWidth="1"/>
+    <col min="4167" max="4167" width="7.109375" style="51" customWidth="1"/>
+    <col min="4168" max="4168" width="8.5546875" style="51" customWidth="1"/>
+    <col min="4169" max="4169" width="9" style="51" customWidth="1"/>
+    <col min="4170" max="4170" width="5.109375" style="51" customWidth="1"/>
+    <col min="4171" max="4171" width="8.44140625" style="51" customWidth="1"/>
+    <col min="4172" max="4172" width="17.109375" style="51" customWidth="1"/>
+    <col min="4173" max="4173" width="18" style="51" customWidth="1"/>
+    <col min="4174" max="4174" width="3.88671875" style="51" customWidth="1"/>
+    <col min="4175" max="4176" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="4177" max="4179" width="9.109375" style="51"/>
+    <col min="4180" max="4180" width="11.33203125" style="51" customWidth="1"/>
+    <col min="4181" max="4418" width="9.109375" style="51"/>
+    <col min="4419" max="4419" width="3.109375" style="51" customWidth="1"/>
+    <col min="4420" max="4420" width="3.44140625" style="51" customWidth="1"/>
+    <col min="4421" max="4421" width="7.33203125" style="51" customWidth="1"/>
+    <col min="4422" max="4422" width="13.5546875" style="51" customWidth="1"/>
+    <col min="4423" max="4423" width="7.109375" style="51" customWidth="1"/>
+    <col min="4424" max="4424" width="8.5546875" style="51" customWidth="1"/>
+    <col min="4425" max="4425" width="9" style="51" customWidth="1"/>
+    <col min="4426" max="4426" width="5.109375" style="51" customWidth="1"/>
+    <col min="4427" max="4427" width="8.44140625" style="51" customWidth="1"/>
+    <col min="4428" max="4428" width="17.109375" style="51" customWidth="1"/>
+    <col min="4429" max="4429" width="18" style="51" customWidth="1"/>
+    <col min="4430" max="4430" width="3.88671875" style="51" customWidth="1"/>
+    <col min="4431" max="4432" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="4433" max="4435" width="9.109375" style="51"/>
+    <col min="4436" max="4436" width="11.33203125" style="51" customWidth="1"/>
+    <col min="4437" max="4674" width="9.109375" style="51"/>
+    <col min="4675" max="4675" width="3.109375" style="51" customWidth="1"/>
+    <col min="4676" max="4676" width="3.44140625" style="51" customWidth="1"/>
+    <col min="4677" max="4677" width="7.33203125" style="51" customWidth="1"/>
+    <col min="4678" max="4678" width="13.5546875" style="51" customWidth="1"/>
+    <col min="4679" max="4679" width="7.109375" style="51" customWidth="1"/>
+    <col min="4680" max="4680" width="8.5546875" style="51" customWidth="1"/>
+    <col min="4681" max="4681" width="9" style="51" customWidth="1"/>
+    <col min="4682" max="4682" width="5.109375" style="51" customWidth="1"/>
+    <col min="4683" max="4683" width="8.44140625" style="51" customWidth="1"/>
+    <col min="4684" max="4684" width="17.109375" style="51" customWidth="1"/>
+    <col min="4685" max="4685" width="18" style="51" customWidth="1"/>
+    <col min="4686" max="4686" width="3.88671875" style="51" customWidth="1"/>
+    <col min="4687" max="4688" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="4689" max="4691" width="9.109375" style="51"/>
+    <col min="4692" max="4692" width="11.33203125" style="51" customWidth="1"/>
+    <col min="4693" max="4930" width="9.109375" style="51"/>
+    <col min="4931" max="4931" width="3.109375" style="51" customWidth="1"/>
+    <col min="4932" max="4932" width="3.44140625" style="51" customWidth="1"/>
+    <col min="4933" max="4933" width="7.33203125" style="51" customWidth="1"/>
+    <col min="4934" max="4934" width="13.5546875" style="51" customWidth="1"/>
+    <col min="4935" max="4935" width="7.109375" style="51" customWidth="1"/>
+    <col min="4936" max="4936" width="8.5546875" style="51" customWidth="1"/>
+    <col min="4937" max="4937" width="9" style="51" customWidth="1"/>
+    <col min="4938" max="4938" width="5.109375" style="51" customWidth="1"/>
+    <col min="4939" max="4939" width="8.44140625" style="51" customWidth="1"/>
+    <col min="4940" max="4940" width="17.109375" style="51" customWidth="1"/>
+    <col min="4941" max="4941" width="18" style="51" customWidth="1"/>
+    <col min="4942" max="4942" width="3.88671875" style="51" customWidth="1"/>
+    <col min="4943" max="4944" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="4945" max="4947" width="9.109375" style="51"/>
+    <col min="4948" max="4948" width="11.33203125" style="51" customWidth="1"/>
+    <col min="4949" max="5186" width="9.109375" style="51"/>
+    <col min="5187" max="5187" width="3.109375" style="51" customWidth="1"/>
+    <col min="5188" max="5188" width="3.44140625" style="51" customWidth="1"/>
+    <col min="5189" max="5189" width="7.33203125" style="51" customWidth="1"/>
+    <col min="5190" max="5190" width="13.5546875" style="51" customWidth="1"/>
+    <col min="5191" max="5191" width="7.109375" style="51" customWidth="1"/>
+    <col min="5192" max="5192" width="8.5546875" style="51" customWidth="1"/>
+    <col min="5193" max="5193" width="9" style="51" customWidth="1"/>
+    <col min="5194" max="5194" width="5.109375" style="51" customWidth="1"/>
+    <col min="5195" max="5195" width="8.44140625" style="51" customWidth="1"/>
+    <col min="5196" max="5196" width="17.109375" style="51" customWidth="1"/>
+    <col min="5197" max="5197" width="18" style="51" customWidth="1"/>
+    <col min="5198" max="5198" width="3.88671875" style="51" customWidth="1"/>
+    <col min="5199" max="5200" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="5201" max="5203" width="9.109375" style="51"/>
+    <col min="5204" max="5204" width="11.33203125" style="51" customWidth="1"/>
+    <col min="5205" max="5442" width="9.109375" style="51"/>
+    <col min="5443" max="5443" width="3.109375" style="51" customWidth="1"/>
+    <col min="5444" max="5444" width="3.44140625" style="51" customWidth="1"/>
+    <col min="5445" max="5445" width="7.33203125" style="51" customWidth="1"/>
+    <col min="5446" max="5446" width="13.5546875" style="51" customWidth="1"/>
+    <col min="5447" max="5447" width="7.109375" style="51" customWidth="1"/>
+    <col min="5448" max="5448" width="8.5546875" style="51" customWidth="1"/>
+    <col min="5449" max="5449" width="9" style="51" customWidth="1"/>
+    <col min="5450" max="5450" width="5.109375" style="51" customWidth="1"/>
+    <col min="5451" max="5451" width="8.44140625" style="51" customWidth="1"/>
+    <col min="5452" max="5452" width="17.109375" style="51" customWidth="1"/>
+    <col min="5453" max="5453" width="18" style="51" customWidth="1"/>
+    <col min="5454" max="5454" width="3.88671875" style="51" customWidth="1"/>
+    <col min="5455" max="5456" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="5457" max="5459" width="9.109375" style="51"/>
+    <col min="5460" max="5460" width="11.33203125" style="51" customWidth="1"/>
+    <col min="5461" max="5698" width="9.109375" style="51"/>
+    <col min="5699" max="5699" width="3.109375" style="51" customWidth="1"/>
+    <col min="5700" max="5700" width="3.44140625" style="51" customWidth="1"/>
+    <col min="5701" max="5701" width="7.33203125" style="51" customWidth="1"/>
+    <col min="5702" max="5702" width="13.5546875" style="51" customWidth="1"/>
+    <col min="5703" max="5703" width="7.109375" style="51" customWidth="1"/>
+    <col min="5704" max="5704" width="8.5546875" style="51" customWidth="1"/>
+    <col min="5705" max="5705" width="9" style="51" customWidth="1"/>
+    <col min="5706" max="5706" width="5.109375" style="51" customWidth="1"/>
+    <col min="5707" max="5707" width="8.44140625" style="51" customWidth="1"/>
+    <col min="5708" max="5708" width="17.109375" style="51" customWidth="1"/>
+    <col min="5709" max="5709" width="18" style="51" customWidth="1"/>
+    <col min="5710" max="5710" width="3.88671875" style="51" customWidth="1"/>
+    <col min="5711" max="5712" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="5713" max="5715" width="9.109375" style="51"/>
+    <col min="5716" max="5716" width="11.33203125" style="51" customWidth="1"/>
+    <col min="5717" max="5954" width="9.109375" style="51"/>
+    <col min="5955" max="5955" width="3.109375" style="51" customWidth="1"/>
+    <col min="5956" max="5956" width="3.44140625" style="51" customWidth="1"/>
+    <col min="5957" max="5957" width="7.33203125" style="51" customWidth="1"/>
+    <col min="5958" max="5958" width="13.5546875" style="51" customWidth="1"/>
+    <col min="5959" max="5959" width="7.109375" style="51" customWidth="1"/>
+    <col min="5960" max="5960" width="8.5546875" style="51" customWidth="1"/>
+    <col min="5961" max="5961" width="9" style="51" customWidth="1"/>
+    <col min="5962" max="5962" width="5.109375" style="51" customWidth="1"/>
+    <col min="5963" max="5963" width="8.44140625" style="51" customWidth="1"/>
+    <col min="5964" max="5964" width="17.109375" style="51" customWidth="1"/>
+    <col min="5965" max="5965" width="18" style="51" customWidth="1"/>
+    <col min="5966" max="5966" width="3.88671875" style="51" customWidth="1"/>
+    <col min="5967" max="5968" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="5969" max="5971" width="9.109375" style="51"/>
+    <col min="5972" max="5972" width="11.33203125" style="51" customWidth="1"/>
+    <col min="5973" max="6210" width="9.109375" style="51"/>
+    <col min="6211" max="6211" width="3.109375" style="51" customWidth="1"/>
+    <col min="6212" max="6212" width="3.44140625" style="51" customWidth="1"/>
+    <col min="6213" max="6213" width="7.33203125" style="51" customWidth="1"/>
+    <col min="6214" max="6214" width="13.5546875" style="51" customWidth="1"/>
+    <col min="6215" max="6215" width="7.109375" style="51" customWidth="1"/>
+    <col min="6216" max="6216" width="8.5546875" style="51" customWidth="1"/>
+    <col min="6217" max="6217" width="9" style="51" customWidth="1"/>
+    <col min="6218" max="6218" width="5.109375" style="51" customWidth="1"/>
+    <col min="6219" max="6219" width="8.44140625" style="51" customWidth="1"/>
+    <col min="6220" max="6220" width="17.109375" style="51" customWidth="1"/>
+    <col min="6221" max="6221" width="18" style="51" customWidth="1"/>
+    <col min="6222" max="6222" width="3.88671875" style="51" customWidth="1"/>
+    <col min="6223" max="6224" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="6225" max="6227" width="9.109375" style="51"/>
+    <col min="6228" max="6228" width="11.33203125" style="51" customWidth="1"/>
+    <col min="6229" max="6466" width="9.109375" style="51"/>
+    <col min="6467" max="6467" width="3.109375" style="51" customWidth="1"/>
+    <col min="6468" max="6468" width="3.44140625" style="51" customWidth="1"/>
+    <col min="6469" max="6469" width="7.33203125" style="51" customWidth="1"/>
+    <col min="6470" max="6470" width="13.5546875" style="51" customWidth="1"/>
+    <col min="6471" max="6471" width="7.109375" style="51" customWidth="1"/>
+    <col min="6472" max="6472" width="8.5546875" style="51" customWidth="1"/>
+    <col min="6473" max="6473" width="9" style="51" customWidth="1"/>
+    <col min="6474" max="6474" width="5.109375" style="51" customWidth="1"/>
+    <col min="6475" max="6475" width="8.44140625" style="51" customWidth="1"/>
+    <col min="6476" max="6476" width="17.109375" style="51" customWidth="1"/>
+    <col min="6477" max="6477" width="18" style="51" customWidth="1"/>
+    <col min="6478" max="6478" width="3.88671875" style="51" customWidth="1"/>
+    <col min="6479" max="6480" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="6481" max="6483" width="9.109375" style="51"/>
+    <col min="6484" max="6484" width="11.33203125" style="51" customWidth="1"/>
+    <col min="6485" max="6722" width="9.109375" style="51"/>
+    <col min="6723" max="6723" width="3.109375" style="51" customWidth="1"/>
+    <col min="6724" max="6724" width="3.44140625" style="51" customWidth="1"/>
+    <col min="6725" max="6725" width="7.33203125" style="51" customWidth="1"/>
+    <col min="6726" max="6726" width="13.5546875" style="51" customWidth="1"/>
+    <col min="6727" max="6727" width="7.109375" style="51" customWidth="1"/>
+    <col min="6728" max="6728" width="8.5546875" style="51" customWidth="1"/>
+    <col min="6729" max="6729" width="9" style="51" customWidth="1"/>
+    <col min="6730" max="6730" width="5.109375" style="51" customWidth="1"/>
+    <col min="6731" max="6731" width="8.44140625" style="51" customWidth="1"/>
+    <col min="6732" max="6732" width="17.109375" style="51" customWidth="1"/>
+    <col min="6733" max="6733" width="18" style="51" customWidth="1"/>
+    <col min="6734" max="6734" width="3.88671875" style="51" customWidth="1"/>
+    <col min="6735" max="6736" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="6737" max="6739" width="9.109375" style="51"/>
+    <col min="6740" max="6740" width="11.33203125" style="51" customWidth="1"/>
+    <col min="6741" max="6978" width="9.109375" style="51"/>
+    <col min="6979" max="6979" width="3.109375" style="51" customWidth="1"/>
+    <col min="6980" max="6980" width="3.44140625" style="51" customWidth="1"/>
+    <col min="6981" max="6981" width="7.33203125" style="51" customWidth="1"/>
+    <col min="6982" max="6982" width="13.5546875" style="51" customWidth="1"/>
+    <col min="6983" max="6983" width="7.109375" style="51" customWidth="1"/>
+    <col min="6984" max="6984" width="8.5546875" style="51" customWidth="1"/>
+    <col min="6985" max="6985" width="9" style="51" customWidth="1"/>
+    <col min="6986" max="6986" width="5.109375" style="51" customWidth="1"/>
+    <col min="6987" max="6987" width="8.44140625" style="51" customWidth="1"/>
+    <col min="6988" max="6988" width="17.109375" style="51" customWidth="1"/>
+    <col min="6989" max="6989" width="18" style="51" customWidth="1"/>
+    <col min="6990" max="6990" width="3.88671875" style="51" customWidth="1"/>
+    <col min="6991" max="6992" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="6993" max="6995" width="9.109375" style="51"/>
+    <col min="6996" max="6996" width="11.33203125" style="51" customWidth="1"/>
+    <col min="6997" max="7234" width="9.109375" style="51"/>
+    <col min="7235" max="7235" width="3.109375" style="51" customWidth="1"/>
+    <col min="7236" max="7236" width="3.44140625" style="51" customWidth="1"/>
+    <col min="7237" max="7237" width="7.33203125" style="51" customWidth="1"/>
+    <col min="7238" max="7238" width="13.5546875" style="51" customWidth="1"/>
+    <col min="7239" max="7239" width="7.109375" style="51" customWidth="1"/>
+    <col min="7240" max="7240" width="8.5546875" style="51" customWidth="1"/>
+    <col min="7241" max="7241" width="9" style="51" customWidth="1"/>
+    <col min="7242" max="7242" width="5.109375" style="51" customWidth="1"/>
+    <col min="7243" max="7243" width="8.44140625" style="51" customWidth="1"/>
+    <col min="7244" max="7244" width="17.109375" style="51" customWidth="1"/>
+    <col min="7245" max="7245" width="18" style="51" customWidth="1"/>
+    <col min="7246" max="7246" width="3.88671875" style="51" customWidth="1"/>
+    <col min="7247" max="7248" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="7249" max="7251" width="9.109375" style="51"/>
+    <col min="7252" max="7252" width="11.33203125" style="51" customWidth="1"/>
+    <col min="7253" max="7490" width="9.109375" style="51"/>
+    <col min="7491" max="7491" width="3.109375" style="51" customWidth="1"/>
+    <col min="7492" max="7492" width="3.44140625" style="51" customWidth="1"/>
+    <col min="7493" max="7493" width="7.33203125" style="51" customWidth="1"/>
+    <col min="7494" max="7494" width="13.5546875" style="51" customWidth="1"/>
+    <col min="7495" max="7495" width="7.109375" style="51" customWidth="1"/>
+    <col min="7496" max="7496" width="8.5546875" style="51" customWidth="1"/>
+    <col min="7497" max="7497" width="9" style="51" customWidth="1"/>
+    <col min="7498" max="7498" width="5.109375" style="51" customWidth="1"/>
+    <col min="7499" max="7499" width="8.44140625" style="51" customWidth="1"/>
+    <col min="7500" max="7500" width="17.109375" style="51" customWidth="1"/>
+    <col min="7501" max="7501" width="18" style="51" customWidth="1"/>
+    <col min="7502" max="7502" width="3.88671875" style="51" customWidth="1"/>
+    <col min="7503" max="7504" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="7505" max="7507" width="9.109375" style="51"/>
+    <col min="7508" max="7508" width="11.33203125" style="51" customWidth="1"/>
+    <col min="7509" max="7746" width="9.109375" style="51"/>
+    <col min="7747" max="7747" width="3.109375" style="51" customWidth="1"/>
+    <col min="7748" max="7748" width="3.44140625" style="51" customWidth="1"/>
+    <col min="7749" max="7749" width="7.33203125" style="51" customWidth="1"/>
+    <col min="7750" max="7750" width="13.5546875" style="51" customWidth="1"/>
+    <col min="7751" max="7751" width="7.109375" style="51" customWidth="1"/>
+    <col min="7752" max="7752" width="8.5546875" style="51" customWidth="1"/>
+    <col min="7753" max="7753" width="9" style="51" customWidth="1"/>
+    <col min="7754" max="7754" width="5.109375" style="51" customWidth="1"/>
+    <col min="7755" max="7755" width="8.44140625" style="51" customWidth="1"/>
+    <col min="7756" max="7756" width="17.109375" style="51" customWidth="1"/>
+    <col min="7757" max="7757" width="18" style="51" customWidth="1"/>
+    <col min="7758" max="7758" width="3.88671875" style="51" customWidth="1"/>
+    <col min="7759" max="7760" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="7761" max="7763" width="9.109375" style="51"/>
+    <col min="7764" max="7764" width="11.33203125" style="51" customWidth="1"/>
+    <col min="7765" max="8002" width="9.109375" style="51"/>
+    <col min="8003" max="8003" width="3.109375" style="51" customWidth="1"/>
+    <col min="8004" max="8004" width="3.44140625" style="51" customWidth="1"/>
+    <col min="8005" max="8005" width="7.33203125" style="51" customWidth="1"/>
+    <col min="8006" max="8006" width="13.5546875" style="51" customWidth="1"/>
+    <col min="8007" max="8007" width="7.109375" style="51" customWidth="1"/>
+    <col min="8008" max="8008" width="8.5546875" style="51" customWidth="1"/>
+    <col min="8009" max="8009" width="9" style="51" customWidth="1"/>
+    <col min="8010" max="8010" width="5.109375" style="51" customWidth="1"/>
+    <col min="8011" max="8011" width="8.44140625" style="51" customWidth="1"/>
+    <col min="8012" max="8012" width="17.109375" style="51" customWidth="1"/>
+    <col min="8013" max="8013" width="18" style="51" customWidth="1"/>
+    <col min="8014" max="8014" width="3.88671875" style="51" customWidth="1"/>
+    <col min="8015" max="8016" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="8017" max="8019" width="9.109375" style="51"/>
+    <col min="8020" max="8020" width="11.33203125" style="51" customWidth="1"/>
+    <col min="8021" max="8258" width="9.109375" style="51"/>
+    <col min="8259" max="8259" width="3.109375" style="51" customWidth="1"/>
+    <col min="8260" max="8260" width="3.44140625" style="51" customWidth="1"/>
+    <col min="8261" max="8261" width="7.33203125" style="51" customWidth="1"/>
+    <col min="8262" max="8262" width="13.5546875" style="51" customWidth="1"/>
+    <col min="8263" max="8263" width="7.109375" style="51" customWidth="1"/>
+    <col min="8264" max="8264" width="8.5546875" style="51" customWidth="1"/>
+    <col min="8265" max="8265" width="9" style="51" customWidth="1"/>
+    <col min="8266" max="8266" width="5.109375" style="51" customWidth="1"/>
+    <col min="8267" max="8267" width="8.44140625" style="51" customWidth="1"/>
+    <col min="8268" max="8268" width="17.109375" style="51" customWidth="1"/>
+    <col min="8269" max="8269" width="18" style="51" customWidth="1"/>
+    <col min="8270" max="8270" width="3.88671875" style="51" customWidth="1"/>
+    <col min="8271" max="8272" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="8273" max="8275" width="9.109375" style="51"/>
+    <col min="8276" max="8276" width="11.33203125" style="51" customWidth="1"/>
+    <col min="8277" max="8514" width="9.109375" style="51"/>
+    <col min="8515" max="8515" width="3.109375" style="51" customWidth="1"/>
+    <col min="8516" max="8516" width="3.44140625" style="51" customWidth="1"/>
+    <col min="8517" max="8517" width="7.33203125" style="51" customWidth="1"/>
+    <col min="8518" max="8518" width="13.5546875" style="51" customWidth="1"/>
+    <col min="8519" max="8519" width="7.109375" style="51" customWidth="1"/>
+    <col min="8520" max="8520" width="8.5546875" style="51" customWidth="1"/>
+    <col min="8521" max="8521" width="9" style="51" customWidth="1"/>
+    <col min="8522" max="8522" width="5.109375" style="51" customWidth="1"/>
+    <col min="8523" max="8523" width="8.44140625" style="51" customWidth="1"/>
+    <col min="8524" max="8524" width="17.109375" style="51" customWidth="1"/>
+    <col min="8525" max="8525" width="18" style="51" customWidth="1"/>
+    <col min="8526" max="8526" width="3.88671875" style="51" customWidth="1"/>
+    <col min="8527" max="8528" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="8529" max="8531" width="9.109375" style="51"/>
+    <col min="8532" max="8532" width="11.33203125" style="51" customWidth="1"/>
+    <col min="8533" max="8770" width="9.109375" style="51"/>
+    <col min="8771" max="8771" width="3.109375" style="51" customWidth="1"/>
+    <col min="8772" max="8772" width="3.44140625" style="51" customWidth="1"/>
+    <col min="8773" max="8773" width="7.33203125" style="51" customWidth="1"/>
+    <col min="8774" max="8774" width="13.5546875" style="51" customWidth="1"/>
+    <col min="8775" max="8775" width="7.109375" style="51" customWidth="1"/>
+    <col min="8776" max="8776" width="8.5546875" style="51" customWidth="1"/>
+    <col min="8777" max="8777" width="9" style="51" customWidth="1"/>
+    <col min="8778" max="8778" width="5.109375" style="51" customWidth="1"/>
+    <col min="8779" max="8779" width="8.44140625" style="51" customWidth="1"/>
+    <col min="8780" max="8780" width="17.109375" style="51" customWidth="1"/>
+    <col min="8781" max="8781" width="18" style="51" customWidth="1"/>
+    <col min="8782" max="8782" width="3.88671875" style="51" customWidth="1"/>
+    <col min="8783" max="8784" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="8785" max="8787" width="9.109375" style="51"/>
+    <col min="8788" max="8788" width="11.33203125" style="51" customWidth="1"/>
+    <col min="8789" max="9026" width="9.109375" style="51"/>
+    <col min="9027" max="9027" width="3.109375" style="51" customWidth="1"/>
+    <col min="9028" max="9028" width="3.44140625" style="51" customWidth="1"/>
+    <col min="9029" max="9029" width="7.33203125" style="51" customWidth="1"/>
+    <col min="9030" max="9030" width="13.5546875" style="51" customWidth="1"/>
+    <col min="9031" max="9031" width="7.109375" style="51" customWidth="1"/>
+    <col min="9032" max="9032" width="8.5546875" style="51" customWidth="1"/>
+    <col min="9033" max="9033" width="9" style="51" customWidth="1"/>
+    <col min="9034" max="9034" width="5.109375" style="51" customWidth="1"/>
+    <col min="9035" max="9035" width="8.44140625" style="51" customWidth="1"/>
+    <col min="9036" max="9036" width="17.109375" style="51" customWidth="1"/>
+    <col min="9037" max="9037" width="18" style="51" customWidth="1"/>
+    <col min="9038" max="9038" width="3.88671875" style="51" customWidth="1"/>
+    <col min="9039" max="9040" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="9041" max="9043" width="9.109375" style="51"/>
+    <col min="9044" max="9044" width="11.33203125" style="51" customWidth="1"/>
+    <col min="9045" max="9282" width="9.109375" style="51"/>
+    <col min="9283" max="9283" width="3.109375" style="51" customWidth="1"/>
+    <col min="9284" max="9284" width="3.44140625" style="51" customWidth="1"/>
+    <col min="9285" max="9285" width="7.33203125" style="51" customWidth="1"/>
+    <col min="9286" max="9286" width="13.5546875" style="51" customWidth="1"/>
+    <col min="9287" max="9287" width="7.109375" style="51" customWidth="1"/>
+    <col min="9288" max="9288" width="8.5546875" style="51" customWidth="1"/>
+    <col min="9289" max="9289" width="9" style="51" customWidth="1"/>
+    <col min="9290" max="9290" width="5.109375" style="51" customWidth="1"/>
+    <col min="9291" max="9291" width="8.44140625" style="51" customWidth="1"/>
+    <col min="9292" max="9292" width="17.109375" style="51" customWidth="1"/>
+    <col min="9293" max="9293" width="18" style="51" customWidth="1"/>
+    <col min="9294" max="9294" width="3.88671875" style="51" customWidth="1"/>
+    <col min="9295" max="9296" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="9297" max="9299" width="9.109375" style="51"/>
+    <col min="9300" max="9300" width="11.33203125" style="51" customWidth="1"/>
+    <col min="9301" max="9538" width="9.109375" style="51"/>
+    <col min="9539" max="9539" width="3.109375" style="51" customWidth="1"/>
+    <col min="9540" max="9540" width="3.44140625" style="51" customWidth="1"/>
+    <col min="9541" max="9541" width="7.33203125" style="51" customWidth="1"/>
+    <col min="9542" max="9542" width="13.5546875" style="51" customWidth="1"/>
+    <col min="9543" max="9543" width="7.109375" style="51" customWidth="1"/>
+    <col min="9544" max="9544" width="8.5546875" style="51" customWidth="1"/>
+    <col min="9545" max="9545" width="9" style="51" customWidth="1"/>
+    <col min="9546" max="9546" width="5.109375" style="51" customWidth="1"/>
+    <col min="9547" max="9547" width="8.44140625" style="51" customWidth="1"/>
+    <col min="9548" max="9548" width="17.109375" style="51" customWidth="1"/>
+    <col min="9549" max="9549" width="18" style="51" customWidth="1"/>
+    <col min="9550" max="9550" width="3.88671875" style="51" customWidth="1"/>
+    <col min="9551" max="9552" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="9553" max="9555" width="9.109375" style="51"/>
+    <col min="9556" max="9556" width="11.33203125" style="51" customWidth="1"/>
+    <col min="9557" max="9794" width="9.109375" style="51"/>
+    <col min="9795" max="9795" width="3.109375" style="51" customWidth="1"/>
+    <col min="9796" max="9796" width="3.44140625" style="51" customWidth="1"/>
+    <col min="9797" max="9797" width="7.33203125" style="51" customWidth="1"/>
+    <col min="9798" max="9798" width="13.5546875" style="51" customWidth="1"/>
+    <col min="9799" max="9799" width="7.109375" style="51" customWidth="1"/>
+    <col min="9800" max="9800" width="8.5546875" style="51" customWidth="1"/>
+    <col min="9801" max="9801" width="9" style="51" customWidth="1"/>
+    <col min="9802" max="9802" width="5.109375" style="51" customWidth="1"/>
+    <col min="9803" max="9803" width="8.44140625" style="51" customWidth="1"/>
+    <col min="9804" max="9804" width="17.109375" style="51" customWidth="1"/>
+    <col min="9805" max="9805" width="18" style="51" customWidth="1"/>
+    <col min="9806" max="9806" width="3.88671875" style="51" customWidth="1"/>
+    <col min="9807" max="9808" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="9809" max="9811" width="9.109375" style="51"/>
+    <col min="9812" max="9812" width="11.33203125" style="51" customWidth="1"/>
+    <col min="9813" max="10050" width="9.109375" style="51"/>
+    <col min="10051" max="10051" width="3.109375" style="51" customWidth="1"/>
+    <col min="10052" max="10052" width="3.44140625" style="51" customWidth="1"/>
+    <col min="10053" max="10053" width="7.33203125" style="51" customWidth="1"/>
+    <col min="10054" max="10054" width="13.5546875" style="51" customWidth="1"/>
+    <col min="10055" max="10055" width="7.109375" style="51" customWidth="1"/>
+    <col min="10056" max="10056" width="8.5546875" style="51" customWidth="1"/>
+    <col min="10057" max="10057" width="9" style="51" customWidth="1"/>
+    <col min="10058" max="10058" width="5.109375" style="51" customWidth="1"/>
+    <col min="10059" max="10059" width="8.44140625" style="51" customWidth="1"/>
+    <col min="10060" max="10060" width="17.109375" style="51" customWidth="1"/>
+    <col min="10061" max="10061" width="18" style="51" customWidth="1"/>
+    <col min="10062" max="10062" width="3.88671875" style="51" customWidth="1"/>
+    <col min="10063" max="10064" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="10065" max="10067" width="9.109375" style="51"/>
+    <col min="10068" max="10068" width="11.33203125" style="51" customWidth="1"/>
+    <col min="10069" max="10306" width="9.109375" style="51"/>
+    <col min="10307" max="10307" width="3.109375" style="51" customWidth="1"/>
+    <col min="10308" max="10308" width="3.44140625" style="51" customWidth="1"/>
+    <col min="10309" max="10309" width="7.33203125" style="51" customWidth="1"/>
+    <col min="10310" max="10310" width="13.5546875" style="51" customWidth="1"/>
+    <col min="10311" max="10311" width="7.109375" style="51" customWidth="1"/>
+    <col min="10312" max="10312" width="8.5546875" style="51" customWidth="1"/>
+    <col min="10313" max="10313" width="9" style="51" customWidth="1"/>
+    <col min="10314" max="10314" width="5.109375" style="51" customWidth="1"/>
+    <col min="10315" max="10315" width="8.44140625" style="51" customWidth="1"/>
+    <col min="10316" max="10316" width="17.109375" style="51" customWidth="1"/>
+    <col min="10317" max="10317" width="18" style="51" customWidth="1"/>
+    <col min="10318" max="10318" width="3.88671875" style="51" customWidth="1"/>
+    <col min="10319" max="10320" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="10321" max="10323" width="9.109375" style="51"/>
+    <col min="10324" max="10324" width="11.33203125" style="51" customWidth="1"/>
+    <col min="10325" max="10562" width="9.109375" style="51"/>
+    <col min="10563" max="10563" width="3.109375" style="51" customWidth="1"/>
+    <col min="10564" max="10564" width="3.44140625" style="51" customWidth="1"/>
+    <col min="10565" max="10565" width="7.33203125" style="51" customWidth="1"/>
+    <col min="10566" max="10566" width="13.5546875" style="51" customWidth="1"/>
+    <col min="10567" max="10567" width="7.109375" style="51" customWidth="1"/>
+    <col min="10568" max="10568" width="8.5546875" style="51" customWidth="1"/>
+    <col min="10569" max="10569" width="9" style="51" customWidth="1"/>
+    <col min="10570" max="10570" width="5.109375" style="51" customWidth="1"/>
+    <col min="10571" max="10571" width="8.44140625" style="51" customWidth="1"/>
+    <col min="10572" max="10572" width="17.109375" style="51" customWidth="1"/>
+    <col min="10573" max="10573" width="18" style="51" customWidth="1"/>
+    <col min="10574" max="10574" width="3.88671875" style="51" customWidth="1"/>
+    <col min="10575" max="10576" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="10577" max="10579" width="9.109375" style="51"/>
+    <col min="10580" max="10580" width="11.33203125" style="51" customWidth="1"/>
+    <col min="10581" max="10818" width="9.109375" style="51"/>
+    <col min="10819" max="10819" width="3.109375" style="51" customWidth="1"/>
+    <col min="10820" max="10820" width="3.44140625" style="51" customWidth="1"/>
+    <col min="10821" max="10821" width="7.33203125" style="51" customWidth="1"/>
+    <col min="10822" max="10822" width="13.5546875" style="51" customWidth="1"/>
+    <col min="10823" max="10823" width="7.109375" style="51" customWidth="1"/>
+    <col min="10824" max="10824" width="8.5546875" style="51" customWidth="1"/>
+    <col min="10825" max="10825" width="9" style="51" customWidth="1"/>
+    <col min="10826" max="10826" width="5.109375" style="51" customWidth="1"/>
+    <col min="10827" max="10827" width="8.44140625" style="51" customWidth="1"/>
+    <col min="10828" max="10828" width="17.109375" style="51" customWidth="1"/>
+    <col min="10829" max="10829" width="18" style="51" customWidth="1"/>
+    <col min="10830" max="10830" width="3.88671875" style="51" customWidth="1"/>
+    <col min="10831" max="10832" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="10833" max="10835" width="9.109375" style="51"/>
+    <col min="10836" max="10836" width="11.33203125" style="51" customWidth="1"/>
+    <col min="10837" max="11074" width="9.109375" style="51"/>
+    <col min="11075" max="11075" width="3.109375" style="51" customWidth="1"/>
+    <col min="11076" max="11076" width="3.44140625" style="51" customWidth="1"/>
+    <col min="11077" max="11077" width="7.33203125" style="51" customWidth="1"/>
+    <col min="11078" max="11078" width="13.5546875" style="51" customWidth="1"/>
+    <col min="11079" max="11079" width="7.109375" style="51" customWidth="1"/>
+    <col min="11080" max="11080" width="8.5546875" style="51" customWidth="1"/>
+    <col min="11081" max="11081" width="9" style="51" customWidth="1"/>
+    <col min="11082" max="11082" width="5.109375" style="51" customWidth="1"/>
+    <col min="11083" max="11083" width="8.44140625" style="51" customWidth="1"/>
+    <col min="11084" max="11084" width="17.109375" style="51" customWidth="1"/>
+    <col min="11085" max="11085" width="18" style="51" customWidth="1"/>
+    <col min="11086" max="11086" width="3.88671875" style="51" customWidth="1"/>
+    <col min="11087" max="11088" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="11089" max="11091" width="9.109375" style="51"/>
+    <col min="11092" max="11092" width="11.33203125" style="51" customWidth="1"/>
+    <col min="11093" max="11330" width="9.109375" style="51"/>
+    <col min="11331" max="11331" width="3.109375" style="51" customWidth="1"/>
+    <col min="11332" max="11332" width="3.44140625" style="51" customWidth="1"/>
+    <col min="11333" max="11333" width="7.33203125" style="51" customWidth="1"/>
+    <col min="11334" max="11334" width="13.5546875" style="51" customWidth="1"/>
+    <col min="11335" max="11335" width="7.109375" style="51" customWidth="1"/>
+    <col min="11336" max="11336" width="8.5546875" style="51" customWidth="1"/>
+    <col min="11337" max="11337" width="9" style="51" customWidth="1"/>
+    <col min="11338" max="11338" width="5.109375" style="51" customWidth="1"/>
+    <col min="11339" max="11339" width="8.44140625" style="51" customWidth="1"/>
+    <col min="11340" max="11340" width="17.109375" style="51" customWidth="1"/>
+    <col min="11341" max="11341" width="18" style="51" customWidth="1"/>
+    <col min="11342" max="11342" width="3.88671875" style="51" customWidth="1"/>
+    <col min="11343" max="11344" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="11345" max="11347" width="9.109375" style="51"/>
+    <col min="11348" max="11348" width="11.33203125" style="51" customWidth="1"/>
+    <col min="11349" max="11586" width="9.109375" style="51"/>
+    <col min="11587" max="11587" width="3.109375" style="51" customWidth="1"/>
+    <col min="11588" max="11588" width="3.44140625" style="51" customWidth="1"/>
+    <col min="11589" max="11589" width="7.33203125" style="51" customWidth="1"/>
+    <col min="11590" max="11590" width="13.5546875" style="51" customWidth="1"/>
+    <col min="11591" max="11591" width="7.109375" style="51" customWidth="1"/>
+    <col min="11592" max="11592" width="8.5546875" style="51" customWidth="1"/>
+    <col min="11593" max="11593" width="9" style="51" customWidth="1"/>
+    <col min="11594" max="11594" width="5.109375" style="51" customWidth="1"/>
+    <col min="11595" max="11595" width="8.44140625" style="51" customWidth="1"/>
+    <col min="11596" max="11596" width="17.109375" style="51" customWidth="1"/>
+    <col min="11597" max="11597" width="18" style="51" customWidth="1"/>
+    <col min="11598" max="11598" width="3.88671875" style="51" customWidth="1"/>
+    <col min="11599" max="11600" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="11601" max="11603" width="9.109375" style="51"/>
+    <col min="11604" max="11604" width="11.33203125" style="51" customWidth="1"/>
+    <col min="11605" max="11842" width="9.109375" style="51"/>
+    <col min="11843" max="11843" width="3.109375" style="51" customWidth="1"/>
+    <col min="11844" max="11844" width="3.44140625" style="51" customWidth="1"/>
+    <col min="11845" max="11845" width="7.33203125" style="51" customWidth="1"/>
+    <col min="11846" max="11846" width="13.5546875" style="51" customWidth="1"/>
+    <col min="11847" max="11847" width="7.109375" style="51" customWidth="1"/>
+    <col min="11848" max="11848" width="8.5546875" style="51" customWidth="1"/>
+    <col min="11849" max="11849" width="9" style="51" customWidth="1"/>
+    <col min="11850" max="11850" width="5.109375" style="51" customWidth="1"/>
+    <col min="11851" max="11851" width="8.44140625" style="51" customWidth="1"/>
+    <col min="11852" max="11852" width="17.109375" style="51" customWidth="1"/>
+    <col min="11853" max="11853" width="18" style="51" customWidth="1"/>
+    <col min="11854" max="11854" width="3.88671875" style="51" customWidth="1"/>
+    <col min="11855" max="11856" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="11857" max="11859" width="9.109375" style="51"/>
+    <col min="11860" max="11860" width="11.33203125" style="51" customWidth="1"/>
+    <col min="11861" max="12098" width="9.109375" style="51"/>
+    <col min="12099" max="12099" width="3.109375" style="51" customWidth="1"/>
+    <col min="12100" max="12100" width="3.44140625" style="51" customWidth="1"/>
+    <col min="12101" max="12101" width="7.33203125" style="51" customWidth="1"/>
+    <col min="12102" max="12102" width="13.5546875" style="51" customWidth="1"/>
+    <col min="12103" max="12103" width="7.109375" style="51" customWidth="1"/>
+    <col min="12104" max="12104" width="8.5546875" style="51" customWidth="1"/>
+    <col min="12105" max="12105" width="9" style="51" customWidth="1"/>
+    <col min="12106" max="12106" width="5.109375" style="51" customWidth="1"/>
+    <col min="12107" max="12107" width="8.44140625" style="51" customWidth="1"/>
+    <col min="12108" max="12108" width="17.109375" style="51" customWidth="1"/>
+    <col min="12109" max="12109" width="18" style="51" customWidth="1"/>
+    <col min="12110" max="12110" width="3.88671875" style="51" customWidth="1"/>
+    <col min="12111" max="12112" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="12113" max="12115" width="9.109375" style="51"/>
+    <col min="12116" max="12116" width="11.33203125" style="51" customWidth="1"/>
+    <col min="12117" max="12354" width="9.109375" style="51"/>
+    <col min="12355" max="12355" width="3.109375" style="51" customWidth="1"/>
+    <col min="12356" max="12356" width="3.44140625" style="51" customWidth="1"/>
+    <col min="12357" max="12357" width="7.33203125" style="51" customWidth="1"/>
+    <col min="12358" max="12358" width="13.5546875" style="51" customWidth="1"/>
+    <col min="12359" max="12359" width="7.109375" style="51" customWidth="1"/>
+    <col min="12360" max="12360" width="8.5546875" style="51" customWidth="1"/>
+    <col min="12361" max="12361" width="9" style="51" customWidth="1"/>
+    <col min="12362" max="12362" width="5.109375" style="51" customWidth="1"/>
+    <col min="12363" max="12363" width="8.44140625" style="51" customWidth="1"/>
+    <col min="12364" max="12364" width="17.109375" style="51" customWidth="1"/>
+    <col min="12365" max="12365" width="18" style="51" customWidth="1"/>
+    <col min="12366" max="12366" width="3.88671875" style="51" customWidth="1"/>
+    <col min="12367" max="12368" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="12369" max="12371" width="9.109375" style="51"/>
+    <col min="12372" max="12372" width="11.33203125" style="51" customWidth="1"/>
+    <col min="12373" max="12610" width="9.109375" style="51"/>
+    <col min="12611" max="12611" width="3.109375" style="51" customWidth="1"/>
+    <col min="12612" max="12612" width="3.44140625" style="51" customWidth="1"/>
+    <col min="12613" max="12613" width="7.33203125" style="51" customWidth="1"/>
+    <col min="12614" max="12614" width="13.5546875" style="51" customWidth="1"/>
+    <col min="12615" max="12615" width="7.109375" style="51" customWidth="1"/>
+    <col min="12616" max="12616" width="8.5546875" style="51" customWidth="1"/>
+    <col min="12617" max="12617" width="9" style="51" customWidth="1"/>
+    <col min="12618" max="12618" width="5.109375" style="51" customWidth="1"/>
+    <col min="12619" max="12619" width="8.44140625" style="51" customWidth="1"/>
+    <col min="12620" max="12620" width="17.109375" style="51" customWidth="1"/>
+    <col min="12621" max="12621" width="18" style="51" customWidth="1"/>
+    <col min="12622" max="12622" width="3.88671875" style="51" customWidth="1"/>
+    <col min="12623" max="12624" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="12625" max="12627" width="9.109375" style="51"/>
+    <col min="12628" max="12628" width="11.33203125" style="51" customWidth="1"/>
+    <col min="12629" max="12866" width="9.109375" style="51"/>
+    <col min="12867" max="12867" width="3.109375" style="51" customWidth="1"/>
+    <col min="12868" max="12868" width="3.44140625" style="51" customWidth="1"/>
+    <col min="12869" max="12869" width="7.33203125" style="51" customWidth="1"/>
+    <col min="12870" max="12870" width="13.5546875" style="51" customWidth="1"/>
+    <col min="12871" max="12871" width="7.109375" style="51" customWidth="1"/>
+    <col min="12872" max="12872" width="8.5546875" style="51" customWidth="1"/>
+    <col min="12873" max="12873" width="9" style="51" customWidth="1"/>
+    <col min="12874" max="12874" width="5.109375" style="51" customWidth="1"/>
+    <col min="12875" max="12875" width="8.44140625" style="51" customWidth="1"/>
+    <col min="12876" max="12876" width="17.109375" style="51" customWidth="1"/>
+    <col min="12877" max="12877" width="18" style="51" customWidth="1"/>
+    <col min="12878" max="12878" width="3.88671875" style="51" customWidth="1"/>
+    <col min="12879" max="12880" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="12881" max="12883" width="9.109375" style="51"/>
+    <col min="12884" max="12884" width="11.33203125" style="51" customWidth="1"/>
+    <col min="12885" max="13122" width="9.109375" style="51"/>
+    <col min="13123" max="13123" width="3.109375" style="51" customWidth="1"/>
+    <col min="13124" max="13124" width="3.44140625" style="51" customWidth="1"/>
+    <col min="13125" max="13125" width="7.33203125" style="51" customWidth="1"/>
+    <col min="13126" max="13126" width="13.5546875" style="51" customWidth="1"/>
+    <col min="13127" max="13127" width="7.109375" style="51" customWidth="1"/>
+    <col min="13128" max="13128" width="8.5546875" style="51" customWidth="1"/>
+    <col min="13129" max="13129" width="9" style="51" customWidth="1"/>
+    <col min="13130" max="13130" width="5.109375" style="51" customWidth="1"/>
+    <col min="13131" max="13131" width="8.44140625" style="51" customWidth="1"/>
+    <col min="13132" max="13132" width="17.109375" style="51" customWidth="1"/>
+    <col min="13133" max="13133" width="18" style="51" customWidth="1"/>
+    <col min="13134" max="13134" width="3.88671875" style="51" customWidth="1"/>
+    <col min="13135" max="13136" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="13137" max="13139" width="9.109375" style="51"/>
+    <col min="13140" max="13140" width="11.33203125" style="51" customWidth="1"/>
+    <col min="13141" max="13378" width="9.109375" style="51"/>
+    <col min="13379" max="13379" width="3.109375" style="51" customWidth="1"/>
+    <col min="13380" max="13380" width="3.44140625" style="51" customWidth="1"/>
+    <col min="13381" max="13381" width="7.33203125" style="51" customWidth="1"/>
+    <col min="13382" max="13382" width="13.5546875" style="51" customWidth="1"/>
+    <col min="13383" max="13383" width="7.109375" style="51" customWidth="1"/>
+    <col min="13384" max="13384" width="8.5546875" style="51" customWidth="1"/>
+    <col min="13385" max="13385" width="9" style="51" customWidth="1"/>
+    <col min="13386" max="13386" width="5.109375" style="51" customWidth="1"/>
+    <col min="13387" max="13387" width="8.44140625" style="51" customWidth="1"/>
+    <col min="13388" max="13388" width="17.109375" style="51" customWidth="1"/>
+    <col min="13389" max="13389" width="18" style="51" customWidth="1"/>
+    <col min="13390" max="13390" width="3.88671875" style="51" customWidth="1"/>
+    <col min="13391" max="13392" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="13393" max="13395" width="9.109375" style="51"/>
+    <col min="13396" max="13396" width="11.33203125" style="51" customWidth="1"/>
+    <col min="13397" max="13634" width="9.109375" style="51"/>
+    <col min="13635" max="13635" width="3.109375" style="51" customWidth="1"/>
+    <col min="13636" max="13636" width="3.44140625" style="51" customWidth="1"/>
+    <col min="13637" max="13637" width="7.33203125" style="51" customWidth="1"/>
+    <col min="13638" max="13638" width="13.5546875" style="51" customWidth="1"/>
+    <col min="13639" max="13639" width="7.109375" style="51" customWidth="1"/>
+    <col min="13640" max="13640" width="8.5546875" style="51" customWidth="1"/>
+    <col min="13641" max="13641" width="9" style="51" customWidth="1"/>
+    <col min="13642" max="13642" width="5.109375" style="51" customWidth="1"/>
+    <col min="13643" max="13643" width="8.44140625" style="51" customWidth="1"/>
+    <col min="13644" max="13644" width="17.109375" style="51" customWidth="1"/>
+    <col min="13645" max="13645" width="18" style="51" customWidth="1"/>
+    <col min="13646" max="13646" width="3.88671875" style="51" customWidth="1"/>
+    <col min="13647" max="13648" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="13649" max="13651" width="9.109375" style="51"/>
+    <col min="13652" max="13652" width="11.33203125" style="51" customWidth="1"/>
+    <col min="13653" max="13890" width="9.109375" style="51"/>
+    <col min="13891" max="13891" width="3.109375" style="51" customWidth="1"/>
+    <col min="13892" max="13892" width="3.44140625" style="51" customWidth="1"/>
+    <col min="13893" max="13893" width="7.33203125" style="51" customWidth="1"/>
+    <col min="13894" max="13894" width="13.5546875" style="51" customWidth="1"/>
+    <col min="13895" max="13895" width="7.109375" style="51" customWidth="1"/>
+    <col min="13896" max="13896" width="8.5546875" style="51" customWidth="1"/>
+    <col min="13897" max="13897" width="9" style="51" customWidth="1"/>
+    <col min="13898" max="13898" width="5.109375" style="51" customWidth="1"/>
+    <col min="13899" max="13899" width="8.44140625" style="51" customWidth="1"/>
+    <col min="13900" max="13900" width="17.109375" style="51" customWidth="1"/>
+    <col min="13901" max="13901" width="18" style="51" customWidth="1"/>
+    <col min="13902" max="13902" width="3.88671875" style="51" customWidth="1"/>
+    <col min="13903" max="13904" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="13905" max="13907" width="9.109375" style="51"/>
+    <col min="13908" max="13908" width="11.33203125" style="51" customWidth="1"/>
+    <col min="13909" max="14146" width="9.109375" style="51"/>
+    <col min="14147" max="14147" width="3.109375" style="51" customWidth="1"/>
+    <col min="14148" max="14148" width="3.44140625" style="51" customWidth="1"/>
+    <col min="14149" max="14149" width="7.33203125" style="51" customWidth="1"/>
+    <col min="14150" max="14150" width="13.5546875" style="51" customWidth="1"/>
+    <col min="14151" max="14151" width="7.109375" style="51" customWidth="1"/>
+    <col min="14152" max="14152" width="8.5546875" style="51" customWidth="1"/>
+    <col min="14153" max="14153" width="9" style="51" customWidth="1"/>
+    <col min="14154" max="14154" width="5.109375" style="51" customWidth="1"/>
+    <col min="14155" max="14155" width="8.44140625" style="51" customWidth="1"/>
+    <col min="14156" max="14156" width="17.109375" style="51" customWidth="1"/>
+    <col min="14157" max="14157" width="18" style="51" customWidth="1"/>
+    <col min="14158" max="14158" width="3.88671875" style="51" customWidth="1"/>
+    <col min="14159" max="14160" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="14161" max="14163" width="9.109375" style="51"/>
+    <col min="14164" max="14164" width="11.33203125" style="51" customWidth="1"/>
+    <col min="14165" max="14402" width="9.109375" style="51"/>
+    <col min="14403" max="14403" width="3.109375" style="51" customWidth="1"/>
+    <col min="14404" max="14404" width="3.44140625" style="51" customWidth="1"/>
+    <col min="14405" max="14405" width="7.33203125" style="51" customWidth="1"/>
+    <col min="14406" max="14406" width="13.5546875" style="51" customWidth="1"/>
+    <col min="14407" max="14407" width="7.109375" style="51" customWidth="1"/>
+    <col min="14408" max="14408" width="8.5546875" style="51" customWidth="1"/>
+    <col min="14409" max="14409" width="9" style="51" customWidth="1"/>
+    <col min="14410" max="14410" width="5.109375" style="51" customWidth="1"/>
+    <col min="14411" max="14411" width="8.44140625" style="51" customWidth="1"/>
+    <col min="14412" max="14412" width="17.109375" style="51" customWidth="1"/>
+    <col min="14413" max="14413" width="18" style="51" customWidth="1"/>
+    <col min="14414" max="14414" width="3.88671875" style="51" customWidth="1"/>
+    <col min="14415" max="14416" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="14417" max="14419" width="9.109375" style="51"/>
+    <col min="14420" max="14420" width="11.33203125" style="51" customWidth="1"/>
+    <col min="14421" max="14658" width="9.109375" style="51"/>
+    <col min="14659" max="14659" width="3.109375" style="51" customWidth="1"/>
+    <col min="14660" max="14660" width="3.44140625" style="51" customWidth="1"/>
+    <col min="14661" max="14661" width="7.33203125" style="51" customWidth="1"/>
+    <col min="14662" max="14662" width="13.5546875" style="51" customWidth="1"/>
+    <col min="14663" max="14663" width="7.109375" style="51" customWidth="1"/>
+    <col min="14664" max="14664" width="8.5546875" style="51" customWidth="1"/>
+    <col min="14665" max="14665" width="9" style="51" customWidth="1"/>
+    <col min="14666" max="14666" width="5.109375" style="51" customWidth="1"/>
+    <col min="14667" max="14667" width="8.44140625" style="51" customWidth="1"/>
+    <col min="14668" max="14668" width="17.109375" style="51" customWidth="1"/>
+    <col min="14669" max="14669" width="18" style="51" customWidth="1"/>
+    <col min="14670" max="14670" width="3.88671875" style="51" customWidth="1"/>
+    <col min="14671" max="14672" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="14673" max="14675" width="9.109375" style="51"/>
+    <col min="14676" max="14676" width="11.33203125" style="51" customWidth="1"/>
+    <col min="14677" max="14914" width="9.109375" style="51"/>
+    <col min="14915" max="14915" width="3.109375" style="51" customWidth="1"/>
+    <col min="14916" max="14916" width="3.44140625" style="51" customWidth="1"/>
+    <col min="14917" max="14917" width="7.33203125" style="51" customWidth="1"/>
+    <col min="14918" max="14918" width="13.5546875" style="51" customWidth="1"/>
+    <col min="14919" max="14919" width="7.109375" style="51" customWidth="1"/>
+    <col min="14920" max="14920" width="8.5546875" style="51" customWidth="1"/>
+    <col min="14921" max="14921" width="9" style="51" customWidth="1"/>
+    <col min="14922" max="14922" width="5.109375" style="51" customWidth="1"/>
+    <col min="14923" max="14923" width="8.44140625" style="51" customWidth="1"/>
+    <col min="14924" max="14924" width="17.109375" style="51" customWidth="1"/>
+    <col min="14925" max="14925" width="18" style="51" customWidth="1"/>
+    <col min="14926" max="14926" width="3.88671875" style="51" customWidth="1"/>
+    <col min="14927" max="14928" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="14929" max="14931" width="9.109375" style="51"/>
+    <col min="14932" max="14932" width="11.33203125" style="51" customWidth="1"/>
+    <col min="14933" max="15170" width="9.109375" style="51"/>
+    <col min="15171" max="15171" width="3.109375" style="51" customWidth="1"/>
+    <col min="15172" max="15172" width="3.44140625" style="51" customWidth="1"/>
+    <col min="15173" max="15173" width="7.33203125" style="51" customWidth="1"/>
+    <col min="15174" max="15174" width="13.5546875" style="51" customWidth="1"/>
+    <col min="15175" max="15175" width="7.109375" style="51" customWidth="1"/>
+    <col min="15176" max="15176" width="8.5546875" style="51" customWidth="1"/>
+    <col min="15177" max="15177" width="9" style="51" customWidth="1"/>
+    <col min="15178" max="15178" width="5.109375" style="51" customWidth="1"/>
+    <col min="15179" max="15179" width="8.44140625" style="51" customWidth="1"/>
+    <col min="15180" max="15180" width="17.109375" style="51" customWidth="1"/>
+    <col min="15181" max="15181" width="18" style="51" customWidth="1"/>
+    <col min="15182" max="15182" width="3.88671875" style="51" customWidth="1"/>
+    <col min="15183" max="15184" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="15185" max="15187" width="9.109375" style="51"/>
+    <col min="15188" max="15188" width="11.33203125" style="51" customWidth="1"/>
+    <col min="15189" max="15426" width="9.109375" style="51"/>
+    <col min="15427" max="15427" width="3.109375" style="51" customWidth="1"/>
+    <col min="15428" max="15428" width="3.44140625" style="51" customWidth="1"/>
+    <col min="15429" max="15429" width="7.33203125" style="51" customWidth="1"/>
+    <col min="15430" max="15430" width="13.5546875" style="51" customWidth="1"/>
+    <col min="15431" max="15431" width="7.109375" style="51" customWidth="1"/>
+    <col min="15432" max="15432" width="8.5546875" style="51" customWidth="1"/>
+    <col min="15433" max="15433" width="9" style="51" customWidth="1"/>
+    <col min="15434" max="15434" width="5.109375" style="51" customWidth="1"/>
+    <col min="15435" max="15435" width="8.44140625" style="51" customWidth="1"/>
+    <col min="15436" max="15436" width="17.109375" style="51" customWidth="1"/>
+    <col min="15437" max="15437" width="18" style="51" customWidth="1"/>
+    <col min="15438" max="15438" width="3.88671875" style="51" customWidth="1"/>
+    <col min="15439" max="15440" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="15441" max="15443" width="9.109375" style="51"/>
+    <col min="15444" max="15444" width="11.33203125" style="51" customWidth="1"/>
+    <col min="15445" max="15682" width="9.109375" style="51"/>
+    <col min="15683" max="15683" width="3.109375" style="51" customWidth="1"/>
+    <col min="15684" max="15684" width="3.44140625" style="51" customWidth="1"/>
+    <col min="15685" max="15685" width="7.33203125" style="51" customWidth="1"/>
+    <col min="15686" max="15686" width="13.5546875" style="51" customWidth="1"/>
+    <col min="15687" max="15687" width="7.109375" style="51" customWidth="1"/>
+    <col min="15688" max="15688" width="8.5546875" style="51" customWidth="1"/>
+    <col min="15689" max="15689" width="9" style="51" customWidth="1"/>
+    <col min="15690" max="15690" width="5.109375" style="51" customWidth="1"/>
+    <col min="15691" max="15691" width="8.44140625" style="51" customWidth="1"/>
+    <col min="15692" max="15692" width="17.109375" style="51" customWidth="1"/>
+    <col min="15693" max="15693" width="18" style="51" customWidth="1"/>
+    <col min="15694" max="15694" width="3.88671875" style="51" customWidth="1"/>
+    <col min="15695" max="15696" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="15697" max="15699" width="9.109375" style="51"/>
+    <col min="15700" max="15700" width="11.33203125" style="51" customWidth="1"/>
+    <col min="15701" max="15938" width="9.109375" style="51"/>
+    <col min="15939" max="15939" width="3.109375" style="51" customWidth="1"/>
+    <col min="15940" max="15940" width="3.44140625" style="51" customWidth="1"/>
+    <col min="15941" max="15941" width="7.33203125" style="51" customWidth="1"/>
+    <col min="15942" max="15942" width="13.5546875" style="51" customWidth="1"/>
+    <col min="15943" max="15943" width="7.109375" style="51" customWidth="1"/>
+    <col min="15944" max="15944" width="8.5546875" style="51" customWidth="1"/>
+    <col min="15945" max="15945" width="9" style="51" customWidth="1"/>
+    <col min="15946" max="15946" width="5.109375" style="51" customWidth="1"/>
+    <col min="15947" max="15947" width="8.44140625" style="51" customWidth="1"/>
+    <col min="15948" max="15948" width="17.109375" style="51" customWidth="1"/>
+    <col min="15949" max="15949" width="18" style="51" customWidth="1"/>
+    <col min="15950" max="15950" width="3.88671875" style="51" customWidth="1"/>
+    <col min="15951" max="15952" width="12.109375" style="51" bestFit="1" customWidth="1"/>
+    <col min="15953" max="15955" width="9.109375" style="51"/>
+    <col min="15956" max="15956" width="11.33203125" style="51" customWidth="1"/>
+    <col min="15957" max="16384" width="9.109375" style="51"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6">
-      <c r="I1" s="359" t="s">
-        <v>635</v>
-      </c>
-      <c r="J1" s="360">
+    <row r="1" spans="1:10" ht="15.6">
+      <c r="H1" s="359" t="s">
+        <v>634</v>
+      </c>
+      <c r="I1" s="360">
         <f>+'Data from DB'!B3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="21.6" customHeight="1">
-      <c r="D2" s="377"/>
-      <c r="E2" s="377"/>
-      <c r="F2" s="377"/>
-      <c r="G2" s="377"/>
-      <c r="H2" s="377"/>
-    </row>
-    <row r="3" spans="1:11" ht="39" customHeight="1"/>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1">
+    <row r="2" spans="1:10" ht="21.6" customHeight="1">
+      <c r="C2" s="381"/>
+      <c r="D2" s="381"/>
+      <c r="E2" s="381"/>
+      <c r="F2" s="381"/>
+      <c r="G2" s="381"/>
+    </row>
+    <row r="3" spans="1:10" ht="39" customHeight="1"/>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <c r="I4" s="306"/>
       <c r="J4" s="306"/>
-      <c r="K4" s="306"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A5" s="378" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="378"/>
-      <c r="C5" s="378"/>
-      <c r="D5" s="378"/>
-      <c r="E5" s="378"/>
-      <c r="F5" s="378"/>
-      <c r="G5" s="378"/>
-      <c r="H5" s="378"/>
-      <c r="I5" s="378"/>
-      <c r="J5" s="378"/>
-      <c r="K5" s="378"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A7" s="60"/>
-      <c r="B7" s="66" t="s">
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A5" s="387"/>
+      <c r="B5" s="387"/>
+      <c r="C5" s="387"/>
+      <c r="D5" s="387"/>
+      <c r="E5" s="387"/>
+      <c r="F5" s="387"/>
+      <c r="G5" s="387"/>
+      <c r="H5" s="387"/>
+      <c r="I5" s="387"/>
+      <c r="J5" s="387"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A7" s="66" t="s">
         <v>63</v>
       </c>
+      <c r="B7" s="66"/>
       <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A8" s="60"/>
-      <c r="B8" s="440" t="s">
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" thickTop="1">
+      <c r="A8" s="391" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="390"/>
-      <c r="D8" s="390"/>
-      <c r="E8" s="390" t="s">
+      <c r="B8" s="389"/>
+      <c r="C8" s="389"/>
+      <c r="D8" s="389" t="s">
         <v>71</v>
       </c>
-      <c r="F8" s="390" t="s">
+      <c r="E8" s="389" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="390" t="s">
+      <c r="F8" s="389" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="390" t="s">
+      <c r="G8" s="389" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="390" t="s">
+      <c r="H8" s="389" t="s">
         <v>74</v>
       </c>
-      <c r="J8" s="390" t="s">
+      <c r="I8" s="389" t="s">
         <v>75</v>
       </c>
-      <c r="K8" s="385" t="s">
+      <c r="J8" s="419" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A9" s="60"/>
-      <c r="B9" s="441"/>
-      <c r="C9" s="391"/>
-      <c r="D9" s="391"/>
-      <c r="E9" s="391"/>
-      <c r="F9" s="391"/>
-      <c r="G9" s="391"/>
-      <c r="H9" s="391"/>
-      <c r="I9" s="391"/>
-      <c r="J9" s="391"/>
-      <c r="K9" s="386"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="444" t="s">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A9" s="392"/>
+      <c r="B9" s="390"/>
+      <c r="C9" s="390"/>
+      <c r="D9" s="390"/>
+      <c r="E9" s="390"/>
+      <c r="F9" s="390"/>
+      <c r="G9" s="390"/>
+      <c r="H9" s="390"/>
+      <c r="I9" s="390"/>
+      <c r="J9" s="420"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A10" s="399" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="445"/>
-      <c r="D10" s="445"/>
-      <c r="E10" s="438">
+      <c r="B10" s="400"/>
+      <c r="C10" s="400"/>
+      <c r="D10" s="401">
         <f>+'Data from DB'!B447</f>
         <v>0</v>
       </c>
-      <c r="F10" s="408" t="str">
+      <c r="E10" s="402" t="str">
         <f>CONCATENATE('Data from DB'!B464,":",'Data from DB'!B465)</f>
         <v>:</v>
       </c>
-      <c r="G10" s="408" t="s">
+      <c r="F10" s="402" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="392">
+      <c r="G10" s="395">
         <f>+'Data from DB'!B46</f>
         <v>0</v>
       </c>
-      <c r="I10" s="392">
+      <c r="H10" s="395">
         <f>+'Data from DB'!B47</f>
         <v>0</v>
       </c>
-      <c r="J10" s="392">
+      <c r="I10" s="395">
         <f>+'Data from DB'!B48</f>
         <v>0</v>
       </c>
-      <c r="K10" s="387">
+      <c r="J10" s="451">
         <f>+'Data from DB'!B49</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A11" s="60"/>
-      <c r="B11" s="444"/>
-      <c r="C11" s="445"/>
-      <c r="D11" s="445"/>
-      <c r="E11" s="438"/>
-      <c r="F11" s="408"/>
-      <c r="G11" s="408"/>
-      <c r="H11" s="392"/>
-      <c r="I11" s="392"/>
-      <c r="J11" s="392"/>
-      <c r="K11" s="387"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A12" s="60"/>
-      <c r="B12" s="421" t="s">
+    <row r="11" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A11" s="399"/>
+      <c r="B11" s="400"/>
+      <c r="C11" s="400"/>
+      <c r="D11" s="401"/>
+      <c r="E11" s="402"/>
+      <c r="F11" s="402"/>
+      <c r="G11" s="395"/>
+      <c r="H11" s="395"/>
+      <c r="I11" s="395"/>
+      <c r="J11" s="451"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A12" s="397" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="422"/>
-      <c r="D12" s="422"/>
-      <c r="E12" s="438">
+      <c r="B12" s="398"/>
+      <c r="C12" s="398"/>
+      <c r="D12" s="401">
         <f>+'Data from DB'!B448</f>
         <v>0</v>
       </c>
-      <c r="F12" s="408" t="str">
+      <c r="E12" s="402" t="str">
         <f>CONCATENATE('Data from DB'!B468,":",'Data from DB'!B469)</f>
         <v>:</v>
       </c>
-      <c r="G12" s="408" t="s">
+      <c r="F12" s="402" t="s">
         <v>73</v>
       </c>
-      <c r="H12" s="392">
+      <c r="G12" s="395">
         <f>+'Data from DB'!C50</f>
         <v>0</v>
       </c>
-      <c r="I12" s="392">
+      <c r="H12" s="395">
         <f>+'Data from DB'!B51</f>
         <v>0</v>
       </c>
-      <c r="J12" s="392">
+      <c r="I12" s="395">
         <f>+'Data from DB'!B52</f>
         <v>0</v>
       </c>
-      <c r="K12" s="387">
+      <c r="J12" s="451">
         <f>+'Data from DB'!C53</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A13" s="60"/>
-      <c r="B13" s="421"/>
-      <c r="C13" s="422"/>
-      <c r="D13" s="422"/>
-      <c r="E13" s="438"/>
-      <c r="F13" s="408"/>
-      <c r="G13" s="408"/>
-      <c r="H13" s="392"/>
-      <c r="I13" s="392"/>
-      <c r="J13" s="392"/>
-      <c r="K13" s="387"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A14" s="60"/>
-      <c r="B14" s="421" t="s">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A13" s="397"/>
+      <c r="B13" s="398"/>
+      <c r="C13" s="398"/>
+      <c r="D13" s="401"/>
+      <c r="E13" s="402"/>
+      <c r="F13" s="402"/>
+      <c r="G13" s="395"/>
+      <c r="H13" s="395"/>
+      <c r="I13" s="395"/>
+      <c r="J13" s="451"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A14" s="397" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="422"/>
-      <c r="D14" s="422"/>
-      <c r="E14" s="438">
+      <c r="B14" s="398"/>
+      <c r="C14" s="398"/>
+      <c r="D14" s="401">
         <f>+'Data from DB'!B449</f>
         <v>0</v>
       </c>
-      <c r="F14" s="408" t="str">
+      <c r="E14" s="402" t="str">
         <f>CONCATENATE('Data from DB'!B466,":",'Data from DB'!B467)</f>
         <v>:</v>
       </c>
-      <c r="G14" s="408" t="s">
+      <c r="F14" s="402" t="s">
         <v>73</v>
       </c>
-      <c r="H14" s="392">
+      <c r="G14" s="395">
         <f>+'Data from DB'!B54</f>
         <v>0</v>
       </c>
-      <c r="I14" s="392">
+      <c r="H14" s="395">
         <f>+'Data from DB'!B55</f>
         <v>0</v>
       </c>
-      <c r="J14" s="392">
+      <c r="I14" s="395">
         <f>+'Data from DB'!B56</f>
         <v>0</v>
       </c>
-      <c r="K14" s="387">
+      <c r="J14" s="451">
         <f>+'Data from DB'!B57</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A15" s="60"/>
-      <c r="B15" s="421"/>
-      <c r="C15" s="422"/>
-      <c r="D15" s="422"/>
-      <c r="E15" s="438"/>
-      <c r="F15" s="408"/>
-      <c r="G15" s="408"/>
-      <c r="H15" s="392"/>
-      <c r="I15" s="392"/>
-      <c r="J15" s="392"/>
-      <c r="K15" s="387"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A16" s="60"/>
-      <c r="B16" s="442" t="s">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A15" s="397"/>
+      <c r="B15" s="398"/>
+      <c r="C15" s="398"/>
+      <c r="D15" s="401"/>
+      <c r="E15" s="402"/>
+      <c r="F15" s="402"/>
+      <c r="G15" s="395"/>
+      <c r="H15" s="395"/>
+      <c r="I15" s="395"/>
+      <c r="J15" s="451"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A16" s="393" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="443"/>
-      <c r="D16" s="443"/>
-      <c r="E16" s="438">
+      <c r="B16" s="394"/>
+      <c r="C16" s="394"/>
+      <c r="D16" s="401">
         <f>+'Data from DB'!B450</f>
         <v>0</v>
       </c>
-      <c r="F16" s="408" t="str">
+      <c r="E16" s="402" t="str">
         <f>CONCATENATE('Data from DB'!B462,":",'Data from DB'!B461)</f>
         <v>:</v>
       </c>
-      <c r="G16" s="408" t="s">
+      <c r="F16" s="402" t="s">
         <v>73</v>
       </c>
-      <c r="H16" s="411">
+      <c r="G16" s="403">
         <f>+'Data from DB'!B58</f>
         <v>0</v>
       </c>
-      <c r="I16" s="392">
+      <c r="H16" s="395">
         <f>+'Data from DB'!B59</f>
         <v>0</v>
       </c>
-      <c r="J16" s="392">
+      <c r="I16" s="395">
         <f>+'Data from DB'!B60</f>
         <v>0</v>
       </c>
-      <c r="K16" s="388">
+      <c r="J16" s="452">
         <f>+'Data from DB'!B61</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A17" s="60"/>
-      <c r="B17" s="442"/>
-      <c r="C17" s="443"/>
-      <c r="D17" s="443"/>
-      <c r="E17" s="438"/>
-      <c r="F17" s="408"/>
-      <c r="G17" s="408"/>
-      <c r="H17" s="411"/>
-      <c r="I17" s="392"/>
-      <c r="J17" s="392"/>
-      <c r="K17" s="388"/>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" customHeight="1">
-      <c r="B18" s="417" t="s">
+    <row r="17" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A17" s="393"/>
+      <c r="B17" s="394"/>
+      <c r="C17" s="394"/>
+      <c r="D17" s="401"/>
+      <c r="E17" s="402"/>
+      <c r="F17" s="402"/>
+      <c r="G17" s="403"/>
+      <c r="H17" s="395"/>
+      <c r="I17" s="395"/>
+      <c r="J17" s="452"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A18" s="415" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="418"/>
-      <c r="D18" s="418"/>
-      <c r="E18" s="424">
+      <c r="B18" s="416"/>
+      <c r="C18" s="416"/>
+      <c r="D18" s="421">
         <f>+'Data from DB'!B451</f>
         <v>0</v>
       </c>
-      <c r="F18" s="477" t="str">
+      <c r="E18" s="423" t="str">
         <f>CONCATENATE('Data from DB'!B460,":",'Data from DB'!B461)</f>
         <v>:</v>
       </c>
-      <c r="G18" s="409" t="s">
+      <c r="F18" s="406" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="411">
+      <c r="G18" s="403">
         <f>+'Data from DB'!B475</f>
         <v>0</v>
       </c>
-      <c r="I18" s="392">
+      <c r="H18" s="395">
         <f>+'Data from DB'!B476</f>
         <v>0</v>
       </c>
-      <c r="J18" s="392">
+      <c r="I18" s="395">
         <f>+'Data from DB'!B477</f>
         <v>0</v>
       </c>
-      <c r="K18" s="388">
+      <c r="J18" s="452">
         <f>+'Data from DB'!B478</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A19" s="60"/>
-      <c r="B19" s="419"/>
-      <c r="C19" s="420"/>
-      <c r="D19" s="420"/>
-      <c r="E19" s="425"/>
-      <c r="F19" s="478"/>
-      <c r="G19" s="410"/>
-      <c r="H19" s="412"/>
-      <c r="I19" s="423"/>
-      <c r="J19" s="423"/>
-      <c r="K19" s="389"/>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A20" s="60"/>
+    <row r="19" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A19" s="417"/>
+      <c r="B19" s="418"/>
+      <c r="C19" s="418"/>
+      <c r="D19" s="422"/>
+      <c r="E19" s="424"/>
+      <c r="F19" s="407"/>
+      <c r="G19" s="408"/>
+      <c r="H19" s="396"/>
+      <c r="I19" s="396"/>
+      <c r="J19" s="453"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" customHeight="1" thickTop="1">
+      <c r="A20" s="116"/>
       <c r="B20" s="116"/>
       <c r="C20" s="116"/>
       <c r="D20" s="116"/>
@@ -11865,208 +11846,199 @@
       <c r="H20" s="116"/>
       <c r="I20" s="116"/>
       <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A21" s="60"/>
-      <c r="B21" s="166"/>
-      <c r="C21" s="167"/>
-      <c r="D21" s="168"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="60"/>
-      <c r="H21" s="338"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A21" s="166"/>
+      <c r="B21" s="167"/>
+      <c r="C21" s="168"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="60"/>
+      <c r="G21" s="338"/>
+      <c r="H21" s="174"/>
       <c r="I21" s="174"/>
       <c r="J21" s="174"/>
-      <c r="K21" s="174"/>
-    </row>
-    <row r="22" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A22" s="60"/>
-      <c r="B22" s="439" t="s">
+    </row>
+    <row r="22" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A22" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="439"/>
-      <c r="D22" s="439"/>
-      <c r="E22" s="439"/>
-      <c r="H22" s="338"/>
-    </row>
-    <row r="23" spans="1:11" ht="13.95" customHeight="1" thickBot="1">
-      <c r="A23" s="60"/>
-      <c r="B23" s="68" t="s">
+      <c r="B22" s="388"/>
+      <c r="C22" s="388"/>
+      <c r="D22" s="388"/>
+      <c r="G22" s="338"/>
+    </row>
+    <row r="23" spans="1:10" ht="13.95" customHeight="1" thickBot="1">
+      <c r="A23" s="68" t="s">
         <v>35</v>
       </c>
+      <c r="B23" s="68"/>
       <c r="C23" s="68"/>
       <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="68"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="70"/>
       <c r="I23" s="70"/>
       <c r="J23" s="70"/>
-      <c r="K23" s="70"/>
-    </row>
-    <row r="24" spans="1:11" ht="13.95" customHeight="1" thickTop="1">
-      <c r="A24" s="60"/>
-      <c r="B24" s="413" t="s">
+    </row>
+    <row r="24" spans="1:10" ht="13.95" customHeight="1" thickTop="1">
+      <c r="A24" s="409" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="414"/>
-      <c r="D24" s="400"/>
-      <c r="E24" s="399" t="s">
+      <c r="B24" s="410"/>
+      <c r="C24" s="411"/>
+      <c r="D24" s="443" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="400"/>
-      <c r="G24" s="395" t="s">
+      <c r="E24" s="411"/>
+      <c r="F24" s="439" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="397" t="s">
+      <c r="G24" s="441" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="385" t="s">
+      <c r="H24" s="419" t="s">
         <v>75</v>
       </c>
-      <c r="J24" s="385" t="s">
+      <c r="I24" s="419" t="s">
         <v>130</v>
       </c>
-      <c r="K24" s="172"/>
-    </row>
-    <row r="25" spans="1:11" ht="15.6" thickBot="1">
-      <c r="B25" s="415"/>
-      <c r="C25" s="416"/>
-      <c r="D25" s="402"/>
-      <c r="E25" s="401"/>
-      <c r="F25" s="402"/>
-      <c r="G25" s="396"/>
-      <c r="H25" s="398"/>
-      <c r="I25" s="386"/>
-      <c r="J25" s="386"/>
-      <c r="K25" s="172"/>
-    </row>
-    <row r="26" spans="1:11" ht="15.6" customHeight="1" thickTop="1">
-      <c r="B26" s="426" t="s">
+      <c r="J24" s="172"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.6" thickBot="1">
+      <c r="A25" s="412"/>
+      <c r="B25" s="413"/>
+      <c r="C25" s="414"/>
+      <c r="D25" s="444"/>
+      <c r="E25" s="414"/>
+      <c r="F25" s="440"/>
+      <c r="G25" s="442"/>
+      <c r="H25" s="420"/>
+      <c r="I25" s="420"/>
+      <c r="J25" s="172"/>
+    </row>
+    <row r="26" spans="1:10" ht="15.6" customHeight="1" thickTop="1">
+      <c r="A26" s="425" t="s">
         <v>76</v>
       </c>
+      <c r="B26" s="426"/>
       <c r="C26" s="427"/>
-      <c r="D26" s="428"/>
-      <c r="E26" s="403" t="s">
+      <c r="D26" s="445" t="s">
         <v>79</v>
       </c>
-      <c r="F26" s="404"/>
-      <c r="G26" s="304">
+      <c r="E26" s="446"/>
+      <c r="F26" s="304">
         <f>+'Data from DB'!B62</f>
         <v>0</v>
       </c>
+      <c r="G26" s="331">
+        <f>+'Data from DB'!B63</f>
+        <v>0</v>
+      </c>
       <c r="H26" s="331">
-        <f>+'Data from DB'!B63</f>
+        <f>+'Data from DB'!B64</f>
         <v>0</v>
       </c>
       <c r="I26" s="331">
-        <f>+'Data from DB'!B64</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="331">
         <f>+'Data from DB'!B65</f>
         <v>0</v>
       </c>
-      <c r="K26" s="173"/>
-    </row>
-    <row r="27" spans="1:11" ht="13.95" customHeight="1">
-      <c r="A27" s="60"/>
+      <c r="J26" s="173"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.95" customHeight="1">
+      <c r="A27" s="428"/>
       <c r="B27" s="429"/>
       <c r="C27" s="430"/>
-      <c r="D27" s="431"/>
-      <c r="E27" s="405" t="s">
+      <c r="D27" s="447" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="406"/>
-      <c r="G27" s="301">
+      <c r="E27" s="448"/>
+      <c r="F27" s="301">
         <f>+'Data from DB'!B66</f>
         <v>0</v>
       </c>
+      <c r="G27" s="332">
+        <f>+'Data from DB'!B67</f>
+        <v>0</v>
+      </c>
       <c r="H27" s="332">
-        <f>+'Data from DB'!B67</f>
+        <f>+'Data from DB'!B68</f>
         <v>0</v>
       </c>
       <c r="I27" s="332">
-        <f>+'Data from DB'!B68</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="332">
         <f>+'Data from DB'!B69</f>
         <v>0</v>
       </c>
-      <c r="K27" s="173"/>
-    </row>
-    <row r="28" spans="1:11" ht="15">
-      <c r="A28" s="60"/>
-      <c r="B28" s="165"/>
+      <c r="J27" s="173"/>
+    </row>
+    <row r="28" spans="1:10" ht="15">
+      <c r="A28" s="165"/>
+      <c r="B28" s="333"/>
       <c r="C28" s="333"/>
-      <c r="D28" s="333"/>
+      <c r="D28" s="334"/>
       <c r="E28" s="334"/>
-      <c r="F28" s="334"/>
-      <c r="G28" s="335"/>
+      <c r="F28" s="335"/>
+      <c r="G28" s="336"/>
       <c r="H28" s="336"/>
       <c r="I28" s="336"/>
-      <c r="J28" s="336"/>
-      <c r="K28" s="173"/>
-    </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1">
-      <c r="A29" s="60"/>
-      <c r="B29" s="432" t="s">
+      <c r="J28" s="173"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1">
+      <c r="A29" s="431" t="s">
         <v>77</v>
       </c>
+      <c r="B29" s="432"/>
       <c r="C29" s="433"/>
-      <c r="D29" s="434"/>
-      <c r="E29" s="405" t="s">
+      <c r="D29" s="447" t="s">
         <v>84</v>
       </c>
-      <c r="F29" s="406"/>
-      <c r="G29" s="303">
+      <c r="E29" s="448"/>
+      <c r="F29" s="303">
         <f>+'Data from DB'!B70</f>
         <v>0</v>
       </c>
+      <c r="G29" s="332">
+        <f>+'Data from DB'!B71</f>
+        <v>0</v>
+      </c>
       <c r="H29" s="332">
-        <f>+'Data from DB'!B71</f>
+        <f>+'Data from DB'!B72</f>
         <v>0</v>
       </c>
       <c r="I29" s="332">
-        <f>+'Data from DB'!B72</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="332">
         <f>+'Data from DB'!B73</f>
         <v>0</v>
       </c>
-      <c r="K29" s="173"/>
-    </row>
-    <row r="30" spans="1:11" ht="15.45" customHeight="1" thickBot="1">
-      <c r="A30" s="60"/>
+      <c r="J29" s="173"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.45" customHeight="1" thickBot="1">
+      <c r="A30" s="434"/>
       <c r="B30" s="435"/>
       <c r="C30" s="436"/>
-      <c r="D30" s="437"/>
-      <c r="E30" s="393" t="s">
+      <c r="D30" s="437" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="394"/>
-      <c r="G30" s="108">
+      <c r="E30" s="438"/>
+      <c r="F30" s="108">
         <f>+'Data from DB'!B74</f>
         <v>0</v>
       </c>
+      <c r="G30" s="337">
+        <f>+'Data from DB'!B75</f>
+        <v>0</v>
+      </c>
       <c r="H30" s="337">
-        <f>+'Data from DB'!B75</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="337">
         <f>+'Data from DB'!B76</f>
         <v>0</v>
       </c>
-      <c r="J30" s="332">
+      <c r="I30" s="332">
         <f>+'Data from DB'!B77</f>
         <v>0</v>
       </c>
-      <c r="K30" s="173"/>
-    </row>
-    <row r="31" spans="1:11" ht="15.6" thickTop="1">
-      <c r="A31" s="60"/>
+      <c r="J30" s="173"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.6" thickTop="1">
+      <c r="A31" s="159"/>
       <c r="B31" s="159"/>
       <c r="C31" s="159"/>
       <c r="D31" s="159"/>
@@ -12075,10 +12047,9 @@
       <c r="G31" s="159"/>
       <c r="H31" s="159"/>
       <c r="I31" s="159"/>
-      <c r="J31" s="159"/>
-      <c r="K31" s="164"/>
-    </row>
-    <row r="32" spans="1:11" ht="15.45" customHeight="1">
+      <c r="J31" s="164"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.45" customHeight="1">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
       <c r="C32" s="60"/>
@@ -12086,157 +12057,149 @@
       <c r="E32" s="60"/>
       <c r="F32" s="60"/>
       <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
+      <c r="H32" s="175"/>
       <c r="I32" s="175"/>
       <c r="J32" s="175"/>
-      <c r="K32" s="175"/>
-    </row>
-    <row r="33" spans="1:11" ht="15" customHeight="1">
-      <c r="A33" s="160"/>
-    </row>
-    <row r="34" spans="1:11" ht="15">
-      <c r="A34" s="60"/>
-    </row>
-    <row r="35" spans="1:11" ht="14.4" customHeight="1">
-      <c r="A35" s="60"/>
-      <c r="E35" s="382"/>
-      <c r="F35" s="382"/>
-      <c r="G35" s="382"/>
-    </row>
-    <row r="36" spans="1:11" ht="15">
-      <c r="A36" s="60"/>
-      <c r="B36" s="305" t="s">
-        <v>162</v>
-      </c>
-      <c r="C36" s="305"/>
-      <c r="E36" s="51">
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1"/>
+    <row r="35" spans="1:10" ht="14.4" customHeight="1">
+      <c r="D35" s="449"/>
+      <c r="E35" s="449"/>
+      <c r="F35" s="449"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="305" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" s="305"/>
+      <c r="D36" s="51">
         <f>+'Data from DB'!B472</f>
         <v>0</v>
       </c>
-      <c r="I36" s="51">
+      <c r="H36" s="51">
         <f>+'Data from DB'!B453</f>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15.6">
-      <c r="B37" s="407"/>
-      <c r="C37" s="407"/>
-      <c r="D37" s="169"/>
-      <c r="E37" s="384"/>
-      <c r="F37" s="384"/>
-      <c r="G37" s="384"/>
-      <c r="I37" s="384">
+    <row r="37" spans="1:10" ht="15.6">
+      <c r="A37" s="404"/>
+      <c r="B37" s="404"/>
+      <c r="C37" s="169"/>
+      <c r="D37" s="405"/>
+      <c r="E37" s="405"/>
+      <c r="F37" s="405"/>
+      <c r="H37" s="405">
         <f>CALCULATIONS!J42</f>
         <v>0</v>
       </c>
-      <c r="J37" s="384"/>
-      <c r="K37" s="384"/>
-    </row>
-    <row r="38" spans="1:11" ht="15">
-      <c r="B38" s="383" t="s">
+      <c r="I37" s="405"/>
+      <c r="J37" s="405"/>
+    </row>
+    <row r="38" spans="1:10" ht="15">
+      <c r="A38" s="450" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="383"/>
-      <c r="D38" s="161"/>
-      <c r="E38" s="382" t="str">
+      <c r="B38" s="450"/>
+      <c r="C38" s="161"/>
+      <c r="D38" s="449" t="str">
         <f xml:space="preserve"> +" C Enginner  "  &amp; + CERTIFICATE!D4</f>
         <v xml:space="preserve"> C Enginner  0</v>
       </c>
-      <c r="F38" s="382"/>
-      <c r="G38" s="382"/>
-      <c r="I38" s="382" t="str">
+      <c r="E38" s="449"/>
+      <c r="F38" s="449"/>
+      <c r="H38" s="449" t="str">
         <f xml:space="preserve"> +" Master  "  &amp; + CERTIFICATE!D4</f>
         <v xml:space="preserve"> Master  0</v>
       </c>
-      <c r="J38" s="382"/>
-      <c r="K38" s="382"/>
-    </row>
-    <row r="39" spans="1:11" ht="15">
+      <c r="I38" s="449"/>
+      <c r="J38" s="449"/>
+    </row>
+    <row r="39" spans="1:10" ht="15">
+      <c r="A39" s="163"/>
       <c r="B39" s="163"/>
       <c r="C39" s="163"/>
-      <c r="D39" s="163"/>
-      <c r="E39" s="161"/>
+      <c r="D39" s="161"/>
+      <c r="E39" s="162"/>
       <c r="F39" s="162"/>
       <c r="G39" s="162"/>
       <c r="H39" s="162"/>
       <c r="I39" s="162"/>
       <c r="J39" s="162"/>
-      <c r="K39" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="B8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="B16:D17"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="B14:D15"/>
-    <mergeCell ref="B10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="B24:D25"/>
-    <mergeCell ref="B18:D19"/>
-    <mergeCell ref="B12:D13"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B26:D27"/>
-    <mergeCell ref="B29:D30"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="E24:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
     <mergeCell ref="J8:J9"/>
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="J12:J13"/>
     <mergeCell ref="J14:J15"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="D24:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A24:C25"/>
+    <mergeCell ref="A18:C19"/>
+    <mergeCell ref="A12:C13"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A26:C27"/>
+    <mergeCell ref="A29:C30"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="A8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A16:C17"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="A14:C15"/>
+    <mergeCell ref="A10:C11"/>
+    <mergeCell ref="D10:D11"/>
   </mergeCells>
-  <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.86614173228346458" bottom="0.59055118110236227" header="0" footer="0.35433070866141736"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"Palatino Linotype,Normal"&amp;9 MV NORD ATOLL ON HIRE  CERTIFICATE&amp;C &amp;R&amp;"Palatino Linotype,Normal"&amp;9Page 3 of 3</oddFooter>
@@ -12255,2395 +12218,2395 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B1" t="s">
         <v>633</v>
-      </c>
-      <c r="B1" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="176" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="298" spans="1:1">
       <c r="A298" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="304" spans="1:1">
       <c r="A304" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="312" spans="1:1">
       <c r="A312" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="313" spans="1:1">
       <c r="A313" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="321" spans="1:1">
       <c r="A321" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="323" spans="1:1">
       <c r="A323" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="326" spans="1:1">
       <c r="A326" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="327" spans="1:1">
       <c r="A327" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="328" spans="1:1">
       <c r="A328" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="329" spans="1:1">
       <c r="A329" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="330" spans="1:1">
       <c r="A330" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="331" spans="1:1">
       <c r="A331" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="332" spans="1:1">
       <c r="A332" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="333" spans="1:1">
       <c r="A333" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="334" spans="1:1">
       <c r="A334" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="335" spans="1:1">
       <c r="A335" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="336" spans="1:1">
       <c r="A336" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="338" spans="1:1">
       <c r="A338" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="339" spans="1:1">
       <c r="A339" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="340" spans="1:1">
       <c r="A340" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="341" spans="1:1">
       <c r="A341" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="342" spans="1:1">
       <c r="A342" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="343" spans="1:1">
       <c r="A343" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="344" spans="1:1">
       <c r="A344" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="345" spans="1:1">
       <c r="A345" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="346" spans="1:1">
       <c r="A346" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="347" spans="1:1">
       <c r="A347" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="348" spans="1:1">
       <c r="A348" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="349" spans="1:1">
       <c r="A349" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="350" spans="1:1">
       <c r="A350" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="351" spans="1:1">
       <c r="A351" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="352" spans="1:1">
       <c r="A352" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="353" spans="1:1">
       <c r="A353" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="354" spans="1:1">
       <c r="A354" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="355" spans="1:1">
       <c r="A355" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="356" spans="1:1">
       <c r="A356" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="357" spans="1:1">
       <c r="A357" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="358" spans="1:1">
       <c r="A358" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="359" spans="1:1">
       <c r="A359" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="360" spans="1:1">
       <c r="A360" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="361" spans="1:1">
       <c r="A361" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="362" spans="1:1">
       <c r="A362" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="363" spans="1:1">
       <c r="A363" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="364" spans="1:1">
       <c r="A364" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="365" spans="1:1">
       <c r="A365" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="366" spans="1:1">
       <c r="A366" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="367" spans="1:1">
       <c r="A367" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="368" spans="1:1">
       <c r="A368" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="369" spans="1:1">
       <c r="A369" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="370" spans="1:1">
       <c r="A370" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="371" spans="1:1">
       <c r="A371" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="372" spans="1:1">
       <c r="A372" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="373" spans="1:1">
       <c r="A373" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="374" spans="1:1">
       <c r="A374" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="375" spans="1:1">
       <c r="A375" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="376" spans="1:1">
       <c r="A376" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="377" spans="1:1">
       <c r="A377" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="378" spans="1:1">
       <c r="A378" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="379" spans="1:1">
       <c r="A379" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="380" spans="1:1">
       <c r="A380" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="381" spans="1:1">
       <c r="A381" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="382" spans="1:1">
       <c r="A382" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="383" spans="1:1">
       <c r="A383" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="384" spans="1:1">
       <c r="A384" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="385" spans="1:1">
       <c r="A385" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="386" spans="1:1">
       <c r="A386" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="387" spans="1:1">
       <c r="A387" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="388" spans="1:1">
       <c r="A388" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="389" spans="1:1">
       <c r="A389" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="390" spans="1:1">
       <c r="A390" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="391" spans="1:1">
       <c r="A391" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="392" spans="1:1">
       <c r="A392" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="393" spans="1:1">
       <c r="A393" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="394" spans="1:1">
       <c r="A394" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="395" spans="1:1">
       <c r="A395" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="396" spans="1:1">
       <c r="A396" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="397" spans="1:1">
       <c r="A397" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="398" spans="1:1">
       <c r="A398" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="399" spans="1:1">
       <c r="A399" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="400" spans="1:1">
       <c r="A400" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="401" spans="1:1">
       <c r="A401" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="402" spans="1:1">
       <c r="A402" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="403" spans="1:1">
       <c r="A403" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="404" spans="1:1">
       <c r="A404" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="405" spans="1:1">
       <c r="A405" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="406" spans="1:1">
       <c r="A406" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="407" spans="1:1">
       <c r="A407" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="408" spans="1:1">
       <c r="A408" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="409" spans="1:1">
       <c r="A409" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="410" spans="1:1">
       <c r="A410" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="411" spans="1:1">
       <c r="A411" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="412" spans="1:1">
       <c r="A412" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="413" spans="1:1">
       <c r="A413" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="414" spans="1:1">
       <c r="A414" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="415" spans="1:1">
       <c r="A415" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="416" spans="1:1">
       <c r="A416" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="417" spans="1:1">
       <c r="A417" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="418" spans="1:1">
       <c r="A418" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="419" spans="1:1">
       <c r="A419" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="420" spans="1:1">
       <c r="A420" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="421" spans="1:1">
       <c r="A421" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="422" spans="1:1">
       <c r="A422" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="423" spans="1:1">
       <c r="A423" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="424" spans="1:1">
       <c r="A424" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="425" spans="1:1">
       <c r="A425" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="426" spans="1:1">
       <c r="A426" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="427" spans="1:1">
       <c r="A427" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="428" spans="1:1">
       <c r="A428" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="429" spans="1:1">
       <c r="A429" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="430" spans="1:1">
       <c r="A430" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="431" spans="1:1">
       <c r="A431" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="432" spans="1:1">
       <c r="A432" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="433" spans="1:1">
       <c r="A433" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="434" spans="1:1">
       <c r="A434" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="435" spans="1:1">
       <c r="A435" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="437" spans="1:1">
       <c r="A437" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="438" spans="1:1">
       <c r="A438" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="439" spans="1:1">
       <c r="A439" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="440" spans="1:1">
       <c r="A440" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="441" spans="1:1">
       <c r="A441" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="442" spans="1:1">
       <c r="A442" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="443" spans="1:1">
       <c r="A443" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="444" spans="1:1">
       <c r="A444" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="445" spans="1:1">
       <c r="A445" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="446" spans="1:1">
       <c r="A446" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="447" spans="1:1">
       <c r="A447" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="448" spans="1:1">
       <c r="A448" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="449" spans="1:1">
       <c r="A449" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="450" spans="1:1">
       <c r="A450" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="451" spans="1:1">
       <c r="A451" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="452" spans="1:1">
       <c r="A452" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="453" spans="1:1">
       <c r="A453" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="454" spans="1:1">
       <c r="A454" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="455" spans="1:1">
       <c r="A455" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="456" spans="1:1">
       <c r="A456" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="457" spans="1:1">
       <c r="A457" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="458" spans="1:1">
       <c r="A458" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="459" spans="1:1">
       <c r="A459" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="460" spans="1:1">
       <c r="A460" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="461" spans="1:1">
       <c r="A461" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="462" spans="1:1">
       <c r="A462" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="463" spans="1:1">
       <c r="A463" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="464" spans="1:1">
       <c r="A464" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="465" spans="1:1">
       <c r="A465" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="466" spans="1:1">
       <c r="A466" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="467" spans="1:1">
       <c r="A467" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="468" spans="1:1">
       <c r="A468" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="469" spans="1:1">
       <c r="A469" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="470" spans="1:1">
       <c r="A470" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="471" spans="1:1">
       <c r="A471" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="472" spans="1:1">
       <c r="A472" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="473" spans="1:1">
       <c r="A473" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="474" spans="1:1">
       <c r="A474" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="475" spans="1:1">
       <c r="A475" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="476" spans="1:1">
       <c r="A476" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="477" spans="1:1">
       <c r="A477" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="478" spans="1:1">
       <c r="A478" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -15698,10 +15661,10 @@
         <v>152</v>
       </c>
       <c r="F23" s="50"/>
-      <c r="G23" s="446" t="s">
+      <c r="G23" s="454" t="s">
         <v>153</v>
       </c>
-      <c r="H23" s="447"/>
+      <c r="H23" s="455"/>
       <c r="J23" s="294" t="s">
         <v>154</v>
       </c>
@@ -15721,11 +15684,11 @@
         <v>139.04000000000002</v>
       </c>
       <c r="F24" s="236"/>
-      <c r="G24" s="448">
+      <c r="G24" s="456">
         <f>J24-E24</f>
         <v>-126.44000000000003</v>
       </c>
-      <c r="H24" s="448"/>
+      <c r="H24" s="456"/>
       <c r="I24" s="296"/>
       <c r="J24" s="297">
         <f>F4</f>
@@ -15752,10 +15715,10 @@
         <v>152</v>
       </c>
       <c r="F26" s="50"/>
-      <c r="G26" s="446" t="s">
+      <c r="G26" s="454" t="s">
         <v>153</v>
       </c>
-      <c r="H26" s="447"/>
+      <c r="H26" s="455"/>
       <c r="J26" s="294" t="s">
         <v>156</v>
       </c>
@@ -15775,11 +15738,11 @@
         <v>-35.940000000000012</v>
       </c>
       <c r="F27" s="236"/>
-      <c r="G27" s="449">
+      <c r="G27" s="457">
         <f>C27-D27</f>
         <v>35.940000000000012</v>
       </c>
-      <c r="H27" s="449"/>
+      <c r="H27" s="457"/>
       <c r="I27" s="296"/>
       <c r="J27" s="299">
         <f>F7</f>
@@ -16715,36 +16678,36 @@
       </c>
     </row>
     <row r="6" spans="1:17" s="3" customFormat="1">
-      <c r="A6" s="451" t="s">
+      <c r="A6" s="459" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="452"/>
-      <c r="C6" s="452"/>
-      <c r="D6" s="453"/>
-      <c r="E6" s="454" t="s">
+      <c r="B6" s="460"/>
+      <c r="C6" s="460"/>
+      <c r="D6" s="461"/>
+      <c r="E6" s="462" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="455"/>
-      <c r="G6" s="455"/>
-      <c r="H6" s="456"/>
+      <c r="F6" s="463"/>
+      <c r="G6" s="463"/>
+      <c r="H6" s="464"/>
     </row>
     <row r="7" spans="1:17" s="3" customFormat="1" ht="15" thickBot="1">
       <c r="A7" s="191" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="457">
+      <c r="B7" s="465">
         <v>43266.000694444447</v>
       </c>
-      <c r="C7" s="457"/>
-      <c r="D7" s="458"/>
+      <c r="C7" s="465"/>
+      <c r="D7" s="466"/>
       <c r="E7" s="191" t="s">
         <v>95</v>
       </c>
-      <c r="F7" s="457">
+      <c r="F7" s="465">
         <v>43268.341666666667</v>
       </c>
-      <c r="G7" s="457"/>
-      <c r="H7" s="458"/>
+      <c r="G7" s="465"/>
+      <c r="H7" s="466"/>
       <c r="J7" s="181" t="s">
         <v>96</v>
       </c>
@@ -16919,18 +16882,18 @@
       <c r="N12" s="38"/>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1">
-      <c r="A13" s="459" t="s">
+      <c r="A13" s="467" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="460"/>
-      <c r="C13" s="460"/>
-      <c r="D13" s="461"/>
-      <c r="E13" s="462" t="s">
+      <c r="B13" s="468"/>
+      <c r="C13" s="468"/>
+      <c r="D13" s="469"/>
+      <c r="E13" s="470" t="s">
         <v>105</v>
       </c>
-      <c r="F13" s="463"/>
-      <c r="G13" s="463"/>
-      <c r="H13" s="464"/>
+      <c r="F13" s="471"/>
+      <c r="G13" s="471"/>
+      <c r="H13" s="472"/>
       <c r="J13" s="183" t="s">
         <v>85</v>
       </c>
@@ -16948,19 +16911,19 @@
       <c r="A14" s="191" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="465" t="s">
+      <c r="B14" s="473" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="465"/>
-      <c r="D14" s="466"/>
+      <c r="C14" s="473"/>
+      <c r="D14" s="474"/>
       <c r="E14" s="191" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="467" t="s">
+      <c r="F14" s="475" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="467"/>
-      <c r="H14" s="468"/>
+      <c r="G14" s="475"/>
+      <c r="H14" s="476"/>
       <c r="J14" s="183" t="s">
         <v>96</v>
       </c>
@@ -17188,12 +17151,12 @@
       </c>
     </row>
     <row r="24" spans="1:14" s="3" customFormat="1" ht="15" thickBot="1">
-      <c r="A24" s="469" t="s">
+      <c r="A24" s="477" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="469"/>
-      <c r="C24" s="469"/>
-      <c r="D24" s="469"/>
+      <c r="B24" s="477"/>
+      <c r="C24" s="477"/>
+      <c r="D24" s="477"/>
       <c r="E24" s="228" t="s">
         <v>97</v>
       </c>
@@ -17211,10 +17174,10 @@
       <c r="N24" s="38"/>
     </row>
     <row r="25" spans="1:14" s="3" customFormat="1" ht="15" thickBot="1">
-      <c r="A25" s="469"/>
-      <c r="B25" s="469"/>
-      <c r="C25" s="469"/>
-      <c r="D25" s="469"/>
+      <c r="A25" s="477"/>
+      <c r="B25" s="477"/>
+      <c r="C25" s="477"/>
+      <c r="D25" s="477"/>
       <c r="E25" s="231">
         <v>70</v>
       </c>
@@ -17247,16 +17210,16 @@
       <c r="H26" s="55"/>
     </row>
     <row r="27" spans="1:14" s="3" customFormat="1">
-      <c r="A27" s="470" t="s">
+      <c r="A27" s="478" t="s">
         <v>119</v>
       </c>
-      <c r="B27" s="470"/>
-      <c r="C27" s="470"/>
-      <c r="D27" s="470"/>
-      <c r="E27" s="470"/>
-      <c r="F27" s="470"/>
-      <c r="G27" s="470"/>
-      <c r="H27" s="470"/>
+      <c r="B27" s="478"/>
+      <c r="C27" s="478"/>
+      <c r="D27" s="478"/>
+      <c r="E27" s="478"/>
+      <c r="F27" s="478"/>
+      <c r="G27" s="478"/>
+      <c r="H27" s="478"/>
       <c r="J27" s="236"/>
       <c r="K27" s="237">
         <f>K23-K25</f>
@@ -17539,11 +17502,11 @@
       <c r="C43" s="189"/>
       <c r="D43" s="189"/>
       <c r="E43" s="189"/>
-      <c r="F43" s="450">
-        <v>0</v>
-      </c>
-      <c r="G43" s="450"/>
-      <c r="H43" s="450"/>
+      <c r="F43" s="458">
+        <v>0</v>
+      </c>
+      <c r="G43" s="458"/>
+      <c r="H43" s="458"/>
     </row>
     <row r="44" spans="1:12" s="3" customFormat="1">
       <c r="B44" s="271" t="s">
@@ -17553,11 +17516,11 @@
         <v>135</v>
       </c>
       <c r="E44" s="271"/>
-      <c r="F44" s="450" t="s">
+      <c r="F44" s="458" t="s">
         <v>136</v>
       </c>
-      <c r="G44" s="450"/>
-      <c r="H44" s="450"/>
+      <c r="G44" s="458"/>
+      <c r="H44" s="458"/>
     </row>
     <row r="45" spans="1:12" s="3" customFormat="1">
       <c r="D45" s="189"/>

--- a/backend_api/templates/on_off_spot_template.xlsx
+++ b/backend_api/templates/on_off_spot_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron Avila\Documents\ERP-SOM\backend_api\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE99AE22-8E87-42B1-8743-1BCCB3A535E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D047DD-74CF-4AF9-BBA9-3A048B549648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{07ADC957-8ABD-40B3-B8CA-6432964576F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{07ADC957-8ABD-40B3-B8CA-6432964576F2}"/>
   </bookViews>
   <sheets>
     <sheet name="CERTIFICATE" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4157,132 +4156,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="37" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="37" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="53" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="70" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="8" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="170" fontId="57" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="170" fontId="57" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="2" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="9" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="9" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="9" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4474,153 +4352,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="67" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="64" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="56" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="65" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="62" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="22" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="34" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="34" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="34" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="34" fillId="3" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="34" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="34" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="34" fillId="3" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="20" fontId="34" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="34" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="22" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="34" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="34" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4637,17 +4381,217 @@
     <xf numFmtId="165" fontId="34" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="0" borderId="65" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="37" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="37" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="56" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="64" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="62" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="62" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="34" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="34" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="34" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="34" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4658,18 +4602,6 @@
     <xf numFmtId="0" fontId="34" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4679,14 +4611,43 @@
     <xf numFmtId="0" fontId="34" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="65" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="34" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="34" fillId="0" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="34" fillId="3" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="34" fillId="3" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4700,6 +4661,68 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="22" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4708,29 +4731,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="22" fillId="0" borderId="65" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="2" fontId="22" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4739,98 +4739,97 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="22" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="34" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="34" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="22" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="34" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="165" fontId="53" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="70" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="8" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="170" fontId="57" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="170" fontId="57" fillId="2" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="9" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="9" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="9" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7337,24 +7336,24 @@
         <v>0</v>
       </c>
       <c r="B3" s="6"/>
-      <c r="C3" s="267">
+      <c r="C3" s="376">
         <f>+'Data from DB'!B4</f>
         <v>0</v>
       </c>
-      <c r="D3" s="267"/>
-      <c r="E3" s="267"/>
+      <c r="D3" s="376"/>
+      <c r="E3" s="376"/>
       <c r="F3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
-      <c r="I3" s="267">
+      <c r="I3" s="376">
         <f>+'Data from DB'!B5</f>
         <v>0</v>
       </c>
-      <c r="J3" s="267"/>
-      <c r="K3" s="267"/>
-      <c r="L3" s="267"/>
+      <c r="J3" s="376"/>
+      <c r="K3" s="376"/>
+      <c r="L3" s="376"/>
     </row>
     <row r="4" spans="1:12" ht="17.399999999999999">
       <c r="A4" s="7"/>
@@ -7375,24 +7374,24 @@
         <v>2</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="268">
+      <c r="C5" s="377">
         <f>+'Data from DB'!B6</f>
         <v>0</v>
       </c>
-      <c r="D5" s="268"/>
-      <c r="E5" s="268"/>
+      <c r="D5" s="377"/>
+      <c r="E5" s="377"/>
       <c r="F5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
-      <c r="I5" s="271">
+      <c r="I5" s="380">
         <f>+'Data from DB'!B7</f>
         <v>0</v>
       </c>
-      <c r="J5" s="271"/>
-      <c r="K5" s="271"/>
-      <c r="L5" s="271"/>
+      <c r="J5" s="380"/>
+      <c r="K5" s="380"/>
+      <c r="L5" s="380"/>
     </row>
     <row r="6" spans="1:12" ht="14.4" customHeight="1">
       <c r="A6" s="10"/>
@@ -7698,16 +7697,16 @@
       <c r="A26" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="269" t="str">
+      <c r="B26" s="378" t="str">
         <f>CONCATENATE("DLOSP at ",'Data from DB'!B16," ","on "," ",'Data from DB'!B15,"at "," ",'Data from DB'!B458,":",'Data from DB'!B459," ","LT")</f>
         <v>DLOSP at  on  at  : LT</v>
       </c>
-      <c r="C26" s="269"/>
-      <c r="D26" s="269"/>
-      <c r="E26" s="269"/>
-      <c r="F26" s="269"/>
-      <c r="G26" s="269"/>
-      <c r="H26" s="269"/>
+      <c r="C26" s="378"/>
+      <c r="D26" s="378"/>
+      <c r="E26" s="378"/>
+      <c r="F26" s="378"/>
+      <c r="G26" s="378"/>
+      <c r="H26" s="378"/>
       <c r="I26" s="255">
         <f>+'Data from DB'!B8</f>
         <v>0</v>
@@ -7939,36 +7938,36 @@
       <c r="L39" s="38"/>
     </row>
     <row r="40" spans="1:12" ht="19.95" customHeight="1">
-      <c r="A40" s="266" t="s">
+      <c r="A40" s="375" t="s">
         <v>156</v>
       </c>
-      <c r="B40" s="266"/>
+      <c r="B40" s="375"/>
       <c r="C40" s="39"/>
       <c r="G40" s="104"/>
-      <c r="H40" s="270"/>
-      <c r="I40" s="270"/>
-      <c r="J40" s="270"/>
-      <c r="K40" s="270"/>
-      <c r="L40" s="270"/>
+      <c r="H40" s="379"/>
+      <c r="I40" s="379"/>
+      <c r="J40" s="379"/>
+      <c r="K40" s="379"/>
+      <c r="L40" s="379"/>
     </row>
     <row r="41" spans="1:12" ht="19.8">
-      <c r="A41" s="264" t="s">
+      <c r="A41" s="373" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="264"/>
+      <c r="B41" s="373"/>
       <c r="C41" s="41"/>
       <c r="D41" s="41"/>
       <c r="E41" s="15"/>
       <c r="F41" s="5"/>
       <c r="G41" s="10"/>
-      <c r="H41" s="265" t="str">
+      <c r="H41" s="374" t="str">
         <f xml:space="preserve"> +" Master  "  &amp; + C3</f>
         <v xml:space="preserve"> Master  0</v>
       </c>
-      <c r="I41" s="265"/>
-      <c r="J41" s="265"/>
-      <c r="K41" s="265"/>
-      <c r="L41" s="265"/>
+      <c r="I41" s="374"/>
+      <c r="J41" s="374"/>
+      <c r="K41" s="374"/>
+      <c r="L41" s="374"/>
     </row>
     <row r="42" spans="1:12" ht="19.8">
       <c r="B42" s="40" t="s">
@@ -8018,11 +8017,9 @@
     <mergeCell ref="I3:L3"/>
     <mergeCell ref="I5:L5"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="77" fitToHeight="2" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;L&amp;"Palatino Linotype,Normal"&amp;9 MV NORD ATOLL ON HIRE  CERTIFICATE&amp;R&amp;"Palatino Linotype,Normal"&amp;9Page 1 of 3</oddFooter>
-  </headerFooter>
+  <headerFooter differentFirst="1" scaleWithDoc="0" alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -8032,16 +8029,16 @@
   <dimension ref="A1:U47"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="302" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="302" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" style="302" customWidth="1"/>
-    <col min="4" max="4" width="7.109375" style="302" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="302" customWidth="1"/>
-    <col min="6" max="6" width="9" style="302" customWidth="1"/>
-    <col min="7" max="7" width="7" style="302" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" style="302" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" style="302" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" style="302" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" style="264" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="264" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="264" customWidth="1"/>
+    <col min="4" max="4" width="7.109375" style="264" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" style="264" customWidth="1"/>
+    <col min="6" max="6" width="9" style="264" customWidth="1"/>
+    <col min="7" max="7" width="7" style="264" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" style="264" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" style="264" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" style="264" customWidth="1"/>
     <col min="11" max="11" width="3.88671875" style="48" customWidth="1"/>
     <col min="12" max="13" width="12.109375" style="48" bestFit="1" customWidth="1"/>
     <col min="14" max="16" width="9.109375" style="48" customWidth="1"/>
@@ -9058,22 +9055,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="I1" s="303" t="s">
+      <c r="I1" s="265" t="s">
         <v>629</v>
       </c>
-      <c r="J1" s="304">
+      <c r="J1" s="266">
         <f>+'Data from DB'!B3</f>
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="21.6" customHeight="1">
-      <c r="C2" s="305"/>
-      <c r="D2" s="305"/>
-      <c r="E2" s="305"/>
-      <c r="F2" s="305"/>
-      <c r="G2" s="305"/>
-      <c r="H2" s="305"/>
-      <c r="I2" s="305"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
     </row>
     <row r="3" spans="1:21" ht="39" customHeight="1">
       <c r="F3" s="102"/>
@@ -9090,16 +9087,16 @@
       <c r="U3" s="51"/>
     </row>
     <row r="4" spans="1:21" ht="13.5" customHeight="1">
-      <c r="A4" s="306"/>
-      <c r="B4" s="306"/>
-      <c r="C4" s="306"/>
-      <c r="D4" s="306"/>
-      <c r="E4" s="306"/>
-      <c r="F4" s="306"/>
-      <c r="G4" s="306"/>
-      <c r="H4" s="306"/>
-      <c r="I4" s="306"/>
-      <c r="J4" s="306"/>
+      <c r="A4" s="372"/>
+      <c r="B4" s="372"/>
+      <c r="C4" s="372"/>
+      <c r="D4" s="372"/>
+      <c r="E4" s="372"/>
+      <c r="F4" s="372"/>
+      <c r="G4" s="372"/>
+      <c r="H4" s="372"/>
+      <c r="I4" s="372"/>
+      <c r="J4" s="372"/>
       <c r="L4" s="49"/>
       <c r="N4" s="52"/>
       <c r="O4" s="52"/>
@@ -9120,29 +9117,29 @@
       <c r="U5" s="55"/>
     </row>
     <row r="6" spans="1:21" ht="13.5" customHeight="1" thickBot="1">
-      <c r="C6" s="307" t="s">
+      <c r="C6" s="267" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="308" t="s">
+      <c r="D6" s="268" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="309">
+      <c r="E6" s="269">
         <f>+'Data from DB'!B26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="308" t="s">
+      <c r="F6" s="268" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="309">
+      <c r="G6" s="269">
         <f>+'Data from DB'!B27</f>
         <v>0</v>
       </c>
-      <c r="H6" s="308"/>
-      <c r="I6" s="310" t="str">
+      <c r="H6" s="268"/>
+      <c r="I6" s="270" t="str">
         <f>"TRIM=" &amp;  G6-E6</f>
         <v>TRIM=0</v>
       </c>
-      <c r="J6" s="311" t="s">
+      <c r="J6" s="271" t="s">
         <v>28</v>
       </c>
       <c r="T6" s="51"/>
@@ -9157,20 +9154,20 @@
         <v>39</v>
       </c>
       <c r="O7" s="61"/>
-      <c r="P7" s="276">
+      <c r="P7" s="367">
         <f>N10/P9</f>
         <v>2.9000000000000002E-3</v>
       </c>
-      <c r="Q7" s="276"/>
+      <c r="Q7" s="367"/>
     </row>
     <row r="8" spans="1:21" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A8" s="312" t="s">
+      <c r="A8" s="272" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="312"/>
-      <c r="C8" s="312"/>
-      <c r="D8" s="313"/>
-      <c r="E8" s="313"/>
+      <c r="B8" s="272"/>
+      <c r="C8" s="272"/>
+      <c r="D8" s="273"/>
+      <c r="E8" s="273"/>
       <c r="L8" s="65"/>
       <c r="M8" s="66">
         <v>1</v>
@@ -9181,34 +9178,34 @@
       <c r="O8" s="67">
         <v>1.5</v>
       </c>
-      <c r="P8" s="272" t="s">
+      <c r="P8" s="368" t="s">
         <v>46</v>
       </c>
-      <c r="Q8" s="273"/>
+      <c r="Q8" s="369"/>
     </row>
     <row r="9" spans="1:21" ht="13.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A9" s="56"/>
-      <c r="B9" s="314" t="s">
+      <c r="B9" s="274" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="315"/>
-      <c r="D9" s="316" t="s">
+      <c r="C9" s="275"/>
+      <c r="D9" s="276" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="315" t="s">
+      <c r="E9" s="275" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="314" t="s">
+      <c r="F9" s="274" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="317" t="s">
+      <c r="G9" s="277" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="315"/>
-      <c r="I9" s="316" t="s">
+      <c r="H9" s="275"/>
+      <c r="I9" s="276" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="318" t="s">
+      <c r="J9" s="278" t="s">
         <v>37</v>
       </c>
       <c r="K9" s="57"/>
@@ -9222,36 +9219,36 @@
       <c r="O9" s="71">
         <v>2.6</v>
       </c>
-      <c r="P9" s="274">
+      <c r="P9" s="370">
         <v>1000</v>
       </c>
-      <c r="Q9" s="275"/>
+      <c r="Q9" s="371"/>
     </row>
     <row r="10" spans="1:21" ht="13.5" customHeight="1" thickBot="1">
       <c r="A10" s="64"/>
-      <c r="B10" s="319" t="s">
+      <c r="B10" s="279" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="320"/>
-      <c r="D10" s="321" t="s">
+      <c r="C10" s="280"/>
+      <c r="D10" s="281" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="320" t="s">
+      <c r="E10" s="280" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="319" t="s">
+      <c r="F10" s="279" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="322" t="s">
+      <c r="G10" s="282" t="s">
         <v>43</v>
       </c>
-      <c r="H10" s="321" t="s">
+      <c r="H10" s="281" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="321" t="s">
+      <c r="I10" s="281" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="323" t="s">
+      <c r="J10" s="283" t="s">
         <v>19</v>
       </c>
       <c r="L10" s="68">
@@ -9278,37 +9275,37 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="13.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="324">
+      <c r="A11" s="284">
         <f>+'Data from DB'!B81</f>
         <v>0</v>
       </c>
-      <c r="B11" s="325"/>
-      <c r="C11" s="326"/>
-      <c r="D11" s="327">
+      <c r="B11" s="285"/>
+      <c r="C11" s="286"/>
+      <c r="D11" s="287">
         <f>+'Data from DB'!B82</f>
         <v>0</v>
       </c>
-      <c r="E11" s="327">
+      <c r="E11" s="287">
         <f>+'Data from DB'!B83</f>
         <v>0</v>
       </c>
-      <c r="F11" s="328">
+      <c r="F11" s="288">
         <f>+'Data from DB'!B84</f>
         <v>0</v>
       </c>
-      <c r="G11" s="329">
+      <c r="G11" s="289">
         <f>+'Data from DB'!B85</f>
         <v>0</v>
       </c>
-      <c r="H11" s="330">
+      <c r="H11" s="290">
         <f>+'Data from DB'!B86</f>
         <v>0</v>
       </c>
-      <c r="I11" s="331">
+      <c r="I11" s="291">
         <f>+'Data from DB'!B87</f>
         <v>0</v>
       </c>
-      <c r="J11" s="332">
+      <c r="J11" s="292">
         <f>+'Data from DB'!B88</f>
         <v>0</v>
       </c>
@@ -9331,37 +9328,37 @@
       </c>
     </row>
     <row r="12" spans="1:21" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A12" s="324">
+      <c r="A12" s="284">
         <f>+'Data from DB'!B89</f>
         <v>0</v>
       </c>
-      <c r="B12" s="325"/>
-      <c r="C12" s="326"/>
-      <c r="D12" s="333">
+      <c r="B12" s="285"/>
+      <c r="C12" s="286"/>
+      <c r="D12" s="293">
         <f>+'Data from DB'!B90</f>
         <v>0</v>
       </c>
-      <c r="E12" s="333">
+      <c r="E12" s="293">
         <f>+'Data from DB'!B91</f>
         <v>0</v>
       </c>
-      <c r="F12" s="328">
+      <c r="F12" s="288">
         <f>+'Data from DB'!B92</f>
         <v>0</v>
       </c>
-      <c r="G12" s="329">
+      <c r="G12" s="289">
         <f>+'Data from DB'!B93</f>
         <v>0</v>
       </c>
-      <c r="H12" s="330">
+      <c r="H12" s="290">
         <f>+'Data from DB'!B94</f>
         <v>0</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="294">
         <f>+'Data from DB'!B95</f>
         <v>0</v>
       </c>
-      <c r="J12" s="335">
+      <c r="J12" s="295">
         <f>+'Data from DB'!B96</f>
         <v>0</v>
       </c>
@@ -9373,37 +9370,37 @@
       <c r="Q12" s="81"/>
     </row>
     <row r="13" spans="1:21" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A13" s="324">
+      <c r="A13" s="284">
         <f>+'Data from DB'!B97</f>
         <v>0</v>
       </c>
-      <c r="B13" s="325"/>
-      <c r="C13" s="326"/>
-      <c r="D13" s="333">
+      <c r="B13" s="285"/>
+      <c r="C13" s="286"/>
+      <c r="D13" s="293">
         <f>+'Data from DB'!B98</f>
         <v>0</v>
       </c>
-      <c r="E13" s="333">
+      <c r="E13" s="293">
         <f>+'Data from DB'!B99</f>
         <v>0</v>
       </c>
-      <c r="F13" s="336">
+      <c r="F13" s="296">
         <f>+'Data from DB'!B100</f>
         <v>0</v>
       </c>
-      <c r="G13" s="329">
+      <c r="G13" s="289">
         <f>+'Data from DB'!B101</f>
         <v>0</v>
       </c>
-      <c r="H13" s="330">
+      <c r="H13" s="290">
         <f>+'Data from DB'!B102</f>
         <v>0</v>
       </c>
-      <c r="I13" s="334">
+      <c r="I13" s="294">
         <f>+'Data from DB'!B103</f>
         <v>0</v>
       </c>
-      <c r="J13" s="335">
+      <c r="J13" s="295">
         <f>+'Data from DB'!B104</f>
         <v>0</v>
       </c>
@@ -9415,44 +9412,44 @@
         <v>50</v>
       </c>
       <c r="O13" s="61"/>
-      <c r="P13" s="276">
+      <c r="P13" s="367">
         <f>N16/P15</f>
         <v>5.8614199999999998E-2</v>
       </c>
-      <c r="Q13" s="276"/>
+      <c r="Q13" s="367"/>
     </row>
     <row r="14" spans="1:21" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A14" s="324">
+      <c r="A14" s="284">
         <f>+'Data from DB'!B105</f>
         <v>0</v>
       </c>
-      <c r="B14" s="325"/>
-      <c r="C14" s="326"/>
-      <c r="D14" s="333">
+      <c r="B14" s="285"/>
+      <c r="C14" s="286"/>
+      <c r="D14" s="293">
         <f>+'Data from DB'!B106</f>
         <v>0</v>
       </c>
-      <c r="E14" s="333">
+      <c r="E14" s="293">
         <f>+'Data from DB'!B107</f>
         <v>0</v>
       </c>
-      <c r="F14" s="336">
+      <c r="F14" s="296">
         <f>+'Data from DB'!B108</f>
         <v>0</v>
       </c>
-      <c r="G14" s="329">
+      <c r="G14" s="289">
         <f>+'Data from DB'!B109</f>
         <v>0</v>
       </c>
-      <c r="H14" s="330">
+      <c r="H14" s="290">
         <f>+'Data from DB'!B110</f>
         <v>0</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="294">
         <f>+'Data from DB'!B111</f>
         <v>0</v>
       </c>
-      <c r="J14" s="335">
+      <c r="J14" s="295">
         <f>+'Data from DB'!B112</f>
         <v>0</v>
       </c>
@@ -9467,43 +9464,43 @@
       <c r="O14" s="67">
         <v>3</v>
       </c>
-      <c r="P14" s="272" t="s">
+      <c r="P14" s="368" t="s">
         <v>46</v>
       </c>
-      <c r="Q14" s="273"/>
+      <c r="Q14" s="369"/>
     </row>
     <row r="15" spans="1:21" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A15" s="324">
+      <c r="A15" s="284">
         <f>+'Data from DB'!B113</f>
         <v>0</v>
       </c>
-      <c r="B15" s="325"/>
-      <c r="C15" s="326"/>
-      <c r="D15" s="324" t="e">
+      <c r="B15" s="285"/>
+      <c r="C15" s="286"/>
+      <c r="D15" s="284" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E15" s="324" t="e">
+      <c r="E15" s="284" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F15" s="324" t="e">
+      <c r="F15" s="284" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="G15" s="324" t="e">
+      <c r="G15" s="284" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H15" s="324" t="e">
+      <c r="H15" s="284" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="I15" s="324" t="e">
+      <c r="I15" s="284" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J15" s="324" t="e">
+      <c r="J15" s="284" t="e">
         <f>+'Data from DB'!#REF!</f>
         <v>#REF!</v>
       </c>
@@ -9517,43 +9514,43 @@
       <c r="O15" s="71">
         <v>5.1660000000000004</v>
       </c>
-      <c r="P15" s="274">
+      <c r="P15" s="370">
         <v>100</v>
       </c>
-      <c r="Q15" s="275"/>
+      <c r="Q15" s="371"/>
     </row>
     <row r="16" spans="1:21" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A16" s="324">
+      <c r="A16" s="284">
         <f>+'Data from DB'!B121</f>
         <v>0</v>
       </c>
-      <c r="B16" s="325"/>
-      <c r="C16" s="326"/>
-      <c r="D16" s="333">
+      <c r="B16" s="285"/>
+      <c r="C16" s="286"/>
+      <c r="D16" s="293">
         <f>+'Data from DB'!B122</f>
         <v>0</v>
       </c>
-      <c r="E16" s="333">
+      <c r="E16" s="293">
         <f>+'Data from DB'!B123</f>
         <v>0</v>
       </c>
-      <c r="F16" s="336">
+      <c r="F16" s="296">
         <f>+'Data from DB'!B124</f>
         <v>0</v>
       </c>
-      <c r="G16" s="329">
+      <c r="G16" s="289">
         <f>+'Data from DB'!B125</f>
         <v>0</v>
       </c>
-      <c r="H16" s="330">
+      <c r="H16" s="290">
         <f>+'Data from DB'!B126</f>
         <v>0</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="294">
         <f>+'Data from DB'!B127</f>
         <v>0</v>
       </c>
-      <c r="J16" s="335">
+      <c r="J16" s="295">
         <f>+'Data from DB'!B128</f>
         <v>0</v>
       </c>
@@ -9581,37 +9578,37 @@
       </c>
     </row>
     <row r="17" spans="1:17" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A17" s="324">
+      <c r="A17" s="284">
         <f>+'Data from DB'!B129</f>
         <v>0</v>
       </c>
-      <c r="B17" s="325"/>
-      <c r="C17" s="326"/>
-      <c r="D17" s="333">
+      <c r="B17" s="285"/>
+      <c r="C17" s="286"/>
+      <c r="D17" s="293">
         <f>+'Data from DB'!B130</f>
         <v>0</v>
       </c>
-      <c r="E17" s="333">
+      <c r="E17" s="293">
         <f>+'Data from DB'!B131</f>
         <v>0</v>
       </c>
-      <c r="F17" s="336">
+      <c r="F17" s="296">
         <f>+'Data from DB'!B132</f>
         <v>0</v>
       </c>
-      <c r="G17" s="329">
+      <c r="G17" s="289">
         <f>+'Data from DB'!B133</f>
         <v>0</v>
       </c>
-      <c r="H17" s="330">
+      <c r="H17" s="290">
         <f>+'Data from DB'!B134</f>
         <v>0</v>
       </c>
-      <c r="I17" s="334">
+      <c r="I17" s="294">
         <f>+'Data from DB'!B135</f>
         <v>0</v>
       </c>
-      <c r="J17" s="335">
+      <c r="J17" s="295">
         <f>+'Data from DB'!B136</f>
         <v>0</v>
       </c>
@@ -9634,73 +9631,73 @@
       </c>
     </row>
     <row r="18" spans="1:17" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A18" s="324">
+      <c r="A18" s="284">
         <f>+'Data from DB'!B137</f>
         <v>0</v>
       </c>
-      <c r="B18" s="325"/>
-      <c r="C18" s="326"/>
-      <c r="D18" s="333">
+      <c r="B18" s="285"/>
+      <c r="C18" s="286"/>
+      <c r="D18" s="293">
         <f>+'Data from DB'!B138</f>
         <v>0</v>
       </c>
-      <c r="E18" s="333">
+      <c r="E18" s="293">
         <f>+'Data from DB'!B139</f>
         <v>0</v>
       </c>
-      <c r="F18" s="336">
+      <c r="F18" s="296">
         <f>+'Data from DB'!B140</f>
         <v>0</v>
       </c>
-      <c r="G18" s="329">
+      <c r="G18" s="289">
         <f>+'Data from DB'!B141</f>
         <v>0</v>
       </c>
-      <c r="H18" s="330">
+      <c r="H18" s="290">
         <f>+'Data from DB'!B142</f>
         <v>0</v>
       </c>
-      <c r="I18" s="334">
+      <c r="I18" s="294">
         <f>+'Data from DB'!B143</f>
         <v>0</v>
       </c>
-      <c r="J18" s="335">
+      <c r="J18" s="295">
         <f>+'Data from DB'!B144</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="13.5" customHeight="1">
-      <c r="A19" s="324">
+      <c r="A19" s="284">
         <f>+'Data from DB'!B145</f>
         <v>0</v>
       </c>
-      <c r="B19" s="325"/>
-      <c r="C19" s="326"/>
-      <c r="D19" s="333">
+      <c r="B19" s="285"/>
+      <c r="C19" s="286"/>
+      <c r="D19" s="293">
         <f>+'Data from DB'!B146</f>
         <v>0</v>
       </c>
-      <c r="E19" s="333">
+      <c r="E19" s="293">
         <f>+'Data from DB'!B147</f>
         <v>0</v>
       </c>
-      <c r="F19" s="333">
+      <c r="F19" s="293">
         <f>+'Data from DB'!B148</f>
         <v>0</v>
       </c>
-      <c r="G19" s="329">
+      <c r="G19" s="289">
         <f>+'Data from DB'!B149</f>
         <v>0</v>
       </c>
-      <c r="H19" s="330">
+      <c r="H19" s="290">
         <f>+'Data from DB'!B150</f>
         <v>0</v>
       </c>
-      <c r="I19" s="334">
+      <c r="I19" s="294">
         <f>+'Data from DB'!B151</f>
         <v>0</v>
       </c>
-      <c r="J19" s="335">
+      <c r="J19" s="295">
         <f>+'Data from DB'!B152</f>
         <v>0</v>
       </c>
@@ -9714,37 +9711,37 @@
       <c r="O19" s="87"/>
     </row>
     <row r="20" spans="1:17" ht="13.5" customHeight="1">
-      <c r="A20" s="324">
+      <c r="A20" s="284">
         <f>+'Data from DB'!B153</f>
         <v>0</v>
       </c>
-      <c r="B20" s="325"/>
-      <c r="C20" s="326"/>
-      <c r="D20" s="333">
+      <c r="B20" s="285"/>
+      <c r="C20" s="286"/>
+      <c r="D20" s="293">
         <f>+'Data from DB'!B154</f>
         <v>0</v>
       </c>
-      <c r="E20" s="333">
+      <c r="E20" s="293">
         <f>+'Data from DB'!B155</f>
         <v>0</v>
       </c>
-      <c r="F20" s="333">
+      <c r="F20" s="293">
         <f>+'Data from DB'!B156</f>
         <v>0</v>
       </c>
-      <c r="G20" s="329">
+      <c r="G20" s="289">
         <f>+'Data from DB'!B157</f>
         <v>0</v>
       </c>
-      <c r="H20" s="330">
+      <c r="H20" s="290">
         <f>+'Data from DB'!B158</f>
         <v>0</v>
       </c>
-      <c r="I20" s="334">
+      <c r="I20" s="294">
         <f>+'Data from DB'!B159</f>
         <v>0</v>
       </c>
-      <c r="J20" s="335">
+      <c r="J20" s="295">
         <f>+'Data from DB'!B160</f>
         <v>0</v>
       </c>
@@ -9762,37 +9759,37 @@
       <c r="Q20"/>
     </row>
     <row r="21" spans="1:17" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A21" s="337">
+      <c r="A21" s="297">
         <f>+'Data from DB'!B161</f>
         <v>0</v>
       </c>
-      <c r="B21" s="338"/>
-      <c r="C21" s="339"/>
-      <c r="D21" s="340">
+      <c r="B21" s="298"/>
+      <c r="C21" s="299"/>
+      <c r="D21" s="300">
         <f>+'Data from DB'!B162</f>
         <v>0</v>
       </c>
-      <c r="E21" s="340">
+      <c r="E21" s="300">
         <f>+'Data from DB'!B163</f>
         <v>0</v>
       </c>
-      <c r="F21" s="341">
+      <c r="F21" s="301">
         <f>+'Data from DB'!B164</f>
         <v>0</v>
       </c>
-      <c r="G21" s="342">
+      <c r="G21" s="302">
         <f>+'Data from DB'!B165</f>
         <v>0</v>
       </c>
-      <c r="H21" s="343">
+      <c r="H21" s="303">
         <f>+'Data from DB'!B166</f>
         <v>0</v>
       </c>
-      <c r="I21" s="344">
+      <c r="I21" s="304">
         <f>+'Data from DB'!B167</f>
         <v>0</v>
       </c>
-      <c r="J21" s="345">
+      <c r="J21" s="305">
         <f>+'Data from DB'!B168</f>
         <v>0</v>
       </c>
@@ -9814,16 +9811,16 @@
         <v>51</v>
       </c>
       <c r="B22" s="83"/>
-      <c r="C22" s="346" t="e">
+      <c r="C22" s="306" t="e">
         <f>+J22&amp;" MT "</f>
         <v>#REF!</v>
       </c>
-      <c r="D22" s="347"/>
+      <c r="D22" s="307"/>
       <c r="E22" s="103"/>
       <c r="I22" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="J22" s="348" t="e">
+      <c r="J22" s="308" t="e">
         <f>SUM(J11:J21)</f>
         <v>#REF!</v>
       </c>
@@ -9869,21 +9866,21 @@
         <v>39</v>
       </c>
       <c r="O25" s="61"/>
-      <c r="P25" s="276">
+      <c r="P25" s="367">
         <f>N28/P27</f>
         <v>2.1454865E-2</v>
       </c>
-      <c r="Q25" s="276"/>
+      <c r="Q25" s="367"/>
     </row>
     <row r="26" spans="1:17" ht="13.5" customHeight="1" thickBot="1">
       <c r="A26" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="349"/>
-      <c r="C26" s="349"/>
-      <c r="D26" s="349"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="B26" s="309"/>
+      <c r="C26" s="309"/>
+      <c r="D26" s="309"/>
+      <c r="E26" s="309"/>
+      <c r="F26" s="309"/>
       <c r="L26" s="230"/>
       <c r="M26" s="66">
         <f>M8</f>
@@ -9897,34 +9894,34 @@
         <f>O8</f>
         <v>1.5</v>
       </c>
-      <c r="P26" s="272" t="s">
+      <c r="P26" s="368" t="s">
         <v>46</v>
       </c>
-      <c r="Q26" s="273"/>
+      <c r="Q26" s="369"/>
     </row>
     <row r="27" spans="1:17" ht="13.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A27" s="56"/>
-      <c r="B27" s="314" t="s">
+      <c r="B27" s="274" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="315"/>
-      <c r="D27" s="316" t="s">
+      <c r="C27" s="275"/>
+      <c r="D27" s="276" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="315" t="s">
+      <c r="E27" s="275" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="314" t="s">
+      <c r="F27" s="274" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="317" t="s">
+      <c r="G27" s="277" t="s">
         <v>54</v>
       </c>
-      <c r="H27" s="315"/>
-      <c r="I27" s="316" t="s">
+      <c r="H27" s="275"/>
+      <c r="I27" s="276" t="s">
         <v>36</v>
       </c>
-      <c r="J27" s="318" t="s">
+      <c r="J27" s="278" t="s">
         <v>37</v>
       </c>
       <c r="L27" s="68">
@@ -9937,36 +9934,36 @@
       <c r="O27" s="71">
         <v>19.54</v>
       </c>
-      <c r="P27" s="274">
+      <c r="P27" s="370">
         <v>1000</v>
       </c>
-      <c r="Q27" s="275"/>
+      <c r="Q27" s="371"/>
     </row>
     <row r="28" spans="1:17" ht="13.5" customHeight="1" thickBot="1">
       <c r="A28" s="64"/>
-      <c r="B28" s="319" t="s">
+      <c r="B28" s="279" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="320"/>
-      <c r="D28" s="321" t="s">
+      <c r="C28" s="280"/>
+      <c r="D28" s="281" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="320" t="s">
+      <c r="E28" s="280" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="319" t="s">
+      <c r="F28" s="279" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="322" t="s">
+      <c r="G28" s="282" t="s">
         <v>43</v>
       </c>
-      <c r="H28" s="320" t="s">
+      <c r="H28" s="280" t="s">
         <v>44</v>
       </c>
-      <c r="I28" s="321" t="s">
+      <c r="I28" s="281" t="s">
         <v>55</v>
       </c>
-      <c r="J28" s="350" t="s">
+      <c r="J28" s="310" t="s">
         <v>19</v>
       </c>
       <c r="L28" s="68">
@@ -9993,37 +9990,37 @@
       </c>
     </row>
     <row r="29" spans="1:17" ht="13.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A29" s="351">
+      <c r="A29" s="311">
         <f>+'Data from DB'!B241</f>
         <v>0</v>
       </c>
-      <c r="B29" s="352"/>
-      <c r="C29" s="353"/>
-      <c r="D29" s="354">
+      <c r="B29" s="312"/>
+      <c r="C29" s="313"/>
+      <c r="D29" s="314">
         <f>+'Data from DB'!B242</f>
         <v>0</v>
       </c>
-      <c r="E29" s="327">
+      <c r="E29" s="287">
         <f>+'Data from DB'!B243</f>
         <v>0</v>
       </c>
-      <c r="F29" s="354">
+      <c r="F29" s="314">
         <f>+'Data from DB'!B244</f>
         <v>0</v>
       </c>
-      <c r="G29" s="327">
+      <c r="G29" s="287">
         <f>+'Data from DB'!B245</f>
         <v>0</v>
       </c>
-      <c r="H29" s="330">
+      <c r="H29" s="290">
         <f>+'Data from DB'!B246</f>
         <v>0</v>
       </c>
-      <c r="I29" s="355">
+      <c r="I29" s="315">
         <f>+'Data from DB'!B247</f>
         <v>0</v>
       </c>
-      <c r="J29" s="356">
+      <c r="J29" s="316">
         <f>+'Data from DB'!B248</f>
         <v>0</v>
       </c>
@@ -10046,36 +10043,36 @@
       </c>
     </row>
     <row r="30" spans="1:17" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A30" s="324">
+      <c r="A30" s="284">
         <f>+'Data from DB'!B249</f>
         <v>0</v>
       </c>
-      <c r="B30" s="357"/>
-      <c r="D30" s="329">
+      <c r="B30" s="317"/>
+      <c r="D30" s="289">
         <f>+'Data from DB'!B250</f>
         <v>0</v>
       </c>
-      <c r="E30" s="330">
+      <c r="E30" s="290">
         <f>+'Data from DB'!B251</f>
         <v>0</v>
       </c>
-      <c r="F30" s="329">
+      <c r="F30" s="289">
         <f>+'Data from DB'!B252</f>
         <v>0</v>
       </c>
-      <c r="G30" s="330">
+      <c r="G30" s="290">
         <f>+'Data from DB'!B253</f>
         <v>0</v>
       </c>
-      <c r="H30" s="330">
+      <c r="H30" s="290">
         <f>+'Data from DB'!B254</f>
         <v>0</v>
       </c>
-      <c r="I30" s="331">
+      <c r="I30" s="291">
         <f>+'Data from DB'!B255</f>
         <v>0</v>
       </c>
-      <c r="J30" s="335">
+      <c r="J30" s="295">
         <f>+'Data from DB'!B256</f>
         <v>0</v>
       </c>
@@ -10087,37 +10084,37 @@
       <c r="Q30" s="81"/>
     </row>
     <row r="31" spans="1:17" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A31" s="337">
+      <c r="A31" s="297">
         <f>+'Data from DB'!B257</f>
         <v>0</v>
       </c>
-      <c r="B31" s="358"/>
-      <c r="C31" s="359"/>
-      <c r="D31" s="360">
+      <c r="B31" s="318"/>
+      <c r="C31" s="319"/>
+      <c r="D31" s="320">
         <f>+'Data from DB'!B258</f>
         <v>0</v>
       </c>
-      <c r="E31" s="343">
+      <c r="E31" s="303">
         <f>+'Data from DB'!B259</f>
         <v>0</v>
       </c>
-      <c r="F31" s="342">
+      <c r="F31" s="302">
         <f>+'Data from DB'!B260</f>
         <v>0</v>
       </c>
-      <c r="G31" s="343">
+      <c r="G31" s="303">
         <f>+'Data from DB'!B261</f>
         <v>0</v>
       </c>
-      <c r="H31" s="343">
+      <c r="H31" s="303">
         <f>+'Data from DB'!B262</f>
         <v>0</v>
       </c>
-      <c r="I31" s="361">
+      <c r="I31" s="321">
         <f>+'Data from DB'!B263</f>
         <v>0</v>
       </c>
-      <c r="J31" s="345">
+      <c r="J31" s="305">
         <f>+'Data from DB'!B264</f>
         <v>0</v>
       </c>
@@ -10129,30 +10126,30 @@
         <v>50</v>
       </c>
       <c r="O31" s="61"/>
-      <c r="P31" s="276">
+      <c r="P31" s="367">
         <f>N34/P33</f>
         <v>0.19149999999999998</v>
       </c>
-      <c r="Q31" s="276"/>
+      <c r="Q31" s="367"/>
     </row>
     <row r="32" spans="1:17" ht="13.5" customHeight="1" thickTop="1" thickBot="1">
       <c r="A32" s="83" t="s">
         <v>56</v>
       </c>
       <c r="B32" s="101"/>
-      <c r="C32" s="362" t="str">
+      <c r="C32" s="322" t="str">
         <f>+J32 &amp;" MT "</f>
         <v xml:space="preserve">0 MT </v>
       </c>
-      <c r="D32" s="363"/>
-      <c r="E32" s="363"/>
-      <c r="F32" s="363"/>
-      <c r="G32" s="364"/>
-      <c r="H32" s="312" t="s">
+      <c r="D32" s="323"/>
+      <c r="E32" s="323"/>
+      <c r="F32" s="323"/>
+      <c r="G32" s="324"/>
+      <c r="H32" s="272" t="s">
         <v>23</v>
       </c>
-      <c r="I32" s="365"/>
-      <c r="J32" s="348">
+      <c r="I32" s="325"/>
+      <c r="J32" s="308">
         <f>SUM(J29:J31)</f>
         <v>0</v>
       </c>
@@ -10167,13 +10164,13 @@
       <c r="O32" s="67">
         <v>1.5</v>
       </c>
-      <c r="P32" s="272" t="s">
+      <c r="P32" s="368" t="s">
         <v>46</v>
       </c>
-      <c r="Q32" s="273"/>
+      <c r="Q32" s="369"/>
     </row>
     <row r="33" spans="1:19" ht="13.5" customHeight="1" thickBot="1">
-      <c r="J33" s="366"/>
+      <c r="J33" s="326"/>
       <c r="L33" s="68">
         <v>6.3</v>
       </c>
@@ -10184,26 +10181,26 @@
       <c r="O33" s="71">
         <v>191.1</v>
       </c>
-      <c r="P33" s="274">
+      <c r="P33" s="370">
         <v>1000</v>
       </c>
-      <c r="Q33" s="275"/>
+      <c r="Q33" s="371"/>
     </row>
     <row r="34" spans="1:19" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A34" s="312" t="s">
+      <c r="A34" s="272" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="312"/>
-      <c r="C34" s="312"/>
-      <c r="D34" s="312"/>
-      <c r="E34" s="348" t="e">
+      <c r="B34" s="272"/>
+      <c r="C34" s="272"/>
+      <c r="D34" s="272"/>
+      <c r="E34" s="308" t="e">
         <f>J22+J32</f>
         <v>#REF!</v>
       </c>
       <c r="F34" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="J34" s="366"/>
+      <c r="J34" s="326"/>
       <c r="L34" s="68">
         <v>6.31</v>
       </c>
@@ -10327,45 +10324,45 @@
       <c r="Q41" s="62"/>
     </row>
     <row r="42" spans="1:19" ht="13.5" customHeight="1">
-      <c r="A42" s="367" t="str">
+      <c r="A42" s="365" t="str">
         <f>CERTIFICATE!A40</f>
         <v>Pabel Peña</v>
       </c>
-      <c r="B42" s="367"/>
-      <c r="C42" s="367"/>
+      <c r="B42" s="365"/>
+      <c r="C42" s="365"/>
       <c r="D42" s="231"/>
-      <c r="E42" s="368">
+      <c r="E42" s="364">
         <f>+'Data from DB'!B472</f>
         <v>0</v>
       </c>
-      <c r="F42" s="368"/>
-      <c r="G42" s="368"/>
-      <c r="H42" s="369"/>
-      <c r="I42" s="368">
+      <c r="F42" s="364"/>
+      <c r="G42" s="364"/>
+      <c r="H42" s="327"/>
+      <c r="I42" s="364">
         <f>CERTIFICATE!H40</f>
         <v>0</v>
       </c>
-      <c r="J42" s="368"/>
+      <c r="J42" s="364"/>
     </row>
     <row r="43" spans="1:19" ht="13.5" customHeight="1">
-      <c r="A43" s="370" t="s">
+      <c r="A43" s="363" t="s">
         <v>24</v>
       </c>
-      <c r="B43" s="370"/>
-      <c r="C43" s="370"/>
-      <c r="D43" s="369"/>
-      <c r="E43" s="370" t="str">
+      <c r="B43" s="363"/>
+      <c r="C43" s="363"/>
+      <c r="D43" s="327"/>
+      <c r="E43" s="363" t="str">
         <f xml:space="preserve"> +" C. Engineer "  &amp; + CERTIFICATE!C3</f>
         <v xml:space="preserve"> C. Engineer 0</v>
       </c>
-      <c r="F43" s="370"/>
-      <c r="G43" s="370"/>
-      <c r="H43" s="369"/>
-      <c r="I43" s="370" t="str">
+      <c r="F43" s="363"/>
+      <c r="G43" s="363"/>
+      <c r="H43" s="327"/>
+      <c r="I43" s="363" t="str">
         <f xml:space="preserve"> +" Master  "  &amp; + CERTIFICATE!C3</f>
         <v xml:space="preserve"> Master  0</v>
       </c>
-      <c r="J43" s="370"/>
+      <c r="J43" s="363"/>
     </row>
     <row r="44" spans="1:19" ht="13.5" customHeight="1"/>
     <row r="45" spans="1:19" ht="13.5" customHeight="1">
@@ -10388,17 +10385,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="C2:I2"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="A4:J4"/>
     <mergeCell ref="P14:Q14"/>
     <mergeCell ref="P15:Q15"/>
     <mergeCell ref="P25:Q25"/>
@@ -10408,6 +10394,17 @@
     <mergeCell ref="P31:Q31"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <phoneticPr fontId="72" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10425,1627 +10422,1681 @@
   <dimension ref="A1:J39"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="10.199999999999999"/>
   <cols>
-    <col min="1" max="2" width="9.5546875" style="371" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" style="371" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" style="371" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" style="371" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" style="371" customWidth="1"/>
-    <col min="7" max="10" width="9.5546875" style="371" customWidth="1"/>
-    <col min="11" max="66" width="9.109375" style="371"/>
-    <col min="67" max="67" width="3.109375" style="371" customWidth="1"/>
-    <col min="68" max="68" width="3.44140625" style="371" customWidth="1"/>
-    <col min="69" max="69" width="7.33203125" style="371" customWidth="1"/>
-    <col min="70" max="70" width="13.5546875" style="371" customWidth="1"/>
-    <col min="71" max="71" width="7.109375" style="371" customWidth="1"/>
-    <col min="72" max="72" width="8.5546875" style="371" customWidth="1"/>
-    <col min="73" max="73" width="9" style="371" customWidth="1"/>
-    <col min="74" max="74" width="5.109375" style="371" customWidth="1"/>
-    <col min="75" max="75" width="8.44140625" style="371" customWidth="1"/>
-    <col min="76" max="76" width="17.109375" style="371" customWidth="1"/>
-    <col min="77" max="77" width="18" style="371" customWidth="1"/>
-    <col min="78" max="78" width="3.88671875" style="371" customWidth="1"/>
-    <col min="79" max="80" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="81" max="83" width="9.109375" style="371"/>
-    <col min="84" max="84" width="11.33203125" style="371" customWidth="1"/>
-    <col min="85" max="322" width="9.109375" style="371"/>
-    <col min="323" max="323" width="3.109375" style="371" customWidth="1"/>
-    <col min="324" max="324" width="3.44140625" style="371" customWidth="1"/>
-    <col min="325" max="325" width="7.33203125" style="371" customWidth="1"/>
-    <col min="326" max="326" width="13.5546875" style="371" customWidth="1"/>
-    <col min="327" max="327" width="7.109375" style="371" customWidth="1"/>
-    <col min="328" max="328" width="8.5546875" style="371" customWidth="1"/>
-    <col min="329" max="329" width="9" style="371" customWidth="1"/>
-    <col min="330" max="330" width="5.109375" style="371" customWidth="1"/>
-    <col min="331" max="331" width="8.44140625" style="371" customWidth="1"/>
-    <col min="332" max="332" width="17.109375" style="371" customWidth="1"/>
-    <col min="333" max="333" width="18" style="371" customWidth="1"/>
-    <col min="334" max="334" width="3.88671875" style="371" customWidth="1"/>
-    <col min="335" max="336" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="337" max="339" width="9.109375" style="371"/>
-    <col min="340" max="340" width="11.33203125" style="371" customWidth="1"/>
-    <col min="341" max="578" width="9.109375" style="371"/>
-    <col min="579" max="579" width="3.109375" style="371" customWidth="1"/>
-    <col min="580" max="580" width="3.44140625" style="371" customWidth="1"/>
-    <col min="581" max="581" width="7.33203125" style="371" customWidth="1"/>
-    <col min="582" max="582" width="13.5546875" style="371" customWidth="1"/>
-    <col min="583" max="583" width="7.109375" style="371" customWidth="1"/>
-    <col min="584" max="584" width="8.5546875" style="371" customWidth="1"/>
-    <col min="585" max="585" width="9" style="371" customWidth="1"/>
-    <col min="586" max="586" width="5.109375" style="371" customWidth="1"/>
-    <col min="587" max="587" width="8.44140625" style="371" customWidth="1"/>
-    <col min="588" max="588" width="17.109375" style="371" customWidth="1"/>
-    <col min="589" max="589" width="18" style="371" customWidth="1"/>
-    <col min="590" max="590" width="3.88671875" style="371" customWidth="1"/>
-    <col min="591" max="592" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="593" max="595" width="9.109375" style="371"/>
-    <col min="596" max="596" width="11.33203125" style="371" customWidth="1"/>
-    <col min="597" max="834" width="9.109375" style="371"/>
-    <col min="835" max="835" width="3.109375" style="371" customWidth="1"/>
-    <col min="836" max="836" width="3.44140625" style="371" customWidth="1"/>
-    <col min="837" max="837" width="7.33203125" style="371" customWidth="1"/>
-    <col min="838" max="838" width="13.5546875" style="371" customWidth="1"/>
-    <col min="839" max="839" width="7.109375" style="371" customWidth="1"/>
-    <col min="840" max="840" width="8.5546875" style="371" customWidth="1"/>
-    <col min="841" max="841" width="9" style="371" customWidth="1"/>
-    <col min="842" max="842" width="5.109375" style="371" customWidth="1"/>
-    <col min="843" max="843" width="8.44140625" style="371" customWidth="1"/>
-    <col min="844" max="844" width="17.109375" style="371" customWidth="1"/>
-    <col min="845" max="845" width="18" style="371" customWidth="1"/>
-    <col min="846" max="846" width="3.88671875" style="371" customWidth="1"/>
-    <col min="847" max="848" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="849" max="851" width="9.109375" style="371"/>
-    <col min="852" max="852" width="11.33203125" style="371" customWidth="1"/>
-    <col min="853" max="1090" width="9.109375" style="371"/>
-    <col min="1091" max="1091" width="3.109375" style="371" customWidth="1"/>
-    <col min="1092" max="1092" width="3.44140625" style="371" customWidth="1"/>
-    <col min="1093" max="1093" width="7.33203125" style="371" customWidth="1"/>
-    <col min="1094" max="1094" width="13.5546875" style="371" customWidth="1"/>
-    <col min="1095" max="1095" width="7.109375" style="371" customWidth="1"/>
-    <col min="1096" max="1096" width="8.5546875" style="371" customWidth="1"/>
-    <col min="1097" max="1097" width="9" style="371" customWidth="1"/>
-    <col min="1098" max="1098" width="5.109375" style="371" customWidth="1"/>
-    <col min="1099" max="1099" width="8.44140625" style="371" customWidth="1"/>
-    <col min="1100" max="1100" width="17.109375" style="371" customWidth="1"/>
-    <col min="1101" max="1101" width="18" style="371" customWidth="1"/>
-    <col min="1102" max="1102" width="3.88671875" style="371" customWidth="1"/>
-    <col min="1103" max="1104" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="1105" max="1107" width="9.109375" style="371"/>
-    <col min="1108" max="1108" width="11.33203125" style="371" customWidth="1"/>
-    <col min="1109" max="1346" width="9.109375" style="371"/>
-    <col min="1347" max="1347" width="3.109375" style="371" customWidth="1"/>
-    <col min="1348" max="1348" width="3.44140625" style="371" customWidth="1"/>
-    <col min="1349" max="1349" width="7.33203125" style="371" customWidth="1"/>
-    <col min="1350" max="1350" width="13.5546875" style="371" customWidth="1"/>
-    <col min="1351" max="1351" width="7.109375" style="371" customWidth="1"/>
-    <col min="1352" max="1352" width="8.5546875" style="371" customWidth="1"/>
-    <col min="1353" max="1353" width="9" style="371" customWidth="1"/>
-    <col min="1354" max="1354" width="5.109375" style="371" customWidth="1"/>
-    <col min="1355" max="1355" width="8.44140625" style="371" customWidth="1"/>
-    <col min="1356" max="1356" width="17.109375" style="371" customWidth="1"/>
-    <col min="1357" max="1357" width="18" style="371" customWidth="1"/>
-    <col min="1358" max="1358" width="3.88671875" style="371" customWidth="1"/>
-    <col min="1359" max="1360" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="1361" max="1363" width="9.109375" style="371"/>
-    <col min="1364" max="1364" width="11.33203125" style="371" customWidth="1"/>
-    <col min="1365" max="1602" width="9.109375" style="371"/>
-    <col min="1603" max="1603" width="3.109375" style="371" customWidth="1"/>
-    <col min="1604" max="1604" width="3.44140625" style="371" customWidth="1"/>
-    <col min="1605" max="1605" width="7.33203125" style="371" customWidth="1"/>
-    <col min="1606" max="1606" width="13.5546875" style="371" customWidth="1"/>
-    <col min="1607" max="1607" width="7.109375" style="371" customWidth="1"/>
-    <col min="1608" max="1608" width="8.5546875" style="371" customWidth="1"/>
-    <col min="1609" max="1609" width="9" style="371" customWidth="1"/>
-    <col min="1610" max="1610" width="5.109375" style="371" customWidth="1"/>
-    <col min="1611" max="1611" width="8.44140625" style="371" customWidth="1"/>
-    <col min="1612" max="1612" width="17.109375" style="371" customWidth="1"/>
-    <col min="1613" max="1613" width="18" style="371" customWidth="1"/>
-    <col min="1614" max="1614" width="3.88671875" style="371" customWidth="1"/>
-    <col min="1615" max="1616" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="1617" max="1619" width="9.109375" style="371"/>
-    <col min="1620" max="1620" width="11.33203125" style="371" customWidth="1"/>
-    <col min="1621" max="1858" width="9.109375" style="371"/>
-    <col min="1859" max="1859" width="3.109375" style="371" customWidth="1"/>
-    <col min="1860" max="1860" width="3.44140625" style="371" customWidth="1"/>
-    <col min="1861" max="1861" width="7.33203125" style="371" customWidth="1"/>
-    <col min="1862" max="1862" width="13.5546875" style="371" customWidth="1"/>
-    <col min="1863" max="1863" width="7.109375" style="371" customWidth="1"/>
-    <col min="1864" max="1864" width="8.5546875" style="371" customWidth="1"/>
-    <col min="1865" max="1865" width="9" style="371" customWidth="1"/>
-    <col min="1866" max="1866" width="5.109375" style="371" customWidth="1"/>
-    <col min="1867" max="1867" width="8.44140625" style="371" customWidth="1"/>
-    <col min="1868" max="1868" width="17.109375" style="371" customWidth="1"/>
-    <col min="1869" max="1869" width="18" style="371" customWidth="1"/>
-    <col min="1870" max="1870" width="3.88671875" style="371" customWidth="1"/>
-    <col min="1871" max="1872" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="1873" max="1875" width="9.109375" style="371"/>
-    <col min="1876" max="1876" width="11.33203125" style="371" customWidth="1"/>
-    <col min="1877" max="2114" width="9.109375" style="371"/>
-    <col min="2115" max="2115" width="3.109375" style="371" customWidth="1"/>
-    <col min="2116" max="2116" width="3.44140625" style="371" customWidth="1"/>
-    <col min="2117" max="2117" width="7.33203125" style="371" customWidth="1"/>
-    <col min="2118" max="2118" width="13.5546875" style="371" customWidth="1"/>
-    <col min="2119" max="2119" width="7.109375" style="371" customWidth="1"/>
-    <col min="2120" max="2120" width="8.5546875" style="371" customWidth="1"/>
-    <col min="2121" max="2121" width="9" style="371" customWidth="1"/>
-    <col min="2122" max="2122" width="5.109375" style="371" customWidth="1"/>
-    <col min="2123" max="2123" width="8.44140625" style="371" customWidth="1"/>
-    <col min="2124" max="2124" width="17.109375" style="371" customWidth="1"/>
-    <col min="2125" max="2125" width="18" style="371" customWidth="1"/>
-    <col min="2126" max="2126" width="3.88671875" style="371" customWidth="1"/>
-    <col min="2127" max="2128" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="2129" max="2131" width="9.109375" style="371"/>
-    <col min="2132" max="2132" width="11.33203125" style="371" customWidth="1"/>
-    <col min="2133" max="2370" width="9.109375" style="371"/>
-    <col min="2371" max="2371" width="3.109375" style="371" customWidth="1"/>
-    <col min="2372" max="2372" width="3.44140625" style="371" customWidth="1"/>
-    <col min="2373" max="2373" width="7.33203125" style="371" customWidth="1"/>
-    <col min="2374" max="2374" width="13.5546875" style="371" customWidth="1"/>
-    <col min="2375" max="2375" width="7.109375" style="371" customWidth="1"/>
-    <col min="2376" max="2376" width="8.5546875" style="371" customWidth="1"/>
-    <col min="2377" max="2377" width="9" style="371" customWidth="1"/>
-    <col min="2378" max="2378" width="5.109375" style="371" customWidth="1"/>
-    <col min="2379" max="2379" width="8.44140625" style="371" customWidth="1"/>
-    <col min="2380" max="2380" width="17.109375" style="371" customWidth="1"/>
-    <col min="2381" max="2381" width="18" style="371" customWidth="1"/>
-    <col min="2382" max="2382" width="3.88671875" style="371" customWidth="1"/>
-    <col min="2383" max="2384" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="2385" max="2387" width="9.109375" style="371"/>
-    <col min="2388" max="2388" width="11.33203125" style="371" customWidth="1"/>
-    <col min="2389" max="2626" width="9.109375" style="371"/>
-    <col min="2627" max="2627" width="3.109375" style="371" customWidth="1"/>
-    <col min="2628" max="2628" width="3.44140625" style="371" customWidth="1"/>
-    <col min="2629" max="2629" width="7.33203125" style="371" customWidth="1"/>
-    <col min="2630" max="2630" width="13.5546875" style="371" customWidth="1"/>
-    <col min="2631" max="2631" width="7.109375" style="371" customWidth="1"/>
-    <col min="2632" max="2632" width="8.5546875" style="371" customWidth="1"/>
-    <col min="2633" max="2633" width="9" style="371" customWidth="1"/>
-    <col min="2634" max="2634" width="5.109375" style="371" customWidth="1"/>
-    <col min="2635" max="2635" width="8.44140625" style="371" customWidth="1"/>
-    <col min="2636" max="2636" width="17.109375" style="371" customWidth="1"/>
-    <col min="2637" max="2637" width="18" style="371" customWidth="1"/>
-    <col min="2638" max="2638" width="3.88671875" style="371" customWidth="1"/>
-    <col min="2639" max="2640" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="2641" max="2643" width="9.109375" style="371"/>
-    <col min="2644" max="2644" width="11.33203125" style="371" customWidth="1"/>
-    <col min="2645" max="2882" width="9.109375" style="371"/>
-    <col min="2883" max="2883" width="3.109375" style="371" customWidth="1"/>
-    <col min="2884" max="2884" width="3.44140625" style="371" customWidth="1"/>
-    <col min="2885" max="2885" width="7.33203125" style="371" customWidth="1"/>
-    <col min="2886" max="2886" width="13.5546875" style="371" customWidth="1"/>
-    <col min="2887" max="2887" width="7.109375" style="371" customWidth="1"/>
-    <col min="2888" max="2888" width="8.5546875" style="371" customWidth="1"/>
-    <col min="2889" max="2889" width="9" style="371" customWidth="1"/>
-    <col min="2890" max="2890" width="5.109375" style="371" customWidth="1"/>
-    <col min="2891" max="2891" width="8.44140625" style="371" customWidth="1"/>
-    <col min="2892" max="2892" width="17.109375" style="371" customWidth="1"/>
-    <col min="2893" max="2893" width="18" style="371" customWidth="1"/>
-    <col min="2894" max="2894" width="3.88671875" style="371" customWidth="1"/>
-    <col min="2895" max="2896" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="2897" max="2899" width="9.109375" style="371"/>
-    <col min="2900" max="2900" width="11.33203125" style="371" customWidth="1"/>
-    <col min="2901" max="3138" width="9.109375" style="371"/>
-    <col min="3139" max="3139" width="3.109375" style="371" customWidth="1"/>
-    <col min="3140" max="3140" width="3.44140625" style="371" customWidth="1"/>
-    <col min="3141" max="3141" width="7.33203125" style="371" customWidth="1"/>
-    <col min="3142" max="3142" width="13.5546875" style="371" customWidth="1"/>
-    <col min="3143" max="3143" width="7.109375" style="371" customWidth="1"/>
-    <col min="3144" max="3144" width="8.5546875" style="371" customWidth="1"/>
-    <col min="3145" max="3145" width="9" style="371" customWidth="1"/>
-    <col min="3146" max="3146" width="5.109375" style="371" customWidth="1"/>
-    <col min="3147" max="3147" width="8.44140625" style="371" customWidth="1"/>
-    <col min="3148" max="3148" width="17.109375" style="371" customWidth="1"/>
-    <col min="3149" max="3149" width="18" style="371" customWidth="1"/>
-    <col min="3150" max="3150" width="3.88671875" style="371" customWidth="1"/>
-    <col min="3151" max="3152" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="3153" max="3155" width="9.109375" style="371"/>
-    <col min="3156" max="3156" width="11.33203125" style="371" customWidth="1"/>
-    <col min="3157" max="3394" width="9.109375" style="371"/>
-    <col min="3395" max="3395" width="3.109375" style="371" customWidth="1"/>
-    <col min="3396" max="3396" width="3.44140625" style="371" customWidth="1"/>
-    <col min="3397" max="3397" width="7.33203125" style="371" customWidth="1"/>
-    <col min="3398" max="3398" width="13.5546875" style="371" customWidth="1"/>
-    <col min="3399" max="3399" width="7.109375" style="371" customWidth="1"/>
-    <col min="3400" max="3400" width="8.5546875" style="371" customWidth="1"/>
-    <col min="3401" max="3401" width="9" style="371" customWidth="1"/>
-    <col min="3402" max="3402" width="5.109375" style="371" customWidth="1"/>
-    <col min="3403" max="3403" width="8.44140625" style="371" customWidth="1"/>
-    <col min="3404" max="3404" width="17.109375" style="371" customWidth="1"/>
-    <col min="3405" max="3405" width="18" style="371" customWidth="1"/>
-    <col min="3406" max="3406" width="3.88671875" style="371" customWidth="1"/>
-    <col min="3407" max="3408" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="3409" max="3411" width="9.109375" style="371"/>
-    <col min="3412" max="3412" width="11.33203125" style="371" customWidth="1"/>
-    <col min="3413" max="3650" width="9.109375" style="371"/>
-    <col min="3651" max="3651" width="3.109375" style="371" customWidth="1"/>
-    <col min="3652" max="3652" width="3.44140625" style="371" customWidth="1"/>
-    <col min="3653" max="3653" width="7.33203125" style="371" customWidth="1"/>
-    <col min="3654" max="3654" width="13.5546875" style="371" customWidth="1"/>
-    <col min="3655" max="3655" width="7.109375" style="371" customWidth="1"/>
-    <col min="3656" max="3656" width="8.5546875" style="371" customWidth="1"/>
-    <col min="3657" max="3657" width="9" style="371" customWidth="1"/>
-    <col min="3658" max="3658" width="5.109375" style="371" customWidth="1"/>
-    <col min="3659" max="3659" width="8.44140625" style="371" customWidth="1"/>
-    <col min="3660" max="3660" width="17.109375" style="371" customWidth="1"/>
-    <col min="3661" max="3661" width="18" style="371" customWidth="1"/>
-    <col min="3662" max="3662" width="3.88671875" style="371" customWidth="1"/>
-    <col min="3663" max="3664" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="3665" max="3667" width="9.109375" style="371"/>
-    <col min="3668" max="3668" width="11.33203125" style="371" customWidth="1"/>
-    <col min="3669" max="3906" width="9.109375" style="371"/>
-    <col min="3907" max="3907" width="3.109375" style="371" customWidth="1"/>
-    <col min="3908" max="3908" width="3.44140625" style="371" customWidth="1"/>
-    <col min="3909" max="3909" width="7.33203125" style="371" customWidth="1"/>
-    <col min="3910" max="3910" width="13.5546875" style="371" customWidth="1"/>
-    <col min="3911" max="3911" width="7.109375" style="371" customWidth="1"/>
-    <col min="3912" max="3912" width="8.5546875" style="371" customWidth="1"/>
-    <col min="3913" max="3913" width="9" style="371" customWidth="1"/>
-    <col min="3914" max="3914" width="5.109375" style="371" customWidth="1"/>
-    <col min="3915" max="3915" width="8.44140625" style="371" customWidth="1"/>
-    <col min="3916" max="3916" width="17.109375" style="371" customWidth="1"/>
-    <col min="3917" max="3917" width="18" style="371" customWidth="1"/>
-    <col min="3918" max="3918" width="3.88671875" style="371" customWidth="1"/>
-    <col min="3919" max="3920" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="3921" max="3923" width="9.109375" style="371"/>
-    <col min="3924" max="3924" width="11.33203125" style="371" customWidth="1"/>
-    <col min="3925" max="4162" width="9.109375" style="371"/>
-    <col min="4163" max="4163" width="3.109375" style="371" customWidth="1"/>
-    <col min="4164" max="4164" width="3.44140625" style="371" customWidth="1"/>
-    <col min="4165" max="4165" width="7.33203125" style="371" customWidth="1"/>
-    <col min="4166" max="4166" width="13.5546875" style="371" customWidth="1"/>
-    <col min="4167" max="4167" width="7.109375" style="371" customWidth="1"/>
-    <col min="4168" max="4168" width="8.5546875" style="371" customWidth="1"/>
-    <col min="4169" max="4169" width="9" style="371" customWidth="1"/>
-    <col min="4170" max="4170" width="5.109375" style="371" customWidth="1"/>
-    <col min="4171" max="4171" width="8.44140625" style="371" customWidth="1"/>
-    <col min="4172" max="4172" width="17.109375" style="371" customWidth="1"/>
-    <col min="4173" max="4173" width="18" style="371" customWidth="1"/>
-    <col min="4174" max="4174" width="3.88671875" style="371" customWidth="1"/>
-    <col min="4175" max="4176" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="4177" max="4179" width="9.109375" style="371"/>
-    <col min="4180" max="4180" width="11.33203125" style="371" customWidth="1"/>
-    <col min="4181" max="4418" width="9.109375" style="371"/>
-    <col min="4419" max="4419" width="3.109375" style="371" customWidth="1"/>
-    <col min="4420" max="4420" width="3.44140625" style="371" customWidth="1"/>
-    <col min="4421" max="4421" width="7.33203125" style="371" customWidth="1"/>
-    <col min="4422" max="4422" width="13.5546875" style="371" customWidth="1"/>
-    <col min="4423" max="4423" width="7.109375" style="371" customWidth="1"/>
-    <col min="4424" max="4424" width="8.5546875" style="371" customWidth="1"/>
-    <col min="4425" max="4425" width="9" style="371" customWidth="1"/>
-    <col min="4426" max="4426" width="5.109375" style="371" customWidth="1"/>
-    <col min="4427" max="4427" width="8.44140625" style="371" customWidth="1"/>
-    <col min="4428" max="4428" width="17.109375" style="371" customWidth="1"/>
-    <col min="4429" max="4429" width="18" style="371" customWidth="1"/>
-    <col min="4430" max="4430" width="3.88671875" style="371" customWidth="1"/>
-    <col min="4431" max="4432" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="4433" max="4435" width="9.109375" style="371"/>
-    <col min="4436" max="4436" width="11.33203125" style="371" customWidth="1"/>
-    <col min="4437" max="4674" width="9.109375" style="371"/>
-    <col min="4675" max="4675" width="3.109375" style="371" customWidth="1"/>
-    <col min="4676" max="4676" width="3.44140625" style="371" customWidth="1"/>
-    <col min="4677" max="4677" width="7.33203125" style="371" customWidth="1"/>
-    <col min="4678" max="4678" width="13.5546875" style="371" customWidth="1"/>
-    <col min="4679" max="4679" width="7.109375" style="371" customWidth="1"/>
-    <col min="4680" max="4680" width="8.5546875" style="371" customWidth="1"/>
-    <col min="4681" max="4681" width="9" style="371" customWidth="1"/>
-    <col min="4682" max="4682" width="5.109375" style="371" customWidth="1"/>
-    <col min="4683" max="4683" width="8.44140625" style="371" customWidth="1"/>
-    <col min="4684" max="4684" width="17.109375" style="371" customWidth="1"/>
-    <col min="4685" max="4685" width="18" style="371" customWidth="1"/>
-    <col min="4686" max="4686" width="3.88671875" style="371" customWidth="1"/>
-    <col min="4687" max="4688" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="4689" max="4691" width="9.109375" style="371"/>
-    <col min="4692" max="4692" width="11.33203125" style="371" customWidth="1"/>
-    <col min="4693" max="4930" width="9.109375" style="371"/>
-    <col min="4931" max="4931" width="3.109375" style="371" customWidth="1"/>
-    <col min="4932" max="4932" width="3.44140625" style="371" customWidth="1"/>
-    <col min="4933" max="4933" width="7.33203125" style="371" customWidth="1"/>
-    <col min="4934" max="4934" width="13.5546875" style="371" customWidth="1"/>
-    <col min="4935" max="4935" width="7.109375" style="371" customWidth="1"/>
-    <col min="4936" max="4936" width="8.5546875" style="371" customWidth="1"/>
-    <col min="4937" max="4937" width="9" style="371" customWidth="1"/>
-    <col min="4938" max="4938" width="5.109375" style="371" customWidth="1"/>
-    <col min="4939" max="4939" width="8.44140625" style="371" customWidth="1"/>
-    <col min="4940" max="4940" width="17.109375" style="371" customWidth="1"/>
-    <col min="4941" max="4941" width="18" style="371" customWidth="1"/>
-    <col min="4942" max="4942" width="3.88671875" style="371" customWidth="1"/>
-    <col min="4943" max="4944" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="4945" max="4947" width="9.109375" style="371"/>
-    <col min="4948" max="4948" width="11.33203125" style="371" customWidth="1"/>
-    <col min="4949" max="5186" width="9.109375" style="371"/>
-    <col min="5187" max="5187" width="3.109375" style="371" customWidth="1"/>
-    <col min="5188" max="5188" width="3.44140625" style="371" customWidth="1"/>
-    <col min="5189" max="5189" width="7.33203125" style="371" customWidth="1"/>
-    <col min="5190" max="5190" width="13.5546875" style="371" customWidth="1"/>
-    <col min="5191" max="5191" width="7.109375" style="371" customWidth="1"/>
-    <col min="5192" max="5192" width="8.5546875" style="371" customWidth="1"/>
-    <col min="5193" max="5193" width="9" style="371" customWidth="1"/>
-    <col min="5194" max="5194" width="5.109375" style="371" customWidth="1"/>
-    <col min="5195" max="5195" width="8.44140625" style="371" customWidth="1"/>
-    <col min="5196" max="5196" width="17.109375" style="371" customWidth="1"/>
-    <col min="5197" max="5197" width="18" style="371" customWidth="1"/>
-    <col min="5198" max="5198" width="3.88671875" style="371" customWidth="1"/>
-    <col min="5199" max="5200" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="5201" max="5203" width="9.109375" style="371"/>
-    <col min="5204" max="5204" width="11.33203125" style="371" customWidth="1"/>
-    <col min="5205" max="5442" width="9.109375" style="371"/>
-    <col min="5443" max="5443" width="3.109375" style="371" customWidth="1"/>
-    <col min="5444" max="5444" width="3.44140625" style="371" customWidth="1"/>
-    <col min="5445" max="5445" width="7.33203125" style="371" customWidth="1"/>
-    <col min="5446" max="5446" width="13.5546875" style="371" customWidth="1"/>
-    <col min="5447" max="5447" width="7.109375" style="371" customWidth="1"/>
-    <col min="5448" max="5448" width="8.5546875" style="371" customWidth="1"/>
-    <col min="5449" max="5449" width="9" style="371" customWidth="1"/>
-    <col min="5450" max="5450" width="5.109375" style="371" customWidth="1"/>
-    <col min="5451" max="5451" width="8.44140625" style="371" customWidth="1"/>
-    <col min="5452" max="5452" width="17.109375" style="371" customWidth="1"/>
-    <col min="5453" max="5453" width="18" style="371" customWidth="1"/>
-    <col min="5454" max="5454" width="3.88671875" style="371" customWidth="1"/>
-    <col min="5455" max="5456" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="5457" max="5459" width="9.109375" style="371"/>
-    <col min="5460" max="5460" width="11.33203125" style="371" customWidth="1"/>
-    <col min="5461" max="5698" width="9.109375" style="371"/>
-    <col min="5699" max="5699" width="3.109375" style="371" customWidth="1"/>
-    <col min="5700" max="5700" width="3.44140625" style="371" customWidth="1"/>
-    <col min="5701" max="5701" width="7.33203125" style="371" customWidth="1"/>
-    <col min="5702" max="5702" width="13.5546875" style="371" customWidth="1"/>
-    <col min="5703" max="5703" width="7.109375" style="371" customWidth="1"/>
-    <col min="5704" max="5704" width="8.5546875" style="371" customWidth="1"/>
-    <col min="5705" max="5705" width="9" style="371" customWidth="1"/>
-    <col min="5706" max="5706" width="5.109375" style="371" customWidth="1"/>
-    <col min="5707" max="5707" width="8.44140625" style="371" customWidth="1"/>
-    <col min="5708" max="5708" width="17.109375" style="371" customWidth="1"/>
-    <col min="5709" max="5709" width="18" style="371" customWidth="1"/>
-    <col min="5710" max="5710" width="3.88671875" style="371" customWidth="1"/>
-    <col min="5711" max="5712" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="5713" max="5715" width="9.109375" style="371"/>
-    <col min="5716" max="5716" width="11.33203125" style="371" customWidth="1"/>
-    <col min="5717" max="5954" width="9.109375" style="371"/>
-    <col min="5955" max="5955" width="3.109375" style="371" customWidth="1"/>
-    <col min="5956" max="5956" width="3.44140625" style="371" customWidth="1"/>
-    <col min="5957" max="5957" width="7.33203125" style="371" customWidth="1"/>
-    <col min="5958" max="5958" width="13.5546875" style="371" customWidth="1"/>
-    <col min="5959" max="5959" width="7.109375" style="371" customWidth="1"/>
-    <col min="5960" max="5960" width="8.5546875" style="371" customWidth="1"/>
-    <col min="5961" max="5961" width="9" style="371" customWidth="1"/>
-    <col min="5962" max="5962" width="5.109375" style="371" customWidth="1"/>
-    <col min="5963" max="5963" width="8.44140625" style="371" customWidth="1"/>
-    <col min="5964" max="5964" width="17.109375" style="371" customWidth="1"/>
-    <col min="5965" max="5965" width="18" style="371" customWidth="1"/>
-    <col min="5966" max="5966" width="3.88671875" style="371" customWidth="1"/>
-    <col min="5967" max="5968" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="5969" max="5971" width="9.109375" style="371"/>
-    <col min="5972" max="5972" width="11.33203125" style="371" customWidth="1"/>
-    <col min="5973" max="6210" width="9.109375" style="371"/>
-    <col min="6211" max="6211" width="3.109375" style="371" customWidth="1"/>
-    <col min="6212" max="6212" width="3.44140625" style="371" customWidth="1"/>
-    <col min="6213" max="6213" width="7.33203125" style="371" customWidth="1"/>
-    <col min="6214" max="6214" width="13.5546875" style="371" customWidth="1"/>
-    <col min="6215" max="6215" width="7.109375" style="371" customWidth="1"/>
-    <col min="6216" max="6216" width="8.5546875" style="371" customWidth="1"/>
-    <col min="6217" max="6217" width="9" style="371" customWidth="1"/>
-    <col min="6218" max="6218" width="5.109375" style="371" customWidth="1"/>
-    <col min="6219" max="6219" width="8.44140625" style="371" customWidth="1"/>
-    <col min="6220" max="6220" width="17.109375" style="371" customWidth="1"/>
-    <col min="6221" max="6221" width="18" style="371" customWidth="1"/>
-    <col min="6222" max="6222" width="3.88671875" style="371" customWidth="1"/>
-    <col min="6223" max="6224" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="6225" max="6227" width="9.109375" style="371"/>
-    <col min="6228" max="6228" width="11.33203125" style="371" customWidth="1"/>
-    <col min="6229" max="6466" width="9.109375" style="371"/>
-    <col min="6467" max="6467" width="3.109375" style="371" customWidth="1"/>
-    <col min="6468" max="6468" width="3.44140625" style="371" customWidth="1"/>
-    <col min="6469" max="6469" width="7.33203125" style="371" customWidth="1"/>
-    <col min="6470" max="6470" width="13.5546875" style="371" customWidth="1"/>
-    <col min="6471" max="6471" width="7.109375" style="371" customWidth="1"/>
-    <col min="6472" max="6472" width="8.5546875" style="371" customWidth="1"/>
-    <col min="6473" max="6473" width="9" style="371" customWidth="1"/>
-    <col min="6474" max="6474" width="5.109375" style="371" customWidth="1"/>
-    <col min="6475" max="6475" width="8.44140625" style="371" customWidth="1"/>
-    <col min="6476" max="6476" width="17.109375" style="371" customWidth="1"/>
-    <col min="6477" max="6477" width="18" style="371" customWidth="1"/>
-    <col min="6478" max="6478" width="3.88671875" style="371" customWidth="1"/>
-    <col min="6479" max="6480" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="6481" max="6483" width="9.109375" style="371"/>
-    <col min="6484" max="6484" width="11.33203125" style="371" customWidth="1"/>
-    <col min="6485" max="6722" width="9.109375" style="371"/>
-    <col min="6723" max="6723" width="3.109375" style="371" customWidth="1"/>
-    <col min="6724" max="6724" width="3.44140625" style="371" customWidth="1"/>
-    <col min="6725" max="6725" width="7.33203125" style="371" customWidth="1"/>
-    <col min="6726" max="6726" width="13.5546875" style="371" customWidth="1"/>
-    <col min="6727" max="6727" width="7.109375" style="371" customWidth="1"/>
-    <col min="6728" max="6728" width="8.5546875" style="371" customWidth="1"/>
-    <col min="6729" max="6729" width="9" style="371" customWidth="1"/>
-    <col min="6730" max="6730" width="5.109375" style="371" customWidth="1"/>
-    <col min="6731" max="6731" width="8.44140625" style="371" customWidth="1"/>
-    <col min="6732" max="6732" width="17.109375" style="371" customWidth="1"/>
-    <col min="6733" max="6733" width="18" style="371" customWidth="1"/>
-    <col min="6734" max="6734" width="3.88671875" style="371" customWidth="1"/>
-    <col min="6735" max="6736" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="6737" max="6739" width="9.109375" style="371"/>
-    <col min="6740" max="6740" width="11.33203125" style="371" customWidth="1"/>
-    <col min="6741" max="6978" width="9.109375" style="371"/>
-    <col min="6979" max="6979" width="3.109375" style="371" customWidth="1"/>
-    <col min="6980" max="6980" width="3.44140625" style="371" customWidth="1"/>
-    <col min="6981" max="6981" width="7.33203125" style="371" customWidth="1"/>
-    <col min="6982" max="6982" width="13.5546875" style="371" customWidth="1"/>
-    <col min="6983" max="6983" width="7.109375" style="371" customWidth="1"/>
-    <col min="6984" max="6984" width="8.5546875" style="371" customWidth="1"/>
-    <col min="6985" max="6985" width="9" style="371" customWidth="1"/>
-    <col min="6986" max="6986" width="5.109375" style="371" customWidth="1"/>
-    <col min="6987" max="6987" width="8.44140625" style="371" customWidth="1"/>
-    <col min="6988" max="6988" width="17.109375" style="371" customWidth="1"/>
-    <col min="6989" max="6989" width="18" style="371" customWidth="1"/>
-    <col min="6990" max="6990" width="3.88671875" style="371" customWidth="1"/>
-    <col min="6991" max="6992" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="6993" max="6995" width="9.109375" style="371"/>
-    <col min="6996" max="6996" width="11.33203125" style="371" customWidth="1"/>
-    <col min="6997" max="7234" width="9.109375" style="371"/>
-    <col min="7235" max="7235" width="3.109375" style="371" customWidth="1"/>
-    <col min="7236" max="7236" width="3.44140625" style="371" customWidth="1"/>
-    <col min="7237" max="7237" width="7.33203125" style="371" customWidth="1"/>
-    <col min="7238" max="7238" width="13.5546875" style="371" customWidth="1"/>
-    <col min="7239" max="7239" width="7.109375" style="371" customWidth="1"/>
-    <col min="7240" max="7240" width="8.5546875" style="371" customWidth="1"/>
-    <col min="7241" max="7241" width="9" style="371" customWidth="1"/>
-    <col min="7242" max="7242" width="5.109375" style="371" customWidth="1"/>
-    <col min="7243" max="7243" width="8.44140625" style="371" customWidth="1"/>
-    <col min="7244" max="7244" width="17.109375" style="371" customWidth="1"/>
-    <col min="7245" max="7245" width="18" style="371" customWidth="1"/>
-    <col min="7246" max="7246" width="3.88671875" style="371" customWidth="1"/>
-    <col min="7247" max="7248" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="7249" max="7251" width="9.109375" style="371"/>
-    <col min="7252" max="7252" width="11.33203125" style="371" customWidth="1"/>
-    <col min="7253" max="7490" width="9.109375" style="371"/>
-    <col min="7491" max="7491" width="3.109375" style="371" customWidth="1"/>
-    <col min="7492" max="7492" width="3.44140625" style="371" customWidth="1"/>
-    <col min="7493" max="7493" width="7.33203125" style="371" customWidth="1"/>
-    <col min="7494" max="7494" width="13.5546875" style="371" customWidth="1"/>
-    <col min="7495" max="7495" width="7.109375" style="371" customWidth="1"/>
-    <col min="7496" max="7496" width="8.5546875" style="371" customWidth="1"/>
-    <col min="7497" max="7497" width="9" style="371" customWidth="1"/>
-    <col min="7498" max="7498" width="5.109375" style="371" customWidth="1"/>
-    <col min="7499" max="7499" width="8.44140625" style="371" customWidth="1"/>
-    <col min="7500" max="7500" width="17.109375" style="371" customWidth="1"/>
-    <col min="7501" max="7501" width="18" style="371" customWidth="1"/>
-    <col min="7502" max="7502" width="3.88671875" style="371" customWidth="1"/>
-    <col min="7503" max="7504" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="7505" max="7507" width="9.109375" style="371"/>
-    <col min="7508" max="7508" width="11.33203125" style="371" customWidth="1"/>
-    <col min="7509" max="7746" width="9.109375" style="371"/>
-    <col min="7747" max="7747" width="3.109375" style="371" customWidth="1"/>
-    <col min="7748" max="7748" width="3.44140625" style="371" customWidth="1"/>
-    <col min="7749" max="7749" width="7.33203125" style="371" customWidth="1"/>
-    <col min="7750" max="7750" width="13.5546875" style="371" customWidth="1"/>
-    <col min="7751" max="7751" width="7.109375" style="371" customWidth="1"/>
-    <col min="7752" max="7752" width="8.5546875" style="371" customWidth="1"/>
-    <col min="7753" max="7753" width="9" style="371" customWidth="1"/>
-    <col min="7754" max="7754" width="5.109375" style="371" customWidth="1"/>
-    <col min="7755" max="7755" width="8.44140625" style="371" customWidth="1"/>
-    <col min="7756" max="7756" width="17.109375" style="371" customWidth="1"/>
-    <col min="7757" max="7757" width="18" style="371" customWidth="1"/>
-    <col min="7758" max="7758" width="3.88671875" style="371" customWidth="1"/>
-    <col min="7759" max="7760" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="7761" max="7763" width="9.109375" style="371"/>
-    <col min="7764" max="7764" width="11.33203125" style="371" customWidth="1"/>
-    <col min="7765" max="8002" width="9.109375" style="371"/>
-    <col min="8003" max="8003" width="3.109375" style="371" customWidth="1"/>
-    <col min="8004" max="8004" width="3.44140625" style="371" customWidth="1"/>
-    <col min="8005" max="8005" width="7.33203125" style="371" customWidth="1"/>
-    <col min="8006" max="8006" width="13.5546875" style="371" customWidth="1"/>
-    <col min="8007" max="8007" width="7.109375" style="371" customWidth="1"/>
-    <col min="8008" max="8008" width="8.5546875" style="371" customWidth="1"/>
-    <col min="8009" max="8009" width="9" style="371" customWidth="1"/>
-    <col min="8010" max="8010" width="5.109375" style="371" customWidth="1"/>
-    <col min="8011" max="8011" width="8.44140625" style="371" customWidth="1"/>
-    <col min="8012" max="8012" width="17.109375" style="371" customWidth="1"/>
-    <col min="8013" max="8013" width="18" style="371" customWidth="1"/>
-    <col min="8014" max="8014" width="3.88671875" style="371" customWidth="1"/>
-    <col min="8015" max="8016" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="8017" max="8019" width="9.109375" style="371"/>
-    <col min="8020" max="8020" width="11.33203125" style="371" customWidth="1"/>
-    <col min="8021" max="8258" width="9.109375" style="371"/>
-    <col min="8259" max="8259" width="3.109375" style="371" customWidth="1"/>
-    <col min="8260" max="8260" width="3.44140625" style="371" customWidth="1"/>
-    <col min="8261" max="8261" width="7.33203125" style="371" customWidth="1"/>
-    <col min="8262" max="8262" width="13.5546875" style="371" customWidth="1"/>
-    <col min="8263" max="8263" width="7.109375" style="371" customWidth="1"/>
-    <col min="8264" max="8264" width="8.5546875" style="371" customWidth="1"/>
-    <col min="8265" max="8265" width="9" style="371" customWidth="1"/>
-    <col min="8266" max="8266" width="5.109375" style="371" customWidth="1"/>
-    <col min="8267" max="8267" width="8.44140625" style="371" customWidth="1"/>
-    <col min="8268" max="8268" width="17.109375" style="371" customWidth="1"/>
-    <col min="8269" max="8269" width="18" style="371" customWidth="1"/>
-    <col min="8270" max="8270" width="3.88671875" style="371" customWidth="1"/>
-    <col min="8271" max="8272" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="8273" max="8275" width="9.109375" style="371"/>
-    <col min="8276" max="8276" width="11.33203125" style="371" customWidth="1"/>
-    <col min="8277" max="8514" width="9.109375" style="371"/>
-    <col min="8515" max="8515" width="3.109375" style="371" customWidth="1"/>
-    <col min="8516" max="8516" width="3.44140625" style="371" customWidth="1"/>
-    <col min="8517" max="8517" width="7.33203125" style="371" customWidth="1"/>
-    <col min="8518" max="8518" width="13.5546875" style="371" customWidth="1"/>
-    <col min="8519" max="8519" width="7.109375" style="371" customWidth="1"/>
-    <col min="8520" max="8520" width="8.5546875" style="371" customWidth="1"/>
-    <col min="8521" max="8521" width="9" style="371" customWidth="1"/>
-    <col min="8522" max="8522" width="5.109375" style="371" customWidth="1"/>
-    <col min="8523" max="8523" width="8.44140625" style="371" customWidth="1"/>
-    <col min="8524" max="8524" width="17.109375" style="371" customWidth="1"/>
-    <col min="8525" max="8525" width="18" style="371" customWidth="1"/>
-    <col min="8526" max="8526" width="3.88671875" style="371" customWidth="1"/>
-    <col min="8527" max="8528" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="8529" max="8531" width="9.109375" style="371"/>
-    <col min="8532" max="8532" width="11.33203125" style="371" customWidth="1"/>
-    <col min="8533" max="8770" width="9.109375" style="371"/>
-    <col min="8771" max="8771" width="3.109375" style="371" customWidth="1"/>
-    <col min="8772" max="8772" width="3.44140625" style="371" customWidth="1"/>
-    <col min="8773" max="8773" width="7.33203125" style="371" customWidth="1"/>
-    <col min="8774" max="8774" width="13.5546875" style="371" customWidth="1"/>
-    <col min="8775" max="8775" width="7.109375" style="371" customWidth="1"/>
-    <col min="8776" max="8776" width="8.5546875" style="371" customWidth="1"/>
-    <col min="8777" max="8777" width="9" style="371" customWidth="1"/>
-    <col min="8778" max="8778" width="5.109375" style="371" customWidth="1"/>
-    <col min="8779" max="8779" width="8.44140625" style="371" customWidth="1"/>
-    <col min="8780" max="8780" width="17.109375" style="371" customWidth="1"/>
-    <col min="8781" max="8781" width="18" style="371" customWidth="1"/>
-    <col min="8782" max="8782" width="3.88671875" style="371" customWidth="1"/>
-    <col min="8783" max="8784" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="8785" max="8787" width="9.109375" style="371"/>
-    <col min="8788" max="8788" width="11.33203125" style="371" customWidth="1"/>
-    <col min="8789" max="9026" width="9.109375" style="371"/>
-    <col min="9027" max="9027" width="3.109375" style="371" customWidth="1"/>
-    <col min="9028" max="9028" width="3.44140625" style="371" customWidth="1"/>
-    <col min="9029" max="9029" width="7.33203125" style="371" customWidth="1"/>
-    <col min="9030" max="9030" width="13.5546875" style="371" customWidth="1"/>
-    <col min="9031" max="9031" width="7.109375" style="371" customWidth="1"/>
-    <col min="9032" max="9032" width="8.5546875" style="371" customWidth="1"/>
-    <col min="9033" max="9033" width="9" style="371" customWidth="1"/>
-    <col min="9034" max="9034" width="5.109375" style="371" customWidth="1"/>
-    <col min="9035" max="9035" width="8.44140625" style="371" customWidth="1"/>
-    <col min="9036" max="9036" width="17.109375" style="371" customWidth="1"/>
-    <col min="9037" max="9037" width="18" style="371" customWidth="1"/>
-    <col min="9038" max="9038" width="3.88671875" style="371" customWidth="1"/>
-    <col min="9039" max="9040" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="9041" max="9043" width="9.109375" style="371"/>
-    <col min="9044" max="9044" width="11.33203125" style="371" customWidth="1"/>
-    <col min="9045" max="9282" width="9.109375" style="371"/>
-    <col min="9283" max="9283" width="3.109375" style="371" customWidth="1"/>
-    <col min="9284" max="9284" width="3.44140625" style="371" customWidth="1"/>
-    <col min="9285" max="9285" width="7.33203125" style="371" customWidth="1"/>
-    <col min="9286" max="9286" width="13.5546875" style="371" customWidth="1"/>
-    <col min="9287" max="9287" width="7.109375" style="371" customWidth="1"/>
-    <col min="9288" max="9288" width="8.5546875" style="371" customWidth="1"/>
-    <col min="9289" max="9289" width="9" style="371" customWidth="1"/>
-    <col min="9290" max="9290" width="5.109375" style="371" customWidth="1"/>
-    <col min="9291" max="9291" width="8.44140625" style="371" customWidth="1"/>
-    <col min="9292" max="9292" width="17.109375" style="371" customWidth="1"/>
-    <col min="9293" max="9293" width="18" style="371" customWidth="1"/>
-    <col min="9294" max="9294" width="3.88671875" style="371" customWidth="1"/>
-    <col min="9295" max="9296" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="9297" max="9299" width="9.109375" style="371"/>
-    <col min="9300" max="9300" width="11.33203125" style="371" customWidth="1"/>
-    <col min="9301" max="9538" width="9.109375" style="371"/>
-    <col min="9539" max="9539" width="3.109375" style="371" customWidth="1"/>
-    <col min="9540" max="9540" width="3.44140625" style="371" customWidth="1"/>
-    <col min="9541" max="9541" width="7.33203125" style="371" customWidth="1"/>
-    <col min="9542" max="9542" width="13.5546875" style="371" customWidth="1"/>
-    <col min="9543" max="9543" width="7.109375" style="371" customWidth="1"/>
-    <col min="9544" max="9544" width="8.5546875" style="371" customWidth="1"/>
-    <col min="9545" max="9545" width="9" style="371" customWidth="1"/>
-    <col min="9546" max="9546" width="5.109375" style="371" customWidth="1"/>
-    <col min="9547" max="9547" width="8.44140625" style="371" customWidth="1"/>
-    <col min="9548" max="9548" width="17.109375" style="371" customWidth="1"/>
-    <col min="9549" max="9549" width="18" style="371" customWidth="1"/>
-    <col min="9550" max="9550" width="3.88671875" style="371" customWidth="1"/>
-    <col min="9551" max="9552" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="9553" max="9555" width="9.109375" style="371"/>
-    <col min="9556" max="9556" width="11.33203125" style="371" customWidth="1"/>
-    <col min="9557" max="9794" width="9.109375" style="371"/>
-    <col min="9795" max="9795" width="3.109375" style="371" customWidth="1"/>
-    <col min="9796" max="9796" width="3.44140625" style="371" customWidth="1"/>
-    <col min="9797" max="9797" width="7.33203125" style="371" customWidth="1"/>
-    <col min="9798" max="9798" width="13.5546875" style="371" customWidth="1"/>
-    <col min="9799" max="9799" width="7.109375" style="371" customWidth="1"/>
-    <col min="9800" max="9800" width="8.5546875" style="371" customWidth="1"/>
-    <col min="9801" max="9801" width="9" style="371" customWidth="1"/>
-    <col min="9802" max="9802" width="5.109375" style="371" customWidth="1"/>
-    <col min="9803" max="9803" width="8.44140625" style="371" customWidth="1"/>
-    <col min="9804" max="9804" width="17.109375" style="371" customWidth="1"/>
-    <col min="9805" max="9805" width="18" style="371" customWidth="1"/>
-    <col min="9806" max="9806" width="3.88671875" style="371" customWidth="1"/>
-    <col min="9807" max="9808" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="9809" max="9811" width="9.109375" style="371"/>
-    <col min="9812" max="9812" width="11.33203125" style="371" customWidth="1"/>
-    <col min="9813" max="10050" width="9.109375" style="371"/>
-    <col min="10051" max="10051" width="3.109375" style="371" customWidth="1"/>
-    <col min="10052" max="10052" width="3.44140625" style="371" customWidth="1"/>
-    <col min="10053" max="10053" width="7.33203125" style="371" customWidth="1"/>
-    <col min="10054" max="10054" width="13.5546875" style="371" customWidth="1"/>
-    <col min="10055" max="10055" width="7.109375" style="371" customWidth="1"/>
-    <col min="10056" max="10056" width="8.5546875" style="371" customWidth="1"/>
-    <col min="10057" max="10057" width="9" style="371" customWidth="1"/>
-    <col min="10058" max="10058" width="5.109375" style="371" customWidth="1"/>
-    <col min="10059" max="10059" width="8.44140625" style="371" customWidth="1"/>
-    <col min="10060" max="10060" width="17.109375" style="371" customWidth="1"/>
-    <col min="10061" max="10061" width="18" style="371" customWidth="1"/>
-    <col min="10062" max="10062" width="3.88671875" style="371" customWidth="1"/>
-    <col min="10063" max="10064" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="10065" max="10067" width="9.109375" style="371"/>
-    <col min="10068" max="10068" width="11.33203125" style="371" customWidth="1"/>
-    <col min="10069" max="10306" width="9.109375" style="371"/>
-    <col min="10307" max="10307" width="3.109375" style="371" customWidth="1"/>
-    <col min="10308" max="10308" width="3.44140625" style="371" customWidth="1"/>
-    <col min="10309" max="10309" width="7.33203125" style="371" customWidth="1"/>
-    <col min="10310" max="10310" width="13.5546875" style="371" customWidth="1"/>
-    <col min="10311" max="10311" width="7.109375" style="371" customWidth="1"/>
-    <col min="10312" max="10312" width="8.5546875" style="371" customWidth="1"/>
-    <col min="10313" max="10313" width="9" style="371" customWidth="1"/>
-    <col min="10314" max="10314" width="5.109375" style="371" customWidth="1"/>
-    <col min="10315" max="10315" width="8.44140625" style="371" customWidth="1"/>
-    <col min="10316" max="10316" width="17.109375" style="371" customWidth="1"/>
-    <col min="10317" max="10317" width="18" style="371" customWidth="1"/>
-    <col min="10318" max="10318" width="3.88671875" style="371" customWidth="1"/>
-    <col min="10319" max="10320" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="10321" max="10323" width="9.109375" style="371"/>
-    <col min="10324" max="10324" width="11.33203125" style="371" customWidth="1"/>
-    <col min="10325" max="10562" width="9.109375" style="371"/>
-    <col min="10563" max="10563" width="3.109375" style="371" customWidth="1"/>
-    <col min="10564" max="10564" width="3.44140625" style="371" customWidth="1"/>
-    <col min="10565" max="10565" width="7.33203125" style="371" customWidth="1"/>
-    <col min="10566" max="10566" width="13.5546875" style="371" customWidth="1"/>
-    <col min="10567" max="10567" width="7.109375" style="371" customWidth="1"/>
-    <col min="10568" max="10568" width="8.5546875" style="371" customWidth="1"/>
-    <col min="10569" max="10569" width="9" style="371" customWidth="1"/>
-    <col min="10570" max="10570" width="5.109375" style="371" customWidth="1"/>
-    <col min="10571" max="10571" width="8.44140625" style="371" customWidth="1"/>
-    <col min="10572" max="10572" width="17.109375" style="371" customWidth="1"/>
-    <col min="10573" max="10573" width="18" style="371" customWidth="1"/>
-    <col min="10574" max="10574" width="3.88671875" style="371" customWidth="1"/>
-    <col min="10575" max="10576" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="10577" max="10579" width="9.109375" style="371"/>
-    <col min="10580" max="10580" width="11.33203125" style="371" customWidth="1"/>
-    <col min="10581" max="10818" width="9.109375" style="371"/>
-    <col min="10819" max="10819" width="3.109375" style="371" customWidth="1"/>
-    <col min="10820" max="10820" width="3.44140625" style="371" customWidth="1"/>
-    <col min="10821" max="10821" width="7.33203125" style="371" customWidth="1"/>
-    <col min="10822" max="10822" width="13.5546875" style="371" customWidth="1"/>
-    <col min="10823" max="10823" width="7.109375" style="371" customWidth="1"/>
-    <col min="10824" max="10824" width="8.5546875" style="371" customWidth="1"/>
-    <col min="10825" max="10825" width="9" style="371" customWidth="1"/>
-    <col min="10826" max="10826" width="5.109375" style="371" customWidth="1"/>
-    <col min="10827" max="10827" width="8.44140625" style="371" customWidth="1"/>
-    <col min="10828" max="10828" width="17.109375" style="371" customWidth="1"/>
-    <col min="10829" max="10829" width="18" style="371" customWidth="1"/>
-    <col min="10830" max="10830" width="3.88671875" style="371" customWidth="1"/>
-    <col min="10831" max="10832" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="10833" max="10835" width="9.109375" style="371"/>
-    <col min="10836" max="10836" width="11.33203125" style="371" customWidth="1"/>
-    <col min="10837" max="11074" width="9.109375" style="371"/>
-    <col min="11075" max="11075" width="3.109375" style="371" customWidth="1"/>
-    <col min="11076" max="11076" width="3.44140625" style="371" customWidth="1"/>
-    <col min="11077" max="11077" width="7.33203125" style="371" customWidth="1"/>
-    <col min="11078" max="11078" width="13.5546875" style="371" customWidth="1"/>
-    <col min="11079" max="11079" width="7.109375" style="371" customWidth="1"/>
-    <col min="11080" max="11080" width="8.5546875" style="371" customWidth="1"/>
-    <col min="11081" max="11081" width="9" style="371" customWidth="1"/>
-    <col min="11082" max="11082" width="5.109375" style="371" customWidth="1"/>
-    <col min="11083" max="11083" width="8.44140625" style="371" customWidth="1"/>
-    <col min="11084" max="11084" width="17.109375" style="371" customWidth="1"/>
-    <col min="11085" max="11085" width="18" style="371" customWidth="1"/>
-    <col min="11086" max="11086" width="3.88671875" style="371" customWidth="1"/>
-    <col min="11087" max="11088" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="11089" max="11091" width="9.109375" style="371"/>
-    <col min="11092" max="11092" width="11.33203125" style="371" customWidth="1"/>
-    <col min="11093" max="11330" width="9.109375" style="371"/>
-    <col min="11331" max="11331" width="3.109375" style="371" customWidth="1"/>
-    <col min="11332" max="11332" width="3.44140625" style="371" customWidth="1"/>
-    <col min="11333" max="11333" width="7.33203125" style="371" customWidth="1"/>
-    <col min="11334" max="11334" width="13.5546875" style="371" customWidth="1"/>
-    <col min="11335" max="11335" width="7.109375" style="371" customWidth="1"/>
-    <col min="11336" max="11336" width="8.5546875" style="371" customWidth="1"/>
-    <col min="11337" max="11337" width="9" style="371" customWidth="1"/>
-    <col min="11338" max="11338" width="5.109375" style="371" customWidth="1"/>
-    <col min="11339" max="11339" width="8.44140625" style="371" customWidth="1"/>
-    <col min="11340" max="11340" width="17.109375" style="371" customWidth="1"/>
-    <col min="11341" max="11341" width="18" style="371" customWidth="1"/>
-    <col min="11342" max="11342" width="3.88671875" style="371" customWidth="1"/>
-    <col min="11343" max="11344" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="11345" max="11347" width="9.109375" style="371"/>
-    <col min="11348" max="11348" width="11.33203125" style="371" customWidth="1"/>
-    <col min="11349" max="11586" width="9.109375" style="371"/>
-    <col min="11587" max="11587" width="3.109375" style="371" customWidth="1"/>
-    <col min="11588" max="11588" width="3.44140625" style="371" customWidth="1"/>
-    <col min="11589" max="11589" width="7.33203125" style="371" customWidth="1"/>
-    <col min="11590" max="11590" width="13.5546875" style="371" customWidth="1"/>
-    <col min="11591" max="11591" width="7.109375" style="371" customWidth="1"/>
-    <col min="11592" max="11592" width="8.5546875" style="371" customWidth="1"/>
-    <col min="11593" max="11593" width="9" style="371" customWidth="1"/>
-    <col min="11594" max="11594" width="5.109375" style="371" customWidth="1"/>
-    <col min="11595" max="11595" width="8.44140625" style="371" customWidth="1"/>
-    <col min="11596" max="11596" width="17.109375" style="371" customWidth="1"/>
-    <col min="11597" max="11597" width="18" style="371" customWidth="1"/>
-    <col min="11598" max="11598" width="3.88671875" style="371" customWidth="1"/>
-    <col min="11599" max="11600" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="11601" max="11603" width="9.109375" style="371"/>
-    <col min="11604" max="11604" width="11.33203125" style="371" customWidth="1"/>
-    <col min="11605" max="11842" width="9.109375" style="371"/>
-    <col min="11843" max="11843" width="3.109375" style="371" customWidth="1"/>
-    <col min="11844" max="11844" width="3.44140625" style="371" customWidth="1"/>
-    <col min="11845" max="11845" width="7.33203125" style="371" customWidth="1"/>
-    <col min="11846" max="11846" width="13.5546875" style="371" customWidth="1"/>
-    <col min="11847" max="11847" width="7.109375" style="371" customWidth="1"/>
-    <col min="11848" max="11848" width="8.5546875" style="371" customWidth="1"/>
-    <col min="11849" max="11849" width="9" style="371" customWidth="1"/>
-    <col min="11850" max="11850" width="5.109375" style="371" customWidth="1"/>
-    <col min="11851" max="11851" width="8.44140625" style="371" customWidth="1"/>
-    <col min="11852" max="11852" width="17.109375" style="371" customWidth="1"/>
-    <col min="11853" max="11853" width="18" style="371" customWidth="1"/>
-    <col min="11854" max="11854" width="3.88671875" style="371" customWidth="1"/>
-    <col min="11855" max="11856" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="11857" max="11859" width="9.109375" style="371"/>
-    <col min="11860" max="11860" width="11.33203125" style="371" customWidth="1"/>
-    <col min="11861" max="12098" width="9.109375" style="371"/>
-    <col min="12099" max="12099" width="3.109375" style="371" customWidth="1"/>
-    <col min="12100" max="12100" width="3.44140625" style="371" customWidth="1"/>
-    <col min="12101" max="12101" width="7.33203125" style="371" customWidth="1"/>
-    <col min="12102" max="12102" width="13.5546875" style="371" customWidth="1"/>
-    <col min="12103" max="12103" width="7.109375" style="371" customWidth="1"/>
-    <col min="12104" max="12104" width="8.5546875" style="371" customWidth="1"/>
-    <col min="12105" max="12105" width="9" style="371" customWidth="1"/>
-    <col min="12106" max="12106" width="5.109375" style="371" customWidth="1"/>
-    <col min="12107" max="12107" width="8.44140625" style="371" customWidth="1"/>
-    <col min="12108" max="12108" width="17.109375" style="371" customWidth="1"/>
-    <col min="12109" max="12109" width="18" style="371" customWidth="1"/>
-    <col min="12110" max="12110" width="3.88671875" style="371" customWidth="1"/>
-    <col min="12111" max="12112" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="12113" max="12115" width="9.109375" style="371"/>
-    <col min="12116" max="12116" width="11.33203125" style="371" customWidth="1"/>
-    <col min="12117" max="12354" width="9.109375" style="371"/>
-    <col min="12355" max="12355" width="3.109375" style="371" customWidth="1"/>
-    <col min="12356" max="12356" width="3.44140625" style="371" customWidth="1"/>
-    <col min="12357" max="12357" width="7.33203125" style="371" customWidth="1"/>
-    <col min="12358" max="12358" width="13.5546875" style="371" customWidth="1"/>
-    <col min="12359" max="12359" width="7.109375" style="371" customWidth="1"/>
-    <col min="12360" max="12360" width="8.5546875" style="371" customWidth="1"/>
-    <col min="12361" max="12361" width="9" style="371" customWidth="1"/>
-    <col min="12362" max="12362" width="5.109375" style="371" customWidth="1"/>
-    <col min="12363" max="12363" width="8.44140625" style="371" customWidth="1"/>
-    <col min="12364" max="12364" width="17.109375" style="371" customWidth="1"/>
-    <col min="12365" max="12365" width="18" style="371" customWidth="1"/>
-    <col min="12366" max="12366" width="3.88671875" style="371" customWidth="1"/>
-    <col min="12367" max="12368" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="12369" max="12371" width="9.109375" style="371"/>
-    <col min="12372" max="12372" width="11.33203125" style="371" customWidth="1"/>
-    <col min="12373" max="12610" width="9.109375" style="371"/>
-    <col min="12611" max="12611" width="3.109375" style="371" customWidth="1"/>
-    <col min="12612" max="12612" width="3.44140625" style="371" customWidth="1"/>
-    <col min="12613" max="12613" width="7.33203125" style="371" customWidth="1"/>
-    <col min="12614" max="12614" width="13.5546875" style="371" customWidth="1"/>
-    <col min="12615" max="12615" width="7.109375" style="371" customWidth="1"/>
-    <col min="12616" max="12616" width="8.5546875" style="371" customWidth="1"/>
-    <col min="12617" max="12617" width="9" style="371" customWidth="1"/>
-    <col min="12618" max="12618" width="5.109375" style="371" customWidth="1"/>
-    <col min="12619" max="12619" width="8.44140625" style="371" customWidth="1"/>
-    <col min="12620" max="12620" width="17.109375" style="371" customWidth="1"/>
-    <col min="12621" max="12621" width="18" style="371" customWidth="1"/>
-    <col min="12622" max="12622" width="3.88671875" style="371" customWidth="1"/>
-    <col min="12623" max="12624" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="12625" max="12627" width="9.109375" style="371"/>
-    <col min="12628" max="12628" width="11.33203125" style="371" customWidth="1"/>
-    <col min="12629" max="12866" width="9.109375" style="371"/>
-    <col min="12867" max="12867" width="3.109375" style="371" customWidth="1"/>
-    <col min="12868" max="12868" width="3.44140625" style="371" customWidth="1"/>
-    <col min="12869" max="12869" width="7.33203125" style="371" customWidth="1"/>
-    <col min="12870" max="12870" width="13.5546875" style="371" customWidth="1"/>
-    <col min="12871" max="12871" width="7.109375" style="371" customWidth="1"/>
-    <col min="12872" max="12872" width="8.5546875" style="371" customWidth="1"/>
-    <col min="12873" max="12873" width="9" style="371" customWidth="1"/>
-    <col min="12874" max="12874" width="5.109375" style="371" customWidth="1"/>
-    <col min="12875" max="12875" width="8.44140625" style="371" customWidth="1"/>
-    <col min="12876" max="12876" width="17.109375" style="371" customWidth="1"/>
-    <col min="12877" max="12877" width="18" style="371" customWidth="1"/>
-    <col min="12878" max="12878" width="3.88671875" style="371" customWidth="1"/>
-    <col min="12879" max="12880" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="12881" max="12883" width="9.109375" style="371"/>
-    <col min="12884" max="12884" width="11.33203125" style="371" customWidth="1"/>
-    <col min="12885" max="13122" width="9.109375" style="371"/>
-    <col min="13123" max="13123" width="3.109375" style="371" customWidth="1"/>
-    <col min="13124" max="13124" width="3.44140625" style="371" customWidth="1"/>
-    <col min="13125" max="13125" width="7.33203125" style="371" customWidth="1"/>
-    <col min="13126" max="13126" width="13.5546875" style="371" customWidth="1"/>
-    <col min="13127" max="13127" width="7.109375" style="371" customWidth="1"/>
-    <col min="13128" max="13128" width="8.5546875" style="371" customWidth="1"/>
-    <col min="13129" max="13129" width="9" style="371" customWidth="1"/>
-    <col min="13130" max="13130" width="5.109375" style="371" customWidth="1"/>
-    <col min="13131" max="13131" width="8.44140625" style="371" customWidth="1"/>
-    <col min="13132" max="13132" width="17.109375" style="371" customWidth="1"/>
-    <col min="13133" max="13133" width="18" style="371" customWidth="1"/>
-    <col min="13134" max="13134" width="3.88671875" style="371" customWidth="1"/>
-    <col min="13135" max="13136" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="13137" max="13139" width="9.109375" style="371"/>
-    <col min="13140" max="13140" width="11.33203125" style="371" customWidth="1"/>
-    <col min="13141" max="13378" width="9.109375" style="371"/>
-    <col min="13379" max="13379" width="3.109375" style="371" customWidth="1"/>
-    <col min="13380" max="13380" width="3.44140625" style="371" customWidth="1"/>
-    <col min="13381" max="13381" width="7.33203125" style="371" customWidth="1"/>
-    <col min="13382" max="13382" width="13.5546875" style="371" customWidth="1"/>
-    <col min="13383" max="13383" width="7.109375" style="371" customWidth="1"/>
-    <col min="13384" max="13384" width="8.5546875" style="371" customWidth="1"/>
-    <col min="13385" max="13385" width="9" style="371" customWidth="1"/>
-    <col min="13386" max="13386" width="5.109375" style="371" customWidth="1"/>
-    <col min="13387" max="13387" width="8.44140625" style="371" customWidth="1"/>
-    <col min="13388" max="13388" width="17.109375" style="371" customWidth="1"/>
-    <col min="13389" max="13389" width="18" style="371" customWidth="1"/>
-    <col min="13390" max="13390" width="3.88671875" style="371" customWidth="1"/>
-    <col min="13391" max="13392" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="13393" max="13395" width="9.109375" style="371"/>
-    <col min="13396" max="13396" width="11.33203125" style="371" customWidth="1"/>
-    <col min="13397" max="13634" width="9.109375" style="371"/>
-    <col min="13635" max="13635" width="3.109375" style="371" customWidth="1"/>
-    <col min="13636" max="13636" width="3.44140625" style="371" customWidth="1"/>
-    <col min="13637" max="13637" width="7.33203125" style="371" customWidth="1"/>
-    <col min="13638" max="13638" width="13.5546875" style="371" customWidth="1"/>
-    <col min="13639" max="13639" width="7.109375" style="371" customWidth="1"/>
-    <col min="13640" max="13640" width="8.5546875" style="371" customWidth="1"/>
-    <col min="13641" max="13641" width="9" style="371" customWidth="1"/>
-    <col min="13642" max="13642" width="5.109375" style="371" customWidth="1"/>
-    <col min="13643" max="13643" width="8.44140625" style="371" customWidth="1"/>
-    <col min="13644" max="13644" width="17.109375" style="371" customWidth="1"/>
-    <col min="13645" max="13645" width="18" style="371" customWidth="1"/>
-    <col min="13646" max="13646" width="3.88671875" style="371" customWidth="1"/>
-    <col min="13647" max="13648" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="13649" max="13651" width="9.109375" style="371"/>
-    <col min="13652" max="13652" width="11.33203125" style="371" customWidth="1"/>
-    <col min="13653" max="13890" width="9.109375" style="371"/>
-    <col min="13891" max="13891" width="3.109375" style="371" customWidth="1"/>
-    <col min="13892" max="13892" width="3.44140625" style="371" customWidth="1"/>
-    <col min="13893" max="13893" width="7.33203125" style="371" customWidth="1"/>
-    <col min="13894" max="13894" width="13.5546875" style="371" customWidth="1"/>
-    <col min="13895" max="13895" width="7.109375" style="371" customWidth="1"/>
-    <col min="13896" max="13896" width="8.5546875" style="371" customWidth="1"/>
-    <col min="13897" max="13897" width="9" style="371" customWidth="1"/>
-    <col min="13898" max="13898" width="5.109375" style="371" customWidth="1"/>
-    <col min="13899" max="13899" width="8.44140625" style="371" customWidth="1"/>
-    <col min="13900" max="13900" width="17.109375" style="371" customWidth="1"/>
-    <col min="13901" max="13901" width="18" style="371" customWidth="1"/>
-    <col min="13902" max="13902" width="3.88671875" style="371" customWidth="1"/>
-    <col min="13903" max="13904" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="13905" max="13907" width="9.109375" style="371"/>
-    <col min="13908" max="13908" width="11.33203125" style="371" customWidth="1"/>
-    <col min="13909" max="14146" width="9.109375" style="371"/>
-    <col min="14147" max="14147" width="3.109375" style="371" customWidth="1"/>
-    <col min="14148" max="14148" width="3.44140625" style="371" customWidth="1"/>
-    <col min="14149" max="14149" width="7.33203125" style="371" customWidth="1"/>
-    <col min="14150" max="14150" width="13.5546875" style="371" customWidth="1"/>
-    <col min="14151" max="14151" width="7.109375" style="371" customWidth="1"/>
-    <col min="14152" max="14152" width="8.5546875" style="371" customWidth="1"/>
-    <col min="14153" max="14153" width="9" style="371" customWidth="1"/>
-    <col min="14154" max="14154" width="5.109375" style="371" customWidth="1"/>
-    <col min="14155" max="14155" width="8.44140625" style="371" customWidth="1"/>
-    <col min="14156" max="14156" width="17.109375" style="371" customWidth="1"/>
-    <col min="14157" max="14157" width="18" style="371" customWidth="1"/>
-    <col min="14158" max="14158" width="3.88671875" style="371" customWidth="1"/>
-    <col min="14159" max="14160" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="14161" max="14163" width="9.109375" style="371"/>
-    <col min="14164" max="14164" width="11.33203125" style="371" customWidth="1"/>
-    <col min="14165" max="14402" width="9.109375" style="371"/>
-    <col min="14403" max="14403" width="3.109375" style="371" customWidth="1"/>
-    <col min="14404" max="14404" width="3.44140625" style="371" customWidth="1"/>
-    <col min="14405" max="14405" width="7.33203125" style="371" customWidth="1"/>
-    <col min="14406" max="14406" width="13.5546875" style="371" customWidth="1"/>
-    <col min="14407" max="14407" width="7.109375" style="371" customWidth="1"/>
-    <col min="14408" max="14408" width="8.5546875" style="371" customWidth="1"/>
-    <col min="14409" max="14409" width="9" style="371" customWidth="1"/>
-    <col min="14410" max="14410" width="5.109375" style="371" customWidth="1"/>
-    <col min="14411" max="14411" width="8.44140625" style="371" customWidth="1"/>
-    <col min="14412" max="14412" width="17.109375" style="371" customWidth="1"/>
-    <col min="14413" max="14413" width="18" style="371" customWidth="1"/>
-    <col min="14414" max="14414" width="3.88671875" style="371" customWidth="1"/>
-    <col min="14415" max="14416" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="14417" max="14419" width="9.109375" style="371"/>
-    <col min="14420" max="14420" width="11.33203125" style="371" customWidth="1"/>
-    <col min="14421" max="14658" width="9.109375" style="371"/>
-    <col min="14659" max="14659" width="3.109375" style="371" customWidth="1"/>
-    <col min="14660" max="14660" width="3.44140625" style="371" customWidth="1"/>
-    <col min="14661" max="14661" width="7.33203125" style="371" customWidth="1"/>
-    <col min="14662" max="14662" width="13.5546875" style="371" customWidth="1"/>
-    <col min="14663" max="14663" width="7.109375" style="371" customWidth="1"/>
-    <col min="14664" max="14664" width="8.5546875" style="371" customWidth="1"/>
-    <col min="14665" max="14665" width="9" style="371" customWidth="1"/>
-    <col min="14666" max="14666" width="5.109375" style="371" customWidth="1"/>
-    <col min="14667" max="14667" width="8.44140625" style="371" customWidth="1"/>
-    <col min="14668" max="14668" width="17.109375" style="371" customWidth="1"/>
-    <col min="14669" max="14669" width="18" style="371" customWidth="1"/>
-    <col min="14670" max="14670" width="3.88671875" style="371" customWidth="1"/>
-    <col min="14671" max="14672" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="14673" max="14675" width="9.109375" style="371"/>
-    <col min="14676" max="14676" width="11.33203125" style="371" customWidth="1"/>
-    <col min="14677" max="14914" width="9.109375" style="371"/>
-    <col min="14915" max="14915" width="3.109375" style="371" customWidth="1"/>
-    <col min="14916" max="14916" width="3.44140625" style="371" customWidth="1"/>
-    <col min="14917" max="14917" width="7.33203125" style="371" customWidth="1"/>
-    <col min="14918" max="14918" width="13.5546875" style="371" customWidth="1"/>
-    <col min="14919" max="14919" width="7.109375" style="371" customWidth="1"/>
-    <col min="14920" max="14920" width="8.5546875" style="371" customWidth="1"/>
-    <col min="14921" max="14921" width="9" style="371" customWidth="1"/>
-    <col min="14922" max="14922" width="5.109375" style="371" customWidth="1"/>
-    <col min="14923" max="14923" width="8.44140625" style="371" customWidth="1"/>
-    <col min="14924" max="14924" width="17.109375" style="371" customWidth="1"/>
-    <col min="14925" max="14925" width="18" style="371" customWidth="1"/>
-    <col min="14926" max="14926" width="3.88671875" style="371" customWidth="1"/>
-    <col min="14927" max="14928" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="14929" max="14931" width="9.109375" style="371"/>
-    <col min="14932" max="14932" width="11.33203125" style="371" customWidth="1"/>
-    <col min="14933" max="15170" width="9.109375" style="371"/>
-    <col min="15171" max="15171" width="3.109375" style="371" customWidth="1"/>
-    <col min="15172" max="15172" width="3.44140625" style="371" customWidth="1"/>
-    <col min="15173" max="15173" width="7.33203125" style="371" customWidth="1"/>
-    <col min="15174" max="15174" width="13.5546875" style="371" customWidth="1"/>
-    <col min="15175" max="15175" width="7.109375" style="371" customWidth="1"/>
-    <col min="15176" max="15176" width="8.5546875" style="371" customWidth="1"/>
-    <col min="15177" max="15177" width="9" style="371" customWidth="1"/>
-    <col min="15178" max="15178" width="5.109375" style="371" customWidth="1"/>
-    <col min="15179" max="15179" width="8.44140625" style="371" customWidth="1"/>
-    <col min="15180" max="15180" width="17.109375" style="371" customWidth="1"/>
-    <col min="15181" max="15181" width="18" style="371" customWidth="1"/>
-    <col min="15182" max="15182" width="3.88671875" style="371" customWidth="1"/>
-    <col min="15183" max="15184" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="15185" max="15187" width="9.109375" style="371"/>
-    <col min="15188" max="15188" width="11.33203125" style="371" customWidth="1"/>
-    <col min="15189" max="15426" width="9.109375" style="371"/>
-    <col min="15427" max="15427" width="3.109375" style="371" customWidth="1"/>
-    <col min="15428" max="15428" width="3.44140625" style="371" customWidth="1"/>
-    <col min="15429" max="15429" width="7.33203125" style="371" customWidth="1"/>
-    <col min="15430" max="15430" width="13.5546875" style="371" customWidth="1"/>
-    <col min="15431" max="15431" width="7.109375" style="371" customWidth="1"/>
-    <col min="15432" max="15432" width="8.5546875" style="371" customWidth="1"/>
-    <col min="15433" max="15433" width="9" style="371" customWidth="1"/>
-    <col min="15434" max="15434" width="5.109375" style="371" customWidth="1"/>
-    <col min="15435" max="15435" width="8.44140625" style="371" customWidth="1"/>
-    <col min="15436" max="15436" width="17.109375" style="371" customWidth="1"/>
-    <col min="15437" max="15437" width="18" style="371" customWidth="1"/>
-    <col min="15438" max="15438" width="3.88671875" style="371" customWidth="1"/>
-    <col min="15439" max="15440" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="15441" max="15443" width="9.109375" style="371"/>
-    <col min="15444" max="15444" width="11.33203125" style="371" customWidth="1"/>
-    <col min="15445" max="15682" width="9.109375" style="371"/>
-    <col min="15683" max="15683" width="3.109375" style="371" customWidth="1"/>
-    <col min="15684" max="15684" width="3.44140625" style="371" customWidth="1"/>
-    <col min="15685" max="15685" width="7.33203125" style="371" customWidth="1"/>
-    <col min="15686" max="15686" width="13.5546875" style="371" customWidth="1"/>
-    <col min="15687" max="15687" width="7.109375" style="371" customWidth="1"/>
-    <col min="15688" max="15688" width="8.5546875" style="371" customWidth="1"/>
-    <col min="15689" max="15689" width="9" style="371" customWidth="1"/>
-    <col min="15690" max="15690" width="5.109375" style="371" customWidth="1"/>
-    <col min="15691" max="15691" width="8.44140625" style="371" customWidth="1"/>
-    <col min="15692" max="15692" width="17.109375" style="371" customWidth="1"/>
-    <col min="15693" max="15693" width="18" style="371" customWidth="1"/>
-    <col min="15694" max="15694" width="3.88671875" style="371" customWidth="1"/>
-    <col min="15695" max="15696" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="15697" max="15699" width="9.109375" style="371"/>
-    <col min="15700" max="15700" width="11.33203125" style="371" customWidth="1"/>
-    <col min="15701" max="15938" width="9.109375" style="371"/>
-    <col min="15939" max="15939" width="3.109375" style="371" customWidth="1"/>
-    <col min="15940" max="15940" width="3.44140625" style="371" customWidth="1"/>
-    <col min="15941" max="15941" width="7.33203125" style="371" customWidth="1"/>
-    <col min="15942" max="15942" width="13.5546875" style="371" customWidth="1"/>
-    <col min="15943" max="15943" width="7.109375" style="371" customWidth="1"/>
-    <col min="15944" max="15944" width="8.5546875" style="371" customWidth="1"/>
-    <col min="15945" max="15945" width="9" style="371" customWidth="1"/>
-    <col min="15946" max="15946" width="5.109375" style="371" customWidth="1"/>
-    <col min="15947" max="15947" width="8.44140625" style="371" customWidth="1"/>
-    <col min="15948" max="15948" width="17.109375" style="371" customWidth="1"/>
-    <col min="15949" max="15949" width="18" style="371" customWidth="1"/>
-    <col min="15950" max="15950" width="3.88671875" style="371" customWidth="1"/>
-    <col min="15951" max="15952" width="12.109375" style="371" bestFit="1" customWidth="1"/>
-    <col min="15953" max="15955" width="9.109375" style="371"/>
-    <col min="15956" max="15956" width="11.33203125" style="371" customWidth="1"/>
-    <col min="15957" max="16384" width="9.109375" style="371"/>
+    <col min="1" max="2" width="9.5546875" style="328" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" style="328" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="328" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" style="328" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="328" customWidth="1"/>
+    <col min="7" max="10" width="9.5546875" style="328" customWidth="1"/>
+    <col min="11" max="66" width="9.109375" style="328"/>
+    <col min="67" max="67" width="3.109375" style="328" customWidth="1"/>
+    <col min="68" max="68" width="3.44140625" style="328" customWidth="1"/>
+    <col min="69" max="69" width="7.33203125" style="328" customWidth="1"/>
+    <col min="70" max="70" width="13.5546875" style="328" customWidth="1"/>
+    <col min="71" max="71" width="7.109375" style="328" customWidth="1"/>
+    <col min="72" max="72" width="8.5546875" style="328" customWidth="1"/>
+    <col min="73" max="73" width="9" style="328" customWidth="1"/>
+    <col min="74" max="74" width="5.109375" style="328" customWidth="1"/>
+    <col min="75" max="75" width="8.44140625" style="328" customWidth="1"/>
+    <col min="76" max="76" width="17.109375" style="328" customWidth="1"/>
+    <col min="77" max="77" width="18" style="328" customWidth="1"/>
+    <col min="78" max="78" width="3.88671875" style="328" customWidth="1"/>
+    <col min="79" max="80" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="81" max="83" width="9.109375" style="328"/>
+    <col min="84" max="84" width="11.33203125" style="328" customWidth="1"/>
+    <col min="85" max="322" width="9.109375" style="328"/>
+    <col min="323" max="323" width="3.109375" style="328" customWidth="1"/>
+    <col min="324" max="324" width="3.44140625" style="328" customWidth="1"/>
+    <col min="325" max="325" width="7.33203125" style="328" customWidth="1"/>
+    <col min="326" max="326" width="13.5546875" style="328" customWidth="1"/>
+    <col min="327" max="327" width="7.109375" style="328" customWidth="1"/>
+    <col min="328" max="328" width="8.5546875" style="328" customWidth="1"/>
+    <col min="329" max="329" width="9" style="328" customWidth="1"/>
+    <col min="330" max="330" width="5.109375" style="328" customWidth="1"/>
+    <col min="331" max="331" width="8.44140625" style="328" customWidth="1"/>
+    <col min="332" max="332" width="17.109375" style="328" customWidth="1"/>
+    <col min="333" max="333" width="18" style="328" customWidth="1"/>
+    <col min="334" max="334" width="3.88671875" style="328" customWidth="1"/>
+    <col min="335" max="336" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="337" max="339" width="9.109375" style="328"/>
+    <col min="340" max="340" width="11.33203125" style="328" customWidth="1"/>
+    <col min="341" max="578" width="9.109375" style="328"/>
+    <col min="579" max="579" width="3.109375" style="328" customWidth="1"/>
+    <col min="580" max="580" width="3.44140625" style="328" customWidth="1"/>
+    <col min="581" max="581" width="7.33203125" style="328" customWidth="1"/>
+    <col min="582" max="582" width="13.5546875" style="328" customWidth="1"/>
+    <col min="583" max="583" width="7.109375" style="328" customWidth="1"/>
+    <col min="584" max="584" width="8.5546875" style="328" customWidth="1"/>
+    <col min="585" max="585" width="9" style="328" customWidth="1"/>
+    <col min="586" max="586" width="5.109375" style="328" customWidth="1"/>
+    <col min="587" max="587" width="8.44140625" style="328" customWidth="1"/>
+    <col min="588" max="588" width="17.109375" style="328" customWidth="1"/>
+    <col min="589" max="589" width="18" style="328" customWidth="1"/>
+    <col min="590" max="590" width="3.88671875" style="328" customWidth="1"/>
+    <col min="591" max="592" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="593" max="595" width="9.109375" style="328"/>
+    <col min="596" max="596" width="11.33203125" style="328" customWidth="1"/>
+    <col min="597" max="834" width="9.109375" style="328"/>
+    <col min="835" max="835" width="3.109375" style="328" customWidth="1"/>
+    <col min="836" max="836" width="3.44140625" style="328" customWidth="1"/>
+    <col min="837" max="837" width="7.33203125" style="328" customWidth="1"/>
+    <col min="838" max="838" width="13.5546875" style="328" customWidth="1"/>
+    <col min="839" max="839" width="7.109375" style="328" customWidth="1"/>
+    <col min="840" max="840" width="8.5546875" style="328" customWidth="1"/>
+    <col min="841" max="841" width="9" style="328" customWidth="1"/>
+    <col min="842" max="842" width="5.109375" style="328" customWidth="1"/>
+    <col min="843" max="843" width="8.44140625" style="328" customWidth="1"/>
+    <col min="844" max="844" width="17.109375" style="328" customWidth="1"/>
+    <col min="845" max="845" width="18" style="328" customWidth="1"/>
+    <col min="846" max="846" width="3.88671875" style="328" customWidth="1"/>
+    <col min="847" max="848" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="849" max="851" width="9.109375" style="328"/>
+    <col min="852" max="852" width="11.33203125" style="328" customWidth="1"/>
+    <col min="853" max="1090" width="9.109375" style="328"/>
+    <col min="1091" max="1091" width="3.109375" style="328" customWidth="1"/>
+    <col min="1092" max="1092" width="3.44140625" style="328" customWidth="1"/>
+    <col min="1093" max="1093" width="7.33203125" style="328" customWidth="1"/>
+    <col min="1094" max="1094" width="13.5546875" style="328" customWidth="1"/>
+    <col min="1095" max="1095" width="7.109375" style="328" customWidth="1"/>
+    <col min="1096" max="1096" width="8.5546875" style="328" customWidth="1"/>
+    <col min="1097" max="1097" width="9" style="328" customWidth="1"/>
+    <col min="1098" max="1098" width="5.109375" style="328" customWidth="1"/>
+    <col min="1099" max="1099" width="8.44140625" style="328" customWidth="1"/>
+    <col min="1100" max="1100" width="17.109375" style="328" customWidth="1"/>
+    <col min="1101" max="1101" width="18" style="328" customWidth="1"/>
+    <col min="1102" max="1102" width="3.88671875" style="328" customWidth="1"/>
+    <col min="1103" max="1104" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="1105" max="1107" width="9.109375" style="328"/>
+    <col min="1108" max="1108" width="11.33203125" style="328" customWidth="1"/>
+    <col min="1109" max="1346" width="9.109375" style="328"/>
+    <col min="1347" max="1347" width="3.109375" style="328" customWidth="1"/>
+    <col min="1348" max="1348" width="3.44140625" style="328" customWidth="1"/>
+    <col min="1349" max="1349" width="7.33203125" style="328" customWidth="1"/>
+    <col min="1350" max="1350" width="13.5546875" style="328" customWidth="1"/>
+    <col min="1351" max="1351" width="7.109375" style="328" customWidth="1"/>
+    <col min="1352" max="1352" width="8.5546875" style="328" customWidth="1"/>
+    <col min="1353" max="1353" width="9" style="328" customWidth="1"/>
+    <col min="1354" max="1354" width="5.109375" style="328" customWidth="1"/>
+    <col min="1355" max="1355" width="8.44140625" style="328" customWidth="1"/>
+    <col min="1356" max="1356" width="17.109375" style="328" customWidth="1"/>
+    <col min="1357" max="1357" width="18" style="328" customWidth="1"/>
+    <col min="1358" max="1358" width="3.88671875" style="328" customWidth="1"/>
+    <col min="1359" max="1360" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="1361" max="1363" width="9.109375" style="328"/>
+    <col min="1364" max="1364" width="11.33203125" style="328" customWidth="1"/>
+    <col min="1365" max="1602" width="9.109375" style="328"/>
+    <col min="1603" max="1603" width="3.109375" style="328" customWidth="1"/>
+    <col min="1604" max="1604" width="3.44140625" style="328" customWidth="1"/>
+    <col min="1605" max="1605" width="7.33203125" style="328" customWidth="1"/>
+    <col min="1606" max="1606" width="13.5546875" style="328" customWidth="1"/>
+    <col min="1607" max="1607" width="7.109375" style="328" customWidth="1"/>
+    <col min="1608" max="1608" width="8.5546875" style="328" customWidth="1"/>
+    <col min="1609" max="1609" width="9" style="328" customWidth="1"/>
+    <col min="1610" max="1610" width="5.109375" style="328" customWidth="1"/>
+    <col min="1611" max="1611" width="8.44140625" style="328" customWidth="1"/>
+    <col min="1612" max="1612" width="17.109375" style="328" customWidth="1"/>
+    <col min="1613" max="1613" width="18" style="328" customWidth="1"/>
+    <col min="1614" max="1614" width="3.88671875" style="328" customWidth="1"/>
+    <col min="1615" max="1616" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="1617" max="1619" width="9.109375" style="328"/>
+    <col min="1620" max="1620" width="11.33203125" style="328" customWidth="1"/>
+    <col min="1621" max="1858" width="9.109375" style="328"/>
+    <col min="1859" max="1859" width="3.109375" style="328" customWidth="1"/>
+    <col min="1860" max="1860" width="3.44140625" style="328" customWidth="1"/>
+    <col min="1861" max="1861" width="7.33203125" style="328" customWidth="1"/>
+    <col min="1862" max="1862" width="13.5546875" style="328" customWidth="1"/>
+    <col min="1863" max="1863" width="7.109375" style="328" customWidth="1"/>
+    <col min="1864" max="1864" width="8.5546875" style="328" customWidth="1"/>
+    <col min="1865" max="1865" width="9" style="328" customWidth="1"/>
+    <col min="1866" max="1866" width="5.109375" style="328" customWidth="1"/>
+    <col min="1867" max="1867" width="8.44140625" style="328" customWidth="1"/>
+    <col min="1868" max="1868" width="17.109375" style="328" customWidth="1"/>
+    <col min="1869" max="1869" width="18" style="328" customWidth="1"/>
+    <col min="1870" max="1870" width="3.88671875" style="328" customWidth="1"/>
+    <col min="1871" max="1872" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="1873" max="1875" width="9.109375" style="328"/>
+    <col min="1876" max="1876" width="11.33203125" style="328" customWidth="1"/>
+    <col min="1877" max="2114" width="9.109375" style="328"/>
+    <col min="2115" max="2115" width="3.109375" style="328" customWidth="1"/>
+    <col min="2116" max="2116" width="3.44140625" style="328" customWidth="1"/>
+    <col min="2117" max="2117" width="7.33203125" style="328" customWidth="1"/>
+    <col min="2118" max="2118" width="13.5546875" style="328" customWidth="1"/>
+    <col min="2119" max="2119" width="7.109375" style="328" customWidth="1"/>
+    <col min="2120" max="2120" width="8.5546875" style="328" customWidth="1"/>
+    <col min="2121" max="2121" width="9" style="328" customWidth="1"/>
+    <col min="2122" max="2122" width="5.109375" style="328" customWidth="1"/>
+    <col min="2123" max="2123" width="8.44140625" style="328" customWidth="1"/>
+    <col min="2124" max="2124" width="17.109375" style="328" customWidth="1"/>
+    <col min="2125" max="2125" width="18" style="328" customWidth="1"/>
+    <col min="2126" max="2126" width="3.88671875" style="328" customWidth="1"/>
+    <col min="2127" max="2128" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="2129" max="2131" width="9.109375" style="328"/>
+    <col min="2132" max="2132" width="11.33203125" style="328" customWidth="1"/>
+    <col min="2133" max="2370" width="9.109375" style="328"/>
+    <col min="2371" max="2371" width="3.109375" style="328" customWidth="1"/>
+    <col min="2372" max="2372" width="3.44140625" style="328" customWidth="1"/>
+    <col min="2373" max="2373" width="7.33203125" style="328" customWidth="1"/>
+    <col min="2374" max="2374" width="13.5546875" style="328" customWidth="1"/>
+    <col min="2375" max="2375" width="7.109375" style="328" customWidth="1"/>
+    <col min="2376" max="2376" width="8.5546875" style="328" customWidth="1"/>
+    <col min="2377" max="2377" width="9" style="328" customWidth="1"/>
+    <col min="2378" max="2378" width="5.109375" style="328" customWidth="1"/>
+    <col min="2379" max="2379" width="8.44140625" style="328" customWidth="1"/>
+    <col min="2380" max="2380" width="17.109375" style="328" customWidth="1"/>
+    <col min="2381" max="2381" width="18" style="328" customWidth="1"/>
+    <col min="2382" max="2382" width="3.88671875" style="328" customWidth="1"/>
+    <col min="2383" max="2384" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="2385" max="2387" width="9.109375" style="328"/>
+    <col min="2388" max="2388" width="11.33203125" style="328" customWidth="1"/>
+    <col min="2389" max="2626" width="9.109375" style="328"/>
+    <col min="2627" max="2627" width="3.109375" style="328" customWidth="1"/>
+    <col min="2628" max="2628" width="3.44140625" style="328" customWidth="1"/>
+    <col min="2629" max="2629" width="7.33203125" style="328" customWidth="1"/>
+    <col min="2630" max="2630" width="13.5546875" style="328" customWidth="1"/>
+    <col min="2631" max="2631" width="7.109375" style="328" customWidth="1"/>
+    <col min="2632" max="2632" width="8.5546875" style="328" customWidth="1"/>
+    <col min="2633" max="2633" width="9" style="328" customWidth="1"/>
+    <col min="2634" max="2634" width="5.109375" style="328" customWidth="1"/>
+    <col min="2635" max="2635" width="8.44140625" style="328" customWidth="1"/>
+    <col min="2636" max="2636" width="17.109375" style="328" customWidth="1"/>
+    <col min="2637" max="2637" width="18" style="328" customWidth="1"/>
+    <col min="2638" max="2638" width="3.88671875" style="328" customWidth="1"/>
+    <col min="2639" max="2640" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="2641" max="2643" width="9.109375" style="328"/>
+    <col min="2644" max="2644" width="11.33203125" style="328" customWidth="1"/>
+    <col min="2645" max="2882" width="9.109375" style="328"/>
+    <col min="2883" max="2883" width="3.109375" style="328" customWidth="1"/>
+    <col min="2884" max="2884" width="3.44140625" style="328" customWidth="1"/>
+    <col min="2885" max="2885" width="7.33203125" style="328" customWidth="1"/>
+    <col min="2886" max="2886" width="13.5546875" style="328" customWidth="1"/>
+    <col min="2887" max="2887" width="7.109375" style="328" customWidth="1"/>
+    <col min="2888" max="2888" width="8.5546875" style="328" customWidth="1"/>
+    <col min="2889" max="2889" width="9" style="328" customWidth="1"/>
+    <col min="2890" max="2890" width="5.109375" style="328" customWidth="1"/>
+    <col min="2891" max="2891" width="8.44140625" style="328" customWidth="1"/>
+    <col min="2892" max="2892" width="17.109375" style="328" customWidth="1"/>
+    <col min="2893" max="2893" width="18" style="328" customWidth="1"/>
+    <col min="2894" max="2894" width="3.88671875" style="328" customWidth="1"/>
+    <col min="2895" max="2896" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="2897" max="2899" width="9.109375" style="328"/>
+    <col min="2900" max="2900" width="11.33203125" style="328" customWidth="1"/>
+    <col min="2901" max="3138" width="9.109375" style="328"/>
+    <col min="3139" max="3139" width="3.109375" style="328" customWidth="1"/>
+    <col min="3140" max="3140" width="3.44140625" style="328" customWidth="1"/>
+    <col min="3141" max="3141" width="7.33203125" style="328" customWidth="1"/>
+    <col min="3142" max="3142" width="13.5546875" style="328" customWidth="1"/>
+    <col min="3143" max="3143" width="7.109375" style="328" customWidth="1"/>
+    <col min="3144" max="3144" width="8.5546875" style="328" customWidth="1"/>
+    <col min="3145" max="3145" width="9" style="328" customWidth="1"/>
+    <col min="3146" max="3146" width="5.109375" style="328" customWidth="1"/>
+    <col min="3147" max="3147" width="8.44140625" style="328" customWidth="1"/>
+    <col min="3148" max="3148" width="17.109375" style="328" customWidth="1"/>
+    <col min="3149" max="3149" width="18" style="328" customWidth="1"/>
+    <col min="3150" max="3150" width="3.88671875" style="328" customWidth="1"/>
+    <col min="3151" max="3152" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="3153" max="3155" width="9.109375" style="328"/>
+    <col min="3156" max="3156" width="11.33203125" style="328" customWidth="1"/>
+    <col min="3157" max="3394" width="9.109375" style="328"/>
+    <col min="3395" max="3395" width="3.109375" style="328" customWidth="1"/>
+    <col min="3396" max="3396" width="3.44140625" style="328" customWidth="1"/>
+    <col min="3397" max="3397" width="7.33203125" style="328" customWidth="1"/>
+    <col min="3398" max="3398" width="13.5546875" style="328" customWidth="1"/>
+    <col min="3399" max="3399" width="7.109375" style="328" customWidth="1"/>
+    <col min="3400" max="3400" width="8.5546875" style="328" customWidth="1"/>
+    <col min="3401" max="3401" width="9" style="328" customWidth="1"/>
+    <col min="3402" max="3402" width="5.109375" style="328" customWidth="1"/>
+    <col min="3403" max="3403" width="8.44140625" style="328" customWidth="1"/>
+    <col min="3404" max="3404" width="17.109375" style="328" customWidth="1"/>
+    <col min="3405" max="3405" width="18" style="328" customWidth="1"/>
+    <col min="3406" max="3406" width="3.88671875" style="328" customWidth="1"/>
+    <col min="3407" max="3408" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="3409" max="3411" width="9.109375" style="328"/>
+    <col min="3412" max="3412" width="11.33203125" style="328" customWidth="1"/>
+    <col min="3413" max="3650" width="9.109375" style="328"/>
+    <col min="3651" max="3651" width="3.109375" style="328" customWidth="1"/>
+    <col min="3652" max="3652" width="3.44140625" style="328" customWidth="1"/>
+    <col min="3653" max="3653" width="7.33203125" style="328" customWidth="1"/>
+    <col min="3654" max="3654" width="13.5546875" style="328" customWidth="1"/>
+    <col min="3655" max="3655" width="7.109375" style="328" customWidth="1"/>
+    <col min="3656" max="3656" width="8.5546875" style="328" customWidth="1"/>
+    <col min="3657" max="3657" width="9" style="328" customWidth="1"/>
+    <col min="3658" max="3658" width="5.109375" style="328" customWidth="1"/>
+    <col min="3659" max="3659" width="8.44140625" style="328" customWidth="1"/>
+    <col min="3660" max="3660" width="17.109375" style="328" customWidth="1"/>
+    <col min="3661" max="3661" width="18" style="328" customWidth="1"/>
+    <col min="3662" max="3662" width="3.88671875" style="328" customWidth="1"/>
+    <col min="3663" max="3664" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="3665" max="3667" width="9.109375" style="328"/>
+    <col min="3668" max="3668" width="11.33203125" style="328" customWidth="1"/>
+    <col min="3669" max="3906" width="9.109375" style="328"/>
+    <col min="3907" max="3907" width="3.109375" style="328" customWidth="1"/>
+    <col min="3908" max="3908" width="3.44140625" style="328" customWidth="1"/>
+    <col min="3909" max="3909" width="7.33203125" style="328" customWidth="1"/>
+    <col min="3910" max="3910" width="13.5546875" style="328" customWidth="1"/>
+    <col min="3911" max="3911" width="7.109375" style="328" customWidth="1"/>
+    <col min="3912" max="3912" width="8.5546875" style="328" customWidth="1"/>
+    <col min="3913" max="3913" width="9" style="328" customWidth="1"/>
+    <col min="3914" max="3914" width="5.109375" style="328" customWidth="1"/>
+    <col min="3915" max="3915" width="8.44140625" style="328" customWidth="1"/>
+    <col min="3916" max="3916" width="17.109375" style="328" customWidth="1"/>
+    <col min="3917" max="3917" width="18" style="328" customWidth="1"/>
+    <col min="3918" max="3918" width="3.88671875" style="328" customWidth="1"/>
+    <col min="3919" max="3920" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="3921" max="3923" width="9.109375" style="328"/>
+    <col min="3924" max="3924" width="11.33203125" style="328" customWidth="1"/>
+    <col min="3925" max="4162" width="9.109375" style="328"/>
+    <col min="4163" max="4163" width="3.109375" style="328" customWidth="1"/>
+    <col min="4164" max="4164" width="3.44140625" style="328" customWidth="1"/>
+    <col min="4165" max="4165" width="7.33203125" style="328" customWidth="1"/>
+    <col min="4166" max="4166" width="13.5546875" style="328" customWidth="1"/>
+    <col min="4167" max="4167" width="7.109375" style="328" customWidth="1"/>
+    <col min="4168" max="4168" width="8.5546875" style="328" customWidth="1"/>
+    <col min="4169" max="4169" width="9" style="328" customWidth="1"/>
+    <col min="4170" max="4170" width="5.109375" style="328" customWidth="1"/>
+    <col min="4171" max="4171" width="8.44140625" style="328" customWidth="1"/>
+    <col min="4172" max="4172" width="17.109375" style="328" customWidth="1"/>
+    <col min="4173" max="4173" width="18" style="328" customWidth="1"/>
+    <col min="4174" max="4174" width="3.88671875" style="328" customWidth="1"/>
+    <col min="4175" max="4176" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="4177" max="4179" width="9.109375" style="328"/>
+    <col min="4180" max="4180" width="11.33203125" style="328" customWidth="1"/>
+    <col min="4181" max="4418" width="9.109375" style="328"/>
+    <col min="4419" max="4419" width="3.109375" style="328" customWidth="1"/>
+    <col min="4420" max="4420" width="3.44140625" style="328" customWidth="1"/>
+    <col min="4421" max="4421" width="7.33203125" style="328" customWidth="1"/>
+    <col min="4422" max="4422" width="13.5546875" style="328" customWidth="1"/>
+    <col min="4423" max="4423" width="7.109375" style="328" customWidth="1"/>
+    <col min="4424" max="4424" width="8.5546875" style="328" customWidth="1"/>
+    <col min="4425" max="4425" width="9" style="328" customWidth="1"/>
+    <col min="4426" max="4426" width="5.109375" style="328" customWidth="1"/>
+    <col min="4427" max="4427" width="8.44140625" style="328" customWidth="1"/>
+    <col min="4428" max="4428" width="17.109375" style="328" customWidth="1"/>
+    <col min="4429" max="4429" width="18" style="328" customWidth="1"/>
+    <col min="4430" max="4430" width="3.88671875" style="328" customWidth="1"/>
+    <col min="4431" max="4432" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="4433" max="4435" width="9.109375" style="328"/>
+    <col min="4436" max="4436" width="11.33203125" style="328" customWidth="1"/>
+    <col min="4437" max="4674" width="9.109375" style="328"/>
+    <col min="4675" max="4675" width="3.109375" style="328" customWidth="1"/>
+    <col min="4676" max="4676" width="3.44140625" style="328" customWidth="1"/>
+    <col min="4677" max="4677" width="7.33203125" style="328" customWidth="1"/>
+    <col min="4678" max="4678" width="13.5546875" style="328" customWidth="1"/>
+    <col min="4679" max="4679" width="7.109375" style="328" customWidth="1"/>
+    <col min="4680" max="4680" width="8.5546875" style="328" customWidth="1"/>
+    <col min="4681" max="4681" width="9" style="328" customWidth="1"/>
+    <col min="4682" max="4682" width="5.109375" style="328" customWidth="1"/>
+    <col min="4683" max="4683" width="8.44140625" style="328" customWidth="1"/>
+    <col min="4684" max="4684" width="17.109375" style="328" customWidth="1"/>
+    <col min="4685" max="4685" width="18" style="328" customWidth="1"/>
+    <col min="4686" max="4686" width="3.88671875" style="328" customWidth="1"/>
+    <col min="4687" max="4688" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="4689" max="4691" width="9.109375" style="328"/>
+    <col min="4692" max="4692" width="11.33203125" style="328" customWidth="1"/>
+    <col min="4693" max="4930" width="9.109375" style="328"/>
+    <col min="4931" max="4931" width="3.109375" style="328" customWidth="1"/>
+    <col min="4932" max="4932" width="3.44140625" style="328" customWidth="1"/>
+    <col min="4933" max="4933" width="7.33203125" style="328" customWidth="1"/>
+    <col min="4934" max="4934" width="13.5546875" style="328" customWidth="1"/>
+    <col min="4935" max="4935" width="7.109375" style="328" customWidth="1"/>
+    <col min="4936" max="4936" width="8.5546875" style="328" customWidth="1"/>
+    <col min="4937" max="4937" width="9" style="328" customWidth="1"/>
+    <col min="4938" max="4938" width="5.109375" style="328" customWidth="1"/>
+    <col min="4939" max="4939" width="8.44140625" style="328" customWidth="1"/>
+    <col min="4940" max="4940" width="17.109375" style="328" customWidth="1"/>
+    <col min="4941" max="4941" width="18" style="328" customWidth="1"/>
+    <col min="4942" max="4942" width="3.88671875" style="328" customWidth="1"/>
+    <col min="4943" max="4944" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="4945" max="4947" width="9.109375" style="328"/>
+    <col min="4948" max="4948" width="11.33203125" style="328" customWidth="1"/>
+    <col min="4949" max="5186" width="9.109375" style="328"/>
+    <col min="5187" max="5187" width="3.109375" style="328" customWidth="1"/>
+    <col min="5188" max="5188" width="3.44140625" style="328" customWidth="1"/>
+    <col min="5189" max="5189" width="7.33203125" style="328" customWidth="1"/>
+    <col min="5190" max="5190" width="13.5546875" style="328" customWidth="1"/>
+    <col min="5191" max="5191" width="7.109375" style="328" customWidth="1"/>
+    <col min="5192" max="5192" width="8.5546875" style="328" customWidth="1"/>
+    <col min="5193" max="5193" width="9" style="328" customWidth="1"/>
+    <col min="5194" max="5194" width="5.109375" style="328" customWidth="1"/>
+    <col min="5195" max="5195" width="8.44140625" style="328" customWidth="1"/>
+    <col min="5196" max="5196" width="17.109375" style="328" customWidth="1"/>
+    <col min="5197" max="5197" width="18" style="328" customWidth="1"/>
+    <col min="5198" max="5198" width="3.88671875" style="328" customWidth="1"/>
+    <col min="5199" max="5200" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="5201" max="5203" width="9.109375" style="328"/>
+    <col min="5204" max="5204" width="11.33203125" style="328" customWidth="1"/>
+    <col min="5205" max="5442" width="9.109375" style="328"/>
+    <col min="5443" max="5443" width="3.109375" style="328" customWidth="1"/>
+    <col min="5444" max="5444" width="3.44140625" style="328" customWidth="1"/>
+    <col min="5445" max="5445" width="7.33203125" style="328" customWidth="1"/>
+    <col min="5446" max="5446" width="13.5546875" style="328" customWidth="1"/>
+    <col min="5447" max="5447" width="7.109375" style="328" customWidth="1"/>
+    <col min="5448" max="5448" width="8.5546875" style="328" customWidth="1"/>
+    <col min="5449" max="5449" width="9" style="328" customWidth="1"/>
+    <col min="5450" max="5450" width="5.109375" style="328" customWidth="1"/>
+    <col min="5451" max="5451" width="8.44140625" style="328" customWidth="1"/>
+    <col min="5452" max="5452" width="17.109375" style="328" customWidth="1"/>
+    <col min="5453" max="5453" width="18" style="328" customWidth="1"/>
+    <col min="5454" max="5454" width="3.88671875" style="328" customWidth="1"/>
+    <col min="5455" max="5456" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="5457" max="5459" width="9.109375" style="328"/>
+    <col min="5460" max="5460" width="11.33203125" style="328" customWidth="1"/>
+    <col min="5461" max="5698" width="9.109375" style="328"/>
+    <col min="5699" max="5699" width="3.109375" style="328" customWidth="1"/>
+    <col min="5700" max="5700" width="3.44140625" style="328" customWidth="1"/>
+    <col min="5701" max="5701" width="7.33203125" style="328" customWidth="1"/>
+    <col min="5702" max="5702" width="13.5546875" style="328" customWidth="1"/>
+    <col min="5703" max="5703" width="7.109375" style="328" customWidth="1"/>
+    <col min="5704" max="5704" width="8.5546875" style="328" customWidth="1"/>
+    <col min="5705" max="5705" width="9" style="328" customWidth="1"/>
+    <col min="5706" max="5706" width="5.109375" style="328" customWidth="1"/>
+    <col min="5707" max="5707" width="8.44140625" style="328" customWidth="1"/>
+    <col min="5708" max="5708" width="17.109375" style="328" customWidth="1"/>
+    <col min="5709" max="5709" width="18" style="328" customWidth="1"/>
+    <col min="5710" max="5710" width="3.88671875" style="328" customWidth="1"/>
+    <col min="5711" max="5712" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="5713" max="5715" width="9.109375" style="328"/>
+    <col min="5716" max="5716" width="11.33203125" style="328" customWidth="1"/>
+    <col min="5717" max="5954" width="9.109375" style="328"/>
+    <col min="5955" max="5955" width="3.109375" style="328" customWidth="1"/>
+    <col min="5956" max="5956" width="3.44140625" style="328" customWidth="1"/>
+    <col min="5957" max="5957" width="7.33203125" style="328" customWidth="1"/>
+    <col min="5958" max="5958" width="13.5546875" style="328" customWidth="1"/>
+    <col min="5959" max="5959" width="7.109375" style="328" customWidth="1"/>
+    <col min="5960" max="5960" width="8.5546875" style="328" customWidth="1"/>
+    <col min="5961" max="5961" width="9" style="328" customWidth="1"/>
+    <col min="5962" max="5962" width="5.109375" style="328" customWidth="1"/>
+    <col min="5963" max="5963" width="8.44140625" style="328" customWidth="1"/>
+    <col min="5964" max="5964" width="17.109375" style="328" customWidth="1"/>
+    <col min="5965" max="5965" width="18" style="328" customWidth="1"/>
+    <col min="5966" max="5966" width="3.88671875" style="328" customWidth="1"/>
+    <col min="5967" max="5968" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="5969" max="5971" width="9.109375" style="328"/>
+    <col min="5972" max="5972" width="11.33203125" style="328" customWidth="1"/>
+    <col min="5973" max="6210" width="9.109375" style="328"/>
+    <col min="6211" max="6211" width="3.109375" style="328" customWidth="1"/>
+    <col min="6212" max="6212" width="3.44140625" style="328" customWidth="1"/>
+    <col min="6213" max="6213" width="7.33203125" style="328" customWidth="1"/>
+    <col min="6214" max="6214" width="13.5546875" style="328" customWidth="1"/>
+    <col min="6215" max="6215" width="7.109375" style="328" customWidth="1"/>
+    <col min="6216" max="6216" width="8.5546875" style="328" customWidth="1"/>
+    <col min="6217" max="6217" width="9" style="328" customWidth="1"/>
+    <col min="6218" max="6218" width="5.109375" style="328" customWidth="1"/>
+    <col min="6219" max="6219" width="8.44140625" style="328" customWidth="1"/>
+    <col min="6220" max="6220" width="17.109375" style="328" customWidth="1"/>
+    <col min="6221" max="6221" width="18" style="328" customWidth="1"/>
+    <col min="6222" max="6222" width="3.88671875" style="328" customWidth="1"/>
+    <col min="6223" max="6224" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="6225" max="6227" width="9.109375" style="328"/>
+    <col min="6228" max="6228" width="11.33203125" style="328" customWidth="1"/>
+    <col min="6229" max="6466" width="9.109375" style="328"/>
+    <col min="6467" max="6467" width="3.109375" style="328" customWidth="1"/>
+    <col min="6468" max="6468" width="3.44140625" style="328" customWidth="1"/>
+    <col min="6469" max="6469" width="7.33203125" style="328" customWidth="1"/>
+    <col min="6470" max="6470" width="13.5546875" style="328" customWidth="1"/>
+    <col min="6471" max="6471" width="7.109375" style="328" customWidth="1"/>
+    <col min="6472" max="6472" width="8.5546875" style="328" customWidth="1"/>
+    <col min="6473" max="6473" width="9" style="328" customWidth="1"/>
+    <col min="6474" max="6474" width="5.109375" style="328" customWidth="1"/>
+    <col min="6475" max="6475" width="8.44140625" style="328" customWidth="1"/>
+    <col min="6476" max="6476" width="17.109375" style="328" customWidth="1"/>
+    <col min="6477" max="6477" width="18" style="328" customWidth="1"/>
+    <col min="6478" max="6478" width="3.88671875" style="328" customWidth="1"/>
+    <col min="6479" max="6480" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="6481" max="6483" width="9.109375" style="328"/>
+    <col min="6484" max="6484" width="11.33203125" style="328" customWidth="1"/>
+    <col min="6485" max="6722" width="9.109375" style="328"/>
+    <col min="6723" max="6723" width="3.109375" style="328" customWidth="1"/>
+    <col min="6724" max="6724" width="3.44140625" style="328" customWidth="1"/>
+    <col min="6725" max="6725" width="7.33203125" style="328" customWidth="1"/>
+    <col min="6726" max="6726" width="13.5546875" style="328" customWidth="1"/>
+    <col min="6727" max="6727" width="7.109375" style="328" customWidth="1"/>
+    <col min="6728" max="6728" width="8.5546875" style="328" customWidth="1"/>
+    <col min="6729" max="6729" width="9" style="328" customWidth="1"/>
+    <col min="6730" max="6730" width="5.109375" style="328" customWidth="1"/>
+    <col min="6731" max="6731" width="8.44140625" style="328" customWidth="1"/>
+    <col min="6732" max="6732" width="17.109375" style="328" customWidth="1"/>
+    <col min="6733" max="6733" width="18" style="328" customWidth="1"/>
+    <col min="6734" max="6734" width="3.88671875" style="328" customWidth="1"/>
+    <col min="6735" max="6736" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="6737" max="6739" width="9.109375" style="328"/>
+    <col min="6740" max="6740" width="11.33203125" style="328" customWidth="1"/>
+    <col min="6741" max="6978" width="9.109375" style="328"/>
+    <col min="6979" max="6979" width="3.109375" style="328" customWidth="1"/>
+    <col min="6980" max="6980" width="3.44140625" style="328" customWidth="1"/>
+    <col min="6981" max="6981" width="7.33203125" style="328" customWidth="1"/>
+    <col min="6982" max="6982" width="13.5546875" style="328" customWidth="1"/>
+    <col min="6983" max="6983" width="7.109375" style="328" customWidth="1"/>
+    <col min="6984" max="6984" width="8.5546875" style="328" customWidth="1"/>
+    <col min="6985" max="6985" width="9" style="328" customWidth="1"/>
+    <col min="6986" max="6986" width="5.109375" style="328" customWidth="1"/>
+    <col min="6987" max="6987" width="8.44140625" style="328" customWidth="1"/>
+    <col min="6988" max="6988" width="17.109375" style="328" customWidth="1"/>
+    <col min="6989" max="6989" width="18" style="328" customWidth="1"/>
+    <col min="6990" max="6990" width="3.88671875" style="328" customWidth="1"/>
+    <col min="6991" max="6992" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="6993" max="6995" width="9.109375" style="328"/>
+    <col min="6996" max="6996" width="11.33203125" style="328" customWidth="1"/>
+    <col min="6997" max="7234" width="9.109375" style="328"/>
+    <col min="7235" max="7235" width="3.109375" style="328" customWidth="1"/>
+    <col min="7236" max="7236" width="3.44140625" style="328" customWidth="1"/>
+    <col min="7237" max="7237" width="7.33203125" style="328" customWidth="1"/>
+    <col min="7238" max="7238" width="13.5546875" style="328" customWidth="1"/>
+    <col min="7239" max="7239" width="7.109375" style="328" customWidth="1"/>
+    <col min="7240" max="7240" width="8.5546875" style="328" customWidth="1"/>
+    <col min="7241" max="7241" width="9" style="328" customWidth="1"/>
+    <col min="7242" max="7242" width="5.109375" style="328" customWidth="1"/>
+    <col min="7243" max="7243" width="8.44140625" style="328" customWidth="1"/>
+    <col min="7244" max="7244" width="17.109375" style="328" customWidth="1"/>
+    <col min="7245" max="7245" width="18" style="328" customWidth="1"/>
+    <col min="7246" max="7246" width="3.88671875" style="328" customWidth="1"/>
+    <col min="7247" max="7248" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="7249" max="7251" width="9.109375" style="328"/>
+    <col min="7252" max="7252" width="11.33203125" style="328" customWidth="1"/>
+    <col min="7253" max="7490" width="9.109375" style="328"/>
+    <col min="7491" max="7491" width="3.109375" style="328" customWidth="1"/>
+    <col min="7492" max="7492" width="3.44140625" style="328" customWidth="1"/>
+    <col min="7493" max="7493" width="7.33203125" style="328" customWidth="1"/>
+    <col min="7494" max="7494" width="13.5546875" style="328" customWidth="1"/>
+    <col min="7495" max="7495" width="7.109375" style="328" customWidth="1"/>
+    <col min="7496" max="7496" width="8.5546875" style="328" customWidth="1"/>
+    <col min="7497" max="7497" width="9" style="328" customWidth="1"/>
+    <col min="7498" max="7498" width="5.109375" style="328" customWidth="1"/>
+    <col min="7499" max="7499" width="8.44140625" style="328" customWidth="1"/>
+    <col min="7500" max="7500" width="17.109375" style="328" customWidth="1"/>
+    <col min="7501" max="7501" width="18" style="328" customWidth="1"/>
+    <col min="7502" max="7502" width="3.88671875" style="328" customWidth="1"/>
+    <col min="7503" max="7504" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="7505" max="7507" width="9.109375" style="328"/>
+    <col min="7508" max="7508" width="11.33203125" style="328" customWidth="1"/>
+    <col min="7509" max="7746" width="9.109375" style="328"/>
+    <col min="7747" max="7747" width="3.109375" style="328" customWidth="1"/>
+    <col min="7748" max="7748" width="3.44140625" style="328" customWidth="1"/>
+    <col min="7749" max="7749" width="7.33203125" style="328" customWidth="1"/>
+    <col min="7750" max="7750" width="13.5546875" style="328" customWidth="1"/>
+    <col min="7751" max="7751" width="7.109375" style="328" customWidth="1"/>
+    <col min="7752" max="7752" width="8.5546875" style="328" customWidth="1"/>
+    <col min="7753" max="7753" width="9" style="328" customWidth="1"/>
+    <col min="7754" max="7754" width="5.109375" style="328" customWidth="1"/>
+    <col min="7755" max="7755" width="8.44140625" style="328" customWidth="1"/>
+    <col min="7756" max="7756" width="17.109375" style="328" customWidth="1"/>
+    <col min="7757" max="7757" width="18" style="328" customWidth="1"/>
+    <col min="7758" max="7758" width="3.88671875" style="328" customWidth="1"/>
+    <col min="7759" max="7760" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="7761" max="7763" width="9.109375" style="328"/>
+    <col min="7764" max="7764" width="11.33203125" style="328" customWidth="1"/>
+    <col min="7765" max="8002" width="9.109375" style="328"/>
+    <col min="8003" max="8003" width="3.109375" style="328" customWidth="1"/>
+    <col min="8004" max="8004" width="3.44140625" style="328" customWidth="1"/>
+    <col min="8005" max="8005" width="7.33203125" style="328" customWidth="1"/>
+    <col min="8006" max="8006" width="13.5546875" style="328" customWidth="1"/>
+    <col min="8007" max="8007" width="7.109375" style="328" customWidth="1"/>
+    <col min="8008" max="8008" width="8.5546875" style="328" customWidth="1"/>
+    <col min="8009" max="8009" width="9" style="328" customWidth="1"/>
+    <col min="8010" max="8010" width="5.109375" style="328" customWidth="1"/>
+    <col min="8011" max="8011" width="8.44140625" style="328" customWidth="1"/>
+    <col min="8012" max="8012" width="17.109375" style="328" customWidth="1"/>
+    <col min="8013" max="8013" width="18" style="328" customWidth="1"/>
+    <col min="8014" max="8014" width="3.88671875" style="328" customWidth="1"/>
+    <col min="8015" max="8016" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="8017" max="8019" width="9.109375" style="328"/>
+    <col min="8020" max="8020" width="11.33203125" style="328" customWidth="1"/>
+    <col min="8021" max="8258" width="9.109375" style="328"/>
+    <col min="8259" max="8259" width="3.109375" style="328" customWidth="1"/>
+    <col min="8260" max="8260" width="3.44140625" style="328" customWidth="1"/>
+    <col min="8261" max="8261" width="7.33203125" style="328" customWidth="1"/>
+    <col min="8262" max="8262" width="13.5546875" style="328" customWidth="1"/>
+    <col min="8263" max="8263" width="7.109375" style="328" customWidth="1"/>
+    <col min="8264" max="8264" width="8.5546875" style="328" customWidth="1"/>
+    <col min="8265" max="8265" width="9" style="328" customWidth="1"/>
+    <col min="8266" max="8266" width="5.109375" style="328" customWidth="1"/>
+    <col min="8267" max="8267" width="8.44140625" style="328" customWidth="1"/>
+    <col min="8268" max="8268" width="17.109375" style="328" customWidth="1"/>
+    <col min="8269" max="8269" width="18" style="328" customWidth="1"/>
+    <col min="8270" max="8270" width="3.88671875" style="328" customWidth="1"/>
+    <col min="8271" max="8272" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="8273" max="8275" width="9.109375" style="328"/>
+    <col min="8276" max="8276" width="11.33203125" style="328" customWidth="1"/>
+    <col min="8277" max="8514" width="9.109375" style="328"/>
+    <col min="8515" max="8515" width="3.109375" style="328" customWidth="1"/>
+    <col min="8516" max="8516" width="3.44140625" style="328" customWidth="1"/>
+    <col min="8517" max="8517" width="7.33203125" style="328" customWidth="1"/>
+    <col min="8518" max="8518" width="13.5546875" style="328" customWidth="1"/>
+    <col min="8519" max="8519" width="7.109375" style="328" customWidth="1"/>
+    <col min="8520" max="8520" width="8.5546875" style="328" customWidth="1"/>
+    <col min="8521" max="8521" width="9" style="328" customWidth="1"/>
+    <col min="8522" max="8522" width="5.109375" style="328" customWidth="1"/>
+    <col min="8523" max="8523" width="8.44140625" style="328" customWidth="1"/>
+    <col min="8524" max="8524" width="17.109375" style="328" customWidth="1"/>
+    <col min="8525" max="8525" width="18" style="328" customWidth="1"/>
+    <col min="8526" max="8526" width="3.88671875" style="328" customWidth="1"/>
+    <col min="8527" max="8528" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="8529" max="8531" width="9.109375" style="328"/>
+    <col min="8532" max="8532" width="11.33203125" style="328" customWidth="1"/>
+    <col min="8533" max="8770" width="9.109375" style="328"/>
+    <col min="8771" max="8771" width="3.109375" style="328" customWidth="1"/>
+    <col min="8772" max="8772" width="3.44140625" style="328" customWidth="1"/>
+    <col min="8773" max="8773" width="7.33203125" style="328" customWidth="1"/>
+    <col min="8774" max="8774" width="13.5546875" style="328" customWidth="1"/>
+    <col min="8775" max="8775" width="7.109375" style="328" customWidth="1"/>
+    <col min="8776" max="8776" width="8.5546875" style="328" customWidth="1"/>
+    <col min="8777" max="8777" width="9" style="328" customWidth="1"/>
+    <col min="8778" max="8778" width="5.109375" style="328" customWidth="1"/>
+    <col min="8779" max="8779" width="8.44140625" style="328" customWidth="1"/>
+    <col min="8780" max="8780" width="17.109375" style="328" customWidth="1"/>
+    <col min="8781" max="8781" width="18" style="328" customWidth="1"/>
+    <col min="8782" max="8782" width="3.88671875" style="328" customWidth="1"/>
+    <col min="8783" max="8784" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="8785" max="8787" width="9.109375" style="328"/>
+    <col min="8788" max="8788" width="11.33203125" style="328" customWidth="1"/>
+    <col min="8789" max="9026" width="9.109375" style="328"/>
+    <col min="9027" max="9027" width="3.109375" style="328" customWidth="1"/>
+    <col min="9028" max="9028" width="3.44140625" style="328" customWidth="1"/>
+    <col min="9029" max="9029" width="7.33203125" style="328" customWidth="1"/>
+    <col min="9030" max="9030" width="13.5546875" style="328" customWidth="1"/>
+    <col min="9031" max="9031" width="7.109375" style="328" customWidth="1"/>
+    <col min="9032" max="9032" width="8.5546875" style="328" customWidth="1"/>
+    <col min="9033" max="9033" width="9" style="328" customWidth="1"/>
+    <col min="9034" max="9034" width="5.109375" style="328" customWidth="1"/>
+    <col min="9035" max="9035" width="8.44140625" style="328" customWidth="1"/>
+    <col min="9036" max="9036" width="17.109375" style="328" customWidth="1"/>
+    <col min="9037" max="9037" width="18" style="328" customWidth="1"/>
+    <col min="9038" max="9038" width="3.88671875" style="328" customWidth="1"/>
+    <col min="9039" max="9040" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="9041" max="9043" width="9.109375" style="328"/>
+    <col min="9044" max="9044" width="11.33203125" style="328" customWidth="1"/>
+    <col min="9045" max="9282" width="9.109375" style="328"/>
+    <col min="9283" max="9283" width="3.109375" style="328" customWidth="1"/>
+    <col min="9284" max="9284" width="3.44140625" style="328" customWidth="1"/>
+    <col min="9285" max="9285" width="7.33203125" style="328" customWidth="1"/>
+    <col min="9286" max="9286" width="13.5546875" style="328" customWidth="1"/>
+    <col min="9287" max="9287" width="7.109375" style="328" customWidth="1"/>
+    <col min="9288" max="9288" width="8.5546875" style="328" customWidth="1"/>
+    <col min="9289" max="9289" width="9" style="328" customWidth="1"/>
+    <col min="9290" max="9290" width="5.109375" style="328" customWidth="1"/>
+    <col min="9291" max="9291" width="8.44140625" style="328" customWidth="1"/>
+    <col min="9292" max="9292" width="17.109375" style="328" customWidth="1"/>
+    <col min="9293" max="9293" width="18" style="328" customWidth="1"/>
+    <col min="9294" max="9294" width="3.88671875" style="328" customWidth="1"/>
+    <col min="9295" max="9296" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="9297" max="9299" width="9.109375" style="328"/>
+    <col min="9300" max="9300" width="11.33203125" style="328" customWidth="1"/>
+    <col min="9301" max="9538" width="9.109375" style="328"/>
+    <col min="9539" max="9539" width="3.109375" style="328" customWidth="1"/>
+    <col min="9540" max="9540" width="3.44140625" style="328" customWidth="1"/>
+    <col min="9541" max="9541" width="7.33203125" style="328" customWidth="1"/>
+    <col min="9542" max="9542" width="13.5546875" style="328" customWidth="1"/>
+    <col min="9543" max="9543" width="7.109375" style="328" customWidth="1"/>
+    <col min="9544" max="9544" width="8.5546875" style="328" customWidth="1"/>
+    <col min="9545" max="9545" width="9" style="328" customWidth="1"/>
+    <col min="9546" max="9546" width="5.109375" style="328" customWidth="1"/>
+    <col min="9547" max="9547" width="8.44140625" style="328" customWidth="1"/>
+    <col min="9548" max="9548" width="17.109375" style="328" customWidth="1"/>
+    <col min="9549" max="9549" width="18" style="328" customWidth="1"/>
+    <col min="9550" max="9550" width="3.88671875" style="328" customWidth="1"/>
+    <col min="9551" max="9552" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="9553" max="9555" width="9.109375" style="328"/>
+    <col min="9556" max="9556" width="11.33203125" style="328" customWidth="1"/>
+    <col min="9557" max="9794" width="9.109375" style="328"/>
+    <col min="9795" max="9795" width="3.109375" style="328" customWidth="1"/>
+    <col min="9796" max="9796" width="3.44140625" style="328" customWidth="1"/>
+    <col min="9797" max="9797" width="7.33203125" style="328" customWidth="1"/>
+    <col min="9798" max="9798" width="13.5546875" style="328" customWidth="1"/>
+    <col min="9799" max="9799" width="7.109375" style="328" customWidth="1"/>
+    <col min="9800" max="9800" width="8.5546875" style="328" customWidth="1"/>
+    <col min="9801" max="9801" width="9" style="328" customWidth="1"/>
+    <col min="9802" max="9802" width="5.109375" style="328" customWidth="1"/>
+    <col min="9803" max="9803" width="8.44140625" style="328" customWidth="1"/>
+    <col min="9804" max="9804" width="17.109375" style="328" customWidth="1"/>
+    <col min="9805" max="9805" width="18" style="328" customWidth="1"/>
+    <col min="9806" max="9806" width="3.88671875" style="328" customWidth="1"/>
+    <col min="9807" max="9808" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="9809" max="9811" width="9.109375" style="328"/>
+    <col min="9812" max="9812" width="11.33203125" style="328" customWidth="1"/>
+    <col min="9813" max="10050" width="9.109375" style="328"/>
+    <col min="10051" max="10051" width="3.109375" style="328" customWidth="1"/>
+    <col min="10052" max="10052" width="3.44140625" style="328" customWidth="1"/>
+    <col min="10053" max="10053" width="7.33203125" style="328" customWidth="1"/>
+    <col min="10054" max="10054" width="13.5546875" style="328" customWidth="1"/>
+    <col min="10055" max="10055" width="7.109375" style="328" customWidth="1"/>
+    <col min="10056" max="10056" width="8.5546875" style="328" customWidth="1"/>
+    <col min="10057" max="10057" width="9" style="328" customWidth="1"/>
+    <col min="10058" max="10058" width="5.109375" style="328" customWidth="1"/>
+    <col min="10059" max="10059" width="8.44140625" style="328" customWidth="1"/>
+    <col min="10060" max="10060" width="17.109375" style="328" customWidth="1"/>
+    <col min="10061" max="10061" width="18" style="328" customWidth="1"/>
+    <col min="10062" max="10062" width="3.88671875" style="328" customWidth="1"/>
+    <col min="10063" max="10064" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="10065" max="10067" width="9.109375" style="328"/>
+    <col min="10068" max="10068" width="11.33203125" style="328" customWidth="1"/>
+    <col min="10069" max="10306" width="9.109375" style="328"/>
+    <col min="10307" max="10307" width="3.109375" style="328" customWidth="1"/>
+    <col min="10308" max="10308" width="3.44140625" style="328" customWidth="1"/>
+    <col min="10309" max="10309" width="7.33203125" style="328" customWidth="1"/>
+    <col min="10310" max="10310" width="13.5546875" style="328" customWidth="1"/>
+    <col min="10311" max="10311" width="7.109375" style="328" customWidth="1"/>
+    <col min="10312" max="10312" width="8.5546875" style="328" customWidth="1"/>
+    <col min="10313" max="10313" width="9" style="328" customWidth="1"/>
+    <col min="10314" max="10314" width="5.109375" style="328" customWidth="1"/>
+    <col min="10315" max="10315" width="8.44140625" style="328" customWidth="1"/>
+    <col min="10316" max="10316" width="17.109375" style="328" customWidth="1"/>
+    <col min="10317" max="10317" width="18" style="328" customWidth="1"/>
+    <col min="10318" max="10318" width="3.88671875" style="328" customWidth="1"/>
+    <col min="10319" max="10320" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="10321" max="10323" width="9.109375" style="328"/>
+    <col min="10324" max="10324" width="11.33203125" style="328" customWidth="1"/>
+    <col min="10325" max="10562" width="9.109375" style="328"/>
+    <col min="10563" max="10563" width="3.109375" style="328" customWidth="1"/>
+    <col min="10564" max="10564" width="3.44140625" style="328" customWidth="1"/>
+    <col min="10565" max="10565" width="7.33203125" style="328" customWidth="1"/>
+    <col min="10566" max="10566" width="13.5546875" style="328" customWidth="1"/>
+    <col min="10567" max="10567" width="7.109375" style="328" customWidth="1"/>
+    <col min="10568" max="10568" width="8.5546875" style="328" customWidth="1"/>
+    <col min="10569" max="10569" width="9" style="328" customWidth="1"/>
+    <col min="10570" max="10570" width="5.109375" style="328" customWidth="1"/>
+    <col min="10571" max="10571" width="8.44140625" style="328" customWidth="1"/>
+    <col min="10572" max="10572" width="17.109375" style="328" customWidth="1"/>
+    <col min="10573" max="10573" width="18" style="328" customWidth="1"/>
+    <col min="10574" max="10574" width="3.88671875" style="328" customWidth="1"/>
+    <col min="10575" max="10576" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="10577" max="10579" width="9.109375" style="328"/>
+    <col min="10580" max="10580" width="11.33203125" style="328" customWidth="1"/>
+    <col min="10581" max="10818" width="9.109375" style="328"/>
+    <col min="10819" max="10819" width="3.109375" style="328" customWidth="1"/>
+    <col min="10820" max="10820" width="3.44140625" style="328" customWidth="1"/>
+    <col min="10821" max="10821" width="7.33203125" style="328" customWidth="1"/>
+    <col min="10822" max="10822" width="13.5546875" style="328" customWidth="1"/>
+    <col min="10823" max="10823" width="7.109375" style="328" customWidth="1"/>
+    <col min="10824" max="10824" width="8.5546875" style="328" customWidth="1"/>
+    <col min="10825" max="10825" width="9" style="328" customWidth="1"/>
+    <col min="10826" max="10826" width="5.109375" style="328" customWidth="1"/>
+    <col min="10827" max="10827" width="8.44140625" style="328" customWidth="1"/>
+    <col min="10828" max="10828" width="17.109375" style="328" customWidth="1"/>
+    <col min="10829" max="10829" width="18" style="328" customWidth="1"/>
+    <col min="10830" max="10830" width="3.88671875" style="328" customWidth="1"/>
+    <col min="10831" max="10832" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="10833" max="10835" width="9.109375" style="328"/>
+    <col min="10836" max="10836" width="11.33203125" style="328" customWidth="1"/>
+    <col min="10837" max="11074" width="9.109375" style="328"/>
+    <col min="11075" max="11075" width="3.109375" style="328" customWidth="1"/>
+    <col min="11076" max="11076" width="3.44140625" style="328" customWidth="1"/>
+    <col min="11077" max="11077" width="7.33203125" style="328" customWidth="1"/>
+    <col min="11078" max="11078" width="13.5546875" style="328" customWidth="1"/>
+    <col min="11079" max="11079" width="7.109375" style="328" customWidth="1"/>
+    <col min="11080" max="11080" width="8.5546875" style="328" customWidth="1"/>
+    <col min="11081" max="11081" width="9" style="328" customWidth="1"/>
+    <col min="11082" max="11082" width="5.109375" style="328" customWidth="1"/>
+    <col min="11083" max="11083" width="8.44140625" style="328" customWidth="1"/>
+    <col min="11084" max="11084" width="17.109375" style="328" customWidth="1"/>
+    <col min="11085" max="11085" width="18" style="328" customWidth="1"/>
+    <col min="11086" max="11086" width="3.88671875" style="328" customWidth="1"/>
+    <col min="11087" max="11088" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="11089" max="11091" width="9.109375" style="328"/>
+    <col min="11092" max="11092" width="11.33203125" style="328" customWidth="1"/>
+    <col min="11093" max="11330" width="9.109375" style="328"/>
+    <col min="11331" max="11331" width="3.109375" style="328" customWidth="1"/>
+    <col min="11332" max="11332" width="3.44140625" style="328" customWidth="1"/>
+    <col min="11333" max="11333" width="7.33203125" style="328" customWidth="1"/>
+    <col min="11334" max="11334" width="13.5546875" style="328" customWidth="1"/>
+    <col min="11335" max="11335" width="7.109375" style="328" customWidth="1"/>
+    <col min="11336" max="11336" width="8.5546875" style="328" customWidth="1"/>
+    <col min="11337" max="11337" width="9" style="328" customWidth="1"/>
+    <col min="11338" max="11338" width="5.109375" style="328" customWidth="1"/>
+    <col min="11339" max="11339" width="8.44140625" style="328" customWidth="1"/>
+    <col min="11340" max="11340" width="17.109375" style="328" customWidth="1"/>
+    <col min="11341" max="11341" width="18" style="328" customWidth="1"/>
+    <col min="11342" max="11342" width="3.88671875" style="328" customWidth="1"/>
+    <col min="11343" max="11344" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="11345" max="11347" width="9.109375" style="328"/>
+    <col min="11348" max="11348" width="11.33203125" style="328" customWidth="1"/>
+    <col min="11349" max="11586" width="9.109375" style="328"/>
+    <col min="11587" max="11587" width="3.109375" style="328" customWidth="1"/>
+    <col min="11588" max="11588" width="3.44140625" style="328" customWidth="1"/>
+    <col min="11589" max="11589" width="7.33203125" style="328" customWidth="1"/>
+    <col min="11590" max="11590" width="13.5546875" style="328" customWidth="1"/>
+    <col min="11591" max="11591" width="7.109375" style="328" customWidth="1"/>
+    <col min="11592" max="11592" width="8.5546875" style="328" customWidth="1"/>
+    <col min="11593" max="11593" width="9" style="328" customWidth="1"/>
+    <col min="11594" max="11594" width="5.109375" style="328" customWidth="1"/>
+    <col min="11595" max="11595" width="8.44140625" style="328" customWidth="1"/>
+    <col min="11596" max="11596" width="17.109375" style="328" customWidth="1"/>
+    <col min="11597" max="11597" width="18" style="328" customWidth="1"/>
+    <col min="11598" max="11598" width="3.88671875" style="328" customWidth="1"/>
+    <col min="11599" max="11600" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="11601" max="11603" width="9.109375" style="328"/>
+    <col min="11604" max="11604" width="11.33203125" style="328" customWidth="1"/>
+    <col min="11605" max="11842" width="9.109375" style="328"/>
+    <col min="11843" max="11843" width="3.109375" style="328" customWidth="1"/>
+    <col min="11844" max="11844" width="3.44140625" style="328" customWidth="1"/>
+    <col min="11845" max="11845" width="7.33203125" style="328" customWidth="1"/>
+    <col min="11846" max="11846" width="13.5546875" style="328" customWidth="1"/>
+    <col min="11847" max="11847" width="7.109375" style="328" customWidth="1"/>
+    <col min="11848" max="11848" width="8.5546875" style="328" customWidth="1"/>
+    <col min="11849" max="11849" width="9" style="328" customWidth="1"/>
+    <col min="11850" max="11850" width="5.109375" style="328" customWidth="1"/>
+    <col min="11851" max="11851" width="8.44140625" style="328" customWidth="1"/>
+    <col min="11852" max="11852" width="17.109375" style="328" customWidth="1"/>
+    <col min="11853" max="11853" width="18" style="328" customWidth="1"/>
+    <col min="11854" max="11854" width="3.88671875" style="328" customWidth="1"/>
+    <col min="11855" max="11856" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="11857" max="11859" width="9.109375" style="328"/>
+    <col min="11860" max="11860" width="11.33203125" style="328" customWidth="1"/>
+    <col min="11861" max="12098" width="9.109375" style="328"/>
+    <col min="12099" max="12099" width="3.109375" style="328" customWidth="1"/>
+    <col min="12100" max="12100" width="3.44140625" style="328" customWidth="1"/>
+    <col min="12101" max="12101" width="7.33203125" style="328" customWidth="1"/>
+    <col min="12102" max="12102" width="13.5546875" style="328" customWidth="1"/>
+    <col min="12103" max="12103" width="7.109375" style="328" customWidth="1"/>
+    <col min="12104" max="12104" width="8.5546875" style="328" customWidth="1"/>
+    <col min="12105" max="12105" width="9" style="328" customWidth="1"/>
+    <col min="12106" max="12106" width="5.109375" style="328" customWidth="1"/>
+    <col min="12107" max="12107" width="8.44140625" style="328" customWidth="1"/>
+    <col min="12108" max="12108" width="17.109375" style="328" customWidth="1"/>
+    <col min="12109" max="12109" width="18" style="328" customWidth="1"/>
+    <col min="12110" max="12110" width="3.88671875" style="328" customWidth="1"/>
+    <col min="12111" max="12112" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="12113" max="12115" width="9.109375" style="328"/>
+    <col min="12116" max="12116" width="11.33203125" style="328" customWidth="1"/>
+    <col min="12117" max="12354" width="9.109375" style="328"/>
+    <col min="12355" max="12355" width="3.109375" style="328" customWidth="1"/>
+    <col min="12356" max="12356" width="3.44140625" style="328" customWidth="1"/>
+    <col min="12357" max="12357" width="7.33203125" style="328" customWidth="1"/>
+    <col min="12358" max="12358" width="13.5546875" style="328" customWidth="1"/>
+    <col min="12359" max="12359" width="7.109375" style="328" customWidth="1"/>
+    <col min="12360" max="12360" width="8.5546875" style="328" customWidth="1"/>
+    <col min="12361" max="12361" width="9" style="328" customWidth="1"/>
+    <col min="12362" max="12362" width="5.109375" style="328" customWidth="1"/>
+    <col min="12363" max="12363" width="8.44140625" style="328" customWidth="1"/>
+    <col min="12364" max="12364" width="17.109375" style="328" customWidth="1"/>
+    <col min="12365" max="12365" width="18" style="328" customWidth="1"/>
+    <col min="12366" max="12366" width="3.88671875" style="328" customWidth="1"/>
+    <col min="12367" max="12368" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="12369" max="12371" width="9.109375" style="328"/>
+    <col min="12372" max="12372" width="11.33203125" style="328" customWidth="1"/>
+    <col min="12373" max="12610" width="9.109375" style="328"/>
+    <col min="12611" max="12611" width="3.109375" style="328" customWidth="1"/>
+    <col min="12612" max="12612" width="3.44140625" style="328" customWidth="1"/>
+    <col min="12613" max="12613" width="7.33203125" style="328" customWidth="1"/>
+    <col min="12614" max="12614" width="13.5546875" style="328" customWidth="1"/>
+    <col min="12615" max="12615" width="7.109375" style="328" customWidth="1"/>
+    <col min="12616" max="12616" width="8.5546875" style="328" customWidth="1"/>
+    <col min="12617" max="12617" width="9" style="328" customWidth="1"/>
+    <col min="12618" max="12618" width="5.109375" style="328" customWidth="1"/>
+    <col min="12619" max="12619" width="8.44140625" style="328" customWidth="1"/>
+    <col min="12620" max="12620" width="17.109375" style="328" customWidth="1"/>
+    <col min="12621" max="12621" width="18" style="328" customWidth="1"/>
+    <col min="12622" max="12622" width="3.88671875" style="328" customWidth="1"/>
+    <col min="12623" max="12624" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="12625" max="12627" width="9.109375" style="328"/>
+    <col min="12628" max="12628" width="11.33203125" style="328" customWidth="1"/>
+    <col min="12629" max="12866" width="9.109375" style="328"/>
+    <col min="12867" max="12867" width="3.109375" style="328" customWidth="1"/>
+    <col min="12868" max="12868" width="3.44140625" style="328" customWidth="1"/>
+    <col min="12869" max="12869" width="7.33203125" style="328" customWidth="1"/>
+    <col min="12870" max="12870" width="13.5546875" style="328" customWidth="1"/>
+    <col min="12871" max="12871" width="7.109375" style="328" customWidth="1"/>
+    <col min="12872" max="12872" width="8.5546875" style="328" customWidth="1"/>
+    <col min="12873" max="12873" width="9" style="328" customWidth="1"/>
+    <col min="12874" max="12874" width="5.109375" style="328" customWidth="1"/>
+    <col min="12875" max="12875" width="8.44140625" style="328" customWidth="1"/>
+    <col min="12876" max="12876" width="17.109375" style="328" customWidth="1"/>
+    <col min="12877" max="12877" width="18" style="328" customWidth="1"/>
+    <col min="12878" max="12878" width="3.88671875" style="328" customWidth="1"/>
+    <col min="12879" max="12880" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="12881" max="12883" width="9.109375" style="328"/>
+    <col min="12884" max="12884" width="11.33203125" style="328" customWidth="1"/>
+    <col min="12885" max="13122" width="9.109375" style="328"/>
+    <col min="13123" max="13123" width="3.109375" style="328" customWidth="1"/>
+    <col min="13124" max="13124" width="3.44140625" style="328" customWidth="1"/>
+    <col min="13125" max="13125" width="7.33203125" style="328" customWidth="1"/>
+    <col min="13126" max="13126" width="13.5546875" style="328" customWidth="1"/>
+    <col min="13127" max="13127" width="7.109375" style="328" customWidth="1"/>
+    <col min="13128" max="13128" width="8.5546875" style="328" customWidth="1"/>
+    <col min="13129" max="13129" width="9" style="328" customWidth="1"/>
+    <col min="13130" max="13130" width="5.109375" style="328" customWidth="1"/>
+    <col min="13131" max="13131" width="8.44140625" style="328" customWidth="1"/>
+    <col min="13132" max="13132" width="17.109375" style="328" customWidth="1"/>
+    <col min="13133" max="13133" width="18" style="328" customWidth="1"/>
+    <col min="13134" max="13134" width="3.88671875" style="328" customWidth="1"/>
+    <col min="13135" max="13136" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="13137" max="13139" width="9.109375" style="328"/>
+    <col min="13140" max="13140" width="11.33203125" style="328" customWidth="1"/>
+    <col min="13141" max="13378" width="9.109375" style="328"/>
+    <col min="13379" max="13379" width="3.109375" style="328" customWidth="1"/>
+    <col min="13380" max="13380" width="3.44140625" style="328" customWidth="1"/>
+    <col min="13381" max="13381" width="7.33203125" style="328" customWidth="1"/>
+    <col min="13382" max="13382" width="13.5546875" style="328" customWidth="1"/>
+    <col min="13383" max="13383" width="7.109375" style="328" customWidth="1"/>
+    <col min="13384" max="13384" width="8.5546875" style="328" customWidth="1"/>
+    <col min="13385" max="13385" width="9" style="328" customWidth="1"/>
+    <col min="13386" max="13386" width="5.109375" style="328" customWidth="1"/>
+    <col min="13387" max="13387" width="8.44140625" style="328" customWidth="1"/>
+    <col min="13388" max="13388" width="17.109375" style="328" customWidth="1"/>
+    <col min="13389" max="13389" width="18" style="328" customWidth="1"/>
+    <col min="13390" max="13390" width="3.88671875" style="328" customWidth="1"/>
+    <col min="13391" max="13392" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="13393" max="13395" width="9.109375" style="328"/>
+    <col min="13396" max="13396" width="11.33203125" style="328" customWidth="1"/>
+    <col min="13397" max="13634" width="9.109375" style="328"/>
+    <col min="13635" max="13635" width="3.109375" style="328" customWidth="1"/>
+    <col min="13636" max="13636" width="3.44140625" style="328" customWidth="1"/>
+    <col min="13637" max="13637" width="7.33203125" style="328" customWidth="1"/>
+    <col min="13638" max="13638" width="13.5546875" style="328" customWidth="1"/>
+    <col min="13639" max="13639" width="7.109375" style="328" customWidth="1"/>
+    <col min="13640" max="13640" width="8.5546875" style="328" customWidth="1"/>
+    <col min="13641" max="13641" width="9" style="328" customWidth="1"/>
+    <col min="13642" max="13642" width="5.109375" style="328" customWidth="1"/>
+    <col min="13643" max="13643" width="8.44140625" style="328" customWidth="1"/>
+    <col min="13644" max="13644" width="17.109375" style="328" customWidth="1"/>
+    <col min="13645" max="13645" width="18" style="328" customWidth="1"/>
+    <col min="13646" max="13646" width="3.88671875" style="328" customWidth="1"/>
+    <col min="13647" max="13648" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="13649" max="13651" width="9.109375" style="328"/>
+    <col min="13652" max="13652" width="11.33203125" style="328" customWidth="1"/>
+    <col min="13653" max="13890" width="9.109375" style="328"/>
+    <col min="13891" max="13891" width="3.109375" style="328" customWidth="1"/>
+    <col min="13892" max="13892" width="3.44140625" style="328" customWidth="1"/>
+    <col min="13893" max="13893" width="7.33203125" style="328" customWidth="1"/>
+    <col min="13894" max="13894" width="13.5546875" style="328" customWidth="1"/>
+    <col min="13895" max="13895" width="7.109375" style="328" customWidth="1"/>
+    <col min="13896" max="13896" width="8.5546875" style="328" customWidth="1"/>
+    <col min="13897" max="13897" width="9" style="328" customWidth="1"/>
+    <col min="13898" max="13898" width="5.109375" style="328" customWidth="1"/>
+    <col min="13899" max="13899" width="8.44140625" style="328" customWidth="1"/>
+    <col min="13900" max="13900" width="17.109375" style="328" customWidth="1"/>
+    <col min="13901" max="13901" width="18" style="328" customWidth="1"/>
+    <col min="13902" max="13902" width="3.88671875" style="328" customWidth="1"/>
+    <col min="13903" max="13904" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="13905" max="13907" width="9.109375" style="328"/>
+    <col min="13908" max="13908" width="11.33203125" style="328" customWidth="1"/>
+    <col min="13909" max="14146" width="9.109375" style="328"/>
+    <col min="14147" max="14147" width="3.109375" style="328" customWidth="1"/>
+    <col min="14148" max="14148" width="3.44140625" style="328" customWidth="1"/>
+    <col min="14149" max="14149" width="7.33203125" style="328" customWidth="1"/>
+    <col min="14150" max="14150" width="13.5546875" style="328" customWidth="1"/>
+    <col min="14151" max="14151" width="7.109375" style="328" customWidth="1"/>
+    <col min="14152" max="14152" width="8.5546875" style="328" customWidth="1"/>
+    <col min="14153" max="14153" width="9" style="328" customWidth="1"/>
+    <col min="14154" max="14154" width="5.109375" style="328" customWidth="1"/>
+    <col min="14155" max="14155" width="8.44140625" style="328" customWidth="1"/>
+    <col min="14156" max="14156" width="17.109375" style="328" customWidth="1"/>
+    <col min="14157" max="14157" width="18" style="328" customWidth="1"/>
+    <col min="14158" max="14158" width="3.88671875" style="328" customWidth="1"/>
+    <col min="14159" max="14160" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="14161" max="14163" width="9.109375" style="328"/>
+    <col min="14164" max="14164" width="11.33203125" style="328" customWidth="1"/>
+    <col min="14165" max="14402" width="9.109375" style="328"/>
+    <col min="14403" max="14403" width="3.109375" style="328" customWidth="1"/>
+    <col min="14404" max="14404" width="3.44140625" style="328" customWidth="1"/>
+    <col min="14405" max="14405" width="7.33203125" style="328" customWidth="1"/>
+    <col min="14406" max="14406" width="13.5546875" style="328" customWidth="1"/>
+    <col min="14407" max="14407" width="7.109375" style="328" customWidth="1"/>
+    <col min="14408" max="14408" width="8.5546875" style="328" customWidth="1"/>
+    <col min="14409" max="14409" width="9" style="328" customWidth="1"/>
+    <col min="14410" max="14410" width="5.109375" style="328" customWidth="1"/>
+    <col min="14411" max="14411" width="8.44140625" style="328" customWidth="1"/>
+    <col min="14412" max="14412" width="17.109375" style="328" customWidth="1"/>
+    <col min="14413" max="14413" width="18" style="328" customWidth="1"/>
+    <col min="14414" max="14414" width="3.88671875" style="328" customWidth="1"/>
+    <col min="14415" max="14416" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="14417" max="14419" width="9.109375" style="328"/>
+    <col min="14420" max="14420" width="11.33203125" style="328" customWidth="1"/>
+    <col min="14421" max="14658" width="9.109375" style="328"/>
+    <col min="14659" max="14659" width="3.109375" style="328" customWidth="1"/>
+    <col min="14660" max="14660" width="3.44140625" style="328" customWidth="1"/>
+    <col min="14661" max="14661" width="7.33203125" style="328" customWidth="1"/>
+    <col min="14662" max="14662" width="13.5546875" style="328" customWidth="1"/>
+    <col min="14663" max="14663" width="7.109375" style="328" customWidth="1"/>
+    <col min="14664" max="14664" width="8.5546875" style="328" customWidth="1"/>
+    <col min="14665" max="14665" width="9" style="328" customWidth="1"/>
+    <col min="14666" max="14666" width="5.109375" style="328" customWidth="1"/>
+    <col min="14667" max="14667" width="8.44140625" style="328" customWidth="1"/>
+    <col min="14668" max="14668" width="17.109375" style="328" customWidth="1"/>
+    <col min="14669" max="14669" width="18" style="328" customWidth="1"/>
+    <col min="14670" max="14670" width="3.88671875" style="328" customWidth="1"/>
+    <col min="14671" max="14672" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="14673" max="14675" width="9.109375" style="328"/>
+    <col min="14676" max="14676" width="11.33203125" style="328" customWidth="1"/>
+    <col min="14677" max="14914" width="9.109375" style="328"/>
+    <col min="14915" max="14915" width="3.109375" style="328" customWidth="1"/>
+    <col min="14916" max="14916" width="3.44140625" style="328" customWidth="1"/>
+    <col min="14917" max="14917" width="7.33203125" style="328" customWidth="1"/>
+    <col min="14918" max="14918" width="13.5546875" style="328" customWidth="1"/>
+    <col min="14919" max="14919" width="7.109375" style="328" customWidth="1"/>
+    <col min="14920" max="14920" width="8.5546875" style="328" customWidth="1"/>
+    <col min="14921" max="14921" width="9" style="328" customWidth="1"/>
+    <col min="14922" max="14922" width="5.109375" style="328" customWidth="1"/>
+    <col min="14923" max="14923" width="8.44140625" style="328" customWidth="1"/>
+    <col min="14924" max="14924" width="17.109375" style="328" customWidth="1"/>
+    <col min="14925" max="14925" width="18" style="328" customWidth="1"/>
+    <col min="14926" max="14926" width="3.88671875" style="328" customWidth="1"/>
+    <col min="14927" max="14928" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="14929" max="14931" width="9.109375" style="328"/>
+    <col min="14932" max="14932" width="11.33203125" style="328" customWidth="1"/>
+    <col min="14933" max="15170" width="9.109375" style="328"/>
+    <col min="15171" max="15171" width="3.109375" style="328" customWidth="1"/>
+    <col min="15172" max="15172" width="3.44140625" style="328" customWidth="1"/>
+    <col min="15173" max="15173" width="7.33203125" style="328" customWidth="1"/>
+    <col min="15174" max="15174" width="13.5546875" style="328" customWidth="1"/>
+    <col min="15175" max="15175" width="7.109375" style="328" customWidth="1"/>
+    <col min="15176" max="15176" width="8.5546875" style="328" customWidth="1"/>
+    <col min="15177" max="15177" width="9" style="328" customWidth="1"/>
+    <col min="15178" max="15178" width="5.109375" style="328" customWidth="1"/>
+    <col min="15179" max="15179" width="8.44140625" style="328" customWidth="1"/>
+    <col min="15180" max="15180" width="17.109375" style="328" customWidth="1"/>
+    <col min="15181" max="15181" width="18" style="328" customWidth="1"/>
+    <col min="15182" max="15182" width="3.88671875" style="328" customWidth="1"/>
+    <col min="15183" max="15184" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="15185" max="15187" width="9.109375" style="328"/>
+    <col min="15188" max="15188" width="11.33203125" style="328" customWidth="1"/>
+    <col min="15189" max="15426" width="9.109375" style="328"/>
+    <col min="15427" max="15427" width="3.109375" style="328" customWidth="1"/>
+    <col min="15428" max="15428" width="3.44140625" style="328" customWidth="1"/>
+    <col min="15429" max="15429" width="7.33203125" style="328" customWidth="1"/>
+    <col min="15430" max="15430" width="13.5546875" style="328" customWidth="1"/>
+    <col min="15431" max="15431" width="7.109375" style="328" customWidth="1"/>
+    <col min="15432" max="15432" width="8.5546875" style="328" customWidth="1"/>
+    <col min="15433" max="15433" width="9" style="328" customWidth="1"/>
+    <col min="15434" max="15434" width="5.109375" style="328" customWidth="1"/>
+    <col min="15435" max="15435" width="8.44140625" style="328" customWidth="1"/>
+    <col min="15436" max="15436" width="17.109375" style="328" customWidth="1"/>
+    <col min="15437" max="15437" width="18" style="328" customWidth="1"/>
+    <col min="15438" max="15438" width="3.88671875" style="328" customWidth="1"/>
+    <col min="15439" max="15440" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="15441" max="15443" width="9.109375" style="328"/>
+    <col min="15444" max="15444" width="11.33203125" style="328" customWidth="1"/>
+    <col min="15445" max="15682" width="9.109375" style="328"/>
+    <col min="15683" max="15683" width="3.109375" style="328" customWidth="1"/>
+    <col min="15684" max="15684" width="3.44140625" style="328" customWidth="1"/>
+    <col min="15685" max="15685" width="7.33203125" style="328" customWidth="1"/>
+    <col min="15686" max="15686" width="13.5546875" style="328" customWidth="1"/>
+    <col min="15687" max="15687" width="7.109375" style="328" customWidth="1"/>
+    <col min="15688" max="15688" width="8.5546875" style="328" customWidth="1"/>
+    <col min="15689" max="15689" width="9" style="328" customWidth="1"/>
+    <col min="15690" max="15690" width="5.109375" style="328" customWidth="1"/>
+    <col min="15691" max="15691" width="8.44140625" style="328" customWidth="1"/>
+    <col min="15692" max="15692" width="17.109375" style="328" customWidth="1"/>
+    <col min="15693" max="15693" width="18" style="328" customWidth="1"/>
+    <col min="15694" max="15694" width="3.88671875" style="328" customWidth="1"/>
+    <col min="15695" max="15696" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="15697" max="15699" width="9.109375" style="328"/>
+    <col min="15700" max="15700" width="11.33203125" style="328" customWidth="1"/>
+    <col min="15701" max="15938" width="9.109375" style="328"/>
+    <col min="15939" max="15939" width="3.109375" style="328" customWidth="1"/>
+    <col min="15940" max="15940" width="3.44140625" style="328" customWidth="1"/>
+    <col min="15941" max="15941" width="7.33203125" style="328" customWidth="1"/>
+    <col min="15942" max="15942" width="13.5546875" style="328" customWidth="1"/>
+    <col min="15943" max="15943" width="7.109375" style="328" customWidth="1"/>
+    <col min="15944" max="15944" width="8.5546875" style="328" customWidth="1"/>
+    <col min="15945" max="15945" width="9" style="328" customWidth="1"/>
+    <col min="15946" max="15946" width="5.109375" style="328" customWidth="1"/>
+    <col min="15947" max="15947" width="8.44140625" style="328" customWidth="1"/>
+    <col min="15948" max="15948" width="17.109375" style="328" customWidth="1"/>
+    <col min="15949" max="15949" width="18" style="328" customWidth="1"/>
+    <col min="15950" max="15950" width="3.88671875" style="328" customWidth="1"/>
+    <col min="15951" max="15952" width="12.109375" style="328" bestFit="1" customWidth="1"/>
+    <col min="15953" max="15955" width="9.109375" style="328"/>
+    <col min="15956" max="15956" width="11.33203125" style="328" customWidth="1"/>
+    <col min="15957" max="16384" width="9.109375" style="328"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="H1" s="372" t="s">
+      <c r="H1" s="329" t="s">
         <v>629</v>
       </c>
-      <c r="I1" s="373">
+      <c r="I1" s="330">
         <f>+'Data from DB'!B3</f>
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="21.6" customHeight="1">
-      <c r="C2" s="374"/>
-      <c r="D2" s="374"/>
-      <c r="E2" s="374"/>
-      <c r="F2" s="374"/>
-      <c r="G2" s="374"/>
+      <c r="C2" s="381"/>
+      <c r="D2" s="381"/>
+      <c r="E2" s="381"/>
+      <c r="F2" s="381"/>
+      <c r="G2" s="381"/>
     </row>
     <row r="3" spans="1:10" ht="39" customHeight="1"/>
     <row r="4" spans="1:10" ht="15.75" customHeight="1">
-      <c r="I4" s="375"/>
-      <c r="J4" s="375"/>
+      <c r="I4" s="331"/>
+      <c r="J4" s="331"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A5" s="376"/>
-      <c r="B5" s="376"/>
-      <c r="C5" s="376"/>
-      <c r="D5" s="376"/>
-      <c r="E5" s="376"/>
-      <c r="F5" s="376"/>
-      <c r="G5" s="376"/>
-      <c r="H5" s="376"/>
-      <c r="I5" s="376"/>
-      <c r="J5" s="376"/>
+      <c r="A5" s="444"/>
+      <c r="B5" s="444"/>
+      <c r="C5" s="444"/>
+      <c r="D5" s="444"/>
+      <c r="E5" s="444"/>
+      <c r="F5" s="444"/>
+      <c r="G5" s="444"/>
+      <c r="H5" s="444"/>
+      <c r="I5" s="444"/>
+      <c r="J5" s="444"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1"/>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A7" s="377" t="s">
+      <c r="A7" s="332" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="377"/>
-      <c r="C7" s="377"/>
+      <c r="B7" s="332"/>
+      <c r="C7" s="332"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A8" s="378" t="s">
+      <c r="A8" s="385" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="379"/>
-      <c r="C8" s="379"/>
-      <c r="D8" s="379" t="s">
+      <c r="B8" s="383"/>
+      <c r="C8" s="383"/>
+      <c r="D8" s="383" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="379" t="s">
+      <c r="E8" s="383" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="379" t="s">
+      <c r="F8" s="383" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="379" t="s">
+      <c r="G8" s="383" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="379" t="s">
+      <c r="H8" s="383" t="s">
         <v>69</v>
       </c>
-      <c r="I8" s="379" t="s">
+      <c r="I8" s="383" t="s">
         <v>70</v>
       </c>
-      <c r="J8" s="380" t="s">
+      <c r="J8" s="413" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A9" s="381"/>
-      <c r="B9" s="382"/>
-      <c r="C9" s="382"/>
-      <c r="D9" s="382"/>
-      <c r="E9" s="382"/>
-      <c r="F9" s="382"/>
-      <c r="G9" s="382"/>
-      <c r="H9" s="382"/>
-      <c r="I9" s="382"/>
-      <c r="J9" s="383"/>
+      <c r="A9" s="386"/>
+      <c r="B9" s="384"/>
+      <c r="C9" s="384"/>
+      <c r="D9" s="384"/>
+      <c r="E9" s="384"/>
+      <c r="F9" s="384"/>
+      <c r="G9" s="384"/>
+      <c r="H9" s="384"/>
+      <c r="I9" s="384"/>
+      <c r="J9" s="414"/>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A10" s="384" t="s">
+      <c r="A10" s="393" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="385"/>
-      <c r="C10" s="385"/>
-      <c r="D10" s="386">
+      <c r="B10" s="394"/>
+      <c r="C10" s="394"/>
+      <c r="D10" s="395">
         <f>+'Data from DB'!B447</f>
         <v>0</v>
       </c>
-      <c r="E10" s="387" t="str">
+      <c r="E10" s="396" t="str">
         <f>CONCATENATE('Data from DB'!B464,":",'Data from DB'!B465)</f>
         <v>:</v>
       </c>
-      <c r="F10" s="387" t="s">
+      <c r="F10" s="396" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="388">
+      <c r="G10" s="389">
         <f>+'Data from DB'!B46</f>
         <v>0</v>
       </c>
-      <c r="H10" s="388">
+      <c r="H10" s="389">
         <f>+'Data from DB'!B47</f>
         <v>0</v>
       </c>
-      <c r="I10" s="388">
+      <c r="I10" s="389">
         <f>+'Data from DB'!B48</f>
         <v>0</v>
       </c>
-      <c r="J10" s="389">
+      <c r="J10" s="445">
         <f>+'Data from DB'!B49</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A11" s="384"/>
-      <c r="B11" s="385"/>
-      <c r="C11" s="385"/>
-      <c r="D11" s="386"/>
-      <c r="E11" s="387"/>
-      <c r="F11" s="387"/>
-      <c r="G11" s="388"/>
-      <c r="H11" s="388"/>
-      <c r="I11" s="388"/>
-      <c r="J11" s="389"/>
+      <c r="A11" s="393"/>
+      <c r="B11" s="394"/>
+      <c r="C11" s="394"/>
+      <c r="D11" s="395"/>
+      <c r="E11" s="396"/>
+      <c r="F11" s="396"/>
+      <c r="G11" s="389"/>
+      <c r="H11" s="389"/>
+      <c r="I11" s="389"/>
+      <c r="J11" s="445"/>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A12" s="390" t="s">
+      <c r="A12" s="391" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="391"/>
-      <c r="C12" s="391"/>
-      <c r="D12" s="386">
+      <c r="B12" s="392"/>
+      <c r="C12" s="392"/>
+      <c r="D12" s="395">
         <f>+'Data from DB'!B448</f>
         <v>0</v>
       </c>
-      <c r="E12" s="387" t="str">
+      <c r="E12" s="396" t="str">
         <f>CONCATENATE('Data from DB'!B468,":",'Data from DB'!B469)</f>
         <v>:</v>
       </c>
-      <c r="F12" s="387" t="s">
+      <c r="F12" s="396" t="s">
         <v>68</v>
       </c>
-      <c r="G12" s="388">
+      <c r="G12" s="389">
         <f>+'Data from DB'!C50</f>
         <v>0</v>
       </c>
-      <c r="H12" s="388">
+      <c r="H12" s="389">
         <f>+'Data from DB'!B51</f>
         <v>0</v>
       </c>
-      <c r="I12" s="388">
+      <c r="I12" s="389">
         <f>+'Data from DB'!B52</f>
         <v>0</v>
       </c>
-      <c r="J12" s="389">
+      <c r="J12" s="445">
         <f>+'Data from DB'!C53</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A13" s="390"/>
-      <c r="B13" s="391"/>
-      <c r="C13" s="391"/>
-      <c r="D13" s="386"/>
-      <c r="E13" s="387"/>
-      <c r="F13" s="387"/>
-      <c r="G13" s="388"/>
-      <c r="H13" s="388"/>
-      <c r="I13" s="388"/>
-      <c r="J13" s="389"/>
+      <c r="A13" s="391"/>
+      <c r="B13" s="392"/>
+      <c r="C13" s="392"/>
+      <c r="D13" s="395"/>
+      <c r="E13" s="396"/>
+      <c r="F13" s="396"/>
+      <c r="G13" s="389"/>
+      <c r="H13" s="389"/>
+      <c r="I13" s="389"/>
+      <c r="J13" s="445"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A14" s="390" t="s">
+      <c r="A14" s="391" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="391"/>
-      <c r="C14" s="391"/>
-      <c r="D14" s="386">
+      <c r="B14" s="392"/>
+      <c r="C14" s="392"/>
+      <c r="D14" s="395">
         <f>+'Data from DB'!B449</f>
         <v>0</v>
       </c>
-      <c r="E14" s="387" t="str">
+      <c r="E14" s="396" t="str">
         <f>CONCATENATE('Data from DB'!B466,":",'Data from DB'!B467)</f>
         <v>:</v>
       </c>
-      <c r="F14" s="387" t="s">
+      <c r="F14" s="396" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="388">
+      <c r="G14" s="389">
         <f>+'Data from DB'!B54</f>
         <v>0</v>
       </c>
-      <c r="H14" s="388">
+      <c r="H14" s="389">
         <f>+'Data from DB'!B55</f>
         <v>0</v>
       </c>
-      <c r="I14" s="388">
+      <c r="I14" s="389">
         <f>+'Data from DB'!B56</f>
         <v>0</v>
       </c>
-      <c r="J14" s="389">
+      <c r="J14" s="445">
         <f>+'Data from DB'!B57</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A15" s="390"/>
-      <c r="B15" s="391"/>
-      <c r="C15" s="391"/>
-      <c r="D15" s="386"/>
-      <c r="E15" s="387"/>
-      <c r="F15" s="387"/>
-      <c r="G15" s="388"/>
-      <c r="H15" s="388"/>
-      <c r="I15" s="388"/>
-      <c r="J15" s="389"/>
+      <c r="A15" s="391"/>
+      <c r="B15" s="392"/>
+      <c r="C15" s="392"/>
+      <c r="D15" s="395"/>
+      <c r="E15" s="396"/>
+      <c r="F15" s="396"/>
+      <c r="G15" s="389"/>
+      <c r="H15" s="389"/>
+      <c r="I15" s="389"/>
+      <c r="J15" s="445"/>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A16" s="392" t="s">
+      <c r="A16" s="387" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="393"/>
-      <c r="C16" s="393"/>
-      <c r="D16" s="386">
+      <c r="B16" s="388"/>
+      <c r="C16" s="388"/>
+      <c r="D16" s="395">
         <f>+'Data from DB'!B450</f>
         <v>0</v>
       </c>
-      <c r="E16" s="387" t="str">
+      <c r="E16" s="396" t="str">
         <f>CONCATENATE('Data from DB'!B462,":",'Data from DB'!B461)</f>
         <v>:</v>
       </c>
-      <c r="F16" s="387" t="s">
+      <c r="F16" s="396" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="394">
+      <c r="G16" s="397">
         <f>+'Data from DB'!B58</f>
         <v>0</v>
       </c>
-      <c r="H16" s="388">
+      <c r="H16" s="389">
         <f>+'Data from DB'!B59</f>
         <v>0</v>
       </c>
-      <c r="I16" s="388">
+      <c r="I16" s="389">
         <f>+'Data from DB'!B60</f>
         <v>0</v>
       </c>
-      <c r="J16" s="395">
+      <c r="J16" s="446">
         <f>+'Data from DB'!B61</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A17" s="392"/>
-      <c r="B17" s="393"/>
-      <c r="C17" s="393"/>
-      <c r="D17" s="386"/>
-      <c r="E17" s="387"/>
-      <c r="F17" s="387"/>
-      <c r="G17" s="394"/>
-      <c r="H17" s="388"/>
-      <c r="I17" s="388"/>
-      <c r="J17" s="395"/>
+      <c r="A17" s="387"/>
+      <c r="B17" s="388"/>
+      <c r="C17" s="388"/>
+      <c r="D17" s="395"/>
+      <c r="E17" s="396"/>
+      <c r="F17" s="396"/>
+      <c r="G17" s="397"/>
+      <c r="H17" s="389"/>
+      <c r="I17" s="389"/>
+      <c r="J17" s="446"/>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A18" s="396" t="s">
+      <c r="A18" s="409" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="397"/>
-      <c r="C18" s="397"/>
-      <c r="D18" s="398">
+      <c r="B18" s="410"/>
+      <c r="C18" s="410"/>
+      <c r="D18" s="415">
         <f>+'Data from DB'!B451</f>
         <v>0</v>
       </c>
-      <c r="E18" s="399" t="str">
+      <c r="E18" s="417" t="str">
         <f>CONCATENATE('Data from DB'!B460,":",'Data from DB'!B461)</f>
         <v>:</v>
       </c>
       <c r="F18" s="400" t="s">
         <v>38</v>
       </c>
-      <c r="G18" s="394">
+      <c r="G18" s="397">
         <f>+'Data from DB'!B475</f>
         <v>0</v>
       </c>
-      <c r="H18" s="388">
+      <c r="H18" s="389">
         <f>+'Data from DB'!B476</f>
         <v>0</v>
       </c>
-      <c r="I18" s="388">
+      <c r="I18" s="389">
         <f>+'Data from DB'!B477</f>
         <v>0</v>
       </c>
-      <c r="J18" s="395">
+      <c r="J18" s="446">
         <f>+'Data from DB'!B478</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A19" s="401"/>
-      <c r="B19" s="402"/>
-      <c r="C19" s="402"/>
-      <c r="D19" s="403"/>
-      <c r="E19" s="404"/>
-      <c r="F19" s="405"/>
-      <c r="G19" s="406"/>
-      <c r="H19" s="407"/>
-      <c r="I19" s="407"/>
-      <c r="J19" s="408"/>
+      <c r="A19" s="411"/>
+      <c r="B19" s="412"/>
+      <c r="C19" s="412"/>
+      <c r="D19" s="416"/>
+      <c r="E19" s="418"/>
+      <c r="F19" s="401"/>
+      <c r="G19" s="402"/>
+      <c r="H19" s="390"/>
+      <c r="I19" s="390"/>
+      <c r="J19" s="447"/>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A20" s="409"/>
-      <c r="B20" s="409"/>
-      <c r="C20" s="409"/>
-      <c r="D20" s="409"/>
-      <c r="E20" s="409"/>
-      <c r="F20" s="409"/>
-      <c r="G20" s="409"/>
-      <c r="H20" s="409"/>
-      <c r="I20" s="409"/>
-      <c r="J20" s="409"/>
+      <c r="A20" s="333"/>
+      <c r="B20" s="333"/>
+      <c r="C20" s="333"/>
+      <c r="D20" s="333"/>
+      <c r="E20" s="333"/>
+      <c r="F20" s="333"/>
+      <c r="G20" s="333"/>
+      <c r="H20" s="333"/>
+      <c r="I20" s="333"/>
+      <c r="J20" s="333"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A21" s="410"/>
-      <c r="B21" s="410"/>
-      <c r="C21" s="411"/>
-      <c r="D21" s="412"/>
-      <c r="E21" s="413"/>
-      <c r="G21" s="414"/>
-      <c r="H21" s="415"/>
-      <c r="I21" s="415"/>
-      <c r="J21" s="415"/>
+      <c r="A21" s="334"/>
+      <c r="B21" s="334"/>
+      <c r="C21" s="335"/>
+      <c r="D21" s="336"/>
+      <c r="E21" s="337"/>
+      <c r="G21" s="338"/>
+      <c r="H21" s="339"/>
+      <c r="I21" s="339"/>
+      <c r="J21" s="339"/>
     </row>
     <row r="22" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A22" s="416" t="s">
+      <c r="A22" s="382" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="416"/>
-      <c r="C22" s="416"/>
-      <c r="D22" s="416"/>
-      <c r="G22" s="414"/>
+      <c r="B22" s="382"/>
+      <c r="C22" s="382"/>
+      <c r="D22" s="382"/>
+      <c r="G22" s="338"/>
     </row>
     <row r="23" spans="1:10" ht="13.95" customHeight="1" thickBot="1">
-      <c r="A23" s="417" t="s">
+      <c r="A23" s="340" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="417"/>
-      <c r="C23" s="417"/>
-      <c r="D23" s="417"/>
-      <c r="E23" s="418"/>
-      <c r="F23" s="419"/>
-      <c r="G23" s="417"/>
-      <c r="H23" s="419"/>
-      <c r="I23" s="419"/>
-      <c r="J23" s="419"/>
+      <c r="B23" s="340"/>
+      <c r="C23" s="340"/>
+      <c r="D23" s="340"/>
+      <c r="E23" s="341"/>
+      <c r="F23" s="342"/>
+      <c r="G23" s="340"/>
+      <c r="H23" s="342"/>
+      <c r="I23" s="342"/>
+      <c r="J23" s="342"/>
     </row>
     <row r="24" spans="1:10" ht="13.95" customHeight="1" thickTop="1">
-      <c r="A24" s="420" t="s">
+      <c r="A24" s="403" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="421"/>
-      <c r="C24" s="422"/>
-      <c r="D24" s="423" t="s">
+      <c r="B24" s="404"/>
+      <c r="C24" s="405"/>
+      <c r="D24" s="437" t="s">
         <v>73</v>
       </c>
-      <c r="E24" s="422"/>
-      <c r="F24" s="424" t="s">
+      <c r="E24" s="405"/>
+      <c r="F24" s="433" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="425" t="s">
+      <c r="G24" s="435" t="s">
         <v>69</v>
       </c>
-      <c r="H24" s="380" t="s">
+      <c r="H24" s="413" t="s">
         <v>70</v>
       </c>
-      <c r="I24" s="380" t="s">
+      <c r="I24" s="413" t="s">
         <v>125</v>
       </c>
-      <c r="J24" s="426"/>
+      <c r="J24" s="343"/>
     </row>
     <row r="25" spans="1:10" ht="12.6" thickBot="1">
-      <c r="A25" s="427"/>
-      <c r="B25" s="428"/>
-      <c r="C25" s="429"/>
-      <c r="D25" s="430"/>
-      <c r="E25" s="429"/>
-      <c r="F25" s="431"/>
-      <c r="G25" s="432"/>
-      <c r="H25" s="383"/>
-      <c r="I25" s="383"/>
-      <c r="J25" s="426"/>
+      <c r="A25" s="406"/>
+      <c r="B25" s="407"/>
+      <c r="C25" s="408"/>
+      <c r="D25" s="438"/>
+      <c r="E25" s="408"/>
+      <c r="F25" s="434"/>
+      <c r="G25" s="436"/>
+      <c r="H25" s="414"/>
+      <c r="I25" s="414"/>
+      <c r="J25" s="343"/>
     </row>
     <row r="26" spans="1:10" ht="15.6" customHeight="1" thickTop="1">
-      <c r="A26" s="433" t="s">
+      <c r="A26" s="419" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="434"/>
-      <c r="C26" s="435"/>
-      <c r="D26" s="436" t="s">
+      <c r="B26" s="420"/>
+      <c r="C26" s="421"/>
+      <c r="D26" s="439" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="437"/>
-      <c r="F26" s="438">
+      <c r="E26" s="440"/>
+      <c r="F26" s="344">
         <f>+'Data from DB'!B62</f>
         <v>0</v>
       </c>
-      <c r="G26" s="439">
+      <c r="G26" s="345">
         <f>+'Data from DB'!B63</f>
         <v>0</v>
       </c>
-      <c r="H26" s="439">
+      <c r="H26" s="345">
         <f>+'Data from DB'!B64</f>
         <v>0</v>
       </c>
-      <c r="I26" s="439">
+      <c r="I26" s="345">
         <f>+'Data from DB'!B65</f>
         <v>0</v>
       </c>
-      <c r="J26" s="440"/>
+      <c r="J26" s="346"/>
     </row>
     <row r="27" spans="1:10" ht="13.95" customHeight="1">
-      <c r="A27" s="441"/>
-      <c r="B27" s="442"/>
-      <c r="C27" s="443"/>
-      <c r="D27" s="444" t="s">
+      <c r="A27" s="422"/>
+      <c r="B27" s="423"/>
+      <c r="C27" s="424"/>
+      <c r="D27" s="441" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="445"/>
-      <c r="F27" s="446">
+      <c r="E27" s="442"/>
+      <c r="F27" s="347">
         <f>+'Data from DB'!B66</f>
         <v>0</v>
       </c>
-      <c r="G27" s="447">
+      <c r="G27" s="348">
         <f>+'Data from DB'!B67</f>
         <v>0</v>
       </c>
-      <c r="H27" s="447">
+      <c r="H27" s="348">
         <f>+'Data from DB'!B68</f>
         <v>0</v>
       </c>
-      <c r="I27" s="447">
+      <c r="I27" s="348">
         <f>+'Data from DB'!B69</f>
         <v>0</v>
       </c>
-      <c r="J27" s="440"/>
+      <c r="J27" s="346"/>
     </row>
     <row r="28" spans="1:10" ht="12">
-      <c r="A28" s="448"/>
-      <c r="B28" s="449"/>
-      <c r="C28" s="449"/>
-      <c r="D28" s="450"/>
-      <c r="E28" s="450"/>
-      <c r="F28" s="451"/>
-      <c r="G28" s="452"/>
-      <c r="H28" s="452"/>
-      <c r="I28" s="452"/>
-      <c r="J28" s="440"/>
+      <c r="A28" s="349"/>
+      <c r="B28" s="350"/>
+      <c r="C28" s="350"/>
+      <c r="D28" s="351"/>
+      <c r="E28" s="351"/>
+      <c r="F28" s="352"/>
+      <c r="G28" s="353"/>
+      <c r="H28" s="353"/>
+      <c r="I28" s="353"/>
+      <c r="J28" s="346"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1">
-      <c r="A29" s="453" t="s">
+      <c r="A29" s="425" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="454"/>
-      <c r="C29" s="455"/>
-      <c r="D29" s="444" t="s">
+      <c r="B29" s="426"/>
+      <c r="C29" s="427"/>
+      <c r="D29" s="441" t="s">
         <v>79</v>
       </c>
-      <c r="E29" s="445"/>
-      <c r="F29" s="456">
+      <c r="E29" s="442"/>
+      <c r="F29" s="354">
         <f>+'Data from DB'!B70</f>
         <v>0</v>
       </c>
-      <c r="G29" s="447">
+      <c r="G29" s="348">
         <f>+'Data from DB'!B71</f>
         <v>0</v>
       </c>
-      <c r="H29" s="447">
+      <c r="H29" s="348">
         <f>+'Data from DB'!B72</f>
         <v>0</v>
       </c>
-      <c r="I29" s="447">
+      <c r="I29" s="348">
         <f>+'Data from DB'!B73</f>
         <v>0</v>
       </c>
-      <c r="J29" s="440"/>
+      <c r="J29" s="346"/>
     </row>
     <row r="30" spans="1:10" ht="15.45" customHeight="1" thickBot="1">
-      <c r="A30" s="457"/>
-      <c r="B30" s="458"/>
-      <c r="C30" s="459"/>
-      <c r="D30" s="460" t="s">
+      <c r="A30" s="428"/>
+      <c r="B30" s="429"/>
+      <c r="C30" s="430"/>
+      <c r="D30" s="431" t="s">
         <v>76</v>
       </c>
-      <c r="E30" s="461"/>
-      <c r="F30" s="462">
+      <c r="E30" s="432"/>
+      <c r="F30" s="355">
         <f>+'Data from DB'!B74</f>
         <v>0</v>
       </c>
-      <c r="G30" s="463">
+      <c r="G30" s="356">
         <f>+'Data from DB'!B75</f>
         <v>0</v>
       </c>
-      <c r="H30" s="463">
+      <c r="H30" s="356">
         <f>+'Data from DB'!B76</f>
         <v>0</v>
       </c>
-      <c r="I30" s="447">
+      <c r="I30" s="348">
         <f>+'Data from DB'!B77</f>
         <v>0</v>
       </c>
-      <c r="J30" s="440"/>
+      <c r="J30" s="346"/>
     </row>
     <row r="31" spans="1:10" ht="12.6" thickTop="1">
-      <c r="A31" s="464"/>
-      <c r="B31" s="464"/>
-      <c r="C31" s="464"/>
-      <c r="D31" s="464"/>
-      <c r="E31" s="464"/>
-      <c r="F31" s="464"/>
-      <c r="G31" s="464"/>
-      <c r="H31" s="464"/>
-      <c r="I31" s="464"/>
-      <c r="J31" s="465"/>
+      <c r="A31" s="357"/>
+      <c r="B31" s="357"/>
+      <c r="C31" s="357"/>
+      <c r="D31" s="357"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
+      <c r="G31" s="357"/>
+      <c r="H31" s="357"/>
+      <c r="I31" s="357"/>
+      <c r="J31" s="358"/>
     </row>
     <row r="32" spans="1:10" ht="15.45" customHeight="1">
-      <c r="A32" s="413"/>
-      <c r="B32" s="413"/>
-      <c r="C32" s="413"/>
-      <c r="D32" s="413"/>
-      <c r="E32" s="413"/>
-      <c r="F32" s="413"/>
-      <c r="G32" s="413"/>
-      <c r="H32" s="466"/>
-      <c r="I32" s="466"/>
-      <c r="J32" s="466"/>
+      <c r="A32" s="337"/>
+      <c r="B32" s="337"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
+      <c r="G32" s="337"/>
+      <c r="H32" s="359"/>
+      <c r="I32" s="359"/>
+      <c r="J32" s="359"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1"/>
     <row r="35" spans="1:10" ht="14.4" customHeight="1">
-      <c r="D35" s="467"/>
-      <c r="E35" s="467"/>
-      <c r="F35" s="467"/>
+      <c r="D35" s="443"/>
+      <c r="E35" s="443"/>
+      <c r="F35" s="443"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="468" t="s">
+      <c r="A36" s="361" t="s">
         <v>156</v>
       </c>
-      <c r="B36" s="468"/>
-      <c r="D36" s="371">
+      <c r="B36" s="361"/>
+      <c r="D36" s="328">
         <f>+'Data from DB'!B472</f>
         <v>0</v>
       </c>
-      <c r="H36" s="371">
+      <c r="H36" s="328">
         <f>+'Data from DB'!B453</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="12">
-      <c r="A37" s="469"/>
-      <c r="B37" s="469"/>
-      <c r="C37" s="470"/>
-      <c r="D37" s="471"/>
-      <c r="E37" s="471"/>
-      <c r="F37" s="471"/>
-      <c r="H37" s="471">
+      <c r="A37" s="398"/>
+      <c r="B37" s="398"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="399"/>
+      <c r="E37" s="399"/>
+      <c r="F37" s="399"/>
+      <c r="H37" s="399">
         <f>CALCULATIONS!I42</f>
         <v>0</v>
       </c>
-      <c r="I37" s="471"/>
-      <c r="J37" s="471"/>
+      <c r="I37" s="399"/>
+      <c r="J37" s="399"/>
     </row>
     <row r="38" spans="1:10" ht="12">
-      <c r="A38" s="467" t="s">
+      <c r="A38" s="443" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="467"/>
-      <c r="C38" s="413"/>
-      <c r="D38" s="467" t="str">
+      <c r="B38" s="443"/>
+      <c r="C38" s="337"/>
+      <c r="D38" s="443" t="str">
         <f xml:space="preserve"> +" C Enginner  "  &amp; + CERTIFICATE!C3</f>
         <v xml:space="preserve"> C Enginner  0</v>
       </c>
-      <c r="E38" s="467"/>
-      <c r="F38" s="467"/>
-      <c r="H38" s="467" t="str">
+      <c r="E38" s="443"/>
+      <c r="F38" s="443"/>
+      <c r="H38" s="443" t="str">
         <f xml:space="preserve"> +" Master  "  &amp; + CERTIFICATE!C3</f>
         <v xml:space="preserve"> Master  0</v>
       </c>
-      <c r="I38" s="467"/>
-      <c r="J38" s="467"/>
+      <c r="I38" s="443"/>
+      <c r="J38" s="443"/>
     </row>
     <row r="39" spans="1:10" ht="12">
-      <c r="A39" s="472"/>
-      <c r="B39" s="472"/>
-      <c r="C39" s="472"/>
-      <c r="D39" s="413"/>
-      <c r="E39" s="472"/>
-      <c r="F39" s="472"/>
-      <c r="G39" s="472"/>
-      <c r="H39" s="472"/>
-      <c r="I39" s="472"/>
-      <c r="J39" s="472"/>
+      <c r="A39" s="360"/>
+      <c r="B39" s="360"/>
+      <c r="C39" s="360"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="360"/>
+      <c r="F39" s="360"/>
+      <c r="G39" s="360"/>
+      <c r="H39" s="360"/>
+      <c r="I39" s="360"/>
+      <c r="J39" s="360"/>
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="D24:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="A24:C25"/>
+    <mergeCell ref="A18:C19"/>
+    <mergeCell ref="A12:C13"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A26:C27"/>
+    <mergeCell ref="A29:C30"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="H8:H9"/>
@@ -12062,60 +12113,6 @@
     <mergeCell ref="A14:C15"/>
     <mergeCell ref="A10:C11"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="H37:J37"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="A24:C25"/>
-    <mergeCell ref="A18:C19"/>
-    <mergeCell ref="A12:C13"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A26:C27"/>
-    <mergeCell ref="A29:C30"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="D24:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="I14:I15"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -15579,10 +15576,10 @@
         <v>147</v>
       </c>
       <c r="F23" s="47"/>
-      <c r="G23" s="277" t="s">
+      <c r="G23" s="448" t="s">
         <v>148</v>
       </c>
-      <c r="H23" s="278"/>
+      <c r="H23" s="449"/>
       <c r="J23" s="222" t="s">
         <v>149</v>
       </c>
@@ -15602,11 +15599,11 @@
         <v>139.04000000000002</v>
       </c>
       <c r="F24" s="164"/>
-      <c r="G24" s="279">
+      <c r="G24" s="450">
         <f>J24-E24</f>
         <v>-126.44000000000003</v>
       </c>
-      <c r="H24" s="279"/>
+      <c r="H24" s="450"/>
       <c r="I24" s="224"/>
       <c r="J24" s="225">
         <f>F4</f>
@@ -15633,10 +15630,10 @@
         <v>147</v>
       </c>
       <c r="F26" s="47"/>
-      <c r="G26" s="277" t="s">
+      <c r="G26" s="448" t="s">
         <v>148</v>
       </c>
-      <c r="H26" s="278"/>
+      <c r="H26" s="449"/>
       <c r="J26" s="222" t="s">
         <v>151</v>
       </c>
@@ -15656,11 +15653,11 @@
         <v>-35.940000000000012</v>
       </c>
       <c r="F27" s="164"/>
-      <c r="G27" s="280">
+      <c r="G27" s="451">
         <f>C27-D27</f>
         <v>35.940000000000012</v>
       </c>
-      <c r="H27" s="280"/>
+      <c r="H27" s="451"/>
       <c r="I27" s="224"/>
       <c r="J27" s="227">
         <f>F7</f>
@@ -16596,36 +16593,36 @@
       </c>
     </row>
     <row r="6" spans="1:17" s="3" customFormat="1">
-      <c r="A6" s="282" t="s">
+      <c r="A6" s="453" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="283"/>
-      <c r="C6" s="283"/>
-      <c r="D6" s="284"/>
-      <c r="E6" s="285" t="s">
+      <c r="B6" s="454"/>
+      <c r="C6" s="454"/>
+      <c r="D6" s="455"/>
+      <c r="E6" s="456" t="s">
         <v>89</v>
       </c>
-      <c r="F6" s="286"/>
-      <c r="G6" s="286"/>
-      <c r="H6" s="287"/>
+      <c r="F6" s="457"/>
+      <c r="G6" s="457"/>
+      <c r="H6" s="458"/>
     </row>
     <row r="7" spans="1:17" s="3" customFormat="1" ht="15" thickBot="1">
       <c r="A7" s="119" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="288">
+      <c r="B7" s="459">
         <v>43266.000694444447</v>
       </c>
-      <c r="C7" s="288"/>
-      <c r="D7" s="289"/>
+      <c r="C7" s="459"/>
+      <c r="D7" s="460"/>
       <c r="E7" s="119" t="s">
         <v>90</v>
       </c>
-      <c r="F7" s="288">
+      <c r="F7" s="459">
         <v>43268.341666666667</v>
       </c>
-      <c r="G7" s="288"/>
-      <c r="H7" s="289"/>
+      <c r="G7" s="459"/>
+      <c r="H7" s="460"/>
       <c r="J7" s="109" t="s">
         <v>91</v>
       </c>
@@ -16800,18 +16797,18 @@
       <c r="N12" s="36"/>
     </row>
     <row r="13" spans="1:17" s="3" customFormat="1">
-      <c r="A13" s="290" t="s">
+      <c r="A13" s="461" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="291"/>
-      <c r="C13" s="291"/>
-      <c r="D13" s="292"/>
-      <c r="E13" s="293" t="s">
+      <c r="B13" s="462"/>
+      <c r="C13" s="462"/>
+      <c r="D13" s="463"/>
+      <c r="E13" s="464" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="294"/>
-      <c r="G13" s="294"/>
-      <c r="H13" s="295"/>
+      <c r="F13" s="465"/>
+      <c r="G13" s="465"/>
+      <c r="H13" s="466"/>
       <c r="J13" s="111" t="s">
         <v>80</v>
       </c>
@@ -16829,19 +16826,19 @@
       <c r="A14" s="119" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="296" t="s">
+      <c r="B14" s="467" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="296"/>
-      <c r="D14" s="297"/>
+      <c r="C14" s="467"/>
+      <c r="D14" s="468"/>
       <c r="E14" s="119" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="298" t="s">
+      <c r="F14" s="469" t="s">
         <v>102</v>
       </c>
-      <c r="G14" s="298"/>
-      <c r="H14" s="299"/>
+      <c r="G14" s="469"/>
+      <c r="H14" s="470"/>
       <c r="J14" s="111" t="s">
         <v>91</v>
       </c>
@@ -17069,12 +17066,12 @@
       </c>
     </row>
     <row r="24" spans="1:14" s="3" customFormat="1" ht="15" thickBot="1">
-      <c r="A24" s="300" t="s">
+      <c r="A24" s="471" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="300"/>
-      <c r="C24" s="300"/>
-      <c r="D24" s="300"/>
+      <c r="B24" s="471"/>
+      <c r="C24" s="471"/>
+      <c r="D24" s="471"/>
       <c r="E24" s="156" t="s">
         <v>92</v>
       </c>
@@ -17092,10 +17089,10 @@
       <c r="N24" s="36"/>
     </row>
     <row r="25" spans="1:14" s="3" customFormat="1" ht="15" thickBot="1">
-      <c r="A25" s="300"/>
-      <c r="B25" s="300"/>
-      <c r="C25" s="300"/>
-      <c r="D25" s="300"/>
+      <c r="A25" s="471"/>
+      <c r="B25" s="471"/>
+      <c r="C25" s="471"/>
+      <c r="D25" s="471"/>
       <c r="E25" s="159">
         <v>70</v>
       </c>
@@ -17128,16 +17125,16 @@
       <c r="H26" s="51"/>
     </row>
     <row r="27" spans="1:14" s="3" customFormat="1">
-      <c r="A27" s="301" t="s">
+      <c r="A27" s="472" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="301"/>
-      <c r="C27" s="301"/>
-      <c r="D27" s="301"/>
-      <c r="E27" s="301"/>
-      <c r="F27" s="301"/>
-      <c r="G27" s="301"/>
-      <c r="H27" s="301"/>
+      <c r="B27" s="472"/>
+      <c r="C27" s="472"/>
+      <c r="D27" s="472"/>
+      <c r="E27" s="472"/>
+      <c r="F27" s="472"/>
+      <c r="G27" s="472"/>
+      <c r="H27" s="472"/>
       <c r="J27" s="164"/>
       <c r="K27" s="165">
         <f>K23-K25</f>
@@ -17420,11 +17417,11 @@
       <c r="C43" s="117"/>
       <c r="D43" s="117"/>
       <c r="E43" s="117"/>
-      <c r="F43" s="281">
-        <v>0</v>
-      </c>
-      <c r="G43" s="281"/>
-      <c r="H43" s="281"/>
+      <c r="F43" s="452">
+        <v>0</v>
+      </c>
+      <c r="G43" s="452"/>
+      <c r="H43" s="452"/>
     </row>
     <row r="44" spans="1:12" s="3" customFormat="1">
       <c r="B44" s="199" t="s">
@@ -17434,11 +17431,11 @@
         <v>130</v>
       </c>
       <c r="E44" s="199"/>
-      <c r="F44" s="281" t="s">
+      <c r="F44" s="452" t="s">
         <v>131</v>
       </c>
-      <c r="G44" s="281"/>
-      <c r="H44" s="281"/>
+      <c r="G44" s="452"/>
+      <c r="H44" s="452"/>
     </row>
     <row r="45" spans="1:12" s="3" customFormat="1">
       <c r="D45" s="117"/>
